--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>265</v>
+        <v>670</v>
       </c>
       <c r="C2">
-        <v>1440</v>
+        <v>1280</v>
       </c>
       <c r="D2">
-        <v>1705</v>
+        <v>1950</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
-        <v>258</v>
+        <v>658</v>
       </c>
       <c r="C3">
-        <v>1423</v>
+        <v>1237</v>
       </c>
       <c r="D3">
-        <v>1681</v>
+        <v>1895</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
-        <v>257</v>
+        <v>661</v>
       </c>
       <c r="C4">
-        <v>1424</v>
+        <v>1238</v>
       </c>
       <c r="D4">
-        <v>1681</v>
+        <v>1899</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
-        <v>248</v>
+        <v>669</v>
       </c>
       <c r="C5">
-        <v>1476</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1724</v>
+        <v>669</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
-        <v>249</v>
+        <v>680</v>
       </c>
       <c r="C6">
-        <v>1520</v>
+        <v>1231</v>
       </c>
       <c r="D6">
-        <v>1769</v>
+        <v>1911</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
-        <v>247</v>
+        <v>676</v>
       </c>
       <c r="C7">
-        <v>1414</v>
+        <v>1228</v>
       </c>
       <c r="D7">
-        <v>1661</v>
+        <v>1904</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
-        <v>257</v>
+        <v>677</v>
       </c>
       <c r="C8">
-        <v>1399</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1656</v>
+        <v>677</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
-        <v>247</v>
+        <v>678</v>
       </c>
       <c r="C9">
-        <v>1364</v>
+        <v>1229</v>
       </c>
       <c r="D9">
-        <v>1611</v>
+        <v>1907</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
-        <v>261</v>
+        <v>666</v>
       </c>
       <c r="C10">
-        <v>1387</v>
+        <v>1238</v>
       </c>
       <c r="D10">
-        <v>1648</v>
+        <v>1904</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
-        <v>264</v>
+        <v>663</v>
       </c>
       <c r="C11">
-        <v>1379</v>
+        <v>1231</v>
       </c>
       <c r="D11">
-        <v>1643</v>
+        <v>1894</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
-        <v>272</v>
+        <v>666</v>
       </c>
       <c r="C12">
-        <v>1381</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1653</v>
+        <v>666</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
-        <v>277</v>
+        <v>664</v>
       </c>
       <c r="C13">
-        <v>1386</v>
+        <v>1229</v>
       </c>
       <c r="D13">
-        <v>1663</v>
+        <v>1893</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
-        <v>216</v>
+        <v>666</v>
       </c>
       <c r="C14">
-        <v>1452</v>
+        <v>1237</v>
       </c>
       <c r="D14">
-        <v>1668</v>
+        <v>1903</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
-        <v>214</v>
+        <v>667</v>
       </c>
       <c r="C15">
-        <v>1455</v>
+        <v>1246</v>
       </c>
       <c r="D15">
-        <v>1669</v>
+        <v>1913</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
-        <v>221</v>
+        <v>669</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="D16">
-        <v>221</v>
+        <v>1913</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
-        <v>216</v>
+        <v>702</v>
       </c>
       <c r="C17">
-        <v>1454</v>
+        <v>1242</v>
       </c>
       <c r="D17">
-        <v>1670</v>
+        <v>1944</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>209</v>
+        <v>723</v>
       </c>
       <c r="C18">
-        <v>1497</v>
+        <v>1249</v>
       </c>
       <c r="D18">
-        <v>1706</v>
+        <v>1972</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
-        <v>207</v>
+        <v>689</v>
       </c>
       <c r="C19">
-        <v>1500</v>
+        <v>1244</v>
       </c>
       <c r="D19">
-        <v>1707</v>
+        <v>1933</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
-        <v>208</v>
+        <v>714</v>
       </c>
       <c r="C20">
-        <v>1502</v>
+        <v>1249</v>
       </c>
       <c r="D20">
-        <v>1710</v>
+        <v>1963</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>201</v>
+        <v>738</v>
       </c>
       <c r="C21">
-        <v>1510</v>
+        <v>1247</v>
       </c>
       <c r="D21">
-        <v>1711</v>
+        <v>1985</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>245</v>
+        <v>787</v>
       </c>
       <c r="C22">
-        <v>1557</v>
+        <v>1259</v>
       </c>
       <c r="D22">
-        <v>1802</v>
+        <v>2046</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>273</v>
+        <v>786</v>
       </c>
       <c r="C23">
-        <v>1619</v>
+        <v>1263</v>
       </c>
       <c r="D23">
-        <v>1892</v>
+        <v>2049</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>309</v>
+        <v>784</v>
       </c>
       <c r="C24">
-        <v>1584</v>
+        <v>1264</v>
       </c>
       <c r="D24">
-        <v>1893</v>
+        <v>2048</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>333</v>
+        <v>780</v>
       </c>
       <c r="C25">
-        <v>1585</v>
+        <v>1259</v>
       </c>
       <c r="D25">
-        <v>1918</v>
+        <v>2039</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1658</v>
+        <v>1361</v>
       </c>
       <c r="D26">
-        <v>2382</v>
+        <v>1361</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>729</v>
+        <v>777</v>
       </c>
       <c r="C27">
-        <v>1690</v>
+        <v>1354</v>
       </c>
       <c r="D27">
-        <v>2419</v>
+        <v>2131</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>725</v>
+        <v>782</v>
       </c>
       <c r="C28">
-        <v>1692</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>2417</v>
+        <v>782</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>697</v>
+        <v>784</v>
       </c>
       <c r="C29">
-        <v>1698</v>
+        <v>1355</v>
       </c>
       <c r="D29">
-        <v>2395</v>
+        <v>2139</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>431</v>
+        <v>765</v>
       </c>
       <c r="C30">
-        <v>1683</v>
+        <v>1342</v>
       </c>
       <c r="D30">
-        <v>2114</v>
+        <v>2107</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>424</v>
+        <v>753</v>
       </c>
       <c r="C31">
-        <v>1680</v>
+        <v>1329</v>
       </c>
       <c r="D31">
-        <v>2104</v>
+        <v>2082</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>416</v>
+        <v>751</v>
       </c>
       <c r="C32">
-        <v>1679</v>
+        <v>1327</v>
       </c>
       <c r="D32">
-        <v>2095</v>
+        <v>2078</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>370</v>
+        <v>746</v>
       </c>
       <c r="C33">
-        <v>1650</v>
+        <v>1328</v>
       </c>
       <c r="D33">
-        <v>2020</v>
+        <v>2074</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>287</v>
+        <v>539</v>
       </c>
       <c r="C34">
-        <v>1391</v>
+        <v>1351</v>
       </c>
       <c r="D34">
-        <v>1678</v>
+        <v>1890</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>270</v>
+        <v>534</v>
       </c>
       <c r="C35">
-        <v>1315</v>
+        <v>1349</v>
       </c>
       <c r="D35">
-        <v>1585</v>
+        <v>1883</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>292</v>
+        <v>544</v>
       </c>
       <c r="C36">
-        <v>1392</v>
+        <v>1348</v>
       </c>
       <c r="D36">
-        <v>1684</v>
+        <v>1892</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>299</v>
+        <v>692</v>
       </c>
       <c r="C37">
-        <v>1398</v>
+        <v>1337</v>
       </c>
       <c r="D37">
-        <v>1697</v>
+        <v>2029</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>227</v>
+        <v>420</v>
       </c>
       <c r="C38">
-        <v>984</v>
+        <v>1143</v>
       </c>
       <c r="D38">
-        <v>1211</v>
+        <v>1563</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>205</v>
+        <v>421</v>
       </c>
       <c r="C39">
-        <v>928</v>
+        <v>1144</v>
       </c>
       <c r="D39">
-        <v>1133</v>
+        <v>1565</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
-        <v>197</v>
+        <v>414</v>
       </c>
       <c r="C40">
-        <v>932</v>
+        <v>1140</v>
       </c>
       <c r="D40">
-        <v>1129</v>
+        <v>1554</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
-        <v>196</v>
+        <v>393</v>
       </c>
       <c r="C41">
-        <v>935</v>
+        <v>1143</v>
       </c>
       <c r="D41">
-        <v>1131</v>
+        <v>1536</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="C42">
-        <v>902</v>
+        <v>1106</v>
       </c>
       <c r="D42">
-        <v>1058</v>
+        <v>1369</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
-        <v>153</v>
+        <v>256</v>
       </c>
       <c r="C43">
-        <v>897</v>
+        <v>1098</v>
       </c>
       <c r="D43">
-        <v>1050</v>
+        <v>1354</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C44">
-        <v>898</v>
+        <v>1100</v>
       </c>
       <c r="D44">
-        <v>1057</v>
+        <v>1265</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C45">
-        <v>897</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1055</v>
+        <v>164</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="C46">
-        <v>873</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1034</v>
+        <v>126</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1099</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="C48">
-        <v>971</v>
+        <v>1061</v>
       </c>
       <c r="D48">
-        <v>971</v>
+        <v>1185</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="C49">
-        <v>980</v>
+        <v>1082</v>
       </c>
       <c r="D49">
-        <v>1143</v>
+        <v>1207</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C50">
-        <v>1008</v>
+        <v>1119</v>
       </c>
       <c r="D50">
-        <v>1169</v>
+        <v>1239</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="C51">
-        <v>1118</v>
+        <v>1133</v>
       </c>
       <c r="D51">
-        <v>1273</v>
+        <v>1252</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="C52">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="D52">
-        <v>1275</v>
+        <v>1251</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="C53">
-        <v>1126</v>
+        <v>1120</v>
       </c>
       <c r="D53">
-        <v>1278</v>
+        <v>1243</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C54">
-        <v>1114</v>
+        <v>990</v>
       </c>
       <c r="D54">
-        <v>1289</v>
+        <v>1178</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="C55">
-        <v>1113</v>
+        <v>867</v>
       </c>
       <c r="D55">
-        <v>1292</v>
+        <v>938</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C56">
-        <v>1034</v>
+        <v>836</v>
       </c>
       <c r="D56">
-        <v>1034</v>
+        <v>909</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="D57">
-        <v>181</v>
+        <v>911</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>216</v>
+        <v>149</v>
       </c>
       <c r="C58">
-        <v>1201</v>
+        <v>887</v>
       </c>
       <c r="D58">
-        <v>1417</v>
+        <v>1036</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="C59">
-        <v>1099</v>
+        <v>890</v>
       </c>
       <c r="D59">
-        <v>1321</v>
+        <v>1058</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="C60">
-        <v>1095</v>
+        <v>889</v>
       </c>
       <c r="D60">
-        <v>1318</v>
+        <v>1059</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="C61">
-        <v>1137</v>
+        <v>900</v>
       </c>
       <c r="D61">
-        <v>1389</v>
+        <v>1124</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>428</v>
+        <v>259</v>
       </c>
       <c r="C62">
-        <v>1614</v>
+        <v>1092</v>
       </c>
       <c r="D62">
-        <v>2042</v>
+        <v>1351</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>448</v>
+        <v>267</v>
       </c>
       <c r="C63">
-        <v>1654</v>
+        <v>1096</v>
       </c>
       <c r="D63">
-        <v>2102</v>
+        <v>1363</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>464</v>
+        <v>345</v>
       </c>
       <c r="C64">
-        <v>1635</v>
+        <v>1112</v>
       </c>
       <c r="D64">
-        <v>2099</v>
+        <v>1457</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>510</v>
+        <v>424</v>
       </c>
       <c r="C65">
-        <v>1633</v>
+        <v>1221</v>
       </c>
       <c r="D65">
-        <v>2143</v>
+        <v>1645</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>861</v>
+        <v>799</v>
       </c>
       <c r="C66">
-        <v>1754</v>
+        <v>1414</v>
       </c>
       <c r="D66">
-        <v>2615</v>
+        <v>2213</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>871</v>
+        <v>816</v>
       </c>
       <c r="C67">
-        <v>1770</v>
+        <v>1437</v>
       </c>
       <c r="D67">
-        <v>2641</v>
+        <v>2253</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C68">
-        <v>1769</v>
+        <v>1439</v>
       </c>
       <c r="D68">
-        <v>2638</v>
+        <v>2270</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="C69">
-        <v>1766</v>
+        <v>1440</v>
       </c>
       <c r="D69">
-        <v>2640</v>
+        <v>2295</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="C70">
-        <v>1774</v>
+        <v>1418</v>
       </c>
       <c r="D70">
-        <v>2702</v>
+        <v>2325</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="C71">
-        <v>1779</v>
+        <v>1422</v>
       </c>
       <c r="D71">
-        <v>2712</v>
+        <v>2343</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>937</v>
+        <v>917</v>
       </c>
       <c r="C72">
-        <v>1776</v>
+        <v>1416</v>
       </c>
       <c r="D72">
-        <v>2713</v>
+        <v>2333</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="C73">
-        <v>1765</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2699</v>
+        <v>946</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>903</v>
+        <v>939</v>
       </c>
       <c r="C74">
-        <v>1763</v>
+        <v>1441</v>
       </c>
       <c r="D74">
-        <v>2666</v>
+        <v>2380</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>904</v>
+        <v>937</v>
       </c>
       <c r="C75">
-        <v>1769</v>
+        <v>1447</v>
       </c>
       <c r="D75">
-        <v>2673</v>
+        <v>2384</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>908</v>
+        <v>983</v>
       </c>
       <c r="C76">
-        <v>1774</v>
+        <v>1443</v>
       </c>
       <c r="D76">
-        <v>2682</v>
+        <v>2426</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>910</v>
+        <v>987</v>
       </c>
       <c r="C77">
-        <v>1777</v>
+        <v>1442</v>
       </c>
       <c r="D77">
-        <v>2687</v>
+        <v>2429</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>872</v>
+        <v>1132</v>
       </c>
       <c r="C78">
-        <v>1794</v>
+        <v>1400</v>
       </c>
       <c r="D78">
-        <v>2666</v>
+        <v>2532</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>871</v>
+        <v>975</v>
       </c>
       <c r="C79">
-        <v>1795</v>
+        <v>1387</v>
       </c>
       <c r="D79">
-        <v>2666</v>
+        <v>2362</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>865</v>
+        <v>967</v>
       </c>
       <c r="C80">
-        <v>1798</v>
+        <v>1385</v>
       </c>
       <c r="D80">
-        <v>2663</v>
+        <v>2352</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>857</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>1808</v>
+        <v>1387</v>
       </c>
       <c r="D81">
-        <v>2665</v>
+        <v>1387</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>842</v>
+        <v>937</v>
       </c>
       <c r="C82">
-        <v>1816</v>
+        <v>1357</v>
       </c>
       <c r="D82">
-        <v>2658</v>
+        <v>2294</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
-        <v>845</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>1814</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2659</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>841</v>
+        <v>938</v>
       </c>
       <c r="C84">
-        <v>1816</v>
+        <v>1358</v>
       </c>
       <c r="D84">
-        <v>2657</v>
+        <v>2296</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>833</v>
+        <v>936</v>
       </c>
       <c r="C85">
-        <v>1809</v>
+        <v>1360</v>
       </c>
       <c r="D85">
-        <v>2642</v>
+        <v>2296</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>631</v>
+        <v>865</v>
       </c>
       <c r="C86">
-        <v>1892</v>
+        <v>1348</v>
       </c>
       <c r="D86">
-        <v>2523</v>
+        <v>2213</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
-        <v>617</v>
+        <v>855</v>
       </c>
       <c r="C87">
-        <v>1896</v>
+        <v>1335</v>
       </c>
       <c r="D87">
-        <v>2513</v>
+        <v>2190</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
-        <v>618</v>
+        <v>854</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1338</v>
       </c>
       <c r="D88">
-        <v>618</v>
+        <v>2192</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>620</v>
+        <v>851</v>
       </c>
       <c r="C89">
-        <v>1898</v>
+        <v>1336</v>
       </c>
       <c r="D89">
-        <v>2518</v>
+        <v>2187</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>458</v>
+        <v>718</v>
       </c>
       <c r="C90">
-        <v>1916</v>
+        <v>1389</v>
       </c>
       <c r="D90">
-        <v>2374</v>
+        <v>2107</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>440</v>
+        <v>722</v>
       </c>
       <c r="C91">
-        <v>1913</v>
+        <v>1360</v>
       </c>
       <c r="D91">
-        <v>2353</v>
+        <v>2082</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
-        <v>439</v>
+        <v>683</v>
       </c>
       <c r="C92">
-        <v>1914</v>
+        <v>1357</v>
       </c>
       <c r="D92">
-        <v>2353</v>
+        <v>2040</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
-        <v>435</v>
+        <v>667</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1361</v>
       </c>
       <c r="D93">
-        <v>435</v>
+        <v>2028</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>298</v>
+        <v>635</v>
       </c>
       <c r="C94">
-        <v>1556</v>
+        <v>1369</v>
       </c>
       <c r="D94">
-        <v>1854</v>
+        <v>2004</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B95">
-        <v>297</v>
+        <v>637</v>
       </c>
       <c r="C95">
-        <v>1511</v>
+        <v>1367</v>
       </c>
       <c r="D95">
-        <v>1808</v>
+        <v>2004</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B96">
-        <v>298</v>
+        <v>635</v>
       </c>
       <c r="C96">
-        <v>1459</v>
+        <v>1362</v>
       </c>
       <c r="D96">
-        <v>1757</v>
+        <v>1997</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B97">
-        <v>305</v>
+        <v>634</v>
       </c>
       <c r="C97">
-        <v>1507</v>
+        <v>1363</v>
       </c>
       <c r="D97">
-        <v>1812</v>
+        <v>1997</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B98">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>1878</v>
+        <v>1270</v>
       </c>
       <c r="D98">
-        <v>2439</v>
+        <v>1270</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B99">
-        <v>572</v>
+        <v>632</v>
       </c>
       <c r="C99">
-        <v>1906</v>
+        <v>1262</v>
       </c>
       <c r="D99">
-        <v>2478</v>
+        <v>1894</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="C100">
-        <v>1905</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>1905</v>
+        <v>616</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B102">
-        <v>360</v>
+        <v>603</v>
       </c>
       <c r="C102">
-        <v>1865</v>
+        <v>1173</v>
       </c>
       <c r="D102">
-        <v>2225</v>
+        <v>1776</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B103">
-        <v>353</v>
+        <v>595</v>
       </c>
       <c r="C103">
-        <v>1861</v>
+        <v>1163</v>
       </c>
       <c r="D103">
-        <v>2214</v>
+        <v>1758</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B104">
-        <v>354</v>
+        <v>596</v>
       </c>
       <c r="C104">
-        <v>1862</v>
+        <v>1161</v>
       </c>
       <c r="D104">
-        <v>2216</v>
+        <v>1757</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B105">
-        <v>352</v>
+        <v>603</v>
       </c>
       <c r="C105">
-        <v>1886</v>
+        <v>1162</v>
       </c>
       <c r="D105">
-        <v>2238</v>
+        <v>1765</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B106">
-        <v>300</v>
+        <v>574</v>
       </c>
       <c r="C106">
-        <v>1891</v>
+        <v>1113</v>
       </c>
       <c r="D106">
-        <v>2191</v>
+        <v>1687</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B107">
-        <v>295</v>
+        <v>566</v>
       </c>
       <c r="C107">
-        <v>1895</v>
+        <v>1112</v>
       </c>
       <c r="D107">
-        <v>2190</v>
+        <v>1678</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B108">
-        <v>296</v>
+        <v>549</v>
       </c>
       <c r="C108">
-        <v>1897</v>
+        <v>1110</v>
       </c>
       <c r="D108">
-        <v>2193</v>
+        <v>1659</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B109">
-        <v>295</v>
+        <v>540</v>
       </c>
       <c r="C109">
-        <v>1896</v>
+        <v>1111</v>
       </c>
       <c r="D109">
-        <v>2191</v>
+        <v>1651</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B110">
-        <v>296</v>
+        <v>535</v>
       </c>
       <c r="C110">
-        <v>1901</v>
+        <v>1108</v>
       </c>
       <c r="D110">
-        <v>2197</v>
+        <v>1643</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B111">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1899</v>
+        <v>1109</v>
       </c>
       <c r="D111">
-        <v>2193</v>
+        <v>1109</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B112">
-        <v>296</v>
+        <v>533</v>
       </c>
       <c r="C112">
-        <v>1901</v>
+        <v>1108</v>
       </c>
       <c r="D112">
-        <v>2197</v>
+        <v>1641</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B113">
-        <v>303</v>
+        <v>535</v>
       </c>
       <c r="C113">
-        <v>1904</v>
+        <v>1126</v>
       </c>
       <c r="D113">
-        <v>2207</v>
+        <v>1661</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B114">
-        <v>361</v>
+        <v>532</v>
       </c>
       <c r="C114">
-        <v>1917</v>
+        <v>1257</v>
       </c>
       <c r="D114">
-        <v>2278</v>
+        <v>1789</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B115">
-        <v>368</v>
+        <v>535</v>
       </c>
       <c r="C115">
-        <v>1912</v>
+        <v>1261</v>
       </c>
       <c r="D115">
-        <v>2280</v>
+        <v>1796</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B116">
-        <v>381</v>
+        <v>536</v>
       </c>
       <c r="C116">
-        <v>1861</v>
+        <v>1262</v>
       </c>
       <c r="D116">
-        <v>2242</v>
+        <v>1798</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B117">
-        <v>394</v>
+        <v>563</v>
       </c>
       <c r="C117">
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>2254</v>
+        <v>563</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B118">
-        <v>505</v>
+        <v>654</v>
       </c>
       <c r="C118">
-        <v>1899</v>
+        <v>1236</v>
       </c>
       <c r="D118">
-        <v>2404</v>
+        <v>1890</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B119">
-        <v>506</v>
+        <v>672</v>
       </c>
       <c r="C119">
-        <v>1895</v>
+        <v>1234</v>
       </c>
       <c r="D119">
-        <v>2401</v>
+        <v>1906</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B120">
-        <v>508</v>
+        <v>671</v>
       </c>
       <c r="C120">
-        <v>1888</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>2396</v>
+        <v>671</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="C121">
-        <v>1880</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1880</v>
+        <v>677</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B122">
-        <v>609</v>
+        <v>829</v>
       </c>
       <c r="C122">
-        <v>1867</v>
+        <v>1272</v>
       </c>
       <c r="D122">
-        <v>2476</v>
+        <v>2101</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B123">
-        <v>616</v>
+        <v>818</v>
       </c>
       <c r="C123">
-        <v>1872</v>
+        <v>1259</v>
       </c>
       <c r="D123">
-        <v>2488</v>
+        <v>2077</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B124">
-        <v>609</v>
+        <v>809</v>
       </c>
       <c r="C124">
-        <v>1893</v>
+        <v>1245</v>
       </c>
       <c r="D124">
-        <v>2502</v>
+        <v>2054</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B125">
-        <v>605</v>
+        <v>807</v>
       </c>
       <c r="C125">
-        <v>1879</v>
+        <v>1243</v>
       </c>
       <c r="D125">
-        <v>2484</v>
+        <v>2050</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B126">
-        <v>301</v>
+        <v>785</v>
       </c>
       <c r="C126">
-        <v>1823</v>
+        <v>1200</v>
       </c>
       <c r="D126">
-        <v>2124</v>
+        <v>1985</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B127">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>1849</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>2129</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B128">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>2125</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B129">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>1833</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>2098</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B130">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>1841</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>2055</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B131">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1833</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>2039</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>1793</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>1793</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B133">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>1784</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>1989</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B134">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>1335</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>1492</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B135">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>1267</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>1412</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B136">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>1263</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>1402</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
-        <v>670</v>
+        <v>362</v>
       </c>
       <c r="C2">
-        <v>1280</v>
+        <v>900</v>
       </c>
       <c r="D2">
-        <v>1950</v>
+        <v>1262</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
-        <v>658</v>
+        <v>354</v>
       </c>
       <c r="C3">
-        <v>1237</v>
+        <v>901</v>
       </c>
       <c r="D3">
-        <v>1895</v>
+        <v>1255</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
-        <v>661</v>
+        <v>357</v>
       </c>
       <c r="C4">
-        <v>1238</v>
+        <v>899</v>
       </c>
       <c r="D4">
-        <v>1899</v>
+        <v>1256</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
-        <v>669</v>
+        <v>359</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>669</v>
+        <v>359</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
-        <v>680</v>
+        <v>366</v>
       </c>
       <c r="C6">
-        <v>1231</v>
+        <v>863</v>
       </c>
       <c r="D6">
-        <v>1911</v>
+        <v>1229</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
-        <v>676</v>
+        <v>363</v>
       </c>
       <c r="C7">
-        <v>1228</v>
+        <v>860</v>
       </c>
       <c r="D7">
-        <v>1904</v>
+        <v>1223</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
-        <v>678</v>
+        <v>366</v>
       </c>
       <c r="C9">
-        <v>1229</v>
+        <v>861</v>
       </c>
       <c r="D9">
-        <v>1907</v>
+        <v>1227</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
-        <v>666</v>
+        <v>341</v>
       </c>
       <c r="C10">
-        <v>1238</v>
+        <v>706</v>
       </c>
       <c r="D10">
-        <v>1904</v>
+        <v>1047</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
-        <v>663</v>
+        <v>350</v>
       </c>
       <c r="C11">
-        <v>1231</v>
+        <v>686</v>
       </c>
       <c r="D11">
-        <v>1894</v>
+        <v>1036</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1229</v>
+        <v>687</v>
       </c>
       <c r="D13">
-        <v>1893</v>
+        <v>687</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
-        <v>666</v>
+        <v>353</v>
       </c>
       <c r="C14">
-        <v>1237</v>
+        <v>690</v>
       </c>
       <c r="D14">
-        <v>1903</v>
+        <v>1043</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
-        <v>667</v>
+        <v>352</v>
       </c>
       <c r="C15">
-        <v>1246</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1913</v>
+        <v>352</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
-        <v>669</v>
+        <v>350</v>
       </c>
       <c r="C16">
-        <v>1244</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1913</v>
+        <v>350</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
-        <v>702</v>
+        <v>361</v>
       </c>
       <c r="C17">
-        <v>1242</v>
+        <v>698</v>
       </c>
       <c r="D17">
-        <v>1944</v>
+        <v>1059</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>723</v>
+        <v>444</v>
       </c>
       <c r="C18">
-        <v>1249</v>
+        <v>883</v>
       </c>
       <c r="D18">
-        <v>1972</v>
+        <v>1327</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
-        <v>689</v>
+        <v>450</v>
       </c>
       <c r="C19">
-        <v>1244</v>
+        <v>890</v>
       </c>
       <c r="D19">
-        <v>1933</v>
+        <v>1340</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
-        <v>714</v>
+        <v>452</v>
       </c>
       <c r="C20">
-        <v>1249</v>
+        <v>891</v>
       </c>
       <c r="D20">
-        <v>1963</v>
+        <v>1343</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>738</v>
+        <v>456</v>
       </c>
       <c r="C21">
-        <v>1247</v>
+        <v>898</v>
       </c>
       <c r="D21">
-        <v>1985</v>
+        <v>1354</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>787</v>
+        <v>498</v>
       </c>
       <c r="C22">
-        <v>1259</v>
+        <v>1025</v>
       </c>
       <c r="D22">
-        <v>2046</v>
+        <v>1523</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>786</v>
+        <v>504</v>
       </c>
       <c r="C23">
-        <v>1263</v>
+        <v>1029</v>
       </c>
       <c r="D23">
-        <v>2049</v>
+        <v>1533</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>784</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>1264</v>
+        <v>1028</v>
       </c>
       <c r="D24">
-        <v>2048</v>
+        <v>1028</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>780</v>
+        <v>503</v>
       </c>
       <c r="C25">
-        <v>1259</v>
+        <v>1029</v>
       </c>
       <c r="D25">
-        <v>2039</v>
+        <v>1532</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="C26">
-        <v>1361</v>
+        <v>1094</v>
       </c>
       <c r="D26">
-        <v>1361</v>
+        <v>1661</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>777</v>
+        <v>559</v>
       </c>
       <c r="C27">
-        <v>1354</v>
+        <v>1095</v>
       </c>
       <c r="D27">
-        <v>2131</v>
+        <v>1654</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>782</v>
+        <v>575</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="D28">
-        <v>782</v>
+        <v>1668</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>784</v>
+        <v>581</v>
       </c>
       <c r="C29">
-        <v>1355</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2139</v>
+        <v>581</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>765</v>
+        <v>472</v>
       </c>
       <c r="C30">
-        <v>1342</v>
+        <v>953</v>
       </c>
       <c r="D30">
-        <v>2107</v>
+        <v>1425</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>753</v>
+        <v>476</v>
       </c>
       <c r="C31">
-        <v>1329</v>
+        <v>909</v>
       </c>
       <c r="D31">
-        <v>2082</v>
+        <v>1385</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>751</v>
+        <v>465</v>
       </c>
       <c r="C32">
-        <v>1327</v>
+        <v>878</v>
       </c>
       <c r="D32">
-        <v>2078</v>
+        <v>1343</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>746</v>
+        <v>458</v>
       </c>
       <c r="C33">
-        <v>1328</v>
+        <v>874</v>
       </c>
       <c r="D33">
-        <v>2074</v>
+        <v>1332</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>539</v>
+        <v>398</v>
       </c>
       <c r="C34">
-        <v>1351</v>
+        <v>742</v>
       </c>
       <c r="D34">
-        <v>1890</v>
+        <v>1140</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>534</v>
+        <v>346</v>
       </c>
       <c r="C35">
-        <v>1349</v>
+        <v>723</v>
       </c>
       <c r="D35">
-        <v>1883</v>
+        <v>1069</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>544</v>
+        <v>332</v>
       </c>
       <c r="C36">
-        <v>1348</v>
+        <v>755</v>
       </c>
       <c r="D36">
-        <v>1892</v>
+        <v>1087</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>692</v>
+        <v>321</v>
       </c>
       <c r="C37">
-        <v>1337</v>
+        <v>778</v>
       </c>
       <c r="D37">
-        <v>2029</v>
+        <v>1099</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>420</v>
+        <v>371</v>
       </c>
       <c r="C38">
-        <v>1143</v>
+        <v>655</v>
       </c>
       <c r="D38">
-        <v>1563</v>
+        <v>1026</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="C39">
-        <v>1144</v>
+        <v>638</v>
       </c>
       <c r="D39">
-        <v>1565</v>
+        <v>1023</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
-        <v>414</v>
+        <v>355</v>
       </c>
       <c r="C40">
-        <v>1140</v>
+        <v>613</v>
       </c>
       <c r="D40">
-        <v>1554</v>
+        <v>968</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="C41">
-        <v>1143</v>
+        <v>623</v>
       </c>
       <c r="D41">
-        <v>1536</v>
+        <v>999</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>263</v>
+        <v>355</v>
       </c>
       <c r="C42">
-        <v>1106</v>
+        <v>568</v>
       </c>
       <c r="D42">
-        <v>1369</v>
+        <v>923</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
-        <v>256</v>
+        <v>322</v>
       </c>
       <c r="C43">
-        <v>1098</v>
+        <v>564</v>
       </c>
       <c r="D43">
-        <v>1354</v>
+        <v>886</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>165</v>
+        <v>355</v>
       </c>
       <c r="C44">
-        <v>1100</v>
+        <v>453</v>
       </c>
       <c r="D44">
-        <v>1265</v>
+        <v>808</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>164</v>
+        <v>330</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="D45">
-        <v>164</v>
+        <v>774</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>126</v>
+        <v>324</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="D46">
-        <v>126</v>
+        <v>837</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
-        <v>121</v>
+        <v>302</v>
       </c>
       <c r="C47">
-        <v>1099</v>
+        <v>518</v>
       </c>
       <c r="D47">
-        <v>1220</v>
+        <v>820</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>124</v>
+        <v>326</v>
       </c>
       <c r="C48">
-        <v>1061</v>
+        <v>510</v>
       </c>
       <c r="D48">
-        <v>1185</v>
+        <v>836</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>125</v>
+        <v>331</v>
       </c>
       <c r="C49">
-        <v>1082</v>
+        <v>458</v>
       </c>
       <c r="D49">
-        <v>1207</v>
+        <v>789</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="C50">
-        <v>1119</v>
+        <v>471</v>
       </c>
       <c r="D50">
-        <v>1239</v>
+        <v>746</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
-        <v>119</v>
+        <v>272</v>
       </c>
       <c r="C51">
-        <v>1133</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1252</v>
+        <v>272</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>120</v>
+        <v>291</v>
       </c>
       <c r="C52">
-        <v>1131</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1251</v>
+        <v>291</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
-        <v>123</v>
+        <v>311</v>
       </c>
       <c r="C53">
-        <v>1120</v>
+        <v>478</v>
       </c>
       <c r="D53">
-        <v>1243</v>
+        <v>789</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="C54">
-        <v>990</v>
+        <v>672</v>
       </c>
       <c r="D54">
-        <v>1178</v>
+        <v>949</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
-        <v>71</v>
+        <v>294</v>
       </c>
       <c r="C55">
-        <v>867</v>
+        <v>680</v>
       </c>
       <c r="D55">
-        <v>938</v>
+        <v>974</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="C56">
-        <v>836</v>
+        <v>698</v>
       </c>
       <c r="D56">
-        <v>909</v>
+        <v>1004</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="C57">
-        <v>834</v>
+        <v>699</v>
       </c>
       <c r="D57">
-        <v>911</v>
+        <v>1013</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>149</v>
+        <v>369</v>
       </c>
       <c r="C58">
-        <v>887</v>
+        <v>687</v>
       </c>
       <c r="D58">
-        <v>1036</v>
+        <v>1056</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
-        <v>168</v>
+        <v>374</v>
       </c>
       <c r="C59">
-        <v>890</v>
+        <v>688</v>
       </c>
       <c r="D59">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>889</v>
+        <v>687</v>
       </c>
       <c r="D60">
-        <v>1059</v>
+        <v>687</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>224</v>
+        <v>389</v>
       </c>
       <c r="C61">
-        <v>900</v>
+        <v>689</v>
       </c>
       <c r="D61">
-        <v>1124</v>
+        <v>1078</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>1092</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1351</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>267</v>
+        <v>477</v>
       </c>
       <c r="C63">
-        <v>1096</v>
+        <v>752</v>
       </c>
       <c r="D63">
-        <v>1363</v>
+        <v>1229</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>345</v>
+        <v>481</v>
       </c>
       <c r="C64">
-        <v>1112</v>
+        <v>753</v>
       </c>
       <c r="D64">
-        <v>1457</v>
+        <v>1234</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>424</v>
+        <v>515</v>
       </c>
       <c r="C65">
-        <v>1221</v>
+        <v>764</v>
       </c>
       <c r="D65">
-        <v>1645</v>
+        <v>1279</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>799</v>
+        <v>656</v>
       </c>
       <c r="C66">
-        <v>1414</v>
+        <v>1087</v>
       </c>
       <c r="D66">
-        <v>2213</v>
+        <v>1743</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>816</v>
+        <v>663</v>
       </c>
       <c r="C67">
-        <v>1437</v>
+        <v>1104</v>
       </c>
       <c r="D67">
-        <v>2253</v>
+        <v>1767</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>831</v>
+        <v>665</v>
       </c>
       <c r="C68">
-        <v>1439</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>2270</v>
+        <v>665</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>855</v>
+        <v>672</v>
       </c>
       <c r="C69">
-        <v>1440</v>
+        <v>1171</v>
       </c>
       <c r="D69">
-        <v>2295</v>
+        <v>1843</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>907</v>
+        <v>694</v>
       </c>
       <c r="C70">
-        <v>1418</v>
+        <v>1231</v>
       </c>
       <c r="D70">
-        <v>2325</v>
+        <v>1925</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>921</v>
+        <v>698</v>
       </c>
       <c r="C71">
-        <v>1422</v>
+        <v>1230</v>
       </c>
       <c r="D71">
-        <v>2343</v>
+        <v>1928</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>917</v>
+        <v>694</v>
       </c>
       <c r="C72">
-        <v>1416</v>
+        <v>1246</v>
       </c>
       <c r="D72">
-        <v>2333</v>
+        <v>1940</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>946</v>
+        <v>706</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="D73">
-        <v>946</v>
+        <v>1992</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>939</v>
+        <v>659</v>
       </c>
       <c r="C74">
-        <v>1441</v>
+        <v>1315</v>
       </c>
       <c r="D74">
-        <v>2380</v>
+        <v>1974</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>937</v>
+        <v>669</v>
       </c>
       <c r="C75">
-        <v>1447</v>
+        <v>1316</v>
       </c>
       <c r="D75">
-        <v>2384</v>
+        <v>1985</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>983</v>
+        <v>674</v>
       </c>
       <c r="C76">
-        <v>1443</v>
+        <v>1315</v>
       </c>
       <c r="D76">
-        <v>2426</v>
+        <v>1989</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>987</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>1442</v>
+        <v>1316</v>
       </c>
       <c r="D77">
-        <v>2429</v>
+        <v>1316</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>1132</v>
+        <v>645</v>
       </c>
       <c r="C78">
-        <v>1400</v>
+        <v>1314</v>
       </c>
       <c r="D78">
-        <v>2532</v>
+        <v>1959</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>975</v>
+        <v>644</v>
       </c>
       <c r="C79">
-        <v>1387</v>
+        <v>1312</v>
       </c>
       <c r="D79">
-        <v>2362</v>
+        <v>1956</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>967</v>
+        <v>645</v>
       </c>
       <c r="C80">
-        <v>1385</v>
+        <v>1316</v>
       </c>
       <c r="D80">
-        <v>2352</v>
+        <v>1961</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="C81">
-        <v>1387</v>
+        <v>1311</v>
       </c>
       <c r="D81">
-        <v>1387</v>
+        <v>1954</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>937</v>
+        <v>593</v>
       </c>
       <c r="C82">
-        <v>1357</v>
+        <v>1314</v>
       </c>
       <c r="D82">
-        <v>2294</v>
+        <v>1907</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1312</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>938</v>
+        <v>587</v>
       </c>
       <c r="C84">
-        <v>1358</v>
+        <v>1315</v>
       </c>
       <c r="D84">
-        <v>2296</v>
+        <v>1902</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
-        <v>936</v>
+        <v>590</v>
       </c>
       <c r="C85">
-        <v>1360</v>
+        <v>1317</v>
       </c>
       <c r="D85">
-        <v>2296</v>
+        <v>1907</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>865</v>
+        <v>546</v>
       </c>
       <c r="C86">
-        <v>1348</v>
+        <v>1249</v>
       </c>
       <c r="D86">
-        <v>2213</v>
+        <v>1795</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>1335</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2190</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>854</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1338</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>2192</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>851</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>1336</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>2187</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>718</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1389</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>2107</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>722</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>1360</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>2082</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>683</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1357</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>667</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>1361</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>2028</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>1369</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>2004</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>1367</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>2004</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1362</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>1997</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>1363</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1997</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>632</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>1262</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1894</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B100">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>1776</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>1163</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>1758</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>596</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1757</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>1162</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>1765</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>1113</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>1687</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B107">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>1678</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>1659</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>1651</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>1643</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>1109</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1109</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B112">
-        <v>533</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>1108</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1641</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>1126</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1661</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>532</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>1789</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1796</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>1262</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1798</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1236</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>1890</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>1234</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1906</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1259</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>2077</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>809</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1245</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>2054</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>1243</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>2050</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>1985</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>09.04.202694</t>
-  </si>
-  <si>
-    <t>09.04.202695</t>
-  </si>
-  <si>
-    <t>09.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>16.04.202694</t>
+  </si>
+  <si>
+    <t>16.04.202695</t>
+  </si>
+  <si>
+    <t>16.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
-        <v>683</v>
+        <v>451</v>
       </c>
       <c r="C2">
-        <v>1765</v>
+        <v>1352</v>
       </c>
       <c r="D2">
-        <v>2448</v>
+        <v>1803</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1752</v>
+        <v>1356</v>
       </c>
       <c r="D3">
-        <v>2402</v>
+        <v>1356</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
-        <v>651</v>
+        <v>448</v>
       </c>
       <c r="C4">
-        <v>1736</v>
+        <v>1351</v>
       </c>
       <c r="D4">
-        <v>2387</v>
+        <v>1799</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1732</v>
+        <v>1353</v>
       </c>
       <c r="D5">
-        <v>2377</v>
+        <v>1353</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
-        <v>617</v>
+        <v>380</v>
       </c>
       <c r="C6">
-        <v>1758</v>
+        <v>1330</v>
       </c>
       <c r="D6">
-        <v>2375</v>
+        <v>1710</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
-        <v>623</v>
+        <v>381</v>
       </c>
       <c r="C7">
-        <v>1757</v>
+        <v>1331</v>
       </c>
       <c r="D7">
-        <v>2380</v>
+        <v>1712</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
-        <v>625</v>
+        <v>376</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>625</v>
+        <v>376</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
-        <v>622</v>
+        <v>396</v>
       </c>
       <c r="C9">
-        <v>1758</v>
+        <v>1332</v>
       </c>
       <c r="D9">
-        <v>2380</v>
+        <v>1728</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="C10">
-        <v>1718</v>
+        <v>1331</v>
       </c>
       <c r="D10">
-        <v>1718</v>
+        <v>1764</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
-        <v>623</v>
+        <v>448</v>
       </c>
       <c r="C11">
-        <v>1695</v>
+        <v>1329</v>
       </c>
       <c r="D11">
-        <v>2318</v>
+        <v>1777</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
-        <v>622</v>
+        <v>390</v>
       </c>
       <c r="C12">
-        <v>1667</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2289</v>
+        <v>390</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
-        <v>623</v>
+        <v>418</v>
       </c>
       <c r="C13">
-        <v>1738</v>
+        <v>1327</v>
       </c>
       <c r="D13">
-        <v>2361</v>
+        <v>1745</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
-        <v>655</v>
+        <v>423</v>
       </c>
       <c r="C14">
-        <v>1760</v>
+        <v>1334</v>
       </c>
       <c r="D14">
-        <v>2415</v>
+        <v>1757</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="C15">
-        <v>1759</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1759</v>
+        <v>458</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
-        <v>654</v>
+        <v>443</v>
       </c>
       <c r="C16">
-        <v>1758</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2412</v>
+        <v>443</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
-        <v>636</v>
+        <v>455</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1333</v>
       </c>
       <c r="D17">
-        <v>636</v>
+        <v>1788</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
-        <v>660</v>
+        <v>480</v>
       </c>
       <c r="C18">
-        <v>1760</v>
+        <v>1336</v>
       </c>
       <c r="D18">
-        <v>2420</v>
+        <v>1816</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
-        <v>667</v>
+        <v>485</v>
       </c>
       <c r="C19">
-        <v>1758</v>
+        <v>1337</v>
       </c>
       <c r="D19">
-        <v>2425</v>
+        <v>1822</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
-        <v>679</v>
+        <v>450</v>
       </c>
       <c r="C20">
-        <v>1763</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2442</v>
+        <v>450</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
-        <v>701</v>
+        <v>476</v>
       </c>
       <c r="C21">
-        <v>1762</v>
+        <v>1336</v>
       </c>
       <c r="D21">
-        <v>2463</v>
+        <v>1812</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
-        <v>690</v>
+        <v>492</v>
       </c>
       <c r="C22">
-        <v>1758</v>
+        <v>1374</v>
       </c>
       <c r="D22">
-        <v>2448</v>
+        <v>1866</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>692</v>
+        <v>522</v>
       </c>
       <c r="C23">
-        <v>1756</v>
+        <v>1373</v>
       </c>
       <c r="D23">
-        <v>2448</v>
+        <v>1895</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
-        <v>676</v>
+        <v>523</v>
       </c>
       <c r="C24">
-        <v>1743</v>
+        <v>1375</v>
       </c>
       <c r="D24">
-        <v>2419</v>
+        <v>1898</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>668</v>
+        <v>515</v>
       </c>
       <c r="C25">
-        <v>1768</v>
+        <v>1374</v>
       </c>
       <c r="D25">
-        <v>2436</v>
+        <v>1889</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>601</v>
+        <v>548</v>
       </c>
       <c r="C26">
-        <v>1773</v>
+        <v>1376</v>
       </c>
       <c r="D26">
-        <v>2374</v>
+        <v>1924</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>614</v>
+        <v>556</v>
       </c>
       <c r="C27">
-        <v>1767</v>
+        <v>1370</v>
       </c>
       <c r="D27">
-        <v>2381</v>
+        <v>1926</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="C28">
-        <v>1766</v>
+        <v>1367</v>
       </c>
       <c r="D28">
-        <v>1766</v>
+        <v>1874</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>615</v>
+        <v>493</v>
       </c>
       <c r="C29">
-        <v>1767</v>
+        <v>1369</v>
       </c>
       <c r="D29">
-        <v>2382</v>
+        <v>1862</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="C30">
-        <v>1772</v>
+        <v>1370</v>
       </c>
       <c r="D30">
-        <v>2361</v>
+        <v>1935</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="C31">
-        <v>1761</v>
+        <v>1365</v>
       </c>
       <c r="D31">
-        <v>2344</v>
+        <v>1936</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="C32">
-        <v>1759</v>
+        <v>1302</v>
       </c>
       <c r="D32">
-        <v>2319</v>
+        <v>1852</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1305</v>
       </c>
       <c r="D33">
-        <v>564</v>
+        <v>1852</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>410</v>
+        <v>634</v>
       </c>
       <c r="C34">
-        <v>1757</v>
+        <v>1238</v>
       </c>
       <c r="D34">
-        <v>2167</v>
+        <v>1872</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>400</v>
+        <v>604</v>
       </c>
       <c r="C35">
-        <v>1715</v>
+        <v>1235</v>
       </c>
       <c r="D35">
-        <v>2115</v>
+        <v>1839</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>396</v>
+        <v>611</v>
       </c>
       <c r="C36">
-        <v>1709</v>
+        <v>1238</v>
       </c>
       <c r="D36">
-        <v>2105</v>
+        <v>1849</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>378</v>
+        <v>596</v>
       </c>
       <c r="C37">
-        <v>1704</v>
+        <v>1237</v>
       </c>
       <c r="D37">
-        <v>2082</v>
+        <v>1833</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>285</v>
+        <v>650</v>
       </c>
       <c r="C38">
-        <v>1478</v>
+        <v>1150</v>
       </c>
       <c r="D38">
-        <v>1763</v>
+        <v>1800</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1397</v>
+        <v>1130</v>
       </c>
       <c r="D39">
-        <v>1633</v>
+        <v>1130</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>238</v>
+        <v>613</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="D40">
-        <v>238</v>
+        <v>1740</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>233</v>
+        <v>554</v>
       </c>
       <c r="C41">
-        <v>1411</v>
+        <v>1126</v>
       </c>
       <c r="D41">
-        <v>1644</v>
+        <v>1680</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>236</v>
+        <v>355</v>
       </c>
       <c r="C42">
-        <v>1271</v>
+        <v>1044</v>
       </c>
       <c r="D42">
-        <v>1507</v>
+        <v>1399</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>235</v>
+        <v>345</v>
       </c>
       <c r="C43">
-        <v>1261</v>
+        <v>1001</v>
       </c>
       <c r="D43">
-        <v>1496</v>
+        <v>1346</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="C44">
-        <v>1396</v>
+        <v>995</v>
       </c>
       <c r="D44">
-        <v>1630</v>
+        <v>1337</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>233</v>
+        <v>329</v>
       </c>
       <c r="C45">
-        <v>1413</v>
+        <v>994</v>
       </c>
       <c r="D45">
-        <v>1646</v>
+        <v>1323</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="C46">
-        <v>1272</v>
+        <v>960</v>
       </c>
       <c r="D46">
-        <v>1506</v>
+        <v>1146</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="C47">
-        <v>1260</v>
+        <v>941</v>
       </c>
       <c r="D47">
-        <v>1496</v>
+        <v>1095</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="D48">
-        <v>217</v>
+        <v>1033</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>253</v>
+        <v>209</v>
       </c>
       <c r="C49">
-        <v>1251</v>
+        <v>848</v>
       </c>
       <c r="D49">
-        <v>1504</v>
+        <v>1057</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="C50">
-        <v>1295</v>
+        <v>866</v>
       </c>
       <c r="D50">
-        <v>1559</v>
+        <v>1034</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="C51">
-        <v>1293</v>
+        <v>876</v>
       </c>
       <c r="D51">
-        <v>1523</v>
+        <v>1051</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="C52">
-        <v>1266</v>
+        <v>1015</v>
       </c>
       <c r="D52">
-        <v>1491</v>
+        <v>1284</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>227</v>
+        <v>307</v>
       </c>
       <c r="C53">
-        <v>1293</v>
+        <v>977</v>
       </c>
       <c r="D53">
-        <v>1520</v>
+        <v>1284</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>223</v>
+        <v>297</v>
       </c>
       <c r="C54">
-        <v>1292</v>
+        <v>979</v>
       </c>
       <c r="D54">
-        <v>1515</v>
+        <v>1276</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>219</v>
+        <v>290</v>
       </c>
       <c r="C55">
-        <v>1285</v>
+        <v>1003</v>
       </c>
       <c r="D55">
-        <v>1504</v>
+        <v>1293</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>1302</v>
+        <v>1002</v>
       </c>
       <c r="D56">
-        <v>1513</v>
+        <v>1002</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
-        <v>214</v>
+        <v>298</v>
       </c>
       <c r="C57">
-        <v>1139</v>
+        <v>1004</v>
       </c>
       <c r="D57">
-        <v>1353</v>
+        <v>1302</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>226</v>
+        <v>380</v>
       </c>
       <c r="C58">
-        <v>971</v>
+        <v>989</v>
       </c>
       <c r="D58">
-        <v>1197</v>
+        <v>1369</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>220</v>
+        <v>381</v>
       </c>
       <c r="C59">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="D59">
-        <v>1214</v>
+        <v>1366</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>191</v>
+        <v>380</v>
       </c>
       <c r="C60">
-        <v>1209</v>
+        <v>982</v>
       </c>
       <c r="D60">
-        <v>1400</v>
+        <v>1362</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>198</v>
+        <v>366</v>
       </c>
       <c r="C61">
-        <v>1222</v>
+        <v>1040</v>
       </c>
       <c r="D61">
-        <v>1420</v>
+        <v>1406</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>276</v>
+        <v>406</v>
       </c>
       <c r="C62">
-        <v>1313</v>
+        <v>1083</v>
       </c>
       <c r="D62">
-        <v>1589</v>
+        <v>1489</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>272</v>
+        <v>420</v>
       </c>
       <c r="C63">
-        <v>1322</v>
+        <v>1090</v>
       </c>
       <c r="D63">
-        <v>1594</v>
+        <v>1510</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>332</v>
+        <v>415</v>
       </c>
       <c r="C64">
-        <v>1366</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1698</v>
+        <v>415</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>350</v>
+        <v>428</v>
       </c>
       <c r="C65">
-        <v>1368</v>
+        <v>1091</v>
       </c>
       <c r="D65">
-        <v>1718</v>
+        <v>1519</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C66">
-        <v>1358</v>
+        <v>1108</v>
       </c>
       <c r="D66">
-        <v>1859</v>
+        <v>1610</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>437</v>
+        <v>550</v>
       </c>
       <c r="C67">
-        <v>1417</v>
+        <v>1112</v>
       </c>
       <c r="D67">
-        <v>1854</v>
+        <v>1662</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>1856</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>431</v>
+        <v>573</v>
       </c>
       <c r="C69">
-        <v>1451</v>
+        <v>1122</v>
       </c>
       <c r="D69">
-        <v>1882</v>
+        <v>1695</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>750</v>
+        <v>782</v>
       </c>
       <c r="C70">
-        <v>1754</v>
+        <v>1396</v>
       </c>
       <c r="D70">
-        <v>2504</v>
+        <v>2178</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>826</v>
+        <v>783</v>
       </c>
       <c r="C71">
-        <v>1786</v>
+        <v>1420</v>
       </c>
       <c r="D71">
-        <v>2612</v>
+        <v>2203</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>822</v>
+        <v>791</v>
       </c>
       <c r="C72">
-        <v>1818</v>
+        <v>1425</v>
       </c>
       <c r="D72">
-        <v>2640</v>
+        <v>2216</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C73">
-        <v>1811</v>
+        <v>1423</v>
       </c>
       <c r="D73">
-        <v>2610</v>
+        <v>2230</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>765</v>
+        <v>814</v>
       </c>
       <c r="C74">
-        <v>1784</v>
+        <v>1444</v>
       </c>
       <c r="D74">
-        <v>2549</v>
+        <v>2258</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>788</v>
+        <v>821</v>
       </c>
       <c r="C75">
-        <v>1803</v>
+        <v>1450</v>
       </c>
       <c r="D75">
-        <v>2591</v>
+        <v>2271</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>703</v>
+        <v>833</v>
       </c>
       <c r="C76">
-        <v>1797</v>
+        <v>1440</v>
       </c>
       <c r="D76">
-        <v>2500</v>
+        <v>2273</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>1790</v>
+        <v>1435</v>
       </c>
       <c r="D77">
-        <v>2410</v>
+        <v>1435</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>580</v>
+        <v>805</v>
       </c>
       <c r="C78">
-        <v>1829</v>
+        <v>1450</v>
       </c>
       <c r="D78">
-        <v>2409</v>
+        <v>2255</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>608</v>
+        <v>801</v>
       </c>
       <c r="C79">
-        <v>1836</v>
+        <v>1455</v>
       </c>
       <c r="D79">
-        <v>2444</v>
+        <v>2256</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>656</v>
+        <v>798</v>
       </c>
       <c r="C80">
-        <v>1828</v>
+        <v>1453</v>
       </c>
       <c r="D80">
-        <v>2484</v>
+        <v>2251</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>739</v>
+        <v>801</v>
       </c>
       <c r="C81">
-        <v>1834</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>2573</v>
+        <v>801</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>718</v>
+        <v>771</v>
       </c>
       <c r="C82">
-        <v>1831</v>
+        <v>1454</v>
       </c>
       <c r="D82">
-        <v>2549</v>
+        <v>2225</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>714</v>
+        <v>769</v>
       </c>
       <c r="C83">
-        <v>1830</v>
+        <v>1455</v>
       </c>
       <c r="D83">
-        <v>2544</v>
+        <v>2224</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>712</v>
+        <v>767</v>
       </c>
       <c r="C84">
-        <v>1831</v>
+        <v>1454</v>
       </c>
       <c r="D84">
-        <v>2543</v>
+        <v>2221</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>710</v>
+        <v>769</v>
       </c>
       <c r="C85">
-        <v>1827</v>
+        <v>1456</v>
       </c>
       <c r="D85">
-        <v>2537</v>
+        <v>2225</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>642</v>
+        <v>753</v>
       </c>
       <c r="C86">
-        <v>1865</v>
+        <v>1416</v>
       </c>
       <c r="D86">
-        <v>2507</v>
+        <v>2169</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>645</v>
+        <v>740</v>
       </c>
       <c r="C87">
-        <v>1861</v>
+        <v>1414</v>
       </c>
       <c r="D87">
-        <v>2506</v>
+        <v>2154</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>643</v>
+        <v>737</v>
       </c>
       <c r="C88">
-        <v>1857</v>
+        <v>1412</v>
       </c>
       <c r="D88">
-        <v>2500</v>
+        <v>2149</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
-        <v>636</v>
+        <v>711</v>
       </c>
       <c r="C89">
-        <v>1856</v>
+        <v>1405</v>
       </c>
       <c r="D89">
-        <v>2492</v>
+        <v>2116</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="C90">
-        <v>1877</v>
+        <v>1414</v>
       </c>
       <c r="D90">
-        <v>2466</v>
+        <v>1980</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C91">
-        <v>1865</v>
+        <v>1415</v>
       </c>
       <c r="D91">
-        <v>2447</v>
+        <v>1993</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C92">
-        <v>1869</v>
+        <v>1414</v>
       </c>
       <c r="D92">
-        <v>2447</v>
+        <v>1999</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C93">
-        <v>1867</v>
+        <v>1413</v>
       </c>
       <c r="D93">
-        <v>2454</v>
+        <v>1995</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
-        <v>612</v>
+        <v>490</v>
       </c>
       <c r="C94">
-        <v>1828</v>
+        <v>1410</v>
       </c>
       <c r="D94">
-        <v>2440</v>
+        <v>1900</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
-        <v>606</v>
+        <v>486</v>
       </c>
       <c r="C95">
-        <v>1818</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>2424</v>
+        <v>486</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
-        <v>604</v>
+        <v>487</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1411</v>
       </c>
       <c r="D96">
-        <v>604</v>
+        <v>1898</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
-        <v>602</v>
+        <v>483</v>
       </c>
       <c r="C97">
-        <v>1814</v>
+        <v>1409</v>
       </c>
       <c r="D97">
-        <v>2416</v>
+        <v>1892</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
-        <v>655</v>
+        <v>452</v>
       </c>
       <c r="C98">
-        <v>1647</v>
+        <v>1296</v>
       </c>
       <c r="D98">
-        <v>2302</v>
+        <v>1748</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B99">
-        <v>665</v>
+        <v>456</v>
       </c>
       <c r="C99">
-        <v>1595</v>
+        <v>1292</v>
       </c>
       <c r="D99">
-        <v>2260</v>
+        <v>1748</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B100">
-        <v>667</v>
+        <v>453</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1289</v>
       </c>
       <c r="D100">
-        <v>667</v>
+        <v>1742</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B101">
-        <v>665</v>
+        <v>464</v>
       </c>
       <c r="C101">
-        <v>1594</v>
+        <v>1291</v>
       </c>
       <c r="D101">
-        <v>2259</v>
+        <v>1755</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B102">
-        <v>670</v>
+        <v>596</v>
       </c>
       <c r="C102">
-        <v>1598</v>
+        <v>1227</v>
       </c>
       <c r="D102">
-        <v>2268</v>
+        <v>1823</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B103">
-        <v>668</v>
+        <v>599</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="D103">
-        <v>668</v>
+        <v>1821</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="C104">
-        <v>1594</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1594</v>
+        <v>598</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B105">
-        <v>663</v>
+        <v>565</v>
       </c>
       <c r="C105">
-        <v>1598</v>
+        <v>1221</v>
       </c>
       <c r="D105">
-        <v>2261</v>
+        <v>1786</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B106">
-        <v>664</v>
+        <v>599</v>
       </c>
       <c r="C106">
-        <v>1552</v>
+        <v>1220</v>
       </c>
       <c r="D106">
-        <v>2216</v>
+        <v>1819</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B107">
-        <v>667</v>
+        <v>545</v>
       </c>
       <c r="C107">
-        <v>1543</v>
+        <v>1216</v>
       </c>
       <c r="D107">
-        <v>2210</v>
+        <v>1761</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B108">
-        <v>666</v>
+        <v>565</v>
       </c>
       <c r="C108">
-        <v>1494</v>
+        <v>1217</v>
       </c>
       <c r="D108">
-        <v>2160</v>
+        <v>1782</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B109">
-        <v>669</v>
+        <v>579</v>
       </c>
       <c r="C109">
-        <v>1586</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>2255</v>
+        <v>579</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B110">
-        <v>724</v>
+        <v>604</v>
       </c>
       <c r="C110">
-        <v>1560</v>
+        <v>1220</v>
       </c>
       <c r="D110">
-        <v>2284</v>
+        <v>1824</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B111">
-        <v>722</v>
+        <v>603</v>
       </c>
       <c r="C111">
-        <v>1540</v>
+        <v>1218</v>
       </c>
       <c r="D111">
-        <v>2262</v>
+        <v>1821</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B112">
-        <v>721</v>
+        <v>602</v>
       </c>
       <c r="C112">
-        <v>1521</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>2242</v>
+        <v>602</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B113">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>1493</v>
+        <v>1219</v>
       </c>
       <c r="D113">
-        <v>2200</v>
+        <v>1219</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B114">
-        <v>709</v>
+        <v>625</v>
       </c>
       <c r="C114">
-        <v>1550</v>
+        <v>1221</v>
       </c>
       <c r="D114">
-        <v>2259</v>
+        <v>1846</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B115">
-        <v>707</v>
+        <v>618</v>
       </c>
       <c r="C115">
-        <v>1583</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>2290</v>
+        <v>618</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B116">
-        <v>709</v>
+        <v>633</v>
       </c>
       <c r="C116">
-        <v>1585</v>
+        <v>1222</v>
       </c>
       <c r="D116">
-        <v>2294</v>
+        <v>1855</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B117">
-        <v>713</v>
+        <v>631</v>
       </c>
       <c r="C117">
-        <v>1584</v>
+        <v>1223</v>
       </c>
       <c r="D117">
-        <v>2297</v>
+        <v>1854</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B118">
-        <v>788</v>
+        <v>662</v>
       </c>
       <c r="C118">
-        <v>1582</v>
+        <v>1236</v>
       </c>
       <c r="D118">
-        <v>2370</v>
+        <v>1898</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B119">
-        <v>799</v>
+        <v>688</v>
       </c>
       <c r="C119">
-        <v>1584</v>
+        <v>1237</v>
       </c>
       <c r="D119">
-        <v>2383</v>
+        <v>1925</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B120">
-        <v>790</v>
+        <v>696</v>
       </c>
       <c r="C120">
-        <v>1570</v>
+        <v>1239</v>
       </c>
       <c r="D120">
-        <v>2360</v>
+        <v>1935</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B121">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>1578</v>
+        <v>1241</v>
       </c>
       <c r="D121">
-        <v>2373</v>
+        <v>1241</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B122">
-        <v>792</v>
+        <v>711</v>
       </c>
       <c r="C122">
-        <v>1763</v>
+        <v>1320</v>
       </c>
       <c r="D122">
-        <v>2555</v>
+        <v>2031</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B123">
-        <v>776</v>
+        <v>708</v>
       </c>
       <c r="C123">
-        <v>1821</v>
+        <v>1321</v>
       </c>
       <c r="D123">
-        <v>2597</v>
+        <v>2029</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B124">
-        <v>787</v>
+        <v>699</v>
       </c>
       <c r="C124">
-        <v>1827</v>
+        <v>1319</v>
       </c>
       <c r="D124">
-        <v>2614</v>
+        <v>2018</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B125">
-        <v>792</v>
+        <v>705</v>
       </c>
       <c r="C125">
-        <v>1836</v>
+        <v>1324</v>
       </c>
       <c r="D125">
-        <v>2628</v>
+        <v>2029</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B126">
-        <v>679</v>
+        <v>704</v>
       </c>
       <c r="C126">
-        <v>1831</v>
+        <v>1328</v>
       </c>
       <c r="D126">
-        <v>2510</v>
+        <v>2032</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B127">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="C127">
-        <v>1824</v>
+        <v>1316</v>
       </c>
       <c r="D127">
-        <v>2493</v>
+        <v>2022</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B128">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C128">
-        <v>1832</v>
+        <v>1312</v>
       </c>
       <c r="D128">
-        <v>2502</v>
+        <v>2000</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B129">
-        <v>664</v>
+        <v>694</v>
       </c>
       <c r="C129">
-        <v>1831</v>
+        <v>1313</v>
       </c>
       <c r="D129">
-        <v>2495</v>
+        <v>2007</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B130">
-        <v>410</v>
+        <v>645</v>
       </c>
       <c r="C130">
-        <v>1827</v>
+        <v>1291</v>
       </c>
       <c r="D130">
-        <v>2237</v>
+        <v>1936</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B131">
-        <v>339</v>
+        <v>640</v>
       </c>
       <c r="C131">
-        <v>1820</v>
+        <v>1293</v>
       </c>
       <c r="D131">
-        <v>2159</v>
+        <v>1933</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B132">
-        <v>320</v>
+        <v>593</v>
       </c>
       <c r="C132">
-        <v>1815</v>
+        <v>1287</v>
       </c>
       <c r="D132">
-        <v>2135</v>
+        <v>1880</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B133">
-        <v>297</v>
+        <v>558</v>
       </c>
       <c r="C133">
-        <v>1812</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>2109</v>
+        <v>558</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B134">
-        <v>138</v>
+        <v>416</v>
       </c>
       <c r="C134">
-        <v>1448</v>
+        <v>1026</v>
       </c>
       <c r="D134">
-        <v>1586</v>
+        <v>1442</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B135">
-        <v>134</v>
+        <v>405</v>
       </c>
       <c r="C135">
-        <v>1423</v>
+        <v>993</v>
       </c>
       <c r="D135">
-        <v>1557</v>
+        <v>1398</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B136">
-        <v>133</v>
+        <v>398</v>
       </c>
       <c r="C136">
-        <v>1424</v>
+        <v>999</v>
       </c>
       <c r="D136">
-        <v>1557</v>
+        <v>1397</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B137">
-        <v>130</v>
+        <v>410</v>
       </c>
       <c r="C137">
-        <v>1421</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>1551</v>
+        <v>410</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B138">
-        <v>155</v>
+        <v>282</v>
       </c>
       <c r="C138">
-        <v>1166</v>
+        <v>911</v>
       </c>
       <c r="D138">
-        <v>1321</v>
+        <v>1193</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1181</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1131</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>1114</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>16.04.202694</t>
-  </si>
-  <si>
-    <t>16.04.202695</t>
-  </si>
-  <si>
-    <t>16.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -608,6 +320,870 @@
   </si>
   <si>
     <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,16 +1570,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C2">
-        <v>1352</v>
+        <v>1296</v>
       </c>
       <c r="D2">
-        <v>1803</v>
+        <v>1748</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1590,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="C3">
-        <v>1356</v>
+        <v>1292</v>
       </c>
       <c r="D3">
-        <v>1356</v>
+        <v>1748</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1610,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C4">
-        <v>1351</v>
+        <v>1289</v>
       </c>
       <c r="D4">
-        <v>1799</v>
+        <v>1742</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1630,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="C5">
-        <v>1353</v>
+        <v>1291</v>
       </c>
       <c r="D5">
-        <v>1353</v>
+        <v>1755</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>380</v>
+        <v>596</v>
       </c>
       <c r="C6">
-        <v>1330</v>
+        <v>1227</v>
       </c>
       <c r="D6">
-        <v>1710</v>
+        <v>1823</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>381</v>
+        <v>599</v>
       </c>
       <c r="C7">
-        <v>1331</v>
+        <v>1222</v>
       </c>
       <c r="D7">
-        <v>1712</v>
+        <v>1821</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>376</v>
+        <v>598</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>376</v>
+        <v>598</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>396</v>
+        <v>565</v>
       </c>
       <c r="C9">
-        <v>1332</v>
+        <v>1221</v>
       </c>
       <c r="D9">
-        <v>1728</v>
+        <v>1786</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>433</v>
+        <v>599</v>
       </c>
       <c r="C10">
-        <v>1331</v>
+        <v>1220</v>
       </c>
       <c r="D10">
-        <v>1764</v>
+        <v>1819</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>448</v>
+        <v>545</v>
       </c>
       <c r="C11">
-        <v>1329</v>
+        <v>1216</v>
       </c>
       <c r="D11">
-        <v>1777</v>
+        <v>1761</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>390</v>
+        <v>565</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1217</v>
       </c>
       <c r="D12">
-        <v>390</v>
+        <v>1782</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>418</v>
+        <v>579</v>
       </c>
       <c r="C13">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1745</v>
+        <v>579</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>423</v>
+        <v>604</v>
       </c>
       <c r="C14">
-        <v>1334</v>
+        <v>1220</v>
       </c>
       <c r="D14">
-        <v>1757</v>
+        <v>1824</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>458</v>
+        <v>603</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1218</v>
       </c>
       <c r="D15">
-        <v>458</v>
+        <v>1821</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>443</v>
+        <v>602</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>443</v>
+        <v>602</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>455</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1333</v>
+        <v>1219</v>
       </c>
       <c r="D17">
-        <v>1788</v>
+        <v>1219</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>480</v>
+        <v>625</v>
       </c>
       <c r="C18">
-        <v>1336</v>
+        <v>1221</v>
       </c>
       <c r="D18">
-        <v>1816</v>
+        <v>1846</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>485</v>
+        <v>618</v>
       </c>
       <c r="C19">
-        <v>1337</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1822</v>
+        <v>618</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>450</v>
+        <v>633</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="D20">
-        <v>450</v>
+        <v>1855</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>476</v>
+        <v>631</v>
       </c>
       <c r="C21">
-        <v>1336</v>
+        <v>1223</v>
       </c>
       <c r="D21">
-        <v>1812</v>
+        <v>1854</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>492</v>
+        <v>662</v>
       </c>
       <c r="C22">
-        <v>1374</v>
+        <v>1236</v>
       </c>
       <c r="D22">
-        <v>1866</v>
+        <v>1898</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>522</v>
+        <v>688</v>
       </c>
       <c r="C23">
-        <v>1373</v>
+        <v>1237</v>
       </c>
       <c r="D23">
-        <v>1895</v>
+        <v>1925</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>523</v>
+        <v>696</v>
       </c>
       <c r="C24">
-        <v>1375</v>
+        <v>1239</v>
       </c>
       <c r="D24">
-        <v>1898</v>
+        <v>1935</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>515</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1374</v>
+        <v>1241</v>
       </c>
       <c r="D25">
-        <v>1889</v>
+        <v>1241</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>548</v>
+        <v>711</v>
       </c>
       <c r="C26">
-        <v>1376</v>
+        <v>1320</v>
       </c>
       <c r="D26">
-        <v>1924</v>
+        <v>2031</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>556</v>
+        <v>708</v>
       </c>
       <c r="C27">
-        <v>1370</v>
+        <v>1321</v>
       </c>
       <c r="D27">
-        <v>1926</v>
+        <v>2029</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>507</v>
+        <v>699</v>
       </c>
       <c r="C28">
-        <v>1367</v>
+        <v>1319</v>
       </c>
       <c r="D28">
-        <v>1874</v>
+        <v>2018</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>493</v>
+        <v>705</v>
       </c>
       <c r="C29">
-        <v>1369</v>
+        <v>1324</v>
       </c>
       <c r="D29">
-        <v>1862</v>
+        <v>2029</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>565</v>
+        <v>704</v>
       </c>
       <c r="C30">
-        <v>1370</v>
+        <v>1328</v>
       </c>
       <c r="D30">
-        <v>1935</v>
+        <v>2032</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>571</v>
+        <v>706</v>
       </c>
       <c r="C31">
-        <v>1365</v>
+        <v>1316</v>
       </c>
       <c r="D31">
-        <v>1936</v>
+        <v>2022</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>550</v>
+        <v>688</v>
       </c>
       <c r="C32">
-        <v>1302</v>
+        <v>1312</v>
       </c>
       <c r="D32">
-        <v>1852</v>
+        <v>2000</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>547</v>
+        <v>694</v>
       </c>
       <c r="C33">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="D33">
-        <v>1852</v>
+        <v>2007</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="C34">
-        <v>1238</v>
+        <v>1291</v>
       </c>
       <c r="D34">
-        <v>1872</v>
+        <v>1936</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="C35">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="D35">
-        <v>1839</v>
+        <v>1933</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="C36">
-        <v>1238</v>
+        <v>1287</v>
       </c>
       <c r="D36">
-        <v>1849</v>
+        <v>1880</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>596</v>
+        <v>558</v>
       </c>
       <c r="C37">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1833</v>
+        <v>558</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>650</v>
+        <v>416</v>
       </c>
       <c r="C38">
-        <v>1150</v>
+        <v>1026</v>
       </c>
       <c r="D38">
-        <v>1800</v>
+        <v>1442</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="C39">
-        <v>1130</v>
+        <v>993</v>
       </c>
       <c r="D39">
-        <v>1130</v>
+        <v>1398</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>613</v>
+        <v>398</v>
       </c>
       <c r="C40">
-        <v>1127</v>
+        <v>999</v>
       </c>
       <c r="D40">
-        <v>1740</v>
+        <v>1397</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>554</v>
+        <v>410</v>
       </c>
       <c r="C41">
-        <v>1126</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1680</v>
+        <v>410</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="C42">
-        <v>1044</v>
+        <v>911</v>
       </c>
       <c r="D42">
-        <v>1399</v>
+        <v>1193</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>345</v>
+        <v>274</v>
       </c>
       <c r="C43">
-        <v>1001</v>
+        <v>900</v>
       </c>
       <c r="D43">
-        <v>1346</v>
+        <v>1174</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>342</v>
+        <v>278</v>
       </c>
       <c r="C44">
-        <v>995</v>
+        <v>903</v>
       </c>
       <c r="D44">
-        <v>1337</v>
+        <v>1181</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>329</v>
+        <v>272</v>
       </c>
       <c r="C45">
-        <v>994</v>
+        <v>899</v>
       </c>
       <c r="D45">
-        <v>1323</v>
+        <v>1171</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="C46">
-        <v>960</v>
+        <v>876</v>
       </c>
       <c r="D46">
-        <v>1146</v>
+        <v>1113</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="C47">
-        <v>941</v>
+        <v>866</v>
       </c>
       <c r="D47">
-        <v>1095</v>
+        <v>1131</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="C49">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="D49">
-        <v>1057</v>
+        <v>1114</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="C50">
-        <v>866</v>
+        <v>825</v>
       </c>
       <c r="D50">
-        <v>1034</v>
+        <v>950</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>175</v>
+        <v>123</v>
       </c>
       <c r="C51">
-        <v>876</v>
+        <v>831</v>
       </c>
       <c r="D51">
-        <v>1051</v>
+        <v>954</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>269</v>
+        <v>142</v>
       </c>
       <c r="C52">
-        <v>1015</v>
+        <v>803</v>
       </c>
       <c r="D52">
-        <v>1284</v>
+        <v>945</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>307</v>
+        <v>132</v>
       </c>
       <c r="C53">
-        <v>977</v>
+        <v>800</v>
       </c>
       <c r="D53">
-        <v>1284</v>
+        <v>932</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>297</v>
+        <v>144</v>
       </c>
       <c r="C54">
-        <v>979</v>
+        <v>818</v>
       </c>
       <c r="D54">
-        <v>1276</v>
+        <v>962</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>290</v>
+        <v>142</v>
       </c>
       <c r="C55">
-        <v>1003</v>
+        <v>812</v>
       </c>
       <c r="D55">
-        <v>1293</v>
+        <v>954</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C56">
-        <v>1002</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>1002</v>
+        <v>119</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="C57">
-        <v>1004</v>
+        <v>745</v>
       </c>
       <c r="D57">
-        <v>1302</v>
+        <v>849</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>380</v>
+        <v>127</v>
       </c>
       <c r="C58">
-        <v>989</v>
+        <v>746</v>
       </c>
       <c r="D58">
-        <v>1369</v>
+        <v>873</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>381</v>
+        <v>143</v>
       </c>
       <c r="C59">
-        <v>985</v>
+        <v>717</v>
       </c>
       <c r="D59">
-        <v>1366</v>
+        <v>860</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>380</v>
+        <v>141</v>
       </c>
       <c r="C60">
-        <v>982</v>
+        <v>771</v>
       </c>
       <c r="D60">
-        <v>1362</v>
+        <v>912</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>366</v>
+        <v>166</v>
       </c>
       <c r="C61">
-        <v>1040</v>
+        <v>778</v>
       </c>
       <c r="D61">
-        <v>1406</v>
+        <v>944</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>406</v>
+        <v>218</v>
       </c>
       <c r="C62">
-        <v>1083</v>
+        <v>977</v>
       </c>
       <c r="D62">
-        <v>1489</v>
+        <v>1195</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>420</v>
+        <v>222</v>
       </c>
       <c r="C63">
-        <v>1090</v>
+        <v>996</v>
       </c>
       <c r="D63">
-        <v>1510</v>
+        <v>1218</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>415</v>
+        <v>238</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="D64">
-        <v>415</v>
+        <v>1290</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>428</v>
+        <v>247</v>
       </c>
       <c r="C65">
-        <v>1091</v>
+        <v>1011</v>
       </c>
       <c r="D65">
-        <v>1519</v>
+        <v>1258</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>502</v>
+        <v>303</v>
       </c>
       <c r="C66">
-        <v>1108</v>
+        <v>1124</v>
       </c>
       <c r="D66">
-        <v>1610</v>
+        <v>1427</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>550</v>
+        <v>335</v>
       </c>
       <c r="C67">
-        <v>1112</v>
+        <v>1144</v>
       </c>
       <c r="D67">
-        <v>1662</v>
+        <v>1479</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1229</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>573</v>
+        <v>369</v>
       </c>
       <c r="C69">
-        <v>1122</v>
+        <v>1278</v>
       </c>
       <c r="D69">
-        <v>1695</v>
+        <v>1647</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>782</v>
+        <v>692</v>
       </c>
       <c r="C70">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="D70">
-        <v>2178</v>
+        <v>2091</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>783</v>
+        <v>715</v>
       </c>
       <c r="C71">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="D71">
-        <v>2203</v>
+        <v>2139</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>791</v>
+        <v>724</v>
       </c>
       <c r="C72">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="D72">
-        <v>2216</v>
+        <v>2145</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>807</v>
+        <v>717</v>
       </c>
       <c r="C73">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="D73">
-        <v>2230</v>
+        <v>2135</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>814</v>
+        <v>874</v>
       </c>
       <c r="C74">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="D74">
-        <v>2258</v>
+        <v>2278</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>821</v>
+        <v>883</v>
       </c>
       <c r="C75">
-        <v>1450</v>
+        <v>1412</v>
       </c>
       <c r="D75">
-        <v>2271</v>
+        <v>2295</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>833</v>
+        <v>903</v>
       </c>
       <c r="C76">
-        <v>1440</v>
+        <v>1415</v>
       </c>
       <c r="D76">
-        <v>2273</v>
+        <v>2318</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>913</v>
       </c>
       <c r="C77">
-        <v>1435</v>
+        <v>1413</v>
       </c>
       <c r="D77">
-        <v>1435</v>
+        <v>2326</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>805</v>
+        <v>848</v>
       </c>
       <c r="C78">
-        <v>1450</v>
+        <v>1416</v>
       </c>
       <c r="D78">
-        <v>2255</v>
+        <v>2264</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>801</v>
+        <v>873</v>
       </c>
       <c r="C79">
-        <v>1455</v>
+        <v>1429</v>
       </c>
       <c r="D79">
-        <v>2256</v>
+        <v>2302</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>798</v>
+        <v>890</v>
       </c>
       <c r="C80">
-        <v>1453</v>
+        <v>1417</v>
       </c>
       <c r="D80">
-        <v>2251</v>
+        <v>2307</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>801</v>
+        <v>896</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1418</v>
       </c>
       <c r="D81">
-        <v>801</v>
+        <v>2314</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>771</v>
+        <v>847</v>
       </c>
       <c r="C82">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="D82">
-        <v>2225</v>
+        <v>2283</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>769</v>
+        <v>867</v>
       </c>
       <c r="C83">
-        <v>1455</v>
+        <v>1440</v>
       </c>
       <c r="D83">
-        <v>2224</v>
+        <v>2307</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>767</v>
+        <v>862</v>
       </c>
       <c r="C84">
-        <v>1454</v>
+        <v>1442</v>
       </c>
       <c r="D84">
-        <v>2221</v>
+        <v>2304</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>769</v>
+        <v>857</v>
       </c>
       <c r="C85">
-        <v>1456</v>
+        <v>1439</v>
       </c>
       <c r="D85">
-        <v>2225</v>
+        <v>2296</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="C86">
-        <v>1416</v>
+        <v>1457</v>
       </c>
       <c r="D86">
-        <v>2169</v>
+        <v>2216</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="C87">
-        <v>1414</v>
+        <v>1454</v>
       </c>
       <c r="D87">
-        <v>2154</v>
+        <v>2201</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="C88">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D88">
-        <v>2149</v>
+        <v>2196</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="C89">
-        <v>1405</v>
+        <v>1453</v>
       </c>
       <c r="D89">
-        <v>2116</v>
+        <v>2196</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>566</v>
+        <v>671</v>
       </c>
       <c r="C90">
-        <v>1414</v>
+        <v>1400</v>
       </c>
       <c r="D90">
-        <v>1980</v>
+        <v>2071</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>578</v>
+        <v>669</v>
       </c>
       <c r="C91">
-        <v>1415</v>
+        <v>1390</v>
       </c>
       <c r="D91">
-        <v>1993</v>
+        <v>2059</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>585</v>
+        <v>668</v>
       </c>
       <c r="C92">
-        <v>1414</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1999</v>
+        <v>668</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>582</v>
+        <v>663</v>
       </c>
       <c r="C93">
-        <v>1413</v>
+        <v>1385</v>
       </c>
       <c r="D93">
-        <v>1995</v>
+        <v>2048</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>490</v>
+        <v>541</v>
       </c>
       <c r="C94">
-        <v>1410</v>
+        <v>1444</v>
       </c>
       <c r="D94">
-        <v>1900</v>
+        <v>1985</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="D95">
-        <v>486</v>
+        <v>1981</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="C96">
-        <v>1411</v>
+        <v>1441</v>
       </c>
       <c r="D96">
-        <v>1898</v>
+        <v>1982</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="C97">
-        <v>1409</v>
+        <v>1439</v>
       </c>
       <c r="D97">
-        <v>1892</v>
+        <v>1970</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
-        <v>452</v>
+        <v>535</v>
       </c>
       <c r="C98">
-        <v>1296</v>
+        <v>1338</v>
       </c>
       <c r="D98">
-        <v>1748</v>
+        <v>1873</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B99">
-        <v>456</v>
+        <v>530</v>
       </c>
       <c r="C99">
-        <v>1292</v>
+        <v>1331</v>
       </c>
       <c r="D99">
-        <v>1748</v>
+        <v>1861</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B100">
-        <v>453</v>
+        <v>527</v>
       </c>
       <c r="C100">
-        <v>1289</v>
+        <v>1332</v>
       </c>
       <c r="D100">
-        <v>1742</v>
+        <v>1859</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B101">
-        <v>464</v>
+        <v>524</v>
       </c>
       <c r="C101">
-        <v>1291</v>
+        <v>1331</v>
       </c>
       <c r="D101">
-        <v>1755</v>
+        <v>1855</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B102">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C102">
-        <v>1227</v>
+        <v>1335</v>
       </c>
       <c r="D102">
-        <v>1823</v>
+        <v>1918</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B103">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C103">
-        <v>1222</v>
+        <v>1332</v>
       </c>
       <c r="D103">
-        <v>1821</v>
+        <v>1918</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B104">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B105">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="C105">
-        <v>1221</v>
+        <v>1333</v>
       </c>
       <c r="D105">
-        <v>1786</v>
+        <v>1919</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B106">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C106">
-        <v>1220</v>
+        <v>1309</v>
       </c>
       <c r="D106">
-        <v>1819</v>
+        <v>1896</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B107">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="C107">
-        <v>1216</v>
+        <v>1303</v>
       </c>
       <c r="D107">
-        <v>1761</v>
+        <v>1887</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B108">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="C108">
-        <v>1217</v>
+        <v>1321</v>
       </c>
       <c r="D108">
-        <v>1782</v>
+        <v>1906</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B109">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1323</v>
       </c>
       <c r="D109">
-        <v>579</v>
+        <v>1900</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B110">
-        <v>604</v>
+        <v>576</v>
       </c>
       <c r="C110">
-        <v>1220</v>
+        <v>1326</v>
       </c>
       <c r="D110">
-        <v>1824</v>
+        <v>1902</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B111">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="C111">
-        <v>1218</v>
+        <v>1321</v>
       </c>
       <c r="D111">
-        <v>1821</v>
+        <v>1895</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B112">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1315</v>
       </c>
       <c r="D112">
-        <v>602</v>
+        <v>1894</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="C113">
-        <v>1219</v>
+        <v>1316</v>
       </c>
       <c r="D113">
-        <v>1219</v>
+        <v>1897</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B114">
-        <v>625</v>
+        <v>598</v>
       </c>
       <c r="C114">
-        <v>1221</v>
+        <v>1320</v>
       </c>
       <c r="D114">
-        <v>1846</v>
+        <v>1918</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B115">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1327</v>
       </c>
       <c r="D115">
-        <v>618</v>
+        <v>1932</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B116">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C116">
-        <v>1222</v>
+        <v>1330</v>
       </c>
       <c r="D116">
-        <v>1855</v>
+        <v>1964</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B117">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C117">
-        <v>1223</v>
+        <v>1329</v>
       </c>
       <c r="D117">
-        <v>1854</v>
+        <v>1968</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B118">
-        <v>662</v>
+        <v>696</v>
       </c>
       <c r="C118">
-        <v>1236</v>
+        <v>1369</v>
       </c>
       <c r="D118">
-        <v>1898</v>
+        <v>2065</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B119">
-        <v>688</v>
+        <v>1002</v>
       </c>
       <c r="C119">
-        <v>1237</v>
+        <v>1371</v>
       </c>
       <c r="D119">
-        <v>1925</v>
+        <v>2373</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B120">
-        <v>696</v>
+        <v>912</v>
       </c>
       <c r="C120">
-        <v>1239</v>
+        <v>1362</v>
       </c>
       <c r="D120">
-        <v>1935</v>
+        <v>2274</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="C121">
-        <v>1241</v>
+        <v>1360</v>
       </c>
       <c r="D121">
-        <v>1241</v>
+        <v>2265</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B122">
-        <v>711</v>
+        <v>893</v>
       </c>
       <c r="C122">
-        <v>1320</v>
+        <v>1406</v>
       </c>
       <c r="D122">
-        <v>2031</v>
+        <v>2299</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B123">
-        <v>708</v>
+        <v>869</v>
       </c>
       <c r="C123">
-        <v>1321</v>
+        <v>1415</v>
       </c>
       <c r="D123">
-        <v>2029</v>
+        <v>2284</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B124">
-        <v>699</v>
+        <v>770</v>
       </c>
       <c r="C124">
-        <v>1319</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>2018</v>
+        <v>770</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B125">
-        <v>705</v>
+        <v>673</v>
       </c>
       <c r="C125">
-        <v>1324</v>
+        <v>1388</v>
       </c>
       <c r="D125">
-        <v>2029</v>
+        <v>2061</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B126">
-        <v>704</v>
+        <v>425</v>
       </c>
       <c r="C126">
-        <v>1328</v>
+        <v>1373</v>
       </c>
       <c r="D126">
-        <v>2032</v>
+        <v>1798</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B127">
-        <v>706</v>
+        <v>511</v>
       </c>
       <c r="C127">
-        <v>1316</v>
+        <v>1411</v>
       </c>
       <c r="D127">
-        <v>2022</v>
+        <v>1922</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B128">
-        <v>688</v>
+        <v>722</v>
       </c>
       <c r="C128">
-        <v>1312</v>
+        <v>1416</v>
       </c>
       <c r="D128">
-        <v>2000</v>
+        <v>2138</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B129">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="C129">
-        <v>1313</v>
+        <v>1418</v>
       </c>
       <c r="D129">
-        <v>2007</v>
+        <v>2096</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B130">
-        <v>645</v>
+        <v>538</v>
       </c>
       <c r="C130">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="D130">
-        <v>1936</v>
+        <v>1835</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B131">
-        <v>640</v>
+        <v>476</v>
       </c>
       <c r="C131">
-        <v>1293</v>
+        <v>1282</v>
       </c>
       <c r="D131">
-        <v>1933</v>
+        <v>1758</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B132">
-        <v>593</v>
+        <v>471</v>
       </c>
       <c r="C132">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="D132">
-        <v>1880</v>
+        <v>1754</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B133">
-        <v>558</v>
+        <v>277</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1258</v>
       </c>
       <c r="D133">
-        <v>558</v>
+        <v>1535</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B134">
-        <v>416</v>
+        <v>148</v>
       </c>
       <c r="C134">
-        <v>1026</v>
+        <v>1110</v>
       </c>
       <c r="D134">
-        <v>1442</v>
+        <v>1258</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B135">
-        <v>405</v>
+        <v>129</v>
       </c>
       <c r="C135">
-        <v>993</v>
+        <v>1092</v>
       </c>
       <c r="D135">
-        <v>1398</v>
+        <v>1221</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B136">
-        <v>398</v>
+        <v>128</v>
       </c>
       <c r="C136">
-        <v>999</v>
+        <v>1041</v>
       </c>
       <c r="D136">
-        <v>1397</v>
+        <v>1169</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B137">
-        <v>410</v>
+        <v>127</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="D137">
-        <v>410</v>
+        <v>1167</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B138">
-        <v>282</v>
+        <v>113</v>
       </c>
       <c r="C138">
-        <v>911</v>
+        <v>853</v>
       </c>
       <c r="D138">
-        <v>1193</v>
+        <v>966</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B139">
-        <v>274</v>
+        <v>112</v>
       </c>
       <c r="C139">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="D139">
-        <v>1174</v>
+        <v>952</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B140">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>903</v>
+        <v>839</v>
       </c>
       <c r="D140">
-        <v>1181</v>
+        <v>839</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B141">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>899</v>
+        <v>790</v>
       </c>
       <c r="D141">
-        <v>1171</v>
+        <v>790</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B142">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="C142">
-        <v>876</v>
+        <v>693</v>
       </c>
       <c r="D142">
-        <v>1113</v>
+        <v>806</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +4390,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B143">
-        <v>265</v>
+        <v>110</v>
       </c>
       <c r="C143">
-        <v>866</v>
+        <v>681</v>
       </c>
       <c r="D143">
-        <v>1131</v>
+        <v>791</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B145">
-        <v>250</v>
+        <v>88</v>
       </c>
       <c r="C145">
-        <v>864</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>1114</v>
+        <v>88</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="C146">
         <v>0</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>794</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4610,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4630,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>844</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,16 +4650,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4094,16 +4670,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1138</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>1143</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1365</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1709</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1748</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,16 +4890,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1752</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4334,16 +4910,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1395</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>2205</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2244</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>764</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1485</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>2249</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1471</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>2268</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1475</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>2281</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1476</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>2278</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1480</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>2285</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>2261</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>770</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1511</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>2281</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>1505</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>2281</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>2229</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1551</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>2243</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1550</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>2236</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>1528</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>2203</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1543</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1539</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>2123</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1541</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>2122</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1527</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>2107</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1502</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>1962</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1493</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>1951</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1495</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1957</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,22 +5390,3862 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1492</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B194">
+        <v>474</v>
+      </c>
+      <c r="C194">
+        <v>1368</v>
+      </c>
+      <c r="D194">
+        <v>1842</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>540</v>
+      </c>
+      <c r="C195">
+        <v>1344</v>
+      </c>
+      <c r="D195">
+        <v>1884</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>1342</v>
+      </c>
+      <c r="D196">
+        <v>1342</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B197">
+        <v>538</v>
+      </c>
+      <c r="C197">
+        <v>1341</v>
+      </c>
+      <c r="D197">
+        <v>1879</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>550</v>
+      </c>
+      <c r="C198">
+        <v>1362</v>
+      </c>
+      <c r="D198">
+        <v>1912</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>1331</v>
+      </c>
+      <c r="D199">
+        <v>1331</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B200">
+        <v>542</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>542</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>543</v>
+      </c>
+      <c r="C201">
+        <v>1329</v>
+      </c>
+      <c r="D201">
+        <v>1872</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>555</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>555</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B203">
+        <v>553</v>
+      </c>
+      <c r="C203">
+        <v>1326</v>
+      </c>
+      <c r="D203">
+        <v>1879</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>552</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>552</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>551</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>551</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B206">
+        <v>550</v>
+      </c>
+      <c r="C206">
+        <v>1325</v>
+      </c>
+      <c r="D206">
+        <v>1875</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>551</v>
+      </c>
+      <c r="C207">
+        <v>1338</v>
+      </c>
+      <c r="D207">
+        <v>1889</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>552</v>
+      </c>
+      <c r="C208">
+        <v>1340</v>
+      </c>
+      <c r="D208">
+        <v>1892</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B209">
+        <v>554</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>554</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>587</v>
+      </c>
+      <c r="C210">
+        <v>1334</v>
+      </c>
+      <c r="D210">
+        <v>1921</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>578</v>
+      </c>
+      <c r="C211">
+        <v>1333</v>
+      </c>
+      <c r="D211">
+        <v>1911</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B212">
+        <v>590</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>590</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>583</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>583</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>602</v>
+      </c>
+      <c r="C214">
+        <v>1350</v>
+      </c>
+      <c r="D214">
+        <v>1952</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B215">
+        <v>611</v>
+      </c>
+      <c r="C215">
+        <v>1347</v>
+      </c>
+      <c r="D215">
+        <v>1958</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>614</v>
+      </c>
+      <c r="C216">
+        <v>1358</v>
+      </c>
+      <c r="D216">
+        <v>1972</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>613</v>
+      </c>
+      <c r="C217">
+        <v>1359</v>
+      </c>
+      <c r="D217">
+        <v>1972</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B218">
+        <v>624</v>
+      </c>
+      <c r="C218">
+        <v>1384</v>
+      </c>
+      <c r="D218">
+        <v>2008</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>612</v>
+      </c>
+      <c r="C219">
+        <v>1386</v>
+      </c>
+      <c r="D219">
+        <v>1998</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>574</v>
+      </c>
+      <c r="C220">
+        <v>1385</v>
+      </c>
+      <c r="D220">
+        <v>1959</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B221">
+        <v>536</v>
+      </c>
+      <c r="C221">
+        <v>1386</v>
+      </c>
+      <c r="D221">
+        <v>1922</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>319</v>
+      </c>
+      <c r="C222">
+        <v>1227</v>
+      </c>
+      <c r="D222">
+        <v>1546</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>244</v>
+      </c>
+      <c r="C223">
+        <v>1218</v>
+      </c>
+      <c r="D223">
+        <v>1462</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B224">
+        <v>243</v>
+      </c>
+      <c r="C224">
+        <v>1221</v>
+      </c>
+      <c r="D224">
+        <v>1464</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>242</v>
+      </c>
+      <c r="C225">
+        <v>1217</v>
+      </c>
+      <c r="D225">
+        <v>1459</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>146</v>
+      </c>
+      <c r="C226">
+        <v>1027</v>
+      </c>
+      <c r="D226">
+        <v>1173</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B227">
+        <v>153</v>
+      </c>
+      <c r="C227">
+        <v>1018</v>
+      </c>
+      <c r="D227">
+        <v>1171</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>141</v>
+      </c>
+      <c r="C228">
+        <v>1013</v>
+      </c>
+      <c r="D228">
+        <v>1154</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>140</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>140</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B230">
+        <v>138</v>
+      </c>
+      <c r="C230">
+        <v>954</v>
+      </c>
+      <c r="D230">
+        <v>1092</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>131</v>
+      </c>
+      <c r="C231">
+        <v>950</v>
+      </c>
+      <c r="D231">
+        <v>1081</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>133</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>133</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B233">
+        <v>135</v>
+      </c>
+      <c r="C233">
+        <v>952</v>
+      </c>
+      <c r="D233">
+        <v>1087</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>145</v>
+      </c>
+      <c r="C234">
+        <v>848</v>
+      </c>
+      <c r="D234">
+        <v>993</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>131</v>
+      </c>
+      <c r="C235">
+        <v>839</v>
+      </c>
+      <c r="D235">
+        <v>970</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>832</v>
+      </c>
+      <c r="D236">
+        <v>832</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>116</v>
+      </c>
+      <c r="C238">
+        <v>837</v>
+      </c>
+      <c r="D238">
+        <v>953</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B239">
+        <v>143</v>
+      </c>
+      <c r="C239">
+        <v>816</v>
+      </c>
+      <c r="D239">
+        <v>959</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>114</v>
+      </c>
+      <c r="C240">
+        <v>806</v>
+      </c>
+      <c r="D240">
+        <v>920</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>115</v>
+      </c>
+      <c r="C241">
+        <v>800</v>
+      </c>
+      <c r="D241">
+        <v>915</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B242">
+        <v>98</v>
+      </c>
+      <c r="C242">
+        <v>807</v>
+      </c>
+      <c r="D242">
+        <v>905</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>88</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>88</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B245">
+        <v>104</v>
+      </c>
+      <c r="C245">
+        <v>806</v>
+      </c>
+      <c r="D245">
+        <v>910</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>121</v>
+      </c>
+      <c r="C246">
+        <v>811</v>
+      </c>
+      <c r="D246">
+        <v>932</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>107</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>107</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B248">
+        <v>121</v>
+      </c>
+      <c r="C248">
+        <v>818</v>
+      </c>
+      <c r="D248">
+        <v>939</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>110</v>
+      </c>
+      <c r="C249">
+        <v>816</v>
+      </c>
+      <c r="D249">
+        <v>926</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>165</v>
+      </c>
+      <c r="C250">
+        <v>801</v>
+      </c>
+      <c r="D250">
+        <v>966</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B251">
+        <v>151</v>
+      </c>
+      <c r="C251">
+        <v>799</v>
+      </c>
+      <c r="D251">
+        <v>950</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>128</v>
+      </c>
+      <c r="C252">
+        <v>809</v>
+      </c>
+      <c r="D252">
+        <v>937</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>126</v>
+      </c>
+      <c r="C253">
+        <v>813</v>
+      </c>
+      <c r="D253">
+        <v>939</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B254">
+        <v>128</v>
+      </c>
+      <c r="C254">
+        <v>923</v>
+      </c>
+      <c r="D254">
+        <v>1051</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>126</v>
+      </c>
+      <c r="C255">
+        <v>926</v>
+      </c>
+      <c r="D255">
+        <v>1052</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>122</v>
+      </c>
+      <c r="C256">
+        <v>925</v>
+      </c>
+      <c r="D256">
+        <v>1047</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B257">
+        <v>137</v>
+      </c>
+      <c r="C257">
+        <v>933</v>
+      </c>
+      <c r="D257">
+        <v>1070</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>227</v>
+      </c>
+      <c r="C258">
+        <v>1193</v>
+      </c>
+      <c r="D258">
+        <v>1420</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>234</v>
+      </c>
+      <c r="C259">
+        <v>1212</v>
+      </c>
+      <c r="D259">
+        <v>1446</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B260">
+        <v>235</v>
+      </c>
+      <c r="C260">
+        <v>1213</v>
+      </c>
+      <c r="D260">
+        <v>1448</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>253</v>
+      </c>
+      <c r="C261">
+        <v>1221</v>
+      </c>
+      <c r="D261">
+        <v>1474</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>361</v>
+      </c>
+      <c r="C262">
+        <v>1359</v>
+      </c>
+      <c r="D262">
+        <v>1720</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B263">
+        <v>367</v>
+      </c>
+      <c r="C263">
+        <v>1390</v>
+      </c>
+      <c r="D263">
+        <v>1757</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>366</v>
+      </c>
+      <c r="C264">
+        <v>1392</v>
+      </c>
+      <c r="D264">
+        <v>1758</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>380</v>
+      </c>
+      <c r="C265">
+        <v>1393</v>
+      </c>
+      <c r="D265">
+        <v>1773</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B266">
+        <v>597</v>
+      </c>
+      <c r="C266">
+        <v>1593</v>
+      </c>
+      <c r="D266">
+        <v>2190</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>670</v>
+      </c>
+      <c r="C267">
+        <v>1605</v>
+      </c>
+      <c r="D267">
+        <v>2275</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>1606</v>
+      </c>
+      <c r="D268">
+        <v>1606</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B269">
+        <v>676</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>676</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>697</v>
+      </c>
+      <c r="C270">
+        <v>1607</v>
+      </c>
+      <c r="D270">
+        <v>2304</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>701</v>
+      </c>
+      <c r="C271">
+        <v>1614</v>
+      </c>
+      <c r="D271">
+        <v>2315</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B272">
+        <v>704</v>
+      </c>
+      <c r="C272">
+        <v>1618</v>
+      </c>
+      <c r="D272">
+        <v>2322</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>1616</v>
+      </c>
+      <c r="D273">
+        <v>1616</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>688</v>
+      </c>
+      <c r="C274">
+        <v>1609</v>
+      </c>
+      <c r="D274">
+        <v>2297</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B275">
+        <v>682</v>
+      </c>
+      <c r="C275">
+        <v>1606</v>
+      </c>
+      <c r="D275">
+        <v>2288</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>1575</v>
+      </c>
+      <c r="D276">
+        <v>1575</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>690</v>
+      </c>
+      <c r="C277">
+        <v>1572</v>
+      </c>
+      <c r="D277">
+        <v>2262</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B278">
+        <v>584</v>
+      </c>
+      <c r="C278">
+        <v>1601</v>
+      </c>
+      <c r="D278">
+        <v>2185</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>578</v>
+      </c>
+      <c r="C279">
+        <v>1614</v>
+      </c>
+      <c r="D279">
+        <v>2192</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>572</v>
+      </c>
+      <c r="C280">
+        <v>1615</v>
+      </c>
+      <c r="D280">
+        <v>2187</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B281">
+        <v>568</v>
+      </c>
+      <c r="C281">
+        <v>1609</v>
+      </c>
+      <c r="D281">
+        <v>2177</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>495</v>
+      </c>
+      <c r="C282">
+        <v>1557</v>
+      </c>
+      <c r="D282">
+        <v>2052</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>488</v>
+      </c>
+      <c r="C283">
+        <v>1545</v>
+      </c>
+      <c r="D283">
+        <v>2033</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B284">
+        <v>484</v>
+      </c>
+      <c r="C284">
+        <v>1544</v>
+      </c>
+      <c r="D284">
+        <v>2028</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>481</v>
+      </c>
+      <c r="C285">
+        <v>1540</v>
+      </c>
+      <c r="D285">
+        <v>2021</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>555</v>
+      </c>
+      <c r="C286">
+        <v>1372</v>
+      </c>
+      <c r="D286">
+        <v>1927</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B287">
+        <v>550</v>
+      </c>
+      <c r="C287">
+        <v>1321</v>
+      </c>
+      <c r="D287">
+        <v>1871</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>564</v>
+      </c>
+      <c r="C288">
+        <v>1322</v>
+      </c>
+      <c r="D288">
+        <v>1886</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>551</v>
+      </c>
+      <c r="C289">
+        <v>1311</v>
+      </c>
+      <c r="D289">
+        <v>1862</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B290">
+        <v>532</v>
+      </c>
+      <c r="C290">
+        <v>1298</v>
+      </c>
+      <c r="D290">
+        <v>1830</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>467</v>
+      </c>
+      <c r="C291">
+        <v>1290</v>
+      </c>
+      <c r="D291">
+        <v>1757</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>481</v>
+      </c>
+      <c r="C292">
+        <v>1322</v>
+      </c>
+      <c r="D292">
+        <v>1803</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B293">
+        <v>478</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>478</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>450</v>
+      </c>
+      <c r="C294">
+        <v>1230</v>
+      </c>
+      <c r="D294">
+        <v>1680</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>1226</v>
+      </c>
+      <c r="D295">
+        <v>1226</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B296">
+        <v>478</v>
+      </c>
+      <c r="C296">
+        <v>1218</v>
+      </c>
+      <c r="D296">
+        <v>1696</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>398</v>
+      </c>
+      <c r="C297">
+        <v>1156</v>
+      </c>
+      <c r="D297">
+        <v>1554</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>362</v>
+      </c>
+      <c r="C298">
+        <v>1045</v>
+      </c>
+      <c r="D298">
+        <v>1407</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B299">
+        <v>378</v>
+      </c>
+      <c r="C299">
+        <v>1038</v>
+      </c>
+      <c r="D299">
+        <v>1416</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>384</v>
+      </c>
+      <c r="C300">
+        <v>1037</v>
+      </c>
+      <c r="D300">
+        <v>1421</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>400</v>
+      </c>
+      <c r="C301">
+        <v>1054</v>
+      </c>
+      <c r="D301">
+        <v>1454</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B302">
+        <v>420</v>
+      </c>
+      <c r="C302">
+        <v>1091</v>
+      </c>
+      <c r="D302">
+        <v>1511</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>417</v>
+      </c>
+      <c r="C303">
+        <v>1094</v>
+      </c>
+      <c r="D303">
+        <v>1511</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>463</v>
+      </c>
+      <c r="C304">
+        <v>1079</v>
+      </c>
+      <c r="D304">
+        <v>1542</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B305">
+        <v>464</v>
+      </c>
+      <c r="C305">
+        <v>1075</v>
+      </c>
+      <c r="D305">
+        <v>1539</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>488</v>
+      </c>
+      <c r="C306">
+        <v>1214</v>
+      </c>
+      <c r="D306">
+        <v>1702</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>498</v>
+      </c>
+      <c r="C307">
+        <v>1225</v>
+      </c>
+      <c r="D307">
+        <v>1723</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>526</v>
+      </c>
+      <c r="C309">
+        <v>1227</v>
+      </c>
+      <c r="D309">
+        <v>1753</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>715</v>
+      </c>
+      <c r="C310">
+        <v>1176</v>
+      </c>
+      <c r="D310">
+        <v>1891</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B311">
+        <v>784</v>
+      </c>
+      <c r="C311">
+        <v>1177</v>
+      </c>
+      <c r="D311">
+        <v>1961</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>782</v>
+      </c>
+      <c r="C312">
+        <v>1197</v>
+      </c>
+      <c r="D312">
+        <v>1979</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>795</v>
+      </c>
+      <c r="C313">
+        <v>1198</v>
+      </c>
+      <c r="D313">
+        <v>1993</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B314">
+        <v>805</v>
+      </c>
+      <c r="C314">
+        <v>1218</v>
+      </c>
+      <c r="D314">
+        <v>2023</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>795</v>
+      </c>
+      <c r="C315">
+        <v>1217</v>
+      </c>
+      <c r="D315">
+        <v>2012</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>789</v>
+      </c>
+      <c r="C316">
+        <v>1221</v>
+      </c>
+      <c r="D316">
+        <v>2010</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B317">
+        <v>780</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>780</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>768</v>
+      </c>
+      <c r="C318">
+        <v>1166</v>
+      </c>
+      <c r="D318">
+        <v>1934</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>802</v>
+      </c>
+      <c r="C319">
+        <v>1193</v>
+      </c>
+      <c r="D319">
+        <v>1995</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B320">
+        <v>815</v>
+      </c>
+      <c r="C320">
+        <v>1203</v>
+      </c>
+      <c r="D320">
+        <v>2018</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>20.04.202694</t>
-  </si>
-  <si>
-    <t>20.04.202695</t>
-  </si>
-  <si>
-    <t>20.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>21.04.202696</t>
+  </si>
+  <si>
+    <t>22.04.20261</t>
+  </si>
+  <si>
+    <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
+    <t>22.04.202695</t>
+  </si>
+  <si>
+    <t>22.04.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C2">
-        <v>1298</v>
+        <v>1363</v>
       </c>
       <c r="D2">
-        <v>1830</v>
+        <v>1910</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
-        <v>467</v>
+        <v>552</v>
       </c>
       <c r="C3">
-        <v>1290</v>
+        <v>1332</v>
       </c>
       <c r="D3">
-        <v>1757</v>
+        <v>1884</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="C4">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="D4">
-        <v>1803</v>
+        <v>1837</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="D5">
-        <v>478</v>
+        <v>1757</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C6">
-        <v>1230</v>
+        <v>1262</v>
       </c>
       <c r="D6">
-        <v>1680</v>
+        <v>1742</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="C7">
-        <v>1226</v>
+        <v>1260</v>
       </c>
       <c r="D7">
-        <v>1226</v>
+        <v>1775</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="C8">
-        <v>1218</v>
+        <v>1259</v>
       </c>
       <c r="D8">
-        <v>1696</v>
+        <v>1719</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
         <v>398</v>
       </c>
       <c r="C9">
-        <v>1156</v>
+        <v>1213</v>
       </c>
       <c r="D9">
-        <v>1554</v>
+        <v>1611</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>362</v>
+        <v>400</v>
       </c>
       <c r="C10">
-        <v>1045</v>
+        <v>1182</v>
       </c>
       <c r="D10">
-        <v>1407</v>
+        <v>1582</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="C11">
-        <v>1038</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1416</v>
+        <v>415</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="C12">
-        <v>1037</v>
+        <v>1180</v>
       </c>
       <c r="D12">
-        <v>1421</v>
+        <v>1599</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="C13">
-        <v>1054</v>
+        <v>1183</v>
       </c>
       <c r="D13">
-        <v>1454</v>
+        <v>1617</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="C14">
-        <v>1091</v>
+        <v>1174</v>
       </c>
       <c r="D14">
-        <v>1511</v>
+        <v>1499</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="C15">
-        <v>1094</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1511</v>
+        <v>329</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>463</v>
+        <v>336</v>
       </c>
       <c r="C16">
-        <v>1079</v>
+        <v>1173</v>
       </c>
       <c r="D16">
-        <v>1542</v>
+        <v>1509</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>464</v>
+        <v>312</v>
       </c>
       <c r="C17">
-        <v>1075</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1539</v>
+        <v>312</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>488</v>
+        <v>350</v>
       </c>
       <c r="C18">
-        <v>1214</v>
+        <v>1183</v>
       </c>
       <c r="D18">
-        <v>1702</v>
+        <v>1533</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>498</v>
+        <v>371</v>
       </c>
       <c r="C19">
-        <v>1225</v>
+        <v>1182</v>
       </c>
       <c r="D19">
-        <v>1723</v>
+        <v>1553</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1183</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1542</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>526</v>
+        <v>417</v>
       </c>
       <c r="C21">
-        <v>1227</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1753</v>
+        <v>417</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>715</v>
+        <v>655</v>
       </c>
       <c r="C22">
-        <v>1176</v>
+        <v>1121</v>
       </c>
       <c r="D22">
-        <v>1891</v>
+        <v>1776</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>784</v>
+        <v>750</v>
       </c>
       <c r="C23">
-        <v>1177</v>
+        <v>1141</v>
       </c>
       <c r="D23">
-        <v>1961</v>
+        <v>1891</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="C24">
-        <v>1197</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1979</v>
+        <v>741</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>795</v>
+        <v>740</v>
       </c>
       <c r="C25">
-        <v>1198</v>
+        <v>1137</v>
       </c>
       <c r="D25">
-        <v>1993</v>
+        <v>1877</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>805</v>
+        <v>748</v>
       </c>
       <c r="C26">
-        <v>1218</v>
+        <v>1190</v>
       </c>
       <c r="D26">
-        <v>2023</v>
+        <v>1938</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="C27">
-        <v>1217</v>
+        <v>1185</v>
       </c>
       <c r="D27">
-        <v>2012</v>
+        <v>1973</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>789</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>2010</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>780</v>
+        <v>801</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="D29">
-        <v>780</v>
+        <v>1988</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>768</v>
+        <v>792</v>
       </c>
       <c r="C30">
-        <v>1166</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1934</v>
+        <v>792</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="C31">
-        <v>1193</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1995</v>
+        <v>793</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="C32">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="D32">
-        <v>2018</v>
+        <v>1993</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1146</v>
+        <v>1210</v>
       </c>
       <c r="D33">
-        <v>1913</v>
+        <v>1210</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="C34">
-        <v>1049</v>
+        <v>1173</v>
       </c>
       <c r="D34">
-        <v>1659</v>
+        <v>1883</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="C35">
-        <v>1029</v>
+        <v>1167</v>
       </c>
       <c r="D35">
-        <v>1631</v>
+        <v>1804</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="C36">
-        <v>1017</v>
+        <v>1185</v>
       </c>
       <c r="D36">
-        <v>1620</v>
+        <v>1801</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>584</v>
+        <v>622</v>
       </c>
       <c r="C37">
-        <v>1010</v>
+        <v>1189</v>
       </c>
       <c r="D37">
-        <v>1594</v>
+        <v>1811</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>450</v>
+        <v>591</v>
       </c>
       <c r="C38">
-        <v>871</v>
+        <v>1135</v>
       </c>
       <c r="D38">
-        <v>1321</v>
+        <v>1726</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>443</v>
+        <v>593</v>
       </c>
       <c r="C39">
-        <v>865</v>
+        <v>1127</v>
       </c>
       <c r="D39">
-        <v>1308</v>
+        <v>1720</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>864</v>
+        <v>1137</v>
       </c>
       <c r="D40">
-        <v>1309</v>
+        <v>1137</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>442</v>
+        <v>610</v>
       </c>
       <c r="C41">
-        <v>866</v>
+        <v>1130</v>
       </c>
       <c r="D41">
-        <v>1308</v>
+        <v>1740</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>293</v>
+        <v>559</v>
       </c>
       <c r="C42">
-        <v>816</v>
+        <v>1006</v>
       </c>
       <c r="D42">
-        <v>1109</v>
+        <v>1565</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>213</v>
+        <v>632</v>
       </c>
       <c r="C43">
-        <v>812</v>
+        <v>1012</v>
       </c>
       <c r="D43">
-        <v>1025</v>
+        <v>1644</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="C44">
-        <v>800</v>
+        <v>1015</v>
       </c>
       <c r="D44">
-        <v>800</v>
+        <v>1651</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="C45">
-        <v>794</v>
+        <v>1017</v>
       </c>
       <c r="D45">
-        <v>794</v>
+        <v>1647</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>155</v>
+        <v>669</v>
       </c>
       <c r="C46">
-        <v>783</v>
+        <v>984</v>
       </c>
       <c r="D46">
-        <v>938</v>
+        <v>1653</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>137</v>
+        <v>677</v>
       </c>
       <c r="C47">
-        <v>734</v>
+        <v>988</v>
       </c>
       <c r="D47">
-        <v>871</v>
+        <v>1665</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>140</v>
+        <v>678</v>
       </c>
       <c r="C48">
-        <v>731</v>
+        <v>977</v>
       </c>
       <c r="D48">
-        <v>871</v>
+        <v>1655</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>135</v>
+        <v>661</v>
       </c>
       <c r="C49">
-        <v>732</v>
+        <v>986</v>
       </c>
       <c r="D49">
-        <v>867</v>
+        <v>1647</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>129</v>
+        <v>608</v>
       </c>
       <c r="C50">
-        <v>701</v>
+        <v>990</v>
       </c>
       <c r="D50">
-        <v>830</v>
+        <v>1598</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>131</v>
+        <v>672</v>
       </c>
       <c r="C51">
-        <v>700</v>
+        <v>981</v>
       </c>
       <c r="D51">
-        <v>831</v>
+        <v>1653</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>151</v>
+        <v>530</v>
       </c>
       <c r="C52">
-        <v>705</v>
+        <v>968</v>
       </c>
       <c r="D52">
-        <v>856</v>
+        <v>1498</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>156</v>
+        <v>549</v>
       </c>
       <c r="C53">
-        <v>699</v>
+        <v>966</v>
       </c>
       <c r="D53">
-        <v>855</v>
+        <v>1515</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>140</v>
+        <v>587</v>
       </c>
       <c r="C54">
-        <v>649</v>
+        <v>950</v>
       </c>
       <c r="D54">
-        <v>789</v>
+        <v>1537</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>142</v>
+        <v>557</v>
       </c>
       <c r="C55">
-        <v>629</v>
+        <v>947</v>
       </c>
       <c r="D55">
-        <v>771</v>
+        <v>1504</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>151</v>
+        <v>600</v>
       </c>
       <c r="C56">
-        <v>630</v>
+        <v>965</v>
       </c>
       <c r="D56">
-        <v>781</v>
+        <v>1565</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>149</v>
+        <v>613</v>
       </c>
       <c r="C57">
-        <v>632</v>
+        <v>966</v>
       </c>
       <c r="D57">
-        <v>781</v>
+        <v>1579</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>186</v>
+        <v>614</v>
       </c>
       <c r="C58">
-        <v>622</v>
+        <v>949</v>
       </c>
       <c r="D58">
-        <v>808</v>
+        <v>1563</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>185</v>
+        <v>574</v>
       </c>
       <c r="C59">
-        <v>621</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>806</v>
+        <v>574</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>623</v>
+        <v>947</v>
       </c>
       <c r="D60">
-        <v>771</v>
+        <v>947</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>143</v>
+        <v>577</v>
       </c>
       <c r="C61">
-        <v>624</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>767</v>
+        <v>577</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>163</v>
+        <v>606</v>
       </c>
       <c r="C62">
-        <v>615</v>
+        <v>964</v>
       </c>
       <c r="D62">
-        <v>778</v>
+        <v>1570</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>185</v>
+        <v>611</v>
       </c>
       <c r="C63">
-        <v>612</v>
+        <v>966</v>
       </c>
       <c r="D63">
-        <v>797</v>
+        <v>1577</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>186</v>
+        <v>609</v>
       </c>
       <c r="C64">
-        <v>614</v>
+        <v>956</v>
       </c>
       <c r="D64">
-        <v>800</v>
+        <v>1565</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>202</v>
+        <v>633</v>
       </c>
       <c r="C65">
-        <v>620</v>
+        <v>960</v>
       </c>
       <c r="D65">
-        <v>822</v>
+        <v>1593</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>378</v>
+        <v>749</v>
       </c>
       <c r="C66">
-        <v>837</v>
+        <v>1110</v>
       </c>
       <c r="D66">
-        <v>1215</v>
+        <v>1859</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>437</v>
+        <v>750</v>
       </c>
       <c r="C67">
-        <v>848</v>
+        <v>1116</v>
       </c>
       <c r="D67">
-        <v>1285</v>
+        <v>1866</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>446</v>
+        <v>759</v>
       </c>
       <c r="C68">
-        <v>867</v>
+        <v>1115</v>
       </c>
       <c r="D68">
-        <v>1313</v>
+        <v>1874</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>607</v>
+        <v>796</v>
       </c>
       <c r="C69">
-        <v>957</v>
+        <v>1122</v>
       </c>
       <c r="D69">
-        <v>1564</v>
+        <v>1918</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>868</v>
+        <v>958</v>
       </c>
       <c r="C70">
-        <v>1417</v>
+        <v>1139</v>
       </c>
       <c r="D70">
-        <v>2285</v>
+        <v>2097</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>862</v>
+        <v>1033</v>
       </c>
       <c r="C71">
-        <v>1434</v>
+        <v>1143</v>
       </c>
       <c r="D71">
-        <v>2296</v>
+        <v>2176</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>852</v>
+        <v>1031</v>
       </c>
       <c r="C72">
-        <v>1441</v>
+        <v>1145</v>
       </c>
       <c r="D72">
-        <v>2293</v>
+        <v>2176</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>846</v>
+        <v>1045</v>
       </c>
       <c r="C73">
-        <v>1456</v>
+        <v>1143</v>
       </c>
       <c r="D73">
-        <v>2302</v>
+        <v>2188</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>718</v>
+        <v>1175</v>
       </c>
       <c r="C74">
-        <v>1603</v>
+        <v>1188</v>
       </c>
       <c r="D74">
-        <v>2321</v>
+        <v>2363</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>707</v>
+        <v>1206</v>
       </c>
       <c r="C75">
-        <v>1627</v>
+        <v>1198</v>
       </c>
       <c r="D75">
-        <v>2334</v>
+        <v>2404</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>660</v>
+        <v>1189</v>
       </c>
       <c r="C76">
-        <v>1538</v>
+        <v>1186</v>
       </c>
       <c r="D76">
-        <v>2198</v>
+        <v>2375</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>666</v>
+        <v>1221</v>
       </c>
       <c r="C77">
-        <v>1530</v>
+        <v>1183</v>
       </c>
       <c r="D77">
-        <v>2196</v>
+        <v>2404</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>698</v>
+        <v>1173</v>
       </c>
       <c r="C78">
-        <v>1557</v>
+        <v>1185</v>
       </c>
       <c r="D78">
-        <v>2255</v>
+        <v>2358</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>566</v>
+        <v>1205</v>
       </c>
       <c r="C79">
-        <v>1572</v>
+        <v>1186</v>
       </c>
       <c r="D79">
-        <v>2138</v>
+        <v>2391</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>575</v>
+        <v>1207</v>
       </c>
       <c r="C80">
-        <v>1602</v>
+        <v>1203</v>
       </c>
       <c r="D80">
-        <v>2177</v>
+        <v>2410</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>668</v>
+        <v>1210</v>
       </c>
       <c r="C81">
-        <v>1669</v>
+        <v>1204</v>
       </c>
       <c r="D81">
-        <v>2337</v>
+        <v>2414</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>741</v>
+        <v>1182</v>
       </c>
       <c r="C82">
-        <v>1697</v>
+        <v>1220</v>
       </c>
       <c r="D82">
-        <v>2438</v>
+        <v>2402</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>736</v>
+        <v>1169</v>
       </c>
       <c r="C83">
-        <v>1695</v>
+        <v>1156</v>
       </c>
       <c r="D83">
-        <v>2431</v>
+        <v>2325</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>757</v>
+        <v>1178</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="D84">
-        <v>757</v>
+        <v>2320</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>808</v>
+        <v>1177</v>
       </c>
       <c r="C85">
-        <v>1697</v>
+        <v>1139</v>
       </c>
       <c r="D85">
-        <v>2505</v>
+        <v>2316</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>677</v>
+        <v>1109</v>
       </c>
       <c r="C86">
-        <v>1677</v>
+        <v>1131</v>
       </c>
       <c r="D86">
-        <v>2354</v>
+        <v>2240</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>658</v>
+        <v>1090</v>
       </c>
       <c r="C87">
-        <v>1645</v>
+        <v>1122</v>
       </c>
       <c r="D87">
-        <v>2303</v>
+        <v>2212</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>656</v>
+        <v>1068</v>
       </c>
       <c r="C88">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>2306</v>
+        <v>1068</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>650</v>
+        <v>1069</v>
       </c>
       <c r="C89">
-        <v>1644</v>
+        <v>1117</v>
       </c>
       <c r="D89">
-        <v>2294</v>
+        <v>2186</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>560</v>
+        <v>967</v>
       </c>
       <c r="C90">
-        <v>1603</v>
+        <v>1092</v>
       </c>
       <c r="D90">
-        <v>2163</v>
+        <v>2059</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>562</v>
+        <v>939</v>
       </c>
       <c r="C91">
-        <v>1597</v>
+        <v>1085</v>
       </c>
       <c r="D91">
-        <v>2159</v>
+        <v>2024</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>559</v>
+        <v>931</v>
       </c>
       <c r="C92">
-        <v>1605</v>
+        <v>1081</v>
       </c>
       <c r="D92">
-        <v>2164</v>
+        <v>2012</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>549</v>
+        <v>932</v>
       </c>
       <c r="C93">
-        <v>1614</v>
+        <v>1083</v>
       </c>
       <c r="D93">
-        <v>2163</v>
+        <v>2015</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>498</v>
+        <v>839</v>
       </c>
       <c r="C94">
-        <v>1500</v>
+        <v>1089</v>
       </c>
       <c r="D94">
-        <v>1998</v>
+        <v>1928</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>497</v>
+        <v>840</v>
       </c>
       <c r="C95">
-        <v>1484</v>
+        <v>1091</v>
       </c>
       <c r="D95">
-        <v>1981</v>
+        <v>1931</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>499</v>
+        <v>843</v>
       </c>
       <c r="C96">
-        <v>1499</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>1998</v>
+        <v>843</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>498</v>
+        <v>842</v>
       </c>
       <c r="C97">
-        <v>1504</v>
+        <v>1090</v>
       </c>
       <c r="D97">
-        <v>2002</v>
+        <v>1932</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
-        <v>547</v>
+        <v>797</v>
       </c>
       <c r="C98">
-        <v>1363</v>
+        <v>1024</v>
       </c>
       <c r="D98">
-        <v>1910</v>
+        <v>1821</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B99">
-        <v>552</v>
+        <v>794</v>
       </c>
       <c r="C99">
-        <v>1332</v>
+        <v>1020</v>
       </c>
       <c r="D99">
-        <v>1884</v>
+        <v>1814</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B100">
-        <v>518</v>
+        <v>795</v>
       </c>
       <c r="C100">
-        <v>1319</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>1837</v>
+        <v>795</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B101">
-        <v>467</v>
+        <v>792</v>
       </c>
       <c r="C101">
-        <v>1290</v>
+        <v>1019</v>
       </c>
       <c r="D101">
-        <v>1757</v>
+        <v>1811</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B102">
-        <v>480</v>
+        <v>783</v>
       </c>
       <c r="C102">
-        <v>1262</v>
+        <v>973</v>
       </c>
       <c r="D102">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B103">
-        <v>515</v>
+        <v>792</v>
       </c>
       <c r="C103">
-        <v>1260</v>
+        <v>970</v>
       </c>
       <c r="D103">
-        <v>1775</v>
+        <v>1762</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B104">
-        <v>460</v>
+        <v>791</v>
       </c>
       <c r="C104">
-        <v>1259</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1719</v>
+        <v>791</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B105">
-        <v>398</v>
+        <v>775</v>
       </c>
       <c r="C105">
-        <v>1213</v>
+        <v>969</v>
       </c>
       <c r="D105">
-        <v>1611</v>
+        <v>1744</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B106">
-        <v>400</v>
+        <v>778</v>
       </c>
       <c r="C106">
-        <v>1182</v>
+        <v>958</v>
       </c>
       <c r="D106">
-        <v>1582</v>
+        <v>1736</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B107">
-        <v>415</v>
+        <v>779</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>957</v>
       </c>
       <c r="D107">
-        <v>415</v>
+        <v>1736</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B108">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1180</v>
+        <v>956</v>
       </c>
       <c r="D108">
-        <v>1599</v>
+        <v>956</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B109">
-        <v>434</v>
+        <v>778</v>
       </c>
       <c r="C109">
-        <v>1183</v>
+        <v>955</v>
       </c>
       <c r="D109">
-        <v>1617</v>
+        <v>1733</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B110">
-        <v>325</v>
+        <v>700</v>
       </c>
       <c r="C110">
-        <v>1174</v>
+        <v>963</v>
       </c>
       <c r="D110">
-        <v>1499</v>
+        <v>1663</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B111">
-        <v>329</v>
+        <v>697</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="D111">
-        <v>329</v>
+        <v>1661</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B112">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1509</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B113">
-        <v>312</v>
+        <v>700</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>963</v>
       </c>
       <c r="D113">
-        <v>312</v>
+        <v>1663</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B114">
-        <v>350</v>
+        <v>790</v>
       </c>
       <c r="C114">
-        <v>1183</v>
+        <v>930</v>
       </c>
       <c r="D114">
-        <v>1533</v>
+        <v>1720</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B115">
-        <v>371</v>
+        <v>789</v>
       </c>
       <c r="C115">
-        <v>1182</v>
+        <v>933</v>
       </c>
       <c r="D115">
-        <v>1553</v>
+        <v>1722</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B116">
-        <v>359</v>
+        <v>788</v>
       </c>
       <c r="C116">
-        <v>1183</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1542</v>
+        <v>788</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B117">
-        <v>417</v>
+        <v>796</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="D117">
-        <v>417</v>
+        <v>1728</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B118">
-        <v>655</v>
+        <v>842</v>
       </c>
       <c r="C118">
-        <v>1121</v>
+        <v>1000</v>
       </c>
       <c r="D118">
-        <v>1776</v>
+        <v>1842</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B119">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>1141</v>
+        <v>1005</v>
       </c>
       <c r="D119">
-        <v>1891</v>
+        <v>1005</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B120">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B121">
-        <v>740</v>
+        <v>843</v>
       </c>
       <c r="C121">
-        <v>1137</v>
+        <v>1008</v>
       </c>
       <c r="D121">
-        <v>1877</v>
+        <v>1851</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B122">
-        <v>748</v>
+        <v>948</v>
       </c>
       <c r="C122">
-        <v>1190</v>
+        <v>1069</v>
       </c>
       <c r="D122">
-        <v>1938</v>
+        <v>2017</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B123">
-        <v>788</v>
+        <v>969</v>
       </c>
       <c r="C123">
-        <v>1185</v>
+        <v>1056</v>
       </c>
       <c r="D123">
-        <v>1973</v>
+        <v>2025</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>973</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1057</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B125">
-        <v>801</v>
+        <v>976</v>
       </c>
       <c r="C125">
-        <v>1187</v>
+        <v>1058</v>
       </c>
       <c r="D125">
-        <v>1988</v>
+        <v>2034</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B126">
-        <v>792</v>
+        <v>944</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1095</v>
       </c>
       <c r="D126">
-        <v>792</v>
+        <v>2039</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B127">
-        <v>793</v>
+        <v>932</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1105</v>
       </c>
       <c r="D127">
-        <v>793</v>
+        <v>2037</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B128">
-        <v>794</v>
+        <v>926</v>
       </c>
       <c r="C128">
-        <v>1199</v>
+        <v>1108</v>
       </c>
       <c r="D128">
-        <v>1993</v>
+        <v>2034</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1109</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1998</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>1735</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1732</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1090</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1643</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1714</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>989</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1505</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>998</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1575</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1575</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1596</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1467</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,580 +34,1156 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.04.20261</t>
-  </si>
-  <si>
-    <t>21.04.20262</t>
-  </si>
-  <si>
-    <t>21.04.20263</t>
-  </si>
-  <si>
-    <t>21.04.20264</t>
-  </si>
-  <si>
-    <t>21.04.20265</t>
-  </si>
-  <si>
-    <t>21.04.20266</t>
-  </si>
-  <si>
-    <t>21.04.20267</t>
-  </si>
-  <si>
-    <t>21.04.20268</t>
-  </si>
-  <si>
-    <t>21.04.20269</t>
-  </si>
-  <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>21.04.202625</t>
-  </si>
-  <si>
-    <t>21.04.202626</t>
-  </si>
-  <si>
-    <t>21.04.202627</t>
-  </si>
-  <si>
-    <t>21.04.202628</t>
-  </si>
-  <si>
-    <t>21.04.202629</t>
-  </si>
-  <si>
-    <t>21.04.202630</t>
-  </si>
-  <si>
-    <t>21.04.202631</t>
-  </si>
-  <si>
-    <t>21.04.202632</t>
-  </si>
-  <si>
-    <t>21.04.202633</t>
-  </si>
-  <si>
-    <t>21.04.202634</t>
-  </si>
-  <si>
-    <t>21.04.202635</t>
-  </si>
-  <si>
-    <t>21.04.202636</t>
-  </si>
-  <si>
-    <t>21.04.202637</t>
-  </si>
-  <si>
-    <t>21.04.202638</t>
-  </si>
-  <si>
-    <t>21.04.202639</t>
-  </si>
-  <si>
-    <t>21.04.202640</t>
-  </si>
-  <si>
-    <t>21.04.202641</t>
-  </si>
-  <si>
-    <t>21.04.202642</t>
-  </si>
-  <si>
-    <t>21.04.202643</t>
-  </si>
-  <si>
-    <t>21.04.202644</t>
-  </si>
-  <si>
-    <t>21.04.202645</t>
-  </si>
-  <si>
-    <t>21.04.202646</t>
-  </si>
-  <si>
-    <t>21.04.202647</t>
-  </si>
-  <si>
-    <t>21.04.202648</t>
-  </si>
-  <si>
-    <t>21.04.202649</t>
-  </si>
-  <si>
-    <t>21.04.202650</t>
-  </si>
-  <si>
-    <t>21.04.202651</t>
-  </si>
-  <si>
-    <t>21.04.202652</t>
-  </si>
-  <si>
-    <t>21.04.202653</t>
-  </si>
-  <si>
-    <t>21.04.202654</t>
-  </si>
-  <si>
-    <t>21.04.202655</t>
-  </si>
-  <si>
-    <t>21.04.202656</t>
-  </si>
-  <si>
-    <t>21.04.202657</t>
-  </si>
-  <si>
-    <t>21.04.202658</t>
-  </si>
-  <si>
-    <t>21.04.202659</t>
-  </si>
-  <si>
-    <t>21.04.202660</t>
-  </si>
-  <si>
-    <t>21.04.202661</t>
-  </si>
-  <si>
-    <t>21.04.202662</t>
-  </si>
-  <si>
-    <t>21.04.202663</t>
-  </si>
-  <si>
-    <t>21.04.202664</t>
-  </si>
-  <si>
-    <t>21.04.202665</t>
-  </si>
-  <si>
-    <t>21.04.202666</t>
-  </si>
-  <si>
-    <t>21.04.202667</t>
-  </si>
-  <si>
-    <t>21.04.202668</t>
-  </si>
-  <si>
-    <t>21.04.202669</t>
-  </si>
-  <si>
-    <t>21.04.202670</t>
-  </si>
-  <si>
-    <t>21.04.202671</t>
-  </si>
-  <si>
-    <t>21.04.202672</t>
-  </si>
-  <si>
-    <t>21.04.202673</t>
-  </si>
-  <si>
-    <t>21.04.202674</t>
-  </si>
-  <si>
-    <t>21.04.202675</t>
-  </si>
-  <si>
-    <t>21.04.202676</t>
-  </si>
-  <si>
-    <t>21.04.202677</t>
-  </si>
-  <si>
-    <t>21.04.202678</t>
-  </si>
-  <si>
-    <t>21.04.202679</t>
-  </si>
-  <si>
-    <t>21.04.202680</t>
-  </si>
-  <si>
-    <t>21.04.202681</t>
-  </si>
-  <si>
-    <t>21.04.202682</t>
-  </si>
-  <si>
-    <t>21.04.202683</t>
-  </si>
-  <si>
-    <t>21.04.202684</t>
-  </si>
-  <si>
-    <t>21.04.202685</t>
-  </si>
-  <si>
-    <t>21.04.202686</t>
-  </si>
-  <si>
-    <t>21.04.202687</t>
-  </si>
-  <si>
-    <t>21.04.202688</t>
-  </si>
-  <si>
-    <t>21.04.202689</t>
-  </si>
-  <si>
-    <t>21.04.202690</t>
-  </si>
-  <si>
-    <t>21.04.202691</t>
-  </si>
-  <si>
-    <t>21.04.202692</t>
-  </si>
-  <si>
-    <t>21.04.202693</t>
-  </si>
-  <si>
-    <t>21.04.202694</t>
-  </si>
-  <si>
-    <t>21.04.202695</t>
-  </si>
-  <si>
-    <t>21.04.202696</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.202625</t>
-  </si>
-  <si>
-    <t>22.04.202626</t>
-  </si>
-  <si>
-    <t>22.04.202627</t>
-  </si>
-  <si>
-    <t>22.04.202628</t>
-  </si>
-  <si>
-    <t>22.04.202629</t>
-  </si>
-  <si>
-    <t>22.04.202630</t>
-  </si>
-  <si>
-    <t>22.04.202631</t>
-  </si>
-  <si>
-    <t>22.04.202632</t>
-  </si>
-  <si>
-    <t>22.04.202633</t>
-  </si>
-  <si>
-    <t>22.04.202634</t>
-  </si>
-  <si>
-    <t>22.04.202635</t>
-  </si>
-  <si>
-    <t>22.04.202636</t>
-  </si>
-  <si>
-    <t>22.04.202637</t>
-  </si>
-  <si>
-    <t>22.04.202638</t>
-  </si>
-  <si>
-    <t>22.04.202639</t>
-  </si>
-  <si>
-    <t>22.04.202640</t>
-  </si>
-  <si>
-    <t>22.04.202641</t>
-  </si>
-  <si>
-    <t>22.04.202642</t>
-  </si>
-  <si>
-    <t>22.04.202643</t>
-  </si>
-  <si>
-    <t>22.04.202644</t>
-  </si>
-  <si>
-    <t>22.04.202645</t>
-  </si>
-  <si>
-    <t>22.04.202646</t>
-  </si>
-  <si>
-    <t>22.04.202647</t>
-  </si>
-  <si>
-    <t>22.04.202648</t>
-  </si>
-  <si>
-    <t>22.04.202649</t>
-  </si>
-  <si>
-    <t>22.04.202650</t>
-  </si>
-  <si>
-    <t>22.04.202651</t>
-  </si>
-  <si>
-    <t>22.04.202652</t>
-  </si>
-  <si>
-    <t>22.04.202653</t>
-  </si>
-  <si>
-    <t>22.04.202654</t>
-  </si>
-  <si>
-    <t>22.04.202655</t>
-  </si>
-  <si>
-    <t>22.04.202656</t>
-  </si>
-  <si>
-    <t>22.04.202657</t>
-  </si>
-  <si>
-    <t>22.04.202658</t>
-  </si>
-  <si>
-    <t>22.04.202659</t>
-  </si>
-  <si>
-    <t>22.04.202660</t>
-  </si>
-  <si>
-    <t>22.04.202661</t>
-  </si>
-  <si>
-    <t>22.04.202662</t>
-  </si>
-  <si>
-    <t>22.04.202663</t>
-  </si>
-  <si>
-    <t>22.04.202664</t>
-  </si>
-  <si>
-    <t>22.04.202665</t>
-  </si>
-  <si>
-    <t>22.04.202666</t>
-  </si>
-  <si>
-    <t>22.04.202667</t>
-  </si>
-  <si>
-    <t>22.04.202668</t>
-  </si>
-  <si>
-    <t>22.04.202669</t>
-  </si>
-  <si>
-    <t>22.04.202670</t>
-  </si>
-  <si>
-    <t>22.04.202671</t>
-  </si>
-  <si>
-    <t>22.04.202672</t>
-  </si>
-  <si>
-    <t>22.04.202673</t>
-  </si>
-  <si>
-    <t>22.04.202674</t>
-  </si>
-  <si>
-    <t>22.04.202675</t>
-  </si>
-  <si>
-    <t>22.04.202676</t>
-  </si>
-  <si>
-    <t>22.04.202677</t>
-  </si>
-  <si>
-    <t>22.04.202678</t>
-  </si>
-  <si>
-    <t>22.04.202679</t>
-  </si>
-  <si>
-    <t>22.04.202680</t>
-  </si>
-  <si>
-    <t>22.04.202681</t>
-  </si>
-  <si>
-    <t>22.04.202682</t>
-  </si>
-  <si>
-    <t>22.04.202683</t>
-  </si>
-  <si>
-    <t>22.04.202684</t>
-  </si>
-  <si>
-    <t>22.04.202685</t>
-  </si>
-  <si>
-    <t>22.04.202686</t>
-  </si>
-  <si>
-    <t>22.04.202687</t>
-  </si>
-  <si>
-    <t>22.04.202688</t>
-  </si>
-  <si>
-    <t>22.04.202689</t>
-  </si>
-  <si>
-    <t>22.04.202690</t>
-  </si>
-  <si>
-    <t>22.04.202691</t>
-  </si>
-  <si>
-    <t>22.04.202692</t>
-  </si>
-  <si>
-    <t>22.04.202693</t>
-  </si>
-  <si>
-    <t>22.04.202694</t>
-  </si>
-  <si>
-    <t>22.04.202695</t>
-  </si>
-  <si>
-    <t>22.04.202696</t>
+    <t>24.04.20261</t>
+  </si>
+  <si>
+    <t>24.04.20262</t>
+  </si>
+  <si>
+    <t>24.04.20263</t>
+  </si>
+  <si>
+    <t>24.04.20264</t>
+  </si>
+  <si>
+    <t>24.04.20265</t>
+  </si>
+  <si>
+    <t>24.04.20266</t>
+  </si>
+  <si>
+    <t>24.04.20267</t>
+  </si>
+  <si>
+    <t>24.04.20268</t>
+  </si>
+  <si>
+    <t>24.04.20269</t>
+  </si>
+  <si>
+    <t>24.04.202610</t>
+  </si>
+  <si>
+    <t>24.04.202611</t>
+  </si>
+  <si>
+    <t>24.04.202612</t>
+  </si>
+  <si>
+    <t>24.04.202613</t>
+  </si>
+  <si>
+    <t>24.04.202614</t>
+  </si>
+  <si>
+    <t>24.04.202615</t>
+  </si>
+  <si>
+    <t>24.04.202616</t>
+  </si>
+  <si>
+    <t>24.04.202617</t>
+  </si>
+  <si>
+    <t>24.04.202618</t>
+  </si>
+  <si>
+    <t>24.04.202619</t>
+  </si>
+  <si>
+    <t>24.04.202620</t>
+  </si>
+  <si>
+    <t>24.04.202621</t>
+  </si>
+  <si>
+    <t>24.04.202622</t>
+  </si>
+  <si>
+    <t>24.04.202623</t>
+  </si>
+  <si>
+    <t>24.04.202624</t>
+  </si>
+  <si>
+    <t>24.04.202625</t>
+  </si>
+  <si>
+    <t>24.04.202626</t>
+  </si>
+  <si>
+    <t>24.04.202627</t>
+  </si>
+  <si>
+    <t>24.04.202628</t>
+  </si>
+  <si>
+    <t>24.04.202629</t>
+  </si>
+  <si>
+    <t>24.04.202630</t>
+  </si>
+  <si>
+    <t>24.04.202631</t>
+  </si>
+  <si>
+    <t>24.04.202632</t>
+  </si>
+  <si>
+    <t>24.04.202633</t>
+  </si>
+  <si>
+    <t>24.04.202634</t>
+  </si>
+  <si>
+    <t>24.04.202635</t>
+  </si>
+  <si>
+    <t>24.04.202636</t>
+  </si>
+  <si>
+    <t>24.04.202637</t>
+  </si>
+  <si>
+    <t>24.04.202638</t>
+  </si>
+  <si>
+    <t>24.04.202639</t>
+  </si>
+  <si>
+    <t>24.04.202640</t>
+  </si>
+  <si>
+    <t>24.04.202641</t>
+  </si>
+  <si>
+    <t>24.04.202642</t>
+  </si>
+  <si>
+    <t>24.04.202643</t>
+  </si>
+  <si>
+    <t>24.04.202644</t>
+  </si>
+  <si>
+    <t>24.04.202645</t>
+  </si>
+  <si>
+    <t>24.04.202646</t>
+  </si>
+  <si>
+    <t>24.04.202647</t>
+  </si>
+  <si>
+    <t>24.04.202648</t>
+  </si>
+  <si>
+    <t>24.04.202649</t>
+  </si>
+  <si>
+    <t>24.04.202650</t>
+  </si>
+  <si>
+    <t>24.04.202651</t>
+  </si>
+  <si>
+    <t>24.04.202652</t>
+  </si>
+  <si>
+    <t>24.04.202653</t>
+  </si>
+  <si>
+    <t>24.04.202654</t>
+  </si>
+  <si>
+    <t>24.04.202655</t>
+  </si>
+  <si>
+    <t>24.04.202656</t>
+  </si>
+  <si>
+    <t>24.04.202657</t>
+  </si>
+  <si>
+    <t>24.04.202658</t>
+  </si>
+  <si>
+    <t>24.04.202659</t>
+  </si>
+  <si>
+    <t>24.04.202660</t>
+  </si>
+  <si>
+    <t>24.04.202661</t>
+  </si>
+  <si>
+    <t>24.04.202662</t>
+  </si>
+  <si>
+    <t>24.04.202663</t>
+  </si>
+  <si>
+    <t>24.04.202664</t>
+  </si>
+  <si>
+    <t>24.04.202665</t>
+  </si>
+  <si>
+    <t>24.04.202666</t>
+  </si>
+  <si>
+    <t>24.04.202667</t>
+  </si>
+  <si>
+    <t>24.04.202668</t>
+  </si>
+  <si>
+    <t>24.04.202669</t>
+  </si>
+  <si>
+    <t>24.04.202670</t>
+  </si>
+  <si>
+    <t>24.04.202671</t>
+  </si>
+  <si>
+    <t>24.04.202672</t>
+  </si>
+  <si>
+    <t>24.04.202673</t>
+  </si>
+  <si>
+    <t>24.04.202674</t>
+  </si>
+  <si>
+    <t>24.04.202675</t>
+  </si>
+  <si>
+    <t>24.04.202676</t>
+  </si>
+  <si>
+    <t>24.04.202677</t>
+  </si>
+  <si>
+    <t>24.04.202678</t>
+  </si>
+  <si>
+    <t>24.04.202679</t>
+  </si>
+  <si>
+    <t>24.04.202680</t>
+  </si>
+  <si>
+    <t>24.04.202681</t>
+  </si>
+  <si>
+    <t>24.04.202682</t>
+  </si>
+  <si>
+    <t>24.04.202683</t>
+  </si>
+  <si>
+    <t>24.04.202684</t>
+  </si>
+  <si>
+    <t>24.04.202685</t>
+  </si>
+  <si>
+    <t>24.04.202686</t>
+  </si>
+  <si>
+    <t>24.04.202687</t>
+  </si>
+  <si>
+    <t>24.04.202688</t>
+  </si>
+  <si>
+    <t>24.04.202689</t>
+  </si>
+  <si>
+    <t>24.04.202690</t>
+  </si>
+  <si>
+    <t>24.04.202691</t>
+  </si>
+  <si>
+    <t>24.04.202692</t>
+  </si>
+  <si>
+    <t>24.04.202693</t>
+  </si>
+  <si>
+    <t>24.04.202694</t>
+  </si>
+  <si>
+    <t>24.04.202695</t>
+  </si>
+  <si>
+    <t>24.04.202696</t>
+  </si>
+  <si>
+    <t>25.04.20261</t>
+  </si>
+  <si>
+    <t>25.04.20262</t>
+  </si>
+  <si>
+    <t>25.04.20263</t>
+  </si>
+  <si>
+    <t>25.04.20264</t>
+  </si>
+  <si>
+    <t>25.04.20265</t>
+  </si>
+  <si>
+    <t>25.04.20266</t>
+  </si>
+  <si>
+    <t>25.04.20267</t>
+  </si>
+  <si>
+    <t>25.04.20268</t>
+  </si>
+  <si>
+    <t>25.04.20269</t>
+  </si>
+  <si>
+    <t>25.04.202610</t>
+  </si>
+  <si>
+    <t>25.04.202611</t>
+  </si>
+  <si>
+    <t>25.04.202612</t>
+  </si>
+  <si>
+    <t>25.04.202613</t>
+  </si>
+  <si>
+    <t>25.04.202614</t>
+  </si>
+  <si>
+    <t>25.04.202615</t>
+  </si>
+  <si>
+    <t>25.04.202616</t>
+  </si>
+  <si>
+    <t>25.04.202617</t>
+  </si>
+  <si>
+    <t>25.04.202618</t>
+  </si>
+  <si>
+    <t>25.04.202619</t>
+  </si>
+  <si>
+    <t>25.04.202620</t>
+  </si>
+  <si>
+    <t>25.04.202621</t>
+  </si>
+  <si>
+    <t>25.04.202622</t>
+  </si>
+  <si>
+    <t>25.04.202623</t>
+  </si>
+  <si>
+    <t>25.04.202624</t>
+  </si>
+  <si>
+    <t>25.04.202625</t>
+  </si>
+  <si>
+    <t>25.04.202626</t>
+  </si>
+  <si>
+    <t>25.04.202627</t>
+  </si>
+  <si>
+    <t>25.04.202628</t>
+  </si>
+  <si>
+    <t>25.04.202629</t>
+  </si>
+  <si>
+    <t>25.04.202630</t>
+  </si>
+  <si>
+    <t>25.04.202631</t>
+  </si>
+  <si>
+    <t>25.04.202632</t>
+  </si>
+  <si>
+    <t>25.04.202633</t>
+  </si>
+  <si>
+    <t>25.04.202634</t>
+  </si>
+  <si>
+    <t>25.04.202635</t>
+  </si>
+  <si>
+    <t>25.04.202636</t>
+  </si>
+  <si>
+    <t>25.04.202637</t>
+  </si>
+  <si>
+    <t>25.04.202638</t>
+  </si>
+  <si>
+    <t>25.04.202639</t>
+  </si>
+  <si>
+    <t>25.04.202640</t>
+  </si>
+  <si>
+    <t>25.04.202641</t>
+  </si>
+  <si>
+    <t>25.04.202642</t>
+  </si>
+  <si>
+    <t>25.04.202643</t>
+  </si>
+  <si>
+    <t>25.04.202644</t>
+  </si>
+  <si>
+    <t>25.04.202645</t>
+  </si>
+  <si>
+    <t>25.04.202646</t>
+  </si>
+  <si>
+    <t>25.04.202647</t>
+  </si>
+  <si>
+    <t>25.04.202648</t>
+  </si>
+  <si>
+    <t>25.04.202649</t>
+  </si>
+  <si>
+    <t>25.04.202650</t>
+  </si>
+  <si>
+    <t>25.04.202651</t>
+  </si>
+  <si>
+    <t>25.04.202652</t>
+  </si>
+  <si>
+    <t>25.04.202653</t>
+  </si>
+  <si>
+    <t>25.04.202654</t>
+  </si>
+  <si>
+    <t>25.04.202655</t>
+  </si>
+  <si>
+    <t>25.04.202656</t>
+  </si>
+  <si>
+    <t>25.04.202657</t>
+  </si>
+  <si>
+    <t>25.04.202658</t>
+  </si>
+  <si>
+    <t>25.04.202659</t>
+  </si>
+  <si>
+    <t>25.04.202660</t>
+  </si>
+  <si>
+    <t>25.04.202661</t>
+  </si>
+  <si>
+    <t>25.04.202662</t>
+  </si>
+  <si>
+    <t>25.04.202663</t>
+  </si>
+  <si>
+    <t>25.04.202664</t>
+  </si>
+  <si>
+    <t>25.04.202665</t>
+  </si>
+  <si>
+    <t>25.04.202666</t>
+  </si>
+  <si>
+    <t>25.04.202667</t>
+  </si>
+  <si>
+    <t>25.04.202668</t>
+  </si>
+  <si>
+    <t>25.04.202669</t>
+  </si>
+  <si>
+    <t>25.04.202670</t>
+  </si>
+  <si>
+    <t>25.04.202671</t>
+  </si>
+  <si>
+    <t>25.04.202672</t>
+  </si>
+  <si>
+    <t>25.04.202673</t>
+  </si>
+  <si>
+    <t>25.04.202674</t>
+  </si>
+  <si>
+    <t>25.04.202675</t>
+  </si>
+  <si>
+    <t>25.04.202676</t>
+  </si>
+  <si>
+    <t>25.04.202677</t>
+  </si>
+  <si>
+    <t>25.04.202678</t>
+  </si>
+  <si>
+    <t>25.04.202679</t>
+  </si>
+  <si>
+    <t>25.04.202680</t>
+  </si>
+  <si>
+    <t>25.04.202681</t>
+  </si>
+  <si>
+    <t>25.04.202682</t>
+  </si>
+  <si>
+    <t>25.04.202683</t>
+  </si>
+  <si>
+    <t>25.04.202684</t>
+  </si>
+  <si>
+    <t>25.04.202685</t>
+  </si>
+  <si>
+    <t>25.04.202686</t>
+  </si>
+  <si>
+    <t>25.04.202687</t>
+  </si>
+  <si>
+    <t>25.04.202688</t>
+  </si>
+  <si>
+    <t>25.04.202689</t>
+  </si>
+  <si>
+    <t>25.04.202690</t>
+  </si>
+  <si>
+    <t>25.04.202691</t>
+  </si>
+  <si>
+    <t>25.04.202692</t>
+  </si>
+  <si>
+    <t>25.04.202693</t>
+  </si>
+  <si>
+    <t>25.04.202694</t>
+  </si>
+  <si>
+    <t>25.04.202695</t>
+  </si>
+  <si>
+    <t>25.04.202696</t>
+  </si>
+  <si>
+    <t>26.04.20261</t>
+  </si>
+  <si>
+    <t>26.04.20262</t>
+  </si>
+  <si>
+    <t>26.04.20263</t>
+  </si>
+  <si>
+    <t>26.04.20264</t>
+  </si>
+  <si>
+    <t>26.04.20265</t>
+  </si>
+  <si>
+    <t>26.04.20266</t>
+  </si>
+  <si>
+    <t>26.04.20267</t>
+  </si>
+  <si>
+    <t>26.04.20268</t>
+  </si>
+  <si>
+    <t>26.04.20269</t>
+  </si>
+  <si>
+    <t>26.04.202610</t>
+  </si>
+  <si>
+    <t>26.04.202611</t>
+  </si>
+  <si>
+    <t>26.04.202612</t>
+  </si>
+  <si>
+    <t>26.04.202613</t>
+  </si>
+  <si>
+    <t>26.04.202614</t>
+  </si>
+  <si>
+    <t>26.04.202615</t>
+  </si>
+  <si>
+    <t>26.04.202616</t>
+  </si>
+  <si>
+    <t>26.04.202617</t>
+  </si>
+  <si>
+    <t>26.04.202618</t>
+  </si>
+  <si>
+    <t>26.04.202619</t>
+  </si>
+  <si>
+    <t>26.04.202620</t>
+  </si>
+  <si>
+    <t>26.04.202621</t>
+  </si>
+  <si>
+    <t>26.04.202622</t>
+  </si>
+  <si>
+    <t>26.04.202623</t>
+  </si>
+  <si>
+    <t>26.04.202624</t>
+  </si>
+  <si>
+    <t>26.04.202625</t>
+  </si>
+  <si>
+    <t>26.04.202626</t>
+  </si>
+  <si>
+    <t>26.04.202627</t>
+  </si>
+  <si>
+    <t>26.04.202628</t>
+  </si>
+  <si>
+    <t>26.04.202629</t>
+  </si>
+  <si>
+    <t>26.04.202630</t>
+  </si>
+  <si>
+    <t>26.04.202631</t>
+  </si>
+  <si>
+    <t>26.04.202632</t>
+  </si>
+  <si>
+    <t>26.04.202633</t>
+  </si>
+  <si>
+    <t>26.04.202634</t>
+  </si>
+  <si>
+    <t>26.04.202635</t>
+  </si>
+  <si>
+    <t>26.04.202636</t>
+  </si>
+  <si>
+    <t>26.04.202637</t>
+  </si>
+  <si>
+    <t>26.04.202638</t>
+  </si>
+  <si>
+    <t>26.04.202639</t>
+  </si>
+  <si>
+    <t>26.04.202640</t>
+  </si>
+  <si>
+    <t>26.04.202641</t>
+  </si>
+  <si>
+    <t>26.04.202642</t>
+  </si>
+  <si>
+    <t>26.04.202643</t>
+  </si>
+  <si>
+    <t>26.04.202644</t>
+  </si>
+  <si>
+    <t>26.04.202645</t>
+  </si>
+  <si>
+    <t>26.04.202646</t>
+  </si>
+  <si>
+    <t>26.04.202647</t>
+  </si>
+  <si>
+    <t>26.04.202648</t>
+  </si>
+  <si>
+    <t>26.04.202649</t>
+  </si>
+  <si>
+    <t>26.04.202650</t>
+  </si>
+  <si>
+    <t>26.04.202651</t>
+  </si>
+  <si>
+    <t>26.04.202652</t>
+  </si>
+  <si>
+    <t>26.04.202653</t>
+  </si>
+  <si>
+    <t>26.04.202654</t>
+  </si>
+  <si>
+    <t>26.04.202655</t>
+  </si>
+  <si>
+    <t>26.04.202656</t>
+  </si>
+  <si>
+    <t>26.04.202657</t>
+  </si>
+  <si>
+    <t>26.04.202658</t>
+  </si>
+  <si>
+    <t>26.04.202659</t>
+  </si>
+  <si>
+    <t>26.04.202660</t>
+  </si>
+  <si>
+    <t>26.04.202661</t>
+  </si>
+  <si>
+    <t>26.04.202662</t>
+  </si>
+  <si>
+    <t>26.04.202663</t>
+  </si>
+  <si>
+    <t>26.04.202664</t>
+  </si>
+  <si>
+    <t>26.04.202665</t>
+  </si>
+  <si>
+    <t>26.04.202666</t>
+  </si>
+  <si>
+    <t>26.04.202667</t>
+  </si>
+  <si>
+    <t>26.04.202668</t>
+  </si>
+  <si>
+    <t>26.04.202669</t>
+  </si>
+  <si>
+    <t>26.04.202670</t>
+  </si>
+  <si>
+    <t>26.04.202671</t>
+  </si>
+  <si>
+    <t>26.04.202672</t>
+  </si>
+  <si>
+    <t>26.04.202673</t>
+  </si>
+  <si>
+    <t>26.04.202674</t>
+  </si>
+  <si>
+    <t>26.04.202675</t>
+  </si>
+  <si>
+    <t>26.04.202676</t>
+  </si>
+  <si>
+    <t>26.04.202677</t>
+  </si>
+  <si>
+    <t>26.04.202678</t>
+  </si>
+  <si>
+    <t>26.04.202679</t>
+  </si>
+  <si>
+    <t>26.04.202680</t>
+  </si>
+  <si>
+    <t>26.04.202681</t>
+  </si>
+  <si>
+    <t>26.04.202682</t>
+  </si>
+  <si>
+    <t>26.04.202683</t>
+  </si>
+  <si>
+    <t>26.04.202684</t>
+  </si>
+  <si>
+    <t>26.04.202685</t>
+  </si>
+  <si>
+    <t>26.04.202686</t>
+  </si>
+  <si>
+    <t>26.04.202687</t>
+  </si>
+  <si>
+    <t>26.04.202688</t>
+  </si>
+  <si>
+    <t>26.04.202689</t>
+  </si>
+  <si>
+    <t>26.04.202690</t>
+  </si>
+  <si>
+    <t>26.04.202691</t>
+  </si>
+  <si>
+    <t>26.04.202692</t>
+  </si>
+  <si>
+    <t>26.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202694</t>
+  </si>
+  <si>
+    <t>26.04.202695</t>
+  </si>
+  <si>
+    <t>26.04.202696</t>
+  </si>
+  <si>
+    <t>27.04.20261</t>
+  </si>
+  <si>
+    <t>27.04.20262</t>
+  </si>
+  <si>
+    <t>27.04.20263</t>
+  </si>
+  <si>
+    <t>27.04.20264</t>
+  </si>
+  <si>
+    <t>27.04.20265</t>
+  </si>
+  <si>
+    <t>27.04.20266</t>
+  </si>
+  <si>
+    <t>27.04.20267</t>
+  </si>
+  <si>
+    <t>27.04.20268</t>
+  </si>
+  <si>
+    <t>27.04.20269</t>
+  </si>
+  <si>
+    <t>27.04.202610</t>
+  </si>
+  <si>
+    <t>27.04.202611</t>
+  </si>
+  <si>
+    <t>27.04.202612</t>
+  </si>
+  <si>
+    <t>27.04.202613</t>
+  </si>
+  <si>
+    <t>27.04.202614</t>
+  </si>
+  <si>
+    <t>27.04.202615</t>
+  </si>
+  <si>
+    <t>27.04.202616</t>
+  </si>
+  <si>
+    <t>27.04.202617</t>
+  </si>
+  <si>
+    <t>27.04.202618</t>
+  </si>
+  <si>
+    <t>27.04.202619</t>
+  </si>
+  <si>
+    <t>27.04.202620</t>
+  </si>
+  <si>
+    <t>27.04.202621</t>
+  </si>
+  <si>
+    <t>27.04.202622</t>
+  </si>
+  <si>
+    <t>27.04.202623</t>
+  </si>
+  <si>
+    <t>27.04.202624</t>
+  </si>
+  <si>
+    <t>27.04.202625</t>
+  </si>
+  <si>
+    <t>27.04.202626</t>
+  </si>
+  <si>
+    <t>27.04.202627</t>
+  </si>
+  <si>
+    <t>27.04.202628</t>
+  </si>
+  <si>
+    <t>27.04.202629</t>
+  </si>
+  <si>
+    <t>27.04.202630</t>
+  </si>
+  <si>
+    <t>27.04.202631</t>
+  </si>
+  <si>
+    <t>27.04.202632</t>
+  </si>
+  <si>
+    <t>27.04.202633</t>
+  </si>
+  <si>
+    <t>27.04.202634</t>
+  </si>
+  <si>
+    <t>27.04.202635</t>
+  </si>
+  <si>
+    <t>27.04.202636</t>
+  </si>
+  <si>
+    <t>27.04.202637</t>
+  </si>
+  <si>
+    <t>27.04.202638</t>
+  </si>
+  <si>
+    <t>27.04.202639</t>
+  </si>
+  <si>
+    <t>27.04.202640</t>
+  </si>
+  <si>
+    <t>27.04.202641</t>
+  </si>
+  <si>
+    <t>27.04.202642</t>
+  </si>
+  <si>
+    <t>27.04.202643</t>
+  </si>
+  <si>
+    <t>27.04.202644</t>
+  </si>
+  <si>
+    <t>27.04.202645</t>
+  </si>
+  <si>
+    <t>27.04.202646</t>
+  </si>
+  <si>
+    <t>27.04.202647</t>
+  </si>
+  <si>
+    <t>27.04.202648</t>
+  </si>
+  <si>
+    <t>27.04.202649</t>
+  </si>
+  <si>
+    <t>27.04.202650</t>
+  </si>
+  <si>
+    <t>27.04.202651</t>
+  </si>
+  <si>
+    <t>27.04.202652</t>
+  </si>
+  <si>
+    <t>27.04.202653</t>
+  </si>
+  <si>
+    <t>27.04.202654</t>
+  </si>
+  <si>
+    <t>27.04.202655</t>
+  </si>
+  <si>
+    <t>27.04.202656</t>
+  </si>
+  <si>
+    <t>27.04.202657</t>
+  </si>
+  <si>
+    <t>27.04.202658</t>
+  </si>
+  <si>
+    <t>27.04.202659</t>
+  </si>
+  <si>
+    <t>27.04.202660</t>
+  </si>
+  <si>
+    <t>27.04.202661</t>
+  </si>
+  <si>
+    <t>27.04.202662</t>
+  </si>
+  <si>
+    <t>27.04.202663</t>
+  </si>
+  <si>
+    <t>27.04.202664</t>
+  </si>
+  <si>
+    <t>27.04.202665</t>
+  </si>
+  <si>
+    <t>27.04.202666</t>
+  </si>
+  <si>
+    <t>27.04.202667</t>
+  </si>
+  <si>
+    <t>27.04.202668</t>
+  </si>
+  <si>
+    <t>27.04.202669</t>
+  </si>
+  <si>
+    <t>27.04.202670</t>
+  </si>
+  <si>
+    <t>27.04.202671</t>
+  </si>
+  <si>
+    <t>27.04.202672</t>
+  </si>
+  <si>
+    <t>27.04.202673</t>
+  </si>
+  <si>
+    <t>27.04.202674</t>
+  </si>
+  <si>
+    <t>27.04.202675</t>
+  </si>
+  <si>
+    <t>27.04.202676</t>
+  </si>
+  <si>
+    <t>27.04.202677</t>
+  </si>
+  <si>
+    <t>27.04.202678</t>
+  </si>
+  <si>
+    <t>27.04.202679</t>
+  </si>
+  <si>
+    <t>27.04.202680</t>
+  </si>
+  <si>
+    <t>27.04.202681</t>
+  </si>
+  <si>
+    <t>27.04.202682</t>
+  </si>
+  <si>
+    <t>27.04.202683</t>
+  </si>
+  <si>
+    <t>27.04.202684</t>
+  </si>
+  <si>
+    <t>27.04.202685</t>
+  </si>
+  <si>
+    <t>27.04.202686</t>
+  </si>
+  <si>
+    <t>27.04.202687</t>
+  </si>
+  <si>
+    <t>27.04.202688</t>
+  </si>
+  <si>
+    <t>27.04.202689</t>
+  </si>
+  <si>
+    <t>27.04.202690</t>
+  </si>
+  <si>
+    <t>27.04.202691</t>
+  </si>
+  <si>
+    <t>27.04.202692</t>
+  </si>
+  <si>
+    <t>27.04.202693</t>
+  </si>
+  <si>
+    <t>27.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202695</t>
+  </si>
+  <si>
+    <t>27.04.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,16 +1570,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2">
-        <v>547</v>
+        <v>603</v>
       </c>
       <c r="C2">
-        <v>1363</v>
+        <v>1545</v>
       </c>
       <c r="D2">
-        <v>1910</v>
+        <v>2148</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1590,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46136.01041666666</v>
       </c>
       <c r="B3">
-        <v>552</v>
+        <v>602</v>
       </c>
       <c r="C3">
-        <v>1332</v>
+        <v>1533</v>
       </c>
       <c r="D3">
-        <v>1884</v>
+        <v>2135</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1610,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46136.02083333334</v>
       </c>
       <c r="B4">
-        <v>518</v>
+        <v>576</v>
       </c>
       <c r="C4">
-        <v>1319</v>
+        <v>1539</v>
       </c>
       <c r="D4">
-        <v>1837</v>
+        <v>2115</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1630,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46136.03125</v>
       </c>
       <c r="B5">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1290</v>
+        <v>1542</v>
       </c>
       <c r="D5">
-        <v>1757</v>
+        <v>1542</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46136.04166666666</v>
       </c>
       <c r="B6">
-        <v>480</v>
+        <v>557</v>
       </c>
       <c r="C6">
-        <v>1262</v>
+        <v>1372</v>
       </c>
       <c r="D6">
-        <v>1742</v>
+        <v>1929</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46136.05208333334</v>
       </c>
       <c r="B7">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="C7">
-        <v>1260</v>
+        <v>1338</v>
       </c>
       <c r="D7">
-        <v>1775</v>
+        <v>1868</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46136.0625</v>
       </c>
       <c r="B8">
-        <v>460</v>
+        <v>504</v>
       </c>
       <c r="C8">
-        <v>1259</v>
+        <v>1340</v>
       </c>
       <c r="D8">
-        <v>1719</v>
+        <v>1844</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46136.07291666666</v>
       </c>
       <c r="B9">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="C9">
-        <v>1213</v>
+        <v>1338</v>
       </c>
       <c r="D9">
-        <v>1611</v>
+        <v>1705</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46136.08333333334</v>
       </c>
       <c r="B10">
-        <v>400</v>
+        <v>332</v>
       </c>
       <c r="C10">
-        <v>1182</v>
+        <v>1322</v>
       </c>
       <c r="D10">
-        <v>1582</v>
+        <v>1654</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46136.09375</v>
       </c>
       <c r="B11">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1319</v>
       </c>
       <c r="D11">
-        <v>415</v>
+        <v>1647</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46136.10416666666</v>
       </c>
       <c r="B12">
-        <v>419</v>
+        <v>336</v>
       </c>
       <c r="C12">
-        <v>1180</v>
+        <v>1321</v>
       </c>
       <c r="D12">
-        <v>1599</v>
+        <v>1657</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46136.11458333334</v>
       </c>
       <c r="B13">
-        <v>434</v>
+        <v>328</v>
       </c>
       <c r="C13">
-        <v>1183</v>
+        <v>1319</v>
       </c>
       <c r="D13">
-        <v>1617</v>
+        <v>1647</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46136.125</v>
       </c>
       <c r="B14">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C14">
-        <v>1174</v>
+        <v>1285</v>
       </c>
       <c r="D14">
-        <v>1499</v>
+        <v>1609</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46136.13541666666</v>
       </c>
       <c r="B15">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1281</v>
       </c>
       <c r="D15">
-        <v>329</v>
+        <v>1604</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46136.14583333334</v>
       </c>
       <c r="B16">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C16">
-        <v>1173</v>
+        <v>1283</v>
       </c>
       <c r="D16">
-        <v>1509</v>
+        <v>1607</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46136.15625</v>
       </c>
       <c r="B17">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46136.16666666666</v>
       </c>
       <c r="B18">
-        <v>350</v>
+        <v>467</v>
       </c>
       <c r="C18">
-        <v>1183</v>
+        <v>1279</v>
       </c>
       <c r="D18">
-        <v>1533</v>
+        <v>1746</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46136.17708333334</v>
       </c>
       <c r="B19">
-        <v>371</v>
+        <v>478</v>
       </c>
       <c r="C19">
-        <v>1182</v>
+        <v>1276</v>
       </c>
       <c r="D19">
-        <v>1553</v>
+        <v>1754</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46136.1875</v>
       </c>
       <c r="B20">
-        <v>359</v>
+        <v>477</v>
       </c>
       <c r="C20">
-        <v>1183</v>
+        <v>1277</v>
       </c>
       <c r="D20">
-        <v>1542</v>
+        <v>1754</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46136.19791666666</v>
       </c>
       <c r="B21">
-        <v>417</v>
+        <v>490</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1274</v>
       </c>
       <c r="D21">
-        <v>417</v>
+        <v>1764</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46136.20833333334</v>
       </c>
       <c r="B22">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="C22">
-        <v>1121</v>
+        <v>1267</v>
       </c>
       <c r="D22">
-        <v>1776</v>
+        <v>1915</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46136.21875</v>
       </c>
       <c r="B23">
-        <v>750</v>
+        <v>649</v>
       </c>
       <c r="C23">
-        <v>1141</v>
+        <v>1261</v>
       </c>
       <c r="D23">
-        <v>1891</v>
+        <v>1910</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46136.22916666666</v>
       </c>
       <c r="B24">
-        <v>741</v>
+        <v>653</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1264</v>
       </c>
       <c r="D24">
-        <v>741</v>
+        <v>1917</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46136.23958333334</v>
       </c>
       <c r="B25">
-        <v>740</v>
+        <v>665</v>
       </c>
       <c r="C25">
-        <v>1137</v>
+        <v>1263</v>
       </c>
       <c r="D25">
-        <v>1877</v>
+        <v>1928</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46136.25</v>
       </c>
       <c r="B26">
-        <v>748</v>
+        <v>670</v>
       </c>
       <c r="C26">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D26">
-        <v>1938</v>
+        <v>1858</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46136.26041666666</v>
       </c>
       <c r="B27">
-        <v>788</v>
+        <v>677</v>
       </c>
       <c r="C27">
         <v>1185</v>
       </c>
       <c r="D27">
-        <v>1973</v>
+        <v>1862</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46136.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1186</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46136.28125</v>
       </c>
       <c r="B29">
-        <v>801</v>
+        <v>669</v>
       </c>
       <c r="C29">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="D29">
-        <v>1988</v>
+        <v>1852</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46136.29166666666</v>
       </c>
       <c r="B30">
-        <v>792</v>
+        <v>473</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1172</v>
       </c>
       <c r="D30">
-        <v>792</v>
+        <v>1645</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46136.30208333334</v>
       </c>
       <c r="B31">
-        <v>793</v>
+        <v>448</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="D31">
-        <v>793</v>
+        <v>1614</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46136.3125</v>
       </c>
       <c r="B32">
-        <v>794</v>
+        <v>436</v>
       </c>
       <c r="C32">
-        <v>1199</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1993</v>
+        <v>436</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46136.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1210</v>
+        <v>1167</v>
       </c>
       <c r="D33">
-        <v>1210</v>
+        <v>1167</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46136.33333333334</v>
       </c>
       <c r="B34">
-        <v>710</v>
+        <v>352</v>
       </c>
       <c r="C34">
-        <v>1173</v>
+        <v>1197</v>
       </c>
       <c r="D34">
-        <v>1883</v>
+        <v>1549</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46136.34375</v>
       </c>
       <c r="B35">
-        <v>637</v>
+        <v>344</v>
       </c>
       <c r="C35">
-        <v>1167</v>
+        <v>1199</v>
       </c>
       <c r="D35">
-        <v>1804</v>
+        <v>1543</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46136.35416666666</v>
       </c>
       <c r="B36">
-        <v>616</v>
+        <v>339</v>
       </c>
       <c r="C36">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="D36">
-        <v>1801</v>
+        <v>1543</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46136.36458333334</v>
       </c>
       <c r="B37">
-        <v>622</v>
+        <v>187</v>
       </c>
       <c r="C37">
-        <v>1189</v>
+        <v>1116</v>
       </c>
       <c r="D37">
-        <v>1811</v>
+        <v>1303</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46136.375</v>
       </c>
       <c r="B38">
-        <v>591</v>
+        <v>245</v>
       </c>
       <c r="C38">
-        <v>1135</v>
+        <v>976</v>
       </c>
       <c r="D38">
-        <v>1726</v>
+        <v>1221</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="B39">
-        <v>593</v>
+        <v>254</v>
       </c>
       <c r="C39">
-        <v>1127</v>
+        <v>958</v>
       </c>
       <c r="D39">
-        <v>1720</v>
+        <v>1212</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46136.39583333334</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="C40">
-        <v>1137</v>
+        <v>954</v>
       </c>
       <c r="D40">
-        <v>1137</v>
+        <v>1184</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46136.40625</v>
       </c>
       <c r="B41">
-        <v>610</v>
+        <v>226</v>
       </c>
       <c r="C41">
-        <v>1130</v>
+        <v>950</v>
       </c>
       <c r="D41">
-        <v>1740</v>
+        <v>1176</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46136.41666666666</v>
       </c>
       <c r="B42">
-        <v>559</v>
+        <v>184</v>
       </c>
       <c r="C42">
-        <v>1006</v>
+        <v>786</v>
       </c>
       <c r="D42">
-        <v>1565</v>
+        <v>970</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46136.42708333334</v>
       </c>
       <c r="B43">
-        <v>632</v>
+        <v>143</v>
       </c>
       <c r="C43">
-        <v>1012</v>
+        <v>759</v>
       </c>
       <c r="D43">
-        <v>1644</v>
+        <v>902</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46136.4375</v>
       </c>
       <c r="B44">
-        <v>636</v>
+        <v>142</v>
       </c>
       <c r="C44">
-        <v>1015</v>
+        <v>763</v>
       </c>
       <c r="D44">
-        <v>1651</v>
+        <v>905</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46136.44791666666</v>
       </c>
       <c r="B45">
-        <v>630</v>
+        <v>131</v>
       </c>
       <c r="C45">
-        <v>1017</v>
+        <v>762</v>
       </c>
       <c r="D45">
-        <v>1647</v>
+        <v>893</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46136.45833333334</v>
       </c>
       <c r="B46">
-        <v>669</v>
+        <v>123</v>
       </c>
       <c r="C46">
-        <v>984</v>
+        <v>764</v>
       </c>
       <c r="D46">
-        <v>1653</v>
+        <v>887</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46136.46875</v>
       </c>
       <c r="B47">
-        <v>677</v>
+        <v>141</v>
       </c>
       <c r="C47">
-        <v>988</v>
+        <v>760</v>
       </c>
       <c r="D47">
-        <v>1665</v>
+        <v>901</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46136.47916666666</v>
       </c>
       <c r="B48">
-        <v>678</v>
+        <v>173</v>
       </c>
       <c r="C48">
-        <v>977</v>
+        <v>762</v>
       </c>
       <c r="D48">
-        <v>1655</v>
+        <v>935</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46136.48958333334</v>
       </c>
       <c r="B49">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>986</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1647</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46136.5</v>
       </c>
       <c r="B50">
-        <v>608</v>
+        <v>286</v>
       </c>
       <c r="C50">
-        <v>990</v>
+        <v>701</v>
       </c>
       <c r="D50">
-        <v>1598</v>
+        <v>987</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46136.51041666666</v>
       </c>
       <c r="B51">
-        <v>672</v>
+        <v>281</v>
       </c>
       <c r="C51">
-        <v>981</v>
+        <v>702</v>
       </c>
       <c r="D51">
-        <v>1653</v>
+        <v>983</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46136.52083333334</v>
       </c>
       <c r="B52">
-        <v>530</v>
+        <v>271</v>
       </c>
       <c r="C52">
-        <v>968</v>
+        <v>700</v>
       </c>
       <c r="D52">
-        <v>1498</v>
+        <v>971</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46136.53125</v>
       </c>
       <c r="B53">
-        <v>549</v>
+        <v>269</v>
       </c>
       <c r="C53">
-        <v>966</v>
+        <v>699</v>
       </c>
       <c r="D53">
-        <v>1515</v>
+        <v>968</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46136.54166666666</v>
       </c>
       <c r="B54">
-        <v>587</v>
+        <v>128</v>
       </c>
       <c r="C54">
-        <v>950</v>
+        <v>704</v>
       </c>
       <c r="D54">
-        <v>1537</v>
+        <v>832</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="B55">
-        <v>557</v>
+        <v>129</v>
       </c>
       <c r="C55">
-        <v>947</v>
+        <v>675</v>
       </c>
       <c r="D55">
-        <v>1504</v>
+        <v>804</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46136.5625</v>
       </c>
       <c r="B56">
-        <v>600</v>
+        <v>128</v>
       </c>
       <c r="C56">
-        <v>965</v>
+        <v>674</v>
       </c>
       <c r="D56">
-        <v>1565</v>
+        <v>802</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46136.57291666666</v>
       </c>
       <c r="B57">
-        <v>613</v>
+        <v>126</v>
       </c>
       <c r="C57">
-        <v>966</v>
+        <v>675</v>
       </c>
       <c r="D57">
-        <v>1579</v>
+        <v>801</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46136.58333333334</v>
       </c>
       <c r="B58">
-        <v>614</v>
+        <v>132</v>
       </c>
       <c r="C58">
-        <v>949</v>
+        <v>706</v>
       </c>
       <c r="D58">
-        <v>1563</v>
+        <v>838</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46136.59375</v>
       </c>
       <c r="B59">
-        <v>574</v>
+        <v>134</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>574</v>
+        <v>134</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46136.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="C60">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>947</v>
+        <v>131</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46136.61458333334</v>
       </c>
       <c r="B61">
-        <v>577</v>
+        <v>127</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="D61">
-        <v>577</v>
+        <v>835</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46136.625</v>
       </c>
       <c r="B62">
-        <v>606</v>
+        <v>138</v>
       </c>
       <c r="C62">
-        <v>964</v>
+        <v>760</v>
       </c>
       <c r="D62">
-        <v>1570</v>
+        <v>898</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46136.63541666666</v>
       </c>
       <c r="B63">
-        <v>611</v>
+        <v>125</v>
       </c>
       <c r="C63">
-        <v>966</v>
+        <v>762</v>
       </c>
       <c r="D63">
-        <v>1577</v>
+        <v>887</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46136.64583333334</v>
       </c>
       <c r="B64">
-        <v>609</v>
+        <v>146</v>
       </c>
       <c r="C64">
-        <v>956</v>
+        <v>770</v>
       </c>
       <c r="D64">
-        <v>1565</v>
+        <v>916</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46136.65625</v>
       </c>
       <c r="B65">
-        <v>633</v>
+        <v>138</v>
       </c>
       <c r="C65">
-        <v>960</v>
+        <v>781</v>
       </c>
       <c r="D65">
-        <v>1593</v>
+        <v>919</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46136.66666666666</v>
       </c>
       <c r="B66">
-        <v>749</v>
+        <v>178</v>
       </c>
       <c r="C66">
-        <v>1110</v>
+        <v>900</v>
       </c>
       <c r="D66">
-        <v>1859</v>
+        <v>1078</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46136.67708333334</v>
       </c>
       <c r="B67">
-        <v>750</v>
+        <v>181</v>
       </c>
       <c r="C67">
-        <v>1116</v>
+        <v>923</v>
       </c>
       <c r="D67">
-        <v>1866</v>
+        <v>1104</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46136.6875</v>
       </c>
       <c r="B68">
-        <v>759</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>1115</v>
+        <v>926</v>
       </c>
       <c r="D68">
-        <v>1874</v>
+        <v>926</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46136.69791666666</v>
       </c>
       <c r="B69">
-        <v>796</v>
+        <v>201</v>
       </c>
       <c r="C69">
-        <v>1122</v>
+        <v>795</v>
       </c>
       <c r="D69">
-        <v>1918</v>
+        <v>996</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="B70">
-        <v>958</v>
+        <v>370</v>
       </c>
       <c r="C70">
-        <v>1139</v>
+        <v>987</v>
       </c>
       <c r="D70">
-        <v>2097</v>
+        <v>1357</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46136.71875</v>
       </c>
       <c r="B71">
-        <v>1033</v>
+        <v>388</v>
       </c>
       <c r="C71">
-        <v>1143</v>
+        <v>1003</v>
       </c>
       <c r="D71">
-        <v>2176</v>
+        <v>1391</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46136.72916666666</v>
       </c>
       <c r="B72">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1145</v>
+        <v>1094</v>
       </c>
       <c r="D72">
-        <v>2176</v>
+        <v>1094</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46136.73958333334</v>
       </c>
       <c r="B73">
-        <v>1045</v>
+        <v>410</v>
       </c>
       <c r="C73">
-        <v>1143</v>
+        <v>1117</v>
       </c>
       <c r="D73">
-        <v>2188</v>
+        <v>1527</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46136.75</v>
       </c>
       <c r="B74">
-        <v>1175</v>
+        <v>864</v>
       </c>
       <c r="C74">
-        <v>1188</v>
+        <v>1327</v>
       </c>
       <c r="D74">
-        <v>2363</v>
+        <v>2191</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B75">
-        <v>1206</v>
+        <v>894</v>
       </c>
       <c r="C75">
-        <v>1198</v>
+        <v>1339</v>
       </c>
       <c r="D75">
-        <v>2404</v>
+        <v>2233</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="B76">
-        <v>1189</v>
+        <v>998</v>
       </c>
       <c r="C76">
-        <v>1186</v>
+        <v>1375</v>
       </c>
       <c r="D76">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46136.78125</v>
       </c>
       <c r="B77">
-        <v>1221</v>
+        <v>997</v>
       </c>
       <c r="C77">
-        <v>1183</v>
+        <v>1395</v>
       </c>
       <c r="D77">
-        <v>2404</v>
+        <v>2392</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46136.79166666666</v>
       </c>
       <c r="B78">
-        <v>1173</v>
+        <v>993</v>
       </c>
       <c r="C78">
-        <v>1185</v>
+        <v>1483</v>
       </c>
       <c r="D78">
-        <v>2358</v>
+        <v>2476</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46136.80208333334</v>
       </c>
       <c r="B79">
-        <v>1205</v>
+        <v>1002</v>
       </c>
       <c r="C79">
-        <v>1186</v>
+        <v>1496</v>
       </c>
       <c r="D79">
-        <v>2391</v>
+        <v>2498</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46136.8125</v>
       </c>
       <c r="B80">
-        <v>1207</v>
+        <v>995</v>
       </c>
       <c r="C80">
-        <v>1203</v>
+        <v>1487</v>
       </c>
       <c r="D80">
-        <v>2410</v>
+        <v>2482</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46136.82291666666</v>
       </c>
       <c r="B81">
-        <v>1210</v>
+        <v>998</v>
       </c>
       <c r="C81">
-        <v>1204</v>
+        <v>1490</v>
       </c>
       <c r="D81">
-        <v>2414</v>
+        <v>2488</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46136.83333333334</v>
       </c>
       <c r="B82">
-        <v>1182</v>
+        <v>958</v>
       </c>
       <c r="C82">
-        <v>1220</v>
+        <v>1483</v>
       </c>
       <c r="D82">
-        <v>2402</v>
+        <v>2441</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46136.84375</v>
       </c>
       <c r="B83">
-        <v>1169</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>1156</v>
+        <v>1482</v>
       </c>
       <c r="D83">
-        <v>2325</v>
+        <v>1482</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46136.85416666666</v>
       </c>
       <c r="B84">
-        <v>1178</v>
+        <v>951</v>
       </c>
       <c r="C84">
-        <v>1142</v>
+        <v>1481</v>
       </c>
       <c r="D84">
-        <v>2320</v>
+        <v>2432</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46136.86458333334</v>
       </c>
       <c r="B85">
-        <v>1177</v>
+        <v>950</v>
       </c>
       <c r="C85">
-        <v>1139</v>
+        <v>1483</v>
       </c>
       <c r="D85">
-        <v>2316</v>
+        <v>2433</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46136.875</v>
       </c>
       <c r="B86">
-        <v>1109</v>
+        <v>854</v>
       </c>
       <c r="C86">
-        <v>1131</v>
+        <v>1422</v>
       </c>
       <c r="D86">
-        <v>2240</v>
+        <v>2276</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46136.88541666666</v>
       </c>
       <c r="B87">
-        <v>1090</v>
+        <v>849</v>
       </c>
       <c r="C87">
-        <v>1122</v>
+        <v>1414</v>
       </c>
       <c r="D87">
-        <v>2212</v>
+        <v>2263</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46136.89583333334</v>
       </c>
       <c r="B88">
-        <v>1068</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="D88">
-        <v>1068</v>
+        <v>1416</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46136.90625</v>
       </c>
       <c r="B89">
-        <v>1069</v>
+        <v>844</v>
       </c>
       <c r="C89">
-        <v>1117</v>
+        <v>1411</v>
       </c>
       <c r="D89">
-        <v>2186</v>
+        <v>2255</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46136.91666666666</v>
       </c>
       <c r="B90">
-        <v>967</v>
+        <v>721</v>
       </c>
       <c r="C90">
-        <v>1092</v>
+        <v>1383</v>
       </c>
       <c r="D90">
-        <v>2059</v>
+        <v>2104</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46136.92708333334</v>
       </c>
       <c r="B91">
-        <v>939</v>
+        <v>693</v>
       </c>
       <c r="C91">
-        <v>1085</v>
+        <v>1382</v>
       </c>
       <c r="D91">
-        <v>2024</v>
+        <v>2075</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46136.9375</v>
       </c>
       <c r="B92">
-        <v>931</v>
+        <v>685</v>
       </c>
       <c r="C92">
-        <v>1081</v>
+        <v>1354</v>
       </c>
       <c r="D92">
-        <v>2012</v>
+        <v>2039</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46136.94791666666</v>
       </c>
       <c r="B93">
-        <v>932</v>
+        <v>682</v>
       </c>
       <c r="C93">
-        <v>1083</v>
+        <v>1350</v>
       </c>
       <c r="D93">
-        <v>2015</v>
+        <v>2032</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46136.95833333334</v>
       </c>
       <c r="B94">
-        <v>839</v>
+        <v>500</v>
       </c>
       <c r="C94">
-        <v>1089</v>
+        <v>1416</v>
       </c>
       <c r="D94">
-        <v>1928</v>
+        <v>1916</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46136.96875</v>
       </c>
       <c r="B95">
-        <v>840</v>
+        <v>496</v>
       </c>
       <c r="C95">
-        <v>1091</v>
+        <v>1392</v>
       </c>
       <c r="D95">
-        <v>1931</v>
+        <v>1888</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46136.97916666666</v>
       </c>
       <c r="B96">
-        <v>843</v>
+        <v>492</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>843</v>
+        <v>492</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46136.98958333334</v>
       </c>
       <c r="B97">
-        <v>842</v>
+        <v>489</v>
       </c>
       <c r="C97">
-        <v>1090</v>
+        <v>1389</v>
       </c>
       <c r="D97">
-        <v>1932</v>
+        <v>1878</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B98">
-        <v>797</v>
+        <v>490</v>
       </c>
       <c r="C98">
-        <v>1024</v>
+        <v>1423</v>
       </c>
       <c r="D98">
-        <v>1821</v>
+        <v>1913</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46134.01041666666</v>
+        <v>46137.01041666666</v>
       </c>
       <c r="B99">
-        <v>794</v>
+        <v>477</v>
       </c>
       <c r="C99">
-        <v>1020</v>
+        <v>1406</v>
       </c>
       <c r="D99">
-        <v>1814</v>
+        <v>1883</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46134.02083333334</v>
+        <v>46137.02083333334</v>
       </c>
       <c r="B100">
-        <v>795</v>
+        <v>481</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1411</v>
       </c>
       <c r="D100">
-        <v>795</v>
+        <v>1892</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46134.03125</v>
+        <v>46137.03125</v>
       </c>
       <c r="B101">
-        <v>792</v>
+        <v>478</v>
       </c>
       <c r="C101">
-        <v>1019</v>
+        <v>1409</v>
       </c>
       <c r="D101">
-        <v>1811</v>
+        <v>1887</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46134.04166666666</v>
+        <v>46137.04166666666</v>
       </c>
       <c r="B102">
-        <v>783</v>
+        <v>276</v>
       </c>
       <c r="C102">
-        <v>973</v>
+        <v>1335</v>
       </c>
       <c r="D102">
-        <v>1756</v>
+        <v>1611</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46134.05208333334</v>
+        <v>46137.05208333334</v>
       </c>
       <c r="B103">
-        <v>792</v>
+        <v>271</v>
       </c>
       <c r="C103">
-        <v>970</v>
+        <v>1330</v>
       </c>
       <c r="D103">
-        <v>1762</v>
+        <v>1601</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46134.0625</v>
+        <v>46137.0625</v>
       </c>
       <c r="B104">
-        <v>791</v>
+        <v>270</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="D104">
-        <v>791</v>
+        <v>1612</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46134.07291666666</v>
+        <v>46137.07291666666</v>
       </c>
       <c r="B105">
-        <v>775</v>
+        <v>268</v>
       </c>
       <c r="C105">
-        <v>969</v>
+        <v>1343</v>
       </c>
       <c r="D105">
-        <v>1744</v>
+        <v>1611</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46134.08333333334</v>
+        <v>46137.08333333334</v>
       </c>
       <c r="B106">
-        <v>778</v>
+        <v>272</v>
       </c>
       <c r="C106">
-        <v>958</v>
+        <v>1208</v>
       </c>
       <c r="D106">
-        <v>1736</v>
+        <v>1480</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46134.09375</v>
+        <v>46137.09375</v>
       </c>
       <c r="B107">
-        <v>779</v>
+        <v>267</v>
       </c>
       <c r="C107">
-        <v>957</v>
+        <v>1195</v>
       </c>
       <c r="D107">
-        <v>1736</v>
+        <v>1462</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46134.10416666666</v>
+        <v>46137.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="C108">
-        <v>956</v>
+        <v>1197</v>
       </c>
       <c r="D108">
-        <v>956</v>
+        <v>1465</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46134.11458333334</v>
+        <v>46137.11458333334</v>
       </c>
       <c r="B109">
-        <v>778</v>
+        <v>266</v>
       </c>
       <c r="C109">
-        <v>955</v>
+        <v>1196</v>
       </c>
       <c r="D109">
-        <v>1733</v>
+        <v>1462</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46134.125</v>
+        <v>46137.125</v>
       </c>
       <c r="B110">
-        <v>700</v>
+        <v>269</v>
       </c>
       <c r="C110">
-        <v>963</v>
+        <v>1168</v>
       </c>
       <c r="D110">
-        <v>1663</v>
+        <v>1437</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46134.13541666666</v>
+        <v>46137.13541666666</v>
       </c>
       <c r="B111">
-        <v>697</v>
+        <v>267</v>
       </c>
       <c r="C111">
-        <v>964</v>
+        <v>1166</v>
       </c>
       <c r="D111">
-        <v>1661</v>
+        <v>1433</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46134.14583333334</v>
+        <v>46137.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46134.15625</v>
+        <v>46137.15625</v>
       </c>
       <c r="B113">
-        <v>700</v>
+        <v>277</v>
       </c>
       <c r="C113">
-        <v>963</v>
+        <v>1166</v>
       </c>
       <c r="D113">
-        <v>1663</v>
+        <v>1443</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46134.16666666666</v>
+        <v>46137.16666666666</v>
       </c>
       <c r="B114">
-        <v>790</v>
+        <v>410</v>
       </c>
       <c r="C114">
-        <v>930</v>
+        <v>1227</v>
       </c>
       <c r="D114">
-        <v>1720</v>
+        <v>1637</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46134.17708333334</v>
+        <v>46137.17708333334</v>
       </c>
       <c r="B115">
-        <v>789</v>
+        <v>421</v>
       </c>
       <c r="C115">
-        <v>933</v>
+        <v>1230</v>
       </c>
       <c r="D115">
-        <v>1722</v>
+        <v>1651</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46134.1875</v>
+        <v>46137.1875</v>
       </c>
       <c r="B116">
-        <v>788</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>1231</v>
       </c>
       <c r="D116">
-        <v>788</v>
+        <v>1231</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46134.19791666666</v>
+        <v>46137.19791666666</v>
       </c>
       <c r="B117">
-        <v>796</v>
+        <v>430</v>
       </c>
       <c r="C117">
-        <v>932</v>
+        <v>1234</v>
       </c>
       <c r="D117">
-        <v>1728</v>
+        <v>1664</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46134.20833333334</v>
+        <v>46137.20833333334</v>
       </c>
       <c r="B118">
-        <v>842</v>
+        <v>534</v>
       </c>
       <c r="C118">
-        <v>1000</v>
+        <v>1348</v>
       </c>
       <c r="D118">
-        <v>1842</v>
+        <v>1882</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46134.21875</v>
+        <v>46137.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="C119">
-        <v>1005</v>
+        <v>1350</v>
       </c>
       <c r="D119">
-        <v>1005</v>
+        <v>1893</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46134.22916666666</v>
+        <v>46137.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1351</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46134.23958333334</v>
+        <v>46137.23958333334</v>
       </c>
       <c r="B121">
-        <v>843</v>
+        <v>533</v>
       </c>
       <c r="C121">
-        <v>1008</v>
+        <v>1359</v>
       </c>
       <c r="D121">
-        <v>1851</v>
+        <v>1892</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46134.25</v>
+        <v>46137.25</v>
       </c>
       <c r="B122">
-        <v>948</v>
+        <v>460</v>
       </c>
       <c r="C122">
-        <v>1069</v>
+        <v>1245</v>
       </c>
       <c r="D122">
-        <v>2017</v>
+        <v>1705</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46134.26041666666</v>
+        <v>46137.26041666666</v>
       </c>
       <c r="B123">
-        <v>969</v>
+        <v>455</v>
       </c>
       <c r="C123">
-        <v>1056</v>
+        <v>1243</v>
       </c>
       <c r="D123">
-        <v>2025</v>
+        <v>1698</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46134.27083333334</v>
+        <v>46137.27083333334</v>
       </c>
       <c r="B124">
-        <v>973</v>
+        <v>450</v>
       </c>
       <c r="C124">
-        <v>1057</v>
+        <v>1240</v>
       </c>
       <c r="D124">
-        <v>2030</v>
+        <v>1690</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46134.28125</v>
+        <v>46137.28125</v>
       </c>
       <c r="B125">
-        <v>976</v>
+        <v>451</v>
       </c>
       <c r="C125">
-        <v>1058</v>
+        <v>1243</v>
       </c>
       <c r="D125">
-        <v>2034</v>
+        <v>1694</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46134.29166666666</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="B126">
-        <v>944</v>
+        <v>329</v>
       </c>
       <c r="C126">
-        <v>1095</v>
+        <v>1158</v>
       </c>
       <c r="D126">
-        <v>2039</v>
+        <v>1487</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46134.30208333334</v>
+        <v>46137.30208333334</v>
       </c>
       <c r="B127">
-        <v>932</v>
+        <v>317</v>
       </c>
       <c r="C127">
-        <v>1105</v>
+        <v>1161</v>
       </c>
       <c r="D127">
-        <v>2037</v>
+        <v>1478</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46134.3125</v>
+        <v>46137.3125</v>
       </c>
       <c r="B128">
-        <v>926</v>
+        <v>322</v>
       </c>
       <c r="C128">
-        <v>1108</v>
+        <v>1162</v>
       </c>
       <c r="D128">
-        <v>2034</v>
+        <v>1484</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46134.32291666666</v>
+        <v>46137.32291666666</v>
       </c>
       <c r="B129">
-        <v>889</v>
+        <v>329</v>
       </c>
       <c r="C129">
-        <v>1109</v>
+        <v>1163</v>
       </c>
       <c r="D129">
-        <v>1998</v>
+        <v>1492</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46134.33333333334</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="B130">
-        <v>650</v>
+        <v>228</v>
       </c>
       <c r="C130">
-        <v>1085</v>
+        <v>1054</v>
       </c>
       <c r="D130">
-        <v>1735</v>
+        <v>1282</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46134.34375</v>
+        <v>46137.34375</v>
       </c>
       <c r="B131">
-        <v>645</v>
+        <v>220</v>
       </c>
       <c r="C131">
-        <v>1087</v>
+        <v>1048</v>
       </c>
       <c r="D131">
-        <v>1732</v>
+        <v>1268</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46134.35416666666</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="B132">
-        <v>553</v>
+        <v>201</v>
       </c>
       <c r="C132">
-        <v>1090</v>
+        <v>1046</v>
       </c>
       <c r="D132">
-        <v>1643</v>
+        <v>1247</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46134.36458333334</v>
+        <v>46137.36458333334</v>
       </c>
       <c r="B133">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>1080</v>
+        <v>1049</v>
       </c>
       <c r="D133">
-        <v>1714</v>
+        <v>1049</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46134.375</v>
+        <v>46137.375</v>
       </c>
       <c r="B134">
-        <v>516</v>
+        <v>136</v>
       </c>
       <c r="C134">
-        <v>989</v>
+        <v>904</v>
       </c>
       <c r="D134">
-        <v>1505</v>
+        <v>1040</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46134.38541666666</v>
+        <v>46137.38541666666</v>
       </c>
       <c r="B135">
-        <v>577</v>
+        <v>133</v>
       </c>
       <c r="C135">
-        <v>998</v>
+        <v>891</v>
       </c>
       <c r="D135">
-        <v>1575</v>
+        <v>1024</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46134.39583333334</v>
+        <v>46137.39583333334</v>
       </c>
       <c r="B136">
-        <v>574</v>
+        <v>130</v>
       </c>
       <c r="C136">
-        <v>1001</v>
+        <v>884</v>
       </c>
       <c r="D136">
-        <v>1575</v>
+        <v>1014</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46134.40625</v>
+        <v>46137.40625</v>
       </c>
       <c r="B137">
-        <v>593</v>
+        <v>133</v>
       </c>
       <c r="C137">
-        <v>1003</v>
+        <v>713</v>
       </c>
       <c r="D137">
-        <v>1596</v>
+        <v>846</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46134.41666666666</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="B138">
-        <v>540</v>
+        <v>146</v>
       </c>
       <c r="C138">
-        <v>927</v>
+        <v>622</v>
       </c>
       <c r="D138">
-        <v>1467</v>
+        <v>768</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46134.42708333334</v>
+        <v>46137.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>616</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46134.4375</v>
+        <v>46137.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46134.44791666666</v>
+        <v>46137.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46134.45833333334</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +4390,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46134.46875</v>
+        <v>46137.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46134.47916666666</v>
+        <v>46137.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>747</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46134.48958333334</v>
+        <v>46137.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>754</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46134.5</v>
+        <v>46137.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46134.51041666666</v>
+        <v>46137.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46134.52083333334</v>
+        <v>46137.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46134.53125</v>
+        <v>46137.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46134.54166666666</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>842</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46134.55208333334</v>
+        <v>46137.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46134.5625</v>
+        <v>46137.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="C152">
         <v>0</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46134.57291666666</v>
+        <v>46137.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4610,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46134.58333333334</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4630,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46134.59375</v>
+        <v>46137.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>738</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,16 +4650,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46134.60416666666</v>
+        <v>46137.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4094,16 +4670,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46134.61458333334</v>
+        <v>46137.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46134.625</v>
+        <v>46137.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46134.63541666666</v>
+        <v>46137.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46134.64583333334</v>
+        <v>46137.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="C160">
         <v>0</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46134.65625</v>
+        <v>46137.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46134.66666666666</v>
+        <v>46137.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46134.67708333334</v>
+        <v>46137.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46134.6875</v>
+        <v>46137.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="C164">
         <v>0</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46134.69791666666</v>
+        <v>46137.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>783</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46134.70833333334</v>
+        <v>46137.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1083</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1412</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46134.71875</v>
+        <v>46137.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1457</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,16 +4890,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46134.72916666666</v>
+        <v>46137.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4334,16 +4910,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46134.73958333334</v>
+        <v>46137.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1216</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46134.75</v>
+        <v>46137.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1381</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>2176</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46134.76041666666</v>
+        <v>46137.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1406</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>2206</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46134.77083333334</v>
+        <v>46137.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1401</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2194</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46134.78125</v>
+        <v>46137.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>2212</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46134.79166666666</v>
+        <v>46137.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1403</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>2202</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46134.80208333334</v>
+        <v>46137.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1415</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46134.8125</v>
+        <v>46137.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>2244</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46134.82291666666</v>
+        <v>46137.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1434</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>2260</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46134.83333333334</v>
+        <v>46137.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1403</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>2193</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46134.84375</v>
+        <v>46137.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1398</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>2173</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46134.85416666666</v>
+        <v>46137.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>2165</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46134.86458333334</v>
+        <v>46137.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1396</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>2165</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46134.875</v>
+        <v>46137.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1414</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>2102</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46134.88541666666</v>
+        <v>46137.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>2116</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46134.89583333334</v>
+        <v>46137.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1428</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46134.90625</v>
+        <v>46137.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46134.91666666666</v>
+        <v>46137.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1436</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>2034</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46134.92708333334</v>
+        <v>46137.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1433</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46134.9375</v>
+        <v>46137.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1445</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>2039</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46134.94791666666</v>
+        <v>46137.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1442</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>2031</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46134.95833333334</v>
+        <v>46137.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>1984</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46134.96875</v>
+        <v>46137.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1497</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46134.97916666666</v>
+        <v>46137.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1501</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1979</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,22 +5390,3862 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46134.98958333334</v>
+        <v>46137.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>1971</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B194">
+        <v>320</v>
+      </c>
+      <c r="C194">
+        <v>1471</v>
+      </c>
+      <c r="D194">
+        <v>1791</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46138.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>319</v>
+      </c>
+      <c r="C195">
+        <v>1465</v>
+      </c>
+      <c r="D195">
+        <v>1784</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46138.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>318</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>318</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46138.03125</v>
+      </c>
+      <c r="B197">
+        <v>317</v>
+      </c>
+      <c r="C197">
+        <v>1466</v>
+      </c>
+      <c r="D197">
+        <v>1783</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46138.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>173</v>
+      </c>
+      <c r="C198">
+        <v>1390</v>
+      </c>
+      <c r="D198">
+        <v>1563</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46138.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>162</v>
+      </c>
+      <c r="C199">
+        <v>1377</v>
+      </c>
+      <c r="D199">
+        <v>1539</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46138.0625</v>
+      </c>
+      <c r="B200">
+        <v>174</v>
+      </c>
+      <c r="C200">
+        <v>1378</v>
+      </c>
+      <c r="D200">
+        <v>1552</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46138.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>158</v>
+      </c>
+      <c r="C201">
+        <v>1377</v>
+      </c>
+      <c r="D201">
+        <v>1535</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46138.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>141</v>
+      </c>
+      <c r="C202">
+        <v>1230</v>
+      </c>
+      <c r="D202">
+        <v>1371</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46138.09375</v>
+      </c>
+      <c r="B203">
+        <v>140</v>
+      </c>
+      <c r="C203">
+        <v>1184</v>
+      </c>
+      <c r="D203">
+        <v>1324</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46138.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>141</v>
+      </c>
+      <c r="C204">
+        <v>1188</v>
+      </c>
+      <c r="D204">
+        <v>1329</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46138.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>139</v>
+      </c>
+      <c r="C205">
+        <v>1185</v>
+      </c>
+      <c r="D205">
+        <v>1324</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46138.125</v>
+      </c>
+      <c r="B206">
+        <v>138</v>
+      </c>
+      <c r="C206">
+        <v>1202</v>
+      </c>
+      <c r="D206">
+        <v>1340</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46138.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>128</v>
+      </c>
+      <c r="C207">
+        <v>1201</v>
+      </c>
+      <c r="D207">
+        <v>1329</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46138.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>118</v>
+      </c>
+      <c r="C208">
+        <v>1195</v>
+      </c>
+      <c r="D208">
+        <v>1313</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46138.15625</v>
+      </c>
+      <c r="B209">
+        <v>125</v>
+      </c>
+      <c r="C209">
+        <v>1186</v>
+      </c>
+      <c r="D209">
+        <v>1311</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46138.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>121</v>
+      </c>
+      <c r="C210">
+        <v>1181</v>
+      </c>
+      <c r="D210">
+        <v>1302</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46138.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>120</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>120</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46138.1875</v>
+      </c>
+      <c r="B212">
+        <v>119</v>
+      </c>
+      <c r="C212">
+        <v>1182</v>
+      </c>
+      <c r="D212">
+        <v>1301</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46138.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>123</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>123</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46138.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>172</v>
+      </c>
+      <c r="C214">
+        <v>1141</v>
+      </c>
+      <c r="D214">
+        <v>1313</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46138.21875</v>
+      </c>
+      <c r="B215">
+        <v>178</v>
+      </c>
+      <c r="C215">
+        <v>1138</v>
+      </c>
+      <c r="D215">
+        <v>1316</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46138.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>184</v>
+      </c>
+      <c r="C216">
+        <v>1140</v>
+      </c>
+      <c r="D216">
+        <v>1324</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46138.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>185</v>
+      </c>
+      <c r="C217">
+        <v>1139</v>
+      </c>
+      <c r="D217">
+        <v>1324</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46138.25</v>
+      </c>
+      <c r="B218">
+        <v>191</v>
+      </c>
+      <c r="C218">
+        <v>1203</v>
+      </c>
+      <c r="D218">
+        <v>1394</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46138.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>189</v>
+      </c>
+      <c r="C219">
+        <v>1194</v>
+      </c>
+      <c r="D219">
+        <v>1383</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46138.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>188</v>
+      </c>
+      <c r="C220">
+        <v>1188</v>
+      </c>
+      <c r="D220">
+        <v>1376</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46138.28125</v>
+      </c>
+      <c r="B221">
+        <v>190</v>
+      </c>
+      <c r="C221">
+        <v>1189</v>
+      </c>
+      <c r="D221">
+        <v>1379</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46138.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>205</v>
+      </c>
+      <c r="C222">
+        <v>1163</v>
+      </c>
+      <c r="D222">
+        <v>1368</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46138.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>207</v>
+      </c>
+      <c r="C223">
+        <v>1162</v>
+      </c>
+      <c r="D223">
+        <v>1369</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46138.3125</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>1165</v>
+      </c>
+      <c r="D224">
+        <v>1165</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46138.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>205</v>
+      </c>
+      <c r="C225">
+        <v>1180</v>
+      </c>
+      <c r="D225">
+        <v>1385</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>168</v>
+      </c>
+      <c r="C226">
+        <v>904</v>
+      </c>
+      <c r="D226">
+        <v>1072</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46138.34375</v>
+      </c>
+      <c r="B227">
+        <v>151</v>
+      </c>
+      <c r="C227">
+        <v>844</v>
+      </c>
+      <c r="D227">
+        <v>995</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46138.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>131</v>
+      </c>
+      <c r="C228">
+        <v>847</v>
+      </c>
+      <c r="D228">
+        <v>978</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46138.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>187</v>
+      </c>
+      <c r="C229">
+        <v>926</v>
+      </c>
+      <c r="D229">
+        <v>1113</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46138.375</v>
+      </c>
+      <c r="B230">
+        <v>198</v>
+      </c>
+      <c r="C230">
+        <v>908</v>
+      </c>
+      <c r="D230">
+        <v>1106</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46138.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>180</v>
+      </c>
+      <c r="C231">
+        <v>903</v>
+      </c>
+      <c r="D231">
+        <v>1083</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46138.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>175</v>
+      </c>
+      <c r="C232">
+        <v>890</v>
+      </c>
+      <c r="D232">
+        <v>1065</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46138.40625</v>
+      </c>
+      <c r="B233">
+        <v>112</v>
+      </c>
+      <c r="C233">
+        <v>861</v>
+      </c>
+      <c r="D233">
+        <v>973</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>110</v>
+      </c>
+      <c r="C234">
+        <v>767</v>
+      </c>
+      <c r="D234">
+        <v>877</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46138.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>108</v>
+      </c>
+      <c r="C235">
+        <v>750</v>
+      </c>
+      <c r="D235">
+        <v>858</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46138.4375</v>
+      </c>
+      <c r="B236">
+        <v>109</v>
+      </c>
+      <c r="C236">
+        <v>722</v>
+      </c>
+      <c r="D236">
+        <v>831</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46138.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>108</v>
+      </c>
+      <c r="C237">
+        <v>647</v>
+      </c>
+      <c r="D237">
+        <v>755</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46138.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>98</v>
+      </c>
+      <c r="C238">
+        <v>614</v>
+      </c>
+      <c r="D238">
+        <v>712</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46138.46875</v>
+      </c>
+      <c r="B239">
+        <v>97</v>
+      </c>
+      <c r="C239">
+        <v>608</v>
+      </c>
+      <c r="D239">
+        <v>705</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46138.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>77</v>
+      </c>
+      <c r="C240">
+        <v>620</v>
+      </c>
+      <c r="D240">
+        <v>697</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46138.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>76</v>
+      </c>
+      <c r="C241">
+        <v>628</v>
+      </c>
+      <c r="D241">
+        <v>704</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46138.5</v>
+      </c>
+      <c r="B242">
+        <v>84</v>
+      </c>
+      <c r="C242">
+        <v>625</v>
+      </c>
+      <c r="D242">
+        <v>709</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46138.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>95</v>
+      </c>
+      <c r="C243">
+        <v>613</v>
+      </c>
+      <c r="D243">
+        <v>708</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46138.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>555</v>
+      </c>
+      <c r="D244">
+        <v>555</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46138.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>466</v>
+      </c>
+      <c r="D245">
+        <v>466</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46138.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>91</v>
+      </c>
+      <c r="C246">
+        <v>460</v>
+      </c>
+      <c r="D246">
+        <v>551</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46138.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>465</v>
+      </c>
+      <c r="D247">
+        <v>465</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46138.5625</v>
+      </c>
+      <c r="B248">
+        <v>89</v>
+      </c>
+      <c r="C248">
+        <v>467</v>
+      </c>
+      <c r="D248">
+        <v>556</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46138.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>91</v>
+      </c>
+      <c r="C249">
+        <v>468</v>
+      </c>
+      <c r="D249">
+        <v>559</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>98</v>
+      </c>
+      <c r="C250">
+        <v>471</v>
+      </c>
+      <c r="D250">
+        <v>569</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46138.59375</v>
+      </c>
+      <c r="B251">
+        <v>102</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>102</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46138.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>98</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>98</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46138.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>99</v>
+      </c>
+      <c r="C253">
+        <v>472</v>
+      </c>
+      <c r="D253">
+        <v>571</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46138.625</v>
+      </c>
+      <c r="B254">
+        <v>97</v>
+      </c>
+      <c r="C254">
+        <v>445</v>
+      </c>
+      <c r="D254">
+        <v>542</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46138.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>95</v>
+      </c>
+      <c r="C255">
+        <v>443</v>
+      </c>
+      <c r="D255">
+        <v>538</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46138.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>123</v>
+      </c>
+      <c r="C256">
+        <v>488</v>
+      </c>
+      <c r="D256">
+        <v>611</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46138.65625</v>
+      </c>
+      <c r="B257">
+        <v>114</v>
+      </c>
+      <c r="C257">
+        <v>494</v>
+      </c>
+      <c r="D257">
+        <v>608</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46138.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>102</v>
+      </c>
+      <c r="C258">
+        <v>536</v>
+      </c>
+      <c r="D258">
+        <v>638</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46138.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>96</v>
+      </c>
+      <c r="C259">
+        <v>625</v>
+      </c>
+      <c r="D259">
+        <v>721</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46138.6875</v>
+      </c>
+      <c r="B260">
+        <v>89</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>89</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46138.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>101</v>
+      </c>
+      <c r="C261">
+        <v>636</v>
+      </c>
+      <c r="D261">
+        <v>737</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46138.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>192</v>
+      </c>
+      <c r="C262">
+        <v>958</v>
+      </c>
+      <c r="D262">
+        <v>1150</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46138.71875</v>
+      </c>
+      <c r="B263">
+        <v>225</v>
+      </c>
+      <c r="C263">
+        <v>925</v>
+      </c>
+      <c r="D263">
+        <v>1150</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46138.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>249</v>
+      </c>
+      <c r="C264">
+        <v>920</v>
+      </c>
+      <c r="D264">
+        <v>1169</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46138.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>263</v>
+      </c>
+      <c r="C265">
+        <v>1031</v>
+      </c>
+      <c r="D265">
+        <v>1294</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46138.75</v>
+      </c>
+      <c r="B266">
+        <v>390</v>
+      </c>
+      <c r="C266">
+        <v>1111</v>
+      </c>
+      <c r="D266">
+        <v>1501</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46138.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>437</v>
+      </c>
+      <c r="C267">
+        <v>1132</v>
+      </c>
+      <c r="D267">
+        <v>1569</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46138.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>403</v>
+      </c>
+      <c r="C268">
+        <v>1227</v>
+      </c>
+      <c r="D268">
+        <v>1630</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46138.78125</v>
+      </c>
+      <c r="B269">
+        <v>419</v>
+      </c>
+      <c r="C269">
+        <v>1235</v>
+      </c>
+      <c r="D269">
+        <v>1654</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46138.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>472</v>
+      </c>
+      <c r="C270">
+        <v>1372</v>
+      </c>
+      <c r="D270">
+        <v>1844</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46138.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>474</v>
+      </c>
+      <c r="C271">
+        <v>1385</v>
+      </c>
+      <c r="D271">
+        <v>1859</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46138.8125</v>
+      </c>
+      <c r="B272">
+        <v>491</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>491</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46138.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>530</v>
+      </c>
+      <c r="C273">
+        <v>1392</v>
+      </c>
+      <c r="D273">
+        <v>1922</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46138.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>747</v>
+      </c>
+      <c r="C274">
+        <v>1468</v>
+      </c>
+      <c r="D274">
+        <v>2215</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46138.84375</v>
+      </c>
+      <c r="B275">
+        <v>772</v>
+      </c>
+      <c r="C275">
+        <v>1474</v>
+      </c>
+      <c r="D275">
+        <v>2246</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46138.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>776</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>776</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46138.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>780</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>780</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46138.875</v>
+      </c>
+      <c r="B278">
+        <v>797</v>
+      </c>
+      <c r="C278">
+        <v>1481</v>
+      </c>
+      <c r="D278">
+        <v>2278</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46138.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>785</v>
+      </c>
+      <c r="C279">
+        <v>1484</v>
+      </c>
+      <c r="D279">
+        <v>2269</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46138.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>773</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>773</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46138.90625</v>
+      </c>
+      <c r="B281">
+        <v>780</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>780</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46138.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>705</v>
+      </c>
+      <c r="C282">
+        <v>1507</v>
+      </c>
+      <c r="D282">
+        <v>2212</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46138.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>711</v>
+      </c>
+      <c r="C283">
+        <v>1502</v>
+      </c>
+      <c r="D283">
+        <v>2213</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46138.9375</v>
+      </c>
+      <c r="B284">
+        <v>707</v>
+      </c>
+      <c r="C284">
+        <v>1495</v>
+      </c>
+      <c r="D284">
+        <v>2202</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46138.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>681</v>
+      </c>
+      <c r="C285">
+        <v>1494</v>
+      </c>
+      <c r="D285">
+        <v>2175</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46138.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>686</v>
+      </c>
+      <c r="C286">
+        <v>1397</v>
+      </c>
+      <c r="D286">
+        <v>2083</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46138.96875</v>
+      </c>
+      <c r="B287">
+        <v>670</v>
+      </c>
+      <c r="C287">
+        <v>1374</v>
+      </c>
+      <c r="D287">
+        <v>2044</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46138.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>619</v>
+      </c>
+      <c r="C288">
+        <v>1407</v>
+      </c>
+      <c r="D288">
+        <v>2026</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46138.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>568</v>
+      </c>
+      <c r="C289">
+        <v>1402</v>
+      </c>
+      <c r="D289">
+        <v>1970</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B290">
+        <v>589</v>
+      </c>
+      <c r="C290">
+        <v>1215</v>
+      </c>
+      <c r="D290">
+        <v>1804</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46139.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>593</v>
+      </c>
+      <c r="C291">
+        <v>1174</v>
+      </c>
+      <c r="D291">
+        <v>1767</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46139.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>532</v>
+      </c>
+      <c r="C292">
+        <v>1173</v>
+      </c>
+      <c r="D292">
+        <v>1705</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46139.03125</v>
+      </c>
+      <c r="B293">
+        <v>524</v>
+      </c>
+      <c r="C293">
+        <v>1171</v>
+      </c>
+      <c r="D293">
+        <v>1695</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46139.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>513</v>
+      </c>
+      <c r="C294">
+        <v>1158</v>
+      </c>
+      <c r="D294">
+        <v>1671</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46139.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>505</v>
+      </c>
+      <c r="C295">
+        <v>1146</v>
+      </c>
+      <c r="D295">
+        <v>1651</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46139.0625</v>
+      </c>
+      <c r="B296">
+        <v>511</v>
+      </c>
+      <c r="C296">
+        <v>1134</v>
+      </c>
+      <c r="D296">
+        <v>1645</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46139.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>497</v>
+      </c>
+      <c r="C297">
+        <v>1196</v>
+      </c>
+      <c r="D297">
+        <v>1693</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>512</v>
+      </c>
+      <c r="C298">
+        <v>1201</v>
+      </c>
+      <c r="D298">
+        <v>1713</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46139.09375</v>
+      </c>
+      <c r="B299">
+        <v>523</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>523</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>533</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>533</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46139.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>523</v>
+      </c>
+      <c r="C301">
+        <v>1203</v>
+      </c>
+      <c r="D301">
+        <v>1726</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46139.125</v>
+      </c>
+      <c r="B302">
+        <v>534</v>
+      </c>
+      <c r="C302">
+        <v>1208</v>
+      </c>
+      <c r="D302">
+        <v>1742</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46139.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>544</v>
+      </c>
+      <c r="C303">
+        <v>1206</v>
+      </c>
+      <c r="D303">
+        <v>1750</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46139.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>548</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>548</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46139.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>1229</v>
+      </c>
+      <c r="D305">
+        <v>1229</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46139.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>509</v>
+      </c>
+      <c r="C306">
+        <v>1332</v>
+      </c>
+      <c r="D306">
+        <v>1841</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46139.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46139.1875</v>
+      </c>
+      <c r="B308">
+        <v>512</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>512</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46139.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>521</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>521</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46139.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>454</v>
+      </c>
+      <c r="C310">
+        <v>1323</v>
+      </c>
+      <c r="D310">
+        <v>1777</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46139.21875</v>
+      </c>
+      <c r="B311">
+        <v>450</v>
+      </c>
+      <c r="C311">
+        <v>1329</v>
+      </c>
+      <c r="D311">
+        <v>1779</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46139.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>455</v>
+      </c>
+      <c r="C312">
+        <v>1332</v>
+      </c>
+      <c r="D312">
+        <v>1787</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46139.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>461</v>
+      </c>
+      <c r="C313">
+        <v>1331</v>
+      </c>
+      <c r="D313">
+        <v>1792</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46139.25</v>
+      </c>
+      <c r="B314">
+        <v>607</v>
+      </c>
+      <c r="C314">
+        <v>1369</v>
+      </c>
+      <c r="D314">
+        <v>1976</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46139.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>620</v>
+      </c>
+      <c r="C315">
+        <v>1366</v>
+      </c>
+      <c r="D315">
+        <v>1986</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46139.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>621</v>
+      </c>
+      <c r="C316">
+        <v>1362</v>
+      </c>
+      <c r="D316">
+        <v>1983</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46139.28125</v>
+      </c>
+      <c r="B317">
+        <v>611</v>
+      </c>
+      <c r="C317">
+        <v>1360</v>
+      </c>
+      <c r="D317">
+        <v>1971</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46139.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>644</v>
+      </c>
+      <c r="C318">
+        <v>1324</v>
+      </c>
+      <c r="D318">
+        <v>1968</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46139.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>630</v>
+      </c>
+      <c r="C319">
+        <v>1316</v>
+      </c>
+      <c r="D319">
+        <v>1946</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46139.3125</v>
+      </c>
+      <c r="B320">
+        <v>641</v>
+      </c>
+      <c r="C320">
+        <v>1309</v>
+      </c>
+      <c r="D320">
+        <v>1950</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46139.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>629</v>
+      </c>
+      <c r="C321">
+        <v>1313</v>
+      </c>
+      <c r="D321">
+        <v>1942</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46139.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>529</v>
+      </c>
+      <c r="C322">
+        <v>1311</v>
+      </c>
+      <c r="D322">
+        <v>1840</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46139.34375</v>
+      </c>
+      <c r="B323">
+        <v>527</v>
+      </c>
+      <c r="C323">
+        <v>1310</v>
+      </c>
+      <c r="D323">
+        <v>1837</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46139.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>501</v>
+      </c>
+      <c r="C324">
+        <v>1255</v>
+      </c>
+      <c r="D324">
+        <v>1756</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46139.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>492</v>
+      </c>
+      <c r="C325">
+        <v>1252</v>
+      </c>
+      <c r="D325">
+        <v>1744</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46139.375</v>
+      </c>
+      <c r="B326">
+        <v>346</v>
+      </c>
+      <c r="C326">
+        <v>1013</v>
+      </c>
+      <c r="D326">
+        <v>1359</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46139.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>336</v>
+      </c>
+      <c r="C327">
+        <v>981</v>
+      </c>
+      <c r="D327">
+        <v>1317</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46139.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>311</v>
+      </c>
+      <c r="C328">
+        <v>976</v>
+      </c>
+      <c r="D328">
+        <v>1287</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46139.40625</v>
+      </c>
+      <c r="B329">
+        <v>301</v>
+      </c>
+      <c r="C329">
+        <v>1007</v>
+      </c>
+      <c r="D329">
+        <v>1308</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46139.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>137</v>
+      </c>
+      <c r="C330">
+        <v>641</v>
+      </c>
+      <c r="D330">
+        <v>778</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46139.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>128</v>
+      </c>
+      <c r="C331">
+        <v>574</v>
+      </c>
+      <c r="D331">
+        <v>702</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B332">
+        <v>130</v>
+      </c>
+      <c r="C332">
+        <v>573</v>
+      </c>
+      <c r="D332">
+        <v>703</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>128</v>
+      </c>
+      <c r="C333">
+        <v>572</v>
+      </c>
+      <c r="D333">
+        <v>700</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>145</v>
+      </c>
+      <c r="C334">
+        <v>569</v>
+      </c>
+      <c r="D334">
+        <v>714</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46139.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46139.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46139.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46139.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46139.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46139.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46139.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46139.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46139.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46139.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46139.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46139.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46139.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46139.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46139.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46139.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46139.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46139.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46139.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46139.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46139.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46139.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46139.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46139.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46139.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46139.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46139.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46139.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46139.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46139.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46139.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46139.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46139.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46139.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46139.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46139.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46139.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46139.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46139.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46139.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46139.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46139.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,1156 +34,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.202625</t>
-  </si>
-  <si>
-    <t>24.04.202626</t>
-  </si>
-  <si>
-    <t>24.04.202627</t>
-  </si>
-  <si>
-    <t>24.04.202628</t>
-  </si>
-  <si>
-    <t>24.04.202629</t>
-  </si>
-  <si>
-    <t>24.04.202630</t>
-  </si>
-  <si>
-    <t>24.04.202631</t>
-  </si>
-  <si>
-    <t>24.04.202632</t>
-  </si>
-  <si>
-    <t>24.04.202633</t>
-  </si>
-  <si>
-    <t>24.04.202634</t>
-  </si>
-  <si>
-    <t>24.04.202635</t>
-  </si>
-  <si>
-    <t>24.04.202636</t>
-  </si>
-  <si>
-    <t>24.04.202637</t>
-  </si>
-  <si>
-    <t>24.04.202638</t>
-  </si>
-  <si>
-    <t>24.04.202639</t>
-  </si>
-  <si>
-    <t>24.04.202640</t>
-  </si>
-  <si>
-    <t>24.04.202641</t>
-  </si>
-  <si>
-    <t>24.04.202642</t>
-  </si>
-  <si>
-    <t>24.04.202643</t>
-  </si>
-  <si>
-    <t>24.04.202644</t>
-  </si>
-  <si>
-    <t>24.04.202645</t>
-  </si>
-  <si>
-    <t>24.04.202646</t>
-  </si>
-  <si>
-    <t>24.04.202647</t>
-  </si>
-  <si>
-    <t>24.04.202648</t>
-  </si>
-  <si>
-    <t>24.04.202649</t>
-  </si>
-  <si>
-    <t>24.04.202650</t>
-  </si>
-  <si>
-    <t>24.04.202651</t>
-  </si>
-  <si>
-    <t>24.04.202652</t>
-  </si>
-  <si>
-    <t>24.04.202653</t>
-  </si>
-  <si>
-    <t>24.04.202654</t>
-  </si>
-  <si>
-    <t>24.04.202655</t>
-  </si>
-  <si>
-    <t>24.04.202656</t>
-  </si>
-  <si>
-    <t>24.04.202657</t>
-  </si>
-  <si>
-    <t>24.04.202658</t>
-  </si>
-  <si>
-    <t>24.04.202659</t>
-  </si>
-  <si>
-    <t>24.04.202660</t>
-  </si>
-  <si>
-    <t>24.04.202661</t>
-  </si>
-  <si>
-    <t>24.04.202662</t>
-  </si>
-  <si>
-    <t>24.04.202663</t>
-  </si>
-  <si>
-    <t>24.04.202664</t>
-  </si>
-  <si>
-    <t>24.04.202665</t>
-  </si>
-  <si>
-    <t>24.04.202666</t>
-  </si>
-  <si>
-    <t>24.04.202667</t>
-  </si>
-  <si>
-    <t>24.04.202668</t>
-  </si>
-  <si>
-    <t>24.04.202669</t>
-  </si>
-  <si>
-    <t>24.04.202670</t>
-  </si>
-  <si>
-    <t>24.04.202671</t>
-  </si>
-  <si>
-    <t>24.04.202672</t>
-  </si>
-  <si>
-    <t>24.04.202673</t>
-  </si>
-  <si>
-    <t>24.04.202674</t>
-  </si>
-  <si>
-    <t>24.04.202675</t>
-  </si>
-  <si>
-    <t>24.04.202676</t>
-  </si>
-  <si>
-    <t>24.04.202677</t>
-  </si>
-  <si>
-    <t>24.04.202678</t>
-  </si>
-  <si>
-    <t>24.04.202679</t>
-  </si>
-  <si>
-    <t>24.04.202680</t>
-  </si>
-  <si>
-    <t>24.04.202681</t>
-  </si>
-  <si>
-    <t>24.04.202682</t>
-  </si>
-  <si>
-    <t>24.04.202683</t>
-  </si>
-  <si>
-    <t>24.04.202684</t>
-  </si>
-  <si>
-    <t>24.04.202685</t>
-  </si>
-  <si>
-    <t>24.04.202686</t>
-  </si>
-  <si>
-    <t>24.04.202687</t>
-  </si>
-  <si>
-    <t>24.04.202688</t>
-  </si>
-  <si>
-    <t>24.04.202689</t>
-  </si>
-  <si>
-    <t>24.04.202690</t>
-  </si>
-  <si>
-    <t>24.04.202691</t>
-  </si>
-  <si>
-    <t>24.04.202692</t>
-  </si>
-  <si>
-    <t>24.04.202693</t>
-  </si>
-  <si>
-    <t>24.04.202694</t>
-  </si>
-  <si>
-    <t>24.04.202695</t>
-  </si>
-  <si>
-    <t>24.04.202696</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.202625</t>
-  </si>
-  <si>
-    <t>25.04.202626</t>
-  </si>
-  <si>
-    <t>25.04.202627</t>
-  </si>
-  <si>
-    <t>25.04.202628</t>
-  </si>
-  <si>
-    <t>25.04.202629</t>
-  </si>
-  <si>
-    <t>25.04.202630</t>
-  </si>
-  <si>
-    <t>25.04.202631</t>
-  </si>
-  <si>
-    <t>25.04.202632</t>
-  </si>
-  <si>
-    <t>25.04.202633</t>
-  </si>
-  <si>
-    <t>25.04.202634</t>
-  </si>
-  <si>
-    <t>25.04.202635</t>
-  </si>
-  <si>
-    <t>25.04.202636</t>
-  </si>
-  <si>
-    <t>25.04.202637</t>
-  </si>
-  <si>
-    <t>25.04.202638</t>
-  </si>
-  <si>
-    <t>25.04.202639</t>
-  </si>
-  <si>
-    <t>25.04.202640</t>
-  </si>
-  <si>
-    <t>25.04.202641</t>
-  </si>
-  <si>
-    <t>25.04.202642</t>
-  </si>
-  <si>
-    <t>25.04.202643</t>
-  </si>
-  <si>
-    <t>25.04.202644</t>
-  </si>
-  <si>
-    <t>25.04.202645</t>
-  </si>
-  <si>
-    <t>25.04.202646</t>
-  </si>
-  <si>
-    <t>25.04.202647</t>
-  </si>
-  <si>
-    <t>25.04.202648</t>
-  </si>
-  <si>
-    <t>25.04.202649</t>
-  </si>
-  <si>
-    <t>25.04.202650</t>
-  </si>
-  <si>
-    <t>25.04.202651</t>
-  </si>
-  <si>
-    <t>25.04.202652</t>
-  </si>
-  <si>
-    <t>25.04.202653</t>
-  </si>
-  <si>
-    <t>25.04.202654</t>
-  </si>
-  <si>
-    <t>25.04.202655</t>
-  </si>
-  <si>
-    <t>25.04.202656</t>
-  </si>
-  <si>
-    <t>25.04.202657</t>
-  </si>
-  <si>
-    <t>25.04.202658</t>
-  </si>
-  <si>
-    <t>25.04.202659</t>
-  </si>
-  <si>
-    <t>25.04.202660</t>
-  </si>
-  <si>
-    <t>25.04.202661</t>
-  </si>
-  <si>
-    <t>25.04.202662</t>
-  </si>
-  <si>
-    <t>25.04.202663</t>
-  </si>
-  <si>
-    <t>25.04.202664</t>
-  </si>
-  <si>
-    <t>25.04.202665</t>
-  </si>
-  <si>
-    <t>25.04.202666</t>
-  </si>
-  <si>
-    <t>25.04.202667</t>
-  </si>
-  <si>
-    <t>25.04.202668</t>
-  </si>
-  <si>
-    <t>25.04.202669</t>
-  </si>
-  <si>
-    <t>25.04.202670</t>
-  </si>
-  <si>
-    <t>25.04.202671</t>
-  </si>
-  <si>
-    <t>25.04.202672</t>
-  </si>
-  <si>
-    <t>25.04.202673</t>
-  </si>
-  <si>
-    <t>25.04.202674</t>
-  </si>
-  <si>
-    <t>25.04.202675</t>
-  </si>
-  <si>
-    <t>25.04.202676</t>
-  </si>
-  <si>
-    <t>25.04.202677</t>
-  </si>
-  <si>
-    <t>25.04.202678</t>
-  </si>
-  <si>
-    <t>25.04.202679</t>
-  </si>
-  <si>
-    <t>25.04.202680</t>
-  </si>
-  <si>
-    <t>25.04.202681</t>
-  </si>
-  <si>
-    <t>25.04.202682</t>
-  </si>
-  <si>
-    <t>25.04.202683</t>
-  </si>
-  <si>
-    <t>25.04.202684</t>
-  </si>
-  <si>
-    <t>25.04.202685</t>
-  </si>
-  <si>
-    <t>25.04.202686</t>
-  </si>
-  <si>
-    <t>25.04.202687</t>
-  </si>
-  <si>
-    <t>25.04.202688</t>
-  </si>
-  <si>
-    <t>25.04.202689</t>
-  </si>
-  <si>
-    <t>25.04.202690</t>
-  </si>
-  <si>
-    <t>25.04.202691</t>
-  </si>
-  <si>
-    <t>25.04.202692</t>
-  </si>
-  <si>
-    <t>25.04.202693</t>
-  </si>
-  <si>
-    <t>25.04.202694</t>
-  </si>
-  <si>
-    <t>25.04.202695</t>
-  </si>
-  <si>
-    <t>25.04.202696</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.202625</t>
-  </si>
-  <si>
-    <t>26.04.202626</t>
-  </si>
-  <si>
-    <t>26.04.202627</t>
-  </si>
-  <si>
-    <t>26.04.202628</t>
-  </si>
-  <si>
-    <t>26.04.202629</t>
-  </si>
-  <si>
-    <t>26.04.202630</t>
-  </si>
-  <si>
-    <t>26.04.202631</t>
-  </si>
-  <si>
-    <t>26.04.202632</t>
-  </si>
-  <si>
-    <t>26.04.202633</t>
-  </si>
-  <si>
-    <t>26.04.202634</t>
-  </si>
-  <si>
-    <t>26.04.202635</t>
-  </si>
-  <si>
-    <t>26.04.202636</t>
-  </si>
-  <si>
-    <t>26.04.202637</t>
-  </si>
-  <si>
-    <t>26.04.202638</t>
-  </si>
-  <si>
-    <t>26.04.202639</t>
-  </si>
-  <si>
-    <t>26.04.202640</t>
-  </si>
-  <si>
-    <t>26.04.202641</t>
-  </si>
-  <si>
-    <t>26.04.202642</t>
-  </si>
-  <si>
-    <t>26.04.202643</t>
-  </si>
-  <si>
-    <t>26.04.202644</t>
-  </si>
-  <si>
-    <t>26.04.202645</t>
-  </si>
-  <si>
-    <t>26.04.202646</t>
-  </si>
-  <si>
-    <t>26.04.202647</t>
-  </si>
-  <si>
-    <t>26.04.202648</t>
-  </si>
-  <si>
-    <t>26.04.202649</t>
-  </si>
-  <si>
-    <t>26.04.202650</t>
-  </si>
-  <si>
-    <t>26.04.202651</t>
-  </si>
-  <si>
-    <t>26.04.202652</t>
-  </si>
-  <si>
-    <t>26.04.202653</t>
-  </si>
-  <si>
-    <t>26.04.202654</t>
-  </si>
-  <si>
-    <t>26.04.202655</t>
-  </si>
-  <si>
-    <t>26.04.202656</t>
-  </si>
-  <si>
-    <t>26.04.202657</t>
-  </si>
-  <si>
-    <t>26.04.202658</t>
-  </si>
-  <si>
-    <t>26.04.202659</t>
-  </si>
-  <si>
-    <t>26.04.202660</t>
-  </si>
-  <si>
-    <t>26.04.202661</t>
-  </si>
-  <si>
-    <t>26.04.202662</t>
-  </si>
-  <si>
-    <t>26.04.202663</t>
-  </si>
-  <si>
-    <t>26.04.202664</t>
-  </si>
-  <si>
-    <t>26.04.202665</t>
-  </si>
-  <si>
-    <t>26.04.202666</t>
-  </si>
-  <si>
-    <t>26.04.202667</t>
-  </si>
-  <si>
-    <t>26.04.202668</t>
-  </si>
-  <si>
-    <t>26.04.202669</t>
-  </si>
-  <si>
-    <t>26.04.202670</t>
-  </si>
-  <si>
-    <t>26.04.202671</t>
-  </si>
-  <si>
-    <t>26.04.202672</t>
-  </si>
-  <si>
-    <t>26.04.202673</t>
-  </si>
-  <si>
-    <t>26.04.202674</t>
-  </si>
-  <si>
-    <t>26.04.202675</t>
-  </si>
-  <si>
-    <t>26.04.202676</t>
-  </si>
-  <si>
-    <t>26.04.202677</t>
-  </si>
-  <si>
-    <t>26.04.202678</t>
-  </si>
-  <si>
-    <t>26.04.202679</t>
-  </si>
-  <si>
-    <t>26.04.202680</t>
-  </si>
-  <si>
-    <t>26.04.202681</t>
-  </si>
-  <si>
-    <t>26.04.202682</t>
-  </si>
-  <si>
-    <t>26.04.202683</t>
-  </si>
-  <si>
-    <t>26.04.202684</t>
-  </si>
-  <si>
-    <t>26.04.202685</t>
-  </si>
-  <si>
-    <t>26.04.202686</t>
-  </si>
-  <si>
-    <t>26.04.202687</t>
-  </si>
-  <si>
-    <t>26.04.202688</t>
-  </si>
-  <si>
-    <t>26.04.202689</t>
-  </si>
-  <si>
-    <t>26.04.202690</t>
-  </si>
-  <si>
-    <t>26.04.202691</t>
-  </si>
-  <si>
-    <t>26.04.202692</t>
-  </si>
-  <si>
-    <t>26.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202694</t>
-  </si>
-  <si>
-    <t>26.04.202695</t>
-  </si>
-  <si>
-    <t>26.04.202696</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.202625</t>
-  </si>
-  <si>
-    <t>27.04.202626</t>
-  </si>
-  <si>
-    <t>27.04.202627</t>
-  </si>
-  <si>
-    <t>27.04.202628</t>
-  </si>
-  <si>
-    <t>27.04.202629</t>
-  </si>
-  <si>
-    <t>27.04.202630</t>
-  </si>
-  <si>
-    <t>27.04.202631</t>
-  </si>
-  <si>
-    <t>27.04.202632</t>
-  </si>
-  <si>
-    <t>27.04.202633</t>
-  </si>
-  <si>
-    <t>27.04.202634</t>
-  </si>
-  <si>
-    <t>27.04.202635</t>
-  </si>
-  <si>
-    <t>27.04.202636</t>
-  </si>
-  <si>
-    <t>27.04.202637</t>
-  </si>
-  <si>
-    <t>27.04.202638</t>
-  </si>
-  <si>
-    <t>27.04.202639</t>
-  </si>
-  <si>
-    <t>27.04.202640</t>
-  </si>
-  <si>
-    <t>27.04.202641</t>
-  </si>
-  <si>
-    <t>27.04.202642</t>
-  </si>
-  <si>
-    <t>27.04.202643</t>
-  </si>
-  <si>
-    <t>27.04.202644</t>
-  </si>
-  <si>
-    <t>27.04.202645</t>
-  </si>
-  <si>
-    <t>27.04.202646</t>
-  </si>
-  <si>
-    <t>27.04.202647</t>
-  </si>
-  <si>
-    <t>27.04.202648</t>
-  </si>
-  <si>
-    <t>27.04.202649</t>
-  </si>
-  <si>
-    <t>27.04.202650</t>
-  </si>
-  <si>
-    <t>27.04.202651</t>
-  </si>
-  <si>
-    <t>27.04.202652</t>
-  </si>
-  <si>
-    <t>27.04.202653</t>
-  </si>
-  <si>
-    <t>27.04.202654</t>
-  </si>
-  <si>
-    <t>27.04.202655</t>
-  </si>
-  <si>
-    <t>27.04.202656</t>
-  </si>
-  <si>
-    <t>27.04.202657</t>
-  </si>
-  <si>
-    <t>27.04.202658</t>
-  </si>
-  <si>
-    <t>27.04.202659</t>
-  </si>
-  <si>
-    <t>27.04.202660</t>
-  </si>
-  <si>
-    <t>27.04.202661</t>
-  </si>
-  <si>
-    <t>27.04.202662</t>
-  </si>
-  <si>
-    <t>27.04.202663</t>
-  </si>
-  <si>
-    <t>27.04.202664</t>
-  </si>
-  <si>
-    <t>27.04.202665</t>
-  </si>
-  <si>
-    <t>27.04.202666</t>
-  </si>
-  <si>
-    <t>27.04.202667</t>
-  </si>
-  <si>
-    <t>27.04.202668</t>
-  </si>
-  <si>
-    <t>27.04.202669</t>
-  </si>
-  <si>
-    <t>27.04.202670</t>
-  </si>
-  <si>
-    <t>27.04.202671</t>
-  </si>
-  <si>
-    <t>27.04.202672</t>
-  </si>
-  <si>
-    <t>27.04.202673</t>
-  </si>
-  <si>
-    <t>27.04.202674</t>
-  </si>
-  <si>
-    <t>27.04.202675</t>
-  </si>
-  <si>
-    <t>27.04.202676</t>
-  </si>
-  <si>
-    <t>27.04.202677</t>
-  </si>
-  <si>
-    <t>27.04.202678</t>
-  </si>
-  <si>
-    <t>27.04.202679</t>
-  </si>
-  <si>
-    <t>27.04.202680</t>
-  </si>
-  <si>
-    <t>27.04.202681</t>
-  </si>
-  <si>
-    <t>27.04.202682</t>
-  </si>
-  <si>
-    <t>27.04.202683</t>
-  </si>
-  <si>
-    <t>27.04.202684</t>
-  </si>
-  <si>
-    <t>27.04.202685</t>
-  </si>
-  <si>
-    <t>27.04.202686</t>
-  </si>
-  <si>
-    <t>27.04.202687</t>
-  </si>
-  <si>
-    <t>27.04.202688</t>
-  </si>
-  <si>
-    <t>27.04.202689</t>
-  </si>
-  <si>
-    <t>27.04.202690</t>
-  </si>
-  <si>
-    <t>27.04.202691</t>
-  </si>
-  <si>
-    <t>27.04.202692</t>
-  </si>
-  <si>
-    <t>27.04.202693</t>
-  </si>
-  <si>
-    <t>27.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202695</t>
-  </si>
-  <si>
-    <t>27.04.202696</t>
+    <t>28.04.20261</t>
+  </si>
+  <si>
+    <t>28.04.20262</t>
+  </si>
+  <si>
+    <t>28.04.20263</t>
+  </si>
+  <si>
+    <t>28.04.20264</t>
+  </si>
+  <si>
+    <t>28.04.20265</t>
+  </si>
+  <si>
+    <t>28.04.20266</t>
+  </si>
+  <si>
+    <t>28.04.20267</t>
+  </si>
+  <si>
+    <t>28.04.20268</t>
+  </si>
+  <si>
+    <t>28.04.20269</t>
+  </si>
+  <si>
+    <t>28.04.202610</t>
+  </si>
+  <si>
+    <t>28.04.202611</t>
+  </si>
+  <si>
+    <t>28.04.202612</t>
+  </si>
+  <si>
+    <t>28.04.202613</t>
+  </si>
+  <si>
+    <t>28.04.202614</t>
+  </si>
+  <si>
+    <t>28.04.202615</t>
+  </si>
+  <si>
+    <t>28.04.202616</t>
+  </si>
+  <si>
+    <t>28.04.202617</t>
+  </si>
+  <si>
+    <t>28.04.202618</t>
+  </si>
+  <si>
+    <t>28.04.202619</t>
+  </si>
+  <si>
+    <t>28.04.202620</t>
+  </si>
+  <si>
+    <t>28.04.202621</t>
+  </si>
+  <si>
+    <t>28.04.202622</t>
+  </si>
+  <si>
+    <t>28.04.202623</t>
+  </si>
+  <si>
+    <t>28.04.202624</t>
+  </si>
+  <si>
+    <t>28.04.202625</t>
+  </si>
+  <si>
+    <t>28.04.202626</t>
+  </si>
+  <si>
+    <t>28.04.202627</t>
+  </si>
+  <si>
+    <t>28.04.202628</t>
+  </si>
+  <si>
+    <t>28.04.202629</t>
+  </si>
+  <si>
+    <t>28.04.202630</t>
+  </si>
+  <si>
+    <t>28.04.202631</t>
+  </si>
+  <si>
+    <t>28.04.202632</t>
+  </si>
+  <si>
+    <t>28.04.202633</t>
+  </si>
+  <si>
+    <t>28.04.202634</t>
+  </si>
+  <si>
+    <t>28.04.202635</t>
+  </si>
+  <si>
+    <t>28.04.202636</t>
+  </si>
+  <si>
+    <t>28.04.202637</t>
+  </si>
+  <si>
+    <t>28.04.202638</t>
+  </si>
+  <si>
+    <t>28.04.202639</t>
+  </si>
+  <si>
+    <t>28.04.202640</t>
+  </si>
+  <si>
+    <t>28.04.202641</t>
+  </si>
+  <si>
+    <t>28.04.202642</t>
+  </si>
+  <si>
+    <t>28.04.202643</t>
+  </si>
+  <si>
+    <t>28.04.202644</t>
+  </si>
+  <si>
+    <t>28.04.202645</t>
+  </si>
+  <si>
+    <t>28.04.202646</t>
+  </si>
+  <si>
+    <t>28.04.202647</t>
+  </si>
+  <si>
+    <t>28.04.202648</t>
+  </si>
+  <si>
+    <t>28.04.202649</t>
+  </si>
+  <si>
+    <t>28.04.202650</t>
+  </si>
+  <si>
+    <t>28.04.202651</t>
+  </si>
+  <si>
+    <t>28.04.202652</t>
+  </si>
+  <si>
+    <t>28.04.202653</t>
+  </si>
+  <si>
+    <t>28.04.202654</t>
+  </si>
+  <si>
+    <t>28.04.202655</t>
+  </si>
+  <si>
+    <t>28.04.202656</t>
+  </si>
+  <si>
+    <t>28.04.202657</t>
+  </si>
+  <si>
+    <t>28.04.202658</t>
+  </si>
+  <si>
+    <t>28.04.202659</t>
+  </si>
+  <si>
+    <t>28.04.202660</t>
+  </si>
+  <si>
+    <t>28.04.202661</t>
+  </si>
+  <si>
+    <t>28.04.202662</t>
+  </si>
+  <si>
+    <t>28.04.202663</t>
+  </si>
+  <si>
+    <t>28.04.202664</t>
+  </si>
+  <si>
+    <t>28.04.202665</t>
+  </si>
+  <si>
+    <t>28.04.202666</t>
+  </si>
+  <si>
+    <t>28.04.202667</t>
+  </si>
+  <si>
+    <t>28.04.202668</t>
+  </si>
+  <si>
+    <t>28.04.202669</t>
+  </si>
+  <si>
+    <t>28.04.202670</t>
+  </si>
+  <si>
+    <t>28.04.202671</t>
+  </si>
+  <si>
+    <t>28.04.202672</t>
+  </si>
+  <si>
+    <t>28.04.202673</t>
+  </si>
+  <si>
+    <t>28.04.202674</t>
+  </si>
+  <si>
+    <t>28.04.202675</t>
+  </si>
+  <si>
+    <t>28.04.202676</t>
+  </si>
+  <si>
+    <t>28.04.202677</t>
+  </si>
+  <si>
+    <t>28.04.202678</t>
+  </si>
+  <si>
+    <t>28.04.202679</t>
+  </si>
+  <si>
+    <t>28.04.202680</t>
+  </si>
+  <si>
+    <t>28.04.202681</t>
+  </si>
+  <si>
+    <t>28.04.202682</t>
+  </si>
+  <si>
+    <t>28.04.202683</t>
+  </si>
+  <si>
+    <t>28.04.202684</t>
+  </si>
+  <si>
+    <t>28.04.202685</t>
+  </si>
+  <si>
+    <t>28.04.202686</t>
+  </si>
+  <si>
+    <t>28.04.202687</t>
+  </si>
+  <si>
+    <t>28.04.202688</t>
+  </si>
+  <si>
+    <t>28.04.202689</t>
+  </si>
+  <si>
+    <t>28.04.202690</t>
+  </si>
+  <si>
+    <t>28.04.202691</t>
+  </si>
+  <si>
+    <t>28.04.202692</t>
+  </si>
+  <si>
+    <t>28.04.202693</t>
+  </si>
+  <si>
+    <t>28.04.202694</t>
+  </si>
+  <si>
+    <t>28.04.202695</t>
+  </si>
+  <si>
+    <t>28.04.202696</t>
+  </si>
+  <si>
+    <t>29.04.20261</t>
+  </si>
+  <si>
+    <t>29.04.20262</t>
+  </si>
+  <si>
+    <t>29.04.20263</t>
+  </si>
+  <si>
+    <t>29.04.20264</t>
+  </si>
+  <si>
+    <t>29.04.20265</t>
+  </si>
+  <si>
+    <t>29.04.20266</t>
+  </si>
+  <si>
+    <t>29.04.20267</t>
+  </si>
+  <si>
+    <t>29.04.20268</t>
+  </si>
+  <si>
+    <t>29.04.20269</t>
+  </si>
+  <si>
+    <t>29.04.202610</t>
+  </si>
+  <si>
+    <t>29.04.202611</t>
+  </si>
+  <si>
+    <t>29.04.202612</t>
+  </si>
+  <si>
+    <t>29.04.202613</t>
+  </si>
+  <si>
+    <t>29.04.202614</t>
+  </si>
+  <si>
+    <t>29.04.202615</t>
+  </si>
+  <si>
+    <t>29.04.202616</t>
+  </si>
+  <si>
+    <t>29.04.202617</t>
+  </si>
+  <si>
+    <t>29.04.202618</t>
+  </si>
+  <si>
+    <t>29.04.202619</t>
+  </si>
+  <si>
+    <t>29.04.202620</t>
+  </si>
+  <si>
+    <t>29.04.202621</t>
+  </si>
+  <si>
+    <t>29.04.202622</t>
+  </si>
+  <si>
+    <t>29.04.202623</t>
+  </si>
+  <si>
+    <t>29.04.202624</t>
+  </si>
+  <si>
+    <t>29.04.202625</t>
+  </si>
+  <si>
+    <t>29.04.202626</t>
+  </si>
+  <si>
+    <t>29.04.202627</t>
+  </si>
+  <si>
+    <t>29.04.202628</t>
+  </si>
+  <si>
+    <t>29.04.202629</t>
+  </si>
+  <si>
+    <t>29.04.202630</t>
+  </si>
+  <si>
+    <t>29.04.202631</t>
+  </si>
+  <si>
+    <t>29.04.202632</t>
+  </si>
+  <si>
+    <t>29.04.202633</t>
+  </si>
+  <si>
+    <t>29.04.202634</t>
+  </si>
+  <si>
+    <t>29.04.202635</t>
+  </si>
+  <si>
+    <t>29.04.202636</t>
+  </si>
+  <si>
+    <t>29.04.202637</t>
+  </si>
+  <si>
+    <t>29.04.202638</t>
+  </si>
+  <si>
+    <t>29.04.202639</t>
+  </si>
+  <si>
+    <t>29.04.202640</t>
+  </si>
+  <si>
+    <t>29.04.202641</t>
+  </si>
+  <si>
+    <t>29.04.202642</t>
+  </si>
+  <si>
+    <t>29.04.202643</t>
+  </si>
+  <si>
+    <t>29.04.202644</t>
+  </si>
+  <si>
+    <t>29.04.202645</t>
+  </si>
+  <si>
+    <t>29.04.202646</t>
+  </si>
+  <si>
+    <t>29.04.202647</t>
+  </si>
+  <si>
+    <t>29.04.202648</t>
+  </si>
+  <si>
+    <t>29.04.202649</t>
+  </si>
+  <si>
+    <t>29.04.202650</t>
+  </si>
+  <si>
+    <t>29.04.202651</t>
+  </si>
+  <si>
+    <t>29.04.202652</t>
+  </si>
+  <si>
+    <t>29.04.202653</t>
+  </si>
+  <si>
+    <t>29.04.202654</t>
+  </si>
+  <si>
+    <t>29.04.202655</t>
+  </si>
+  <si>
+    <t>29.04.202656</t>
+  </si>
+  <si>
+    <t>29.04.202657</t>
+  </si>
+  <si>
+    <t>29.04.202658</t>
+  </si>
+  <si>
+    <t>29.04.202659</t>
+  </si>
+  <si>
+    <t>29.04.202660</t>
+  </si>
+  <si>
+    <t>29.04.202661</t>
+  </si>
+  <si>
+    <t>29.04.202662</t>
+  </si>
+  <si>
+    <t>29.04.202663</t>
+  </si>
+  <si>
+    <t>29.04.202664</t>
+  </si>
+  <si>
+    <t>29.04.202665</t>
+  </si>
+  <si>
+    <t>29.04.202666</t>
+  </si>
+  <si>
+    <t>29.04.202667</t>
+  </si>
+  <si>
+    <t>29.04.202668</t>
+  </si>
+  <si>
+    <t>29.04.202669</t>
+  </si>
+  <si>
+    <t>29.04.202670</t>
+  </si>
+  <si>
+    <t>29.04.202671</t>
+  </si>
+  <si>
+    <t>29.04.202672</t>
+  </si>
+  <si>
+    <t>29.04.202673</t>
+  </si>
+  <si>
+    <t>29.04.202674</t>
+  </si>
+  <si>
+    <t>29.04.202675</t>
+  </si>
+  <si>
+    <t>29.04.202676</t>
+  </si>
+  <si>
+    <t>29.04.202677</t>
+  </si>
+  <si>
+    <t>29.04.202678</t>
+  </si>
+  <si>
+    <t>29.04.202679</t>
+  </si>
+  <si>
+    <t>29.04.202680</t>
+  </si>
+  <si>
+    <t>29.04.202681</t>
+  </si>
+  <si>
+    <t>29.04.202682</t>
+  </si>
+  <si>
+    <t>29.04.202683</t>
+  </si>
+  <si>
+    <t>29.04.202684</t>
+  </si>
+  <si>
+    <t>29.04.202685</t>
+  </si>
+  <si>
+    <t>29.04.202686</t>
+  </si>
+  <si>
+    <t>29.04.202687</t>
+  </si>
+  <si>
+    <t>29.04.202688</t>
+  </si>
+  <si>
+    <t>29.04.202689</t>
+  </si>
+  <si>
+    <t>29.04.202690</t>
+  </si>
+  <si>
+    <t>29.04.202691</t>
+  </si>
+  <si>
+    <t>29.04.202692</t>
+  </si>
+  <si>
+    <t>29.04.202693</t>
+  </si>
+  <si>
+    <t>29.04.202694</t>
+  </si>
+  <si>
+    <t>29.04.202695</t>
+  </si>
+  <si>
+    <t>29.04.202696</t>
+  </si>
+  <si>
+    <t>30.04.20261</t>
+  </si>
+  <si>
+    <t>30.04.20262</t>
+  </si>
+  <si>
+    <t>30.04.20263</t>
+  </si>
+  <si>
+    <t>30.04.20264</t>
+  </si>
+  <si>
+    <t>30.04.20265</t>
+  </si>
+  <si>
+    <t>30.04.20266</t>
+  </si>
+  <si>
+    <t>30.04.20267</t>
+  </si>
+  <si>
+    <t>30.04.20268</t>
+  </si>
+  <si>
+    <t>30.04.20269</t>
+  </si>
+  <si>
+    <t>30.04.202610</t>
+  </si>
+  <si>
+    <t>30.04.202611</t>
+  </si>
+  <si>
+    <t>30.04.202612</t>
+  </si>
+  <si>
+    <t>30.04.202613</t>
+  </si>
+  <si>
+    <t>30.04.202614</t>
+  </si>
+  <si>
+    <t>30.04.202615</t>
+  </si>
+  <si>
+    <t>30.04.202616</t>
+  </si>
+  <si>
+    <t>30.04.202617</t>
+  </si>
+  <si>
+    <t>30.04.202618</t>
+  </si>
+  <si>
+    <t>30.04.202619</t>
+  </si>
+  <si>
+    <t>30.04.202620</t>
+  </si>
+  <si>
+    <t>30.04.202621</t>
+  </si>
+  <si>
+    <t>30.04.202622</t>
+  </si>
+  <si>
+    <t>30.04.202623</t>
+  </si>
+  <si>
+    <t>30.04.202624</t>
+  </si>
+  <si>
+    <t>30.04.202625</t>
+  </si>
+  <si>
+    <t>30.04.202626</t>
+  </si>
+  <si>
+    <t>30.04.202627</t>
+  </si>
+  <si>
+    <t>30.04.202628</t>
+  </si>
+  <si>
+    <t>30.04.202629</t>
+  </si>
+  <si>
+    <t>30.04.202630</t>
+  </si>
+  <si>
+    <t>30.04.202631</t>
+  </si>
+  <si>
+    <t>30.04.202632</t>
+  </si>
+  <si>
+    <t>30.04.202633</t>
+  </si>
+  <si>
+    <t>30.04.202634</t>
+  </si>
+  <si>
+    <t>30.04.202635</t>
+  </si>
+  <si>
+    <t>30.04.202636</t>
+  </si>
+  <si>
+    <t>30.04.202637</t>
+  </si>
+  <si>
+    <t>30.04.202638</t>
+  </si>
+  <si>
+    <t>30.04.202639</t>
+  </si>
+  <si>
+    <t>30.04.202640</t>
+  </si>
+  <si>
+    <t>30.04.202641</t>
+  </si>
+  <si>
+    <t>30.04.202642</t>
+  </si>
+  <si>
+    <t>30.04.202643</t>
+  </si>
+  <si>
+    <t>30.04.202644</t>
+  </si>
+  <si>
+    <t>30.04.202645</t>
+  </si>
+  <si>
+    <t>30.04.202646</t>
+  </si>
+  <si>
+    <t>30.04.202647</t>
+  </si>
+  <si>
+    <t>30.04.202648</t>
+  </si>
+  <si>
+    <t>30.04.202649</t>
+  </si>
+  <si>
+    <t>30.04.202650</t>
+  </si>
+  <si>
+    <t>30.04.202651</t>
+  </si>
+  <si>
+    <t>30.04.202652</t>
+  </si>
+  <si>
+    <t>30.04.202653</t>
+  </si>
+  <si>
+    <t>30.04.202654</t>
+  </si>
+  <si>
+    <t>30.04.202655</t>
+  </si>
+  <si>
+    <t>30.04.202656</t>
+  </si>
+  <si>
+    <t>30.04.202657</t>
+  </si>
+  <si>
+    <t>30.04.202658</t>
+  </si>
+  <si>
+    <t>30.04.202659</t>
+  </si>
+  <si>
+    <t>30.04.202660</t>
+  </si>
+  <si>
+    <t>30.04.202661</t>
+  </si>
+  <si>
+    <t>30.04.202662</t>
+  </si>
+  <si>
+    <t>30.04.202663</t>
+  </si>
+  <si>
+    <t>30.04.202664</t>
+  </si>
+  <si>
+    <t>30.04.202665</t>
+  </si>
+  <si>
+    <t>30.04.202666</t>
+  </si>
+  <si>
+    <t>30.04.202667</t>
+  </si>
+  <si>
+    <t>30.04.202668</t>
+  </si>
+  <si>
+    <t>30.04.202669</t>
+  </si>
+  <si>
+    <t>30.04.202670</t>
+  </si>
+  <si>
+    <t>30.04.202671</t>
+  </si>
+  <si>
+    <t>30.04.202672</t>
+  </si>
+  <si>
+    <t>30.04.202673</t>
+  </si>
+  <si>
+    <t>30.04.202674</t>
+  </si>
+  <si>
+    <t>30.04.202675</t>
+  </si>
+  <si>
+    <t>30.04.202676</t>
+  </si>
+  <si>
+    <t>30.04.202677</t>
+  </si>
+  <si>
+    <t>30.04.202678</t>
+  </si>
+  <si>
+    <t>30.04.202679</t>
+  </si>
+  <si>
+    <t>30.04.202680</t>
+  </si>
+  <si>
+    <t>30.04.202681</t>
+  </si>
+  <si>
+    <t>30.04.202682</t>
+  </si>
+  <si>
+    <t>30.04.202683</t>
+  </si>
+  <si>
+    <t>30.04.202684</t>
+  </si>
+  <si>
+    <t>30.04.202685</t>
+  </si>
+  <si>
+    <t>30.04.202686</t>
+  </si>
+  <si>
+    <t>30.04.202687</t>
+  </si>
+  <si>
+    <t>30.04.202688</t>
+  </si>
+  <si>
+    <t>30.04.202689</t>
+  </si>
+  <si>
+    <t>30.04.202690</t>
+  </si>
+  <si>
+    <t>30.04.202691</t>
+  </si>
+  <si>
+    <t>30.04.202692</t>
+  </si>
+  <si>
+    <t>30.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202694</t>
+  </si>
+  <si>
+    <t>30.04.202695</t>
+  </si>
+  <si>
+    <t>30.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F385"/>
+  <dimension ref="A1:F289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1570,16 +1282,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B2">
-        <v>603</v>
+        <v>805</v>
       </c>
       <c r="C2">
-        <v>1545</v>
+        <v>1123</v>
       </c>
       <c r="D2">
-        <v>2148</v>
+        <v>1928</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1590,16 +1302,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46136.01041666666</v>
+        <v>46140.01041666666</v>
       </c>
       <c r="B3">
-        <v>602</v>
+        <v>798</v>
       </c>
       <c r="C3">
-        <v>1533</v>
+        <v>1112</v>
       </c>
       <c r="D3">
-        <v>2135</v>
+        <v>1910</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1610,16 +1322,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46136.02083333334</v>
+        <v>46140.02083333334</v>
       </c>
       <c r="B4">
-        <v>576</v>
+        <v>816</v>
       </c>
       <c r="C4">
-        <v>1539</v>
+        <v>1119</v>
       </c>
       <c r="D4">
-        <v>2115</v>
+        <v>1935</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1630,16 +1342,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46136.03125</v>
+        <v>46140.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="C5">
-        <v>1542</v>
+        <v>1154</v>
       </c>
       <c r="D5">
-        <v>1542</v>
+        <v>1953</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1650,16 +1362,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46136.04166666666</v>
+        <v>46140.04166666666</v>
       </c>
       <c r="B6">
-        <v>557</v>
+        <v>837</v>
       </c>
       <c r="C6">
-        <v>1372</v>
+        <v>1058</v>
       </c>
       <c r="D6">
-        <v>1929</v>
+        <v>1895</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1670,16 +1382,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46136.05208333334</v>
+        <v>46140.05208333334</v>
       </c>
       <c r="B7">
-        <v>530</v>
+        <v>836</v>
       </c>
       <c r="C7">
-        <v>1338</v>
+        <v>1044</v>
       </c>
       <c r="D7">
-        <v>1868</v>
+        <v>1880</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1690,16 +1402,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46136.0625</v>
+        <v>46140.0625</v>
       </c>
       <c r="B8">
-        <v>504</v>
+        <v>833</v>
       </c>
       <c r="C8">
-        <v>1340</v>
+        <v>1050</v>
       </c>
       <c r="D8">
-        <v>1844</v>
+        <v>1883</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1710,16 +1422,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46136.07291666666</v>
+        <v>46140.07291666666</v>
       </c>
       <c r="B9">
-        <v>367</v>
+        <v>837</v>
       </c>
       <c r="C9">
-        <v>1338</v>
+        <v>1052</v>
       </c>
       <c r="D9">
-        <v>1705</v>
+        <v>1889</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1730,16 +1442,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46136.08333333334</v>
+        <v>46140.08333333334</v>
       </c>
       <c r="B10">
-        <v>332</v>
+        <v>796</v>
       </c>
       <c r="C10">
-        <v>1322</v>
+        <v>1057</v>
       </c>
       <c r="D10">
-        <v>1654</v>
+        <v>1853</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1750,16 +1462,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46136.09375</v>
+        <v>46140.09375</v>
       </c>
       <c r="B11">
-        <v>328</v>
+        <v>822</v>
       </c>
       <c r="C11">
-        <v>1319</v>
+        <v>1058</v>
       </c>
       <c r="D11">
-        <v>1647</v>
+        <v>1880</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1770,16 +1482,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46136.10416666666</v>
+        <v>46140.10416666666</v>
       </c>
       <c r="B12">
-        <v>336</v>
+        <v>820</v>
       </c>
       <c r="C12">
-        <v>1321</v>
+        <v>1056</v>
       </c>
       <c r="D12">
-        <v>1657</v>
+        <v>1876</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1790,16 +1502,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46136.11458333334</v>
+        <v>46140.11458333334</v>
       </c>
       <c r="B13">
-        <v>328</v>
+        <v>818</v>
       </c>
       <c r="C13">
-        <v>1319</v>
+        <v>1055</v>
       </c>
       <c r="D13">
-        <v>1647</v>
+        <v>1873</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1810,16 +1522,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46136.125</v>
+        <v>46140.125</v>
       </c>
       <c r="B14">
-        <v>324</v>
+        <v>823</v>
       </c>
       <c r="C14">
-        <v>1285</v>
+        <v>926</v>
       </c>
       <c r="D14">
-        <v>1609</v>
+        <v>1749</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1830,16 +1542,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46136.13541666666</v>
+        <v>46140.13541666666</v>
       </c>
       <c r="B15">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>1281</v>
+        <v>921</v>
       </c>
       <c r="D15">
-        <v>1604</v>
+        <v>921</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1850,16 +1562,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46136.14583333334</v>
+        <v>46140.14583333334</v>
       </c>
       <c r="B16">
-        <v>324</v>
+        <v>824</v>
       </c>
       <c r="C16">
-        <v>1283</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1607</v>
+        <v>824</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1870,16 +1582,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46136.15625</v>
+        <v>46140.15625</v>
       </c>
       <c r="B17">
-        <v>329</v>
+        <v>825</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>329</v>
+        <v>825</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1890,16 +1602,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46136.16666666666</v>
+        <v>46140.16666666666</v>
       </c>
       <c r="B18">
-        <v>467</v>
+        <v>836</v>
       </c>
       <c r="C18">
-        <v>1279</v>
+        <v>927</v>
       </c>
       <c r="D18">
-        <v>1746</v>
+        <v>1763</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1910,16 +1622,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46136.17708333334</v>
+        <v>46140.17708333334</v>
       </c>
       <c r="B19">
-        <v>478</v>
+        <v>844</v>
       </c>
       <c r="C19">
-        <v>1276</v>
+        <v>926</v>
       </c>
       <c r="D19">
-        <v>1754</v>
+        <v>1770</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1930,16 +1642,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46136.1875</v>
+        <v>46140.1875</v>
       </c>
       <c r="B20">
-        <v>477</v>
+        <v>848</v>
       </c>
       <c r="C20">
-        <v>1277</v>
+        <v>927</v>
       </c>
       <c r="D20">
-        <v>1754</v>
+        <v>1775</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1950,16 +1662,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46136.19791666666</v>
+        <v>46140.19791666666</v>
       </c>
       <c r="B21">
-        <v>490</v>
+        <v>852</v>
       </c>
       <c r="C21">
-        <v>1274</v>
+        <v>923</v>
       </c>
       <c r="D21">
-        <v>1764</v>
+        <v>1775</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1970,16 +1682,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46136.20833333334</v>
+        <v>46140.20833333334</v>
       </c>
       <c r="B22">
-        <v>648</v>
+        <v>1055</v>
       </c>
       <c r="C22">
-        <v>1267</v>
+        <v>1116</v>
       </c>
       <c r="D22">
-        <v>1915</v>
+        <v>2171</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1990,16 +1702,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46136.21875</v>
+        <v>46140.21875</v>
       </c>
       <c r="B23">
-        <v>649</v>
+        <v>1054</v>
       </c>
       <c r="C23">
-        <v>1261</v>
+        <v>1135</v>
       </c>
       <c r="D23">
-        <v>1910</v>
+        <v>2189</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -2010,16 +1722,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46136.22916666666</v>
+        <v>46140.22916666666</v>
       </c>
       <c r="B24">
-        <v>653</v>
+        <v>1055</v>
       </c>
       <c r="C24">
-        <v>1264</v>
+        <v>1134</v>
       </c>
       <c r="D24">
-        <v>1917</v>
+        <v>2189</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -2030,16 +1742,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46136.23958333334</v>
+        <v>46140.23958333334</v>
       </c>
       <c r="B25">
-        <v>665</v>
+        <v>1050</v>
       </c>
       <c r="C25">
-        <v>1263</v>
+        <v>1132</v>
       </c>
       <c r="D25">
-        <v>1928</v>
+        <v>2182</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -2050,16 +1762,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46136.25</v>
+        <v>46140.25</v>
       </c>
       <c r="B26">
-        <v>670</v>
+        <v>1111</v>
       </c>
       <c r="C26">
-        <v>1188</v>
+        <v>1209</v>
       </c>
       <c r="D26">
-        <v>1858</v>
+        <v>2320</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -2070,16 +1782,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46136.26041666666</v>
+        <v>46140.26041666666</v>
       </c>
       <c r="B27">
-        <v>677</v>
+        <v>1115</v>
       </c>
       <c r="C27">
-        <v>1185</v>
+        <v>1202</v>
       </c>
       <c r="D27">
-        <v>1862</v>
+        <v>2317</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -2090,16 +1802,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46136.27083333334</v>
+        <v>46140.27083333334</v>
       </c>
       <c r="B28">
-        <v>676</v>
+        <v>1085</v>
       </c>
       <c r="C28">
-        <v>1186</v>
+        <v>1203</v>
       </c>
       <c r="D28">
-        <v>1862</v>
+        <v>2288</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -2110,16 +1822,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46136.28125</v>
+        <v>46140.28125</v>
       </c>
       <c r="B29">
-        <v>669</v>
+        <v>1066</v>
       </c>
       <c r="C29">
-        <v>1183</v>
+        <v>1204</v>
       </c>
       <c r="D29">
-        <v>1852</v>
+        <v>2270</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -2130,16 +1842,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46136.29166666666</v>
+        <v>46140.29166666666</v>
       </c>
       <c r="B30">
-        <v>473</v>
+        <v>614</v>
       </c>
       <c r="C30">
-        <v>1172</v>
+        <v>1191</v>
       </c>
       <c r="D30">
-        <v>1645</v>
+        <v>1805</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -2150,16 +1862,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46136.30208333334</v>
+        <v>46140.30208333334</v>
       </c>
       <c r="B31">
-        <v>448</v>
+        <v>607</v>
       </c>
       <c r="C31">
-        <v>1166</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1614</v>
+        <v>607</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -2170,16 +1882,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46136.3125</v>
+        <v>46140.3125</v>
       </c>
       <c r="B32">
-        <v>436</v>
+        <v>605</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="D32">
-        <v>436</v>
+        <v>1792</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -2190,16 +1902,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46136.32291666666</v>
+        <v>46140.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1167</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>1167</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -2210,16 +1922,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46136.33333333334</v>
+        <v>46140.33333333334</v>
       </c>
       <c r="B34">
-        <v>352</v>
+        <v>557</v>
       </c>
       <c r="C34">
-        <v>1197</v>
+        <v>995</v>
       </c>
       <c r="D34">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -2230,16 +1942,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46136.34375</v>
+        <v>46140.34375</v>
       </c>
       <c r="B35">
-        <v>344</v>
+        <v>538</v>
       </c>
       <c r="C35">
-        <v>1199</v>
+        <v>989</v>
       </c>
       <c r="D35">
-        <v>1543</v>
+        <v>1527</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -2250,16 +1962,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46136.35416666666</v>
+        <v>46140.35416666666</v>
       </c>
       <c r="B36">
-        <v>339</v>
+        <v>481</v>
       </c>
       <c r="C36">
-        <v>1204</v>
+        <v>980</v>
       </c>
       <c r="D36">
-        <v>1543</v>
+        <v>1461</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -2270,16 +1982,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46136.36458333334</v>
+        <v>46140.36458333334</v>
       </c>
       <c r="B37">
-        <v>187</v>
+        <v>407</v>
       </c>
       <c r="C37">
-        <v>1116</v>
+        <v>938</v>
       </c>
       <c r="D37">
-        <v>1303</v>
+        <v>1345</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -2290,16 +2002,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46136.375</v>
+        <v>46140.375</v>
       </c>
       <c r="B38">
-        <v>245</v>
+        <v>334</v>
       </c>
       <c r="C38">
-        <v>976</v>
+        <v>954</v>
       </c>
       <c r="D38">
-        <v>1221</v>
+        <v>1288</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -2310,16 +2022,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46136.38541666666</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="B39">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="C39">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="D39">
-        <v>1212</v>
+        <v>1277</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -2330,16 +2042,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46136.39583333334</v>
+        <v>46140.39583333334</v>
       </c>
       <c r="B40">
-        <v>230</v>
+        <v>329</v>
       </c>
       <c r="C40">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D40">
-        <v>1184</v>
+        <v>1282</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -2350,16 +2062,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46136.40625</v>
+        <v>46140.40625</v>
       </c>
       <c r="B41">
-        <v>226</v>
+        <v>326</v>
       </c>
       <c r="C41">
         <v>950</v>
       </c>
       <c r="D41">
-        <v>1176</v>
+        <v>1276</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -2370,16 +2082,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46136.41666666666</v>
+        <v>46140.41666666666</v>
       </c>
       <c r="B42">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C42">
-        <v>786</v>
+        <v>607</v>
       </c>
       <c r="D42">
-        <v>970</v>
+        <v>800</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -2390,16 +2102,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46136.42708333334</v>
+        <v>46140.42708333334</v>
       </c>
       <c r="B43">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="C43">
-        <v>759</v>
+        <v>587</v>
       </c>
       <c r="D43">
-        <v>902</v>
+        <v>775</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -2410,16 +2122,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46136.4375</v>
+        <v>46140.4375</v>
       </c>
       <c r="B44">
-        <v>142</v>
+        <v>192</v>
       </c>
       <c r="C44">
-        <v>763</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>905</v>
+        <v>192</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -2430,16 +2142,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46136.44791666666</v>
+        <v>46140.44791666666</v>
       </c>
       <c r="B45">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="C45">
-        <v>762</v>
+        <v>588</v>
       </c>
       <c r="D45">
-        <v>893</v>
+        <v>777</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -2450,16 +2162,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46136.45833333334</v>
+        <v>46140.45833333334</v>
       </c>
       <c r="B46">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="C46">
-        <v>764</v>
+        <v>519</v>
       </c>
       <c r="D46">
-        <v>887</v>
+        <v>695</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -2470,16 +2182,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46136.46875</v>
+        <v>46140.46875</v>
       </c>
       <c r="B47">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="C47">
-        <v>760</v>
+        <v>517</v>
       </c>
       <c r="D47">
-        <v>901</v>
+        <v>701</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -2490,16 +2202,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46136.47916666666</v>
+        <v>46140.47916666666</v>
       </c>
       <c r="B48">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C48">
-        <v>762</v>
+        <v>515</v>
       </c>
       <c r="D48">
-        <v>935</v>
+        <v>713</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -2510,16 +2222,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46136.48958333334</v>
+        <v>46140.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2530,16 +2242,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46136.5</v>
+        <v>46140.5</v>
       </c>
       <c r="B50">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="C50">
-        <v>701</v>
+        <v>513</v>
       </c>
       <c r="D50">
-        <v>987</v>
+        <v>700</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2550,16 +2262,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46136.51041666666</v>
+        <v>46140.51041666666</v>
       </c>
       <c r="B51">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="C51">
-        <v>702</v>
+        <v>511</v>
       </c>
       <c r="D51">
-        <v>983</v>
+        <v>700</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2570,16 +2282,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46136.52083333334</v>
+        <v>46140.52083333334</v>
       </c>
       <c r="B52">
-        <v>271</v>
+        <v>191</v>
       </c>
       <c r="C52">
-        <v>700</v>
+        <v>512</v>
       </c>
       <c r="D52">
-        <v>971</v>
+        <v>703</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2590,16 +2302,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46136.53125</v>
+        <v>46140.53125</v>
       </c>
       <c r="B53">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>968</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2610,16 +2322,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46136.54166666666</v>
+        <v>46140.54166666666</v>
       </c>
       <c r="B54">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="C54">
-        <v>704</v>
+        <v>474</v>
       </c>
       <c r="D54">
-        <v>832</v>
+        <v>648</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2630,16 +2342,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46136.55208333334</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="B55">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="C55">
-        <v>675</v>
+        <v>468</v>
       </c>
       <c r="D55">
-        <v>804</v>
+        <v>656</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2650,16 +2362,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46136.5625</v>
+        <v>46140.5625</v>
       </c>
       <c r="B56">
-        <v>128</v>
+        <v>189</v>
       </c>
       <c r="C56">
-        <v>674</v>
+        <v>466</v>
       </c>
       <c r="D56">
-        <v>802</v>
+        <v>655</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2670,16 +2382,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46136.57291666666</v>
+        <v>46140.57291666666</v>
       </c>
       <c r="B57">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="C57">
-        <v>675</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>801</v>
+        <v>179</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2690,16 +2402,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46136.58333333334</v>
+        <v>46140.58333333334</v>
       </c>
       <c r="B58">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="C58">
-        <v>706</v>
+        <v>474</v>
       </c>
       <c r="D58">
-        <v>838</v>
+        <v>682</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2710,16 +2422,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46136.59375</v>
+        <v>46140.59375</v>
       </c>
       <c r="B59">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="D59">
-        <v>134</v>
+        <v>668</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2730,16 +2442,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46136.60416666666</v>
+        <v>46140.60416666666</v>
       </c>
       <c r="B60">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="D60">
-        <v>131</v>
+        <v>682</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2750,16 +2462,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46136.61458333334</v>
+        <v>46140.61458333334</v>
       </c>
       <c r="B61">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="C61">
-        <v>708</v>
+        <v>486</v>
       </c>
       <c r="D61">
-        <v>835</v>
+        <v>694</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2770,16 +2482,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46136.625</v>
+        <v>46140.625</v>
       </c>
       <c r="B62">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>760</v>
+        <v>603</v>
       </c>
       <c r="D62">
-        <v>898</v>
+        <v>603</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2790,16 +2502,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46136.63541666666</v>
+        <v>46140.63541666666</v>
       </c>
       <c r="B63">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="C63">
-        <v>762</v>
+        <v>607</v>
       </c>
       <c r="D63">
-        <v>887</v>
+        <v>816</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2810,16 +2522,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46136.64583333334</v>
+        <v>46140.64583333334</v>
       </c>
       <c r="B64">
-        <v>146</v>
+        <v>226</v>
       </c>
       <c r="C64">
-        <v>770</v>
+        <v>616</v>
       </c>
       <c r="D64">
-        <v>916</v>
+        <v>842</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2830,16 +2542,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46136.65625</v>
+        <v>46140.65625</v>
       </c>
       <c r="B65">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="C65">
-        <v>781</v>
+        <v>628</v>
       </c>
       <c r="D65">
-        <v>919</v>
+        <v>849</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2850,16 +2562,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46136.66666666666</v>
+        <v>46140.66666666666</v>
       </c>
       <c r="B66">
-        <v>178</v>
+        <v>311</v>
       </c>
       <c r="C66">
-        <v>900</v>
+        <v>950</v>
       </c>
       <c r="D66">
-        <v>1078</v>
+        <v>1261</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2870,16 +2582,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46136.67708333334</v>
+        <v>46140.67708333334</v>
       </c>
       <c r="B67">
-        <v>181</v>
+        <v>340</v>
       </c>
       <c r="C67">
-        <v>923</v>
+        <v>969</v>
       </c>
       <c r="D67">
-        <v>1104</v>
+        <v>1309</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2890,16 +2602,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46136.6875</v>
+        <v>46140.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="C68">
-        <v>926</v>
+        <v>973</v>
       </c>
       <c r="D68">
-        <v>926</v>
+        <v>1316</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2910,16 +2622,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46136.69791666666</v>
+        <v>46140.69791666666</v>
       </c>
       <c r="B69">
-        <v>201</v>
+        <v>367</v>
       </c>
       <c r="C69">
-        <v>795</v>
+        <v>976</v>
       </c>
       <c r="D69">
-        <v>996</v>
+        <v>1343</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2930,16 +2642,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46136.70833333334</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="B70">
-        <v>370</v>
+        <v>558</v>
       </c>
       <c r="C70">
-        <v>987</v>
+        <v>1241</v>
       </c>
       <c r="D70">
-        <v>1357</v>
+        <v>1799</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2950,16 +2662,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46136.71875</v>
+        <v>46140.71875</v>
       </c>
       <c r="B71">
-        <v>388</v>
+        <v>569</v>
       </c>
       <c r="C71">
-        <v>1003</v>
+        <v>1285</v>
       </c>
       <c r="D71">
-        <v>1391</v>
+        <v>1854</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2970,16 +2682,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46136.72916666666</v>
+        <v>46140.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="C72">
-        <v>1094</v>
+        <v>1287</v>
       </c>
       <c r="D72">
-        <v>1094</v>
+        <v>1876</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2990,16 +2702,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46136.73958333334</v>
+        <v>46140.73958333334</v>
       </c>
       <c r="B73">
-        <v>410</v>
+        <v>636</v>
       </c>
       <c r="C73">
-        <v>1117</v>
+        <v>1285</v>
       </c>
       <c r="D73">
-        <v>1527</v>
+        <v>1921</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -3010,16 +2722,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46136.75</v>
+        <v>46140.75</v>
       </c>
       <c r="B74">
-        <v>864</v>
+        <v>1122</v>
       </c>
       <c r="C74">
-        <v>1327</v>
+        <v>1318</v>
       </c>
       <c r="D74">
-        <v>2191</v>
+        <v>2440</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -3030,16 +2742,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46136.76041666666</v>
+        <v>46140.76041666666</v>
       </c>
       <c r="B75">
-        <v>894</v>
+        <v>1132</v>
       </c>
       <c r="C75">
-        <v>1339</v>
+        <v>1320</v>
       </c>
       <c r="D75">
-        <v>2233</v>
+        <v>2452</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -3050,16 +2762,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46136.77083333334</v>
+        <v>46140.77083333334</v>
       </c>
       <c r="B76">
-        <v>998</v>
+        <v>1127</v>
       </c>
       <c r="C76">
-        <v>1375</v>
+        <v>1353</v>
       </c>
       <c r="D76">
-        <v>2373</v>
+        <v>2480</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -3070,16 +2782,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46136.78125</v>
+        <v>46140.78125</v>
       </c>
       <c r="B77">
-        <v>997</v>
+        <v>1136</v>
       </c>
       <c r="C77">
-        <v>1395</v>
+        <v>1358</v>
       </c>
       <c r="D77">
-        <v>2392</v>
+        <v>2494</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -3090,16 +2802,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46136.79166666666</v>
+        <v>46140.79166666666</v>
       </c>
       <c r="B78">
-        <v>993</v>
+        <v>1131</v>
       </c>
       <c r="C78">
-        <v>1483</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>2476</v>
+        <v>1131</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -3110,16 +2822,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46136.80208333334</v>
+        <v>46140.80208333334</v>
       </c>
       <c r="B79">
-        <v>1002</v>
+        <v>1135</v>
       </c>
       <c r="C79">
-        <v>1496</v>
+        <v>1361</v>
       </c>
       <c r="D79">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -3130,16 +2842,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46136.8125</v>
+        <v>46140.8125</v>
       </c>
       <c r="B80">
-        <v>995</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>1487</v>
+        <v>1362</v>
       </c>
       <c r="D80">
-        <v>2482</v>
+        <v>1362</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -3150,16 +2862,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46136.82291666666</v>
+        <v>46140.82291666666</v>
       </c>
       <c r="B81">
-        <v>998</v>
+        <v>1134</v>
       </c>
       <c r="C81">
-        <v>1490</v>
+        <v>1360</v>
       </c>
       <c r="D81">
-        <v>2488</v>
+        <v>2494</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -3170,16 +2882,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46136.83333333334</v>
+        <v>46140.83333333334</v>
       </c>
       <c r="B82">
-        <v>958</v>
+        <v>1133</v>
       </c>
       <c r="C82">
-        <v>1483</v>
+        <v>1382</v>
       </c>
       <c r="D82">
-        <v>2441</v>
+        <v>2515</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -3190,16 +2902,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46136.84375</v>
+        <v>46140.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="C83">
-        <v>1482</v>
+        <v>1379</v>
       </c>
       <c r="D83">
-        <v>1482</v>
+        <v>2509</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -3210,16 +2922,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46136.85416666666</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="B84">
-        <v>951</v>
+        <v>1131</v>
       </c>
       <c r="C84">
-        <v>1481</v>
+        <v>1369</v>
       </c>
       <c r="D84">
-        <v>2432</v>
+        <v>2500</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -3230,16 +2942,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46136.86458333334</v>
+        <v>46140.86458333334</v>
       </c>
       <c r="B85">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>1483</v>
+        <v>1370</v>
       </c>
       <c r="D85">
-        <v>2433</v>
+        <v>1370</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -3250,16 +2962,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46136.875</v>
+        <v>46140.875</v>
       </c>
       <c r="B86">
-        <v>854</v>
+        <v>1023</v>
       </c>
       <c r="C86">
-        <v>1422</v>
+        <v>1365</v>
       </c>
       <c r="D86">
-        <v>2276</v>
+        <v>2388</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -3270,16 +2982,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46136.88541666666</v>
+        <v>46140.88541666666</v>
       </c>
       <c r="B87">
-        <v>849</v>
+        <v>1017</v>
       </c>
       <c r="C87">
-        <v>1414</v>
+        <v>1387</v>
       </c>
       <c r="D87">
-        <v>2263</v>
+        <v>2404</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -3290,16 +3002,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46136.89583333334</v>
+        <v>46140.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="C88">
-        <v>1416</v>
+        <v>1393</v>
       </c>
       <c r="D88">
-        <v>1416</v>
+        <v>2413</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -3310,16 +3022,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46136.90625</v>
+        <v>46140.90625</v>
       </c>
       <c r="B89">
-        <v>844</v>
+        <v>1015</v>
       </c>
       <c r="C89">
-        <v>1411</v>
+        <v>1390</v>
       </c>
       <c r="D89">
-        <v>2255</v>
+        <v>2405</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -3330,16 +3042,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46136.91666666666</v>
+        <v>46140.91666666666</v>
       </c>
       <c r="B90">
-        <v>721</v>
+        <v>999</v>
       </c>
       <c r="C90">
-        <v>1383</v>
+        <v>1311</v>
       </c>
       <c r="D90">
-        <v>2104</v>
+        <v>2310</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -3350,16 +3062,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46136.92708333334</v>
+        <v>46140.92708333334</v>
       </c>
       <c r="B91">
-        <v>693</v>
+        <v>977</v>
       </c>
       <c r="C91">
-        <v>1382</v>
+        <v>1297</v>
       </c>
       <c r="D91">
-        <v>2075</v>
+        <v>2274</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -3370,16 +3082,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46136.9375</v>
+        <v>46140.9375</v>
       </c>
       <c r="B92">
-        <v>685</v>
+        <v>965</v>
       </c>
       <c r="C92">
-        <v>1354</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>2039</v>
+        <v>965</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -3390,16 +3102,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46136.94791666666</v>
+        <v>46140.94791666666</v>
       </c>
       <c r="B93">
-        <v>682</v>
+        <v>962</v>
       </c>
       <c r="C93">
-        <v>1350</v>
+        <v>1298</v>
       </c>
       <c r="D93">
-        <v>2032</v>
+        <v>2260</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -3410,16 +3122,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46136.95833333334</v>
+        <v>46140.95833333334</v>
       </c>
       <c r="B94">
-        <v>500</v>
+        <v>883</v>
       </c>
       <c r="C94">
-        <v>1416</v>
+        <v>1230</v>
       </c>
       <c r="D94">
-        <v>1916</v>
+        <v>2113</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -3430,16 +3142,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46136.96875</v>
+        <v>46140.96875</v>
       </c>
       <c r="B95">
-        <v>496</v>
+        <v>870</v>
       </c>
       <c r="C95">
-        <v>1392</v>
+        <v>1225</v>
       </c>
       <c r="D95">
-        <v>1888</v>
+        <v>2095</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -3450,16 +3162,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46136.97916666666</v>
+        <v>46140.97916666666</v>
       </c>
       <c r="B96">
-        <v>492</v>
+        <v>865</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="D96">
-        <v>492</v>
+        <v>2087</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -3470,16 +3182,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46136.98958333334</v>
+        <v>46140.98958333334</v>
       </c>
       <c r="B97">
-        <v>489</v>
+        <v>863</v>
       </c>
       <c r="C97">
-        <v>1389</v>
+        <v>1221</v>
       </c>
       <c r="D97">
-        <v>1878</v>
+        <v>2084</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -3490,16 +3202,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="B98">
-        <v>490</v>
+        <v>826</v>
       </c>
       <c r="C98">
-        <v>1423</v>
+        <v>1055</v>
       </c>
       <c r="D98">
-        <v>1913</v>
+        <v>1881</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3510,16 +3222,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46137.01041666666</v>
+        <v>46141.01041666666</v>
       </c>
       <c r="B99">
-        <v>477</v>
+        <v>821</v>
       </c>
       <c r="C99">
-        <v>1406</v>
+        <v>1032</v>
       </c>
       <c r="D99">
-        <v>1883</v>
+        <v>1853</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -3530,16 +3242,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46137.02083333334</v>
+        <v>46141.02083333334</v>
       </c>
       <c r="B100">
-        <v>481</v>
+        <v>816</v>
       </c>
       <c r="C100">
-        <v>1411</v>
+        <v>1031</v>
       </c>
       <c r="D100">
-        <v>1892</v>
+        <v>1847</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3550,16 +3262,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46137.03125</v>
+        <v>46141.03125</v>
       </c>
       <c r="B101">
-        <v>478</v>
+        <v>817</v>
       </c>
       <c r="C101">
-        <v>1409</v>
+        <v>1023</v>
       </c>
       <c r="D101">
-        <v>1887</v>
+        <v>1840</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3570,16 +3282,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46137.04166666666</v>
+        <v>46141.04166666666</v>
       </c>
       <c r="B102">
-        <v>276</v>
+        <v>498</v>
       </c>
       <c r="C102">
-        <v>1335</v>
+        <v>1015</v>
       </c>
       <c r="D102">
-        <v>1611</v>
+        <v>1513</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3590,16 +3302,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46137.05208333334</v>
+        <v>46141.05208333334</v>
       </c>
       <c r="B103">
-        <v>271</v>
+        <v>492</v>
       </c>
       <c r="C103">
-        <v>1330</v>
+        <v>1012</v>
       </c>
       <c r="D103">
-        <v>1601</v>
+        <v>1504</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3610,16 +3322,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46137.0625</v>
+        <v>46141.0625</v>
       </c>
       <c r="B104">
-        <v>270</v>
+        <v>496</v>
       </c>
       <c r="C104">
-        <v>1342</v>
+        <v>1013</v>
       </c>
       <c r="D104">
-        <v>1612</v>
+        <v>1509</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3630,16 +3342,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46137.07291666666</v>
+        <v>46141.07291666666</v>
       </c>
       <c r="B105">
-        <v>268</v>
+        <v>491</v>
       </c>
       <c r="C105">
-        <v>1343</v>
+        <v>1012</v>
       </c>
       <c r="D105">
-        <v>1611</v>
+        <v>1503</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3650,16 +3362,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46137.08333333334</v>
+        <v>46141.08333333334</v>
       </c>
       <c r="B106">
-        <v>272</v>
+        <v>408</v>
       </c>
       <c r="C106">
-        <v>1208</v>
+        <v>1013</v>
       </c>
       <c r="D106">
-        <v>1480</v>
+        <v>1421</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3670,16 +3382,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46137.09375</v>
+        <v>46141.09375</v>
       </c>
       <c r="B107">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="C107">
-        <v>1195</v>
+        <v>1012</v>
       </c>
       <c r="D107">
-        <v>1462</v>
+        <v>1419</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3690,16 +3402,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46137.10416666666</v>
+        <v>46141.10416666666</v>
       </c>
       <c r="B108">
-        <v>268</v>
+        <v>428</v>
       </c>
       <c r="C108">
-        <v>1197</v>
+        <v>1014</v>
       </c>
       <c r="D108">
-        <v>1465</v>
+        <v>1442</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3710,16 +3422,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46137.11458333334</v>
+        <v>46141.11458333334</v>
       </c>
       <c r="B109">
-        <v>266</v>
+        <v>410</v>
       </c>
       <c r="C109">
-        <v>1196</v>
+        <v>1011</v>
       </c>
       <c r="D109">
-        <v>1462</v>
+        <v>1421</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3730,16 +3442,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46137.125</v>
+        <v>46141.125</v>
       </c>
       <c r="B110">
-        <v>269</v>
+        <v>438</v>
       </c>
       <c r="C110">
-        <v>1168</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>1437</v>
+        <v>438</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3750,16 +3462,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46137.13541666666</v>
+        <v>46141.13541666666</v>
       </c>
       <c r="B111">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="C111">
-        <v>1166</v>
+        <v>1012</v>
       </c>
       <c r="D111">
-        <v>1433</v>
+        <v>1453</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3770,16 +3482,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46137.14583333334</v>
+        <v>46141.14583333334</v>
       </c>
       <c r="B112">
-        <v>268</v>
+        <v>440</v>
       </c>
       <c r="C112">
-        <v>1167</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1435</v>
+        <v>440</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3790,16 +3502,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46137.15625</v>
+        <v>46141.15625</v>
       </c>
       <c r="B113">
-        <v>277</v>
+        <v>444</v>
       </c>
       <c r="C113">
-        <v>1166</v>
+        <v>1009</v>
       </c>
       <c r="D113">
-        <v>1443</v>
+        <v>1453</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3810,16 +3522,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46137.16666666666</v>
+        <v>46141.16666666666</v>
       </c>
       <c r="B114">
-        <v>410</v>
+        <v>571</v>
       </c>
       <c r="C114">
-        <v>1227</v>
+        <v>1015</v>
       </c>
       <c r="D114">
-        <v>1637</v>
+        <v>1586</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3830,16 +3542,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46137.17708333334</v>
+        <v>46141.17708333334</v>
       </c>
       <c r="B115">
-        <v>421</v>
+        <v>574</v>
       </c>
       <c r="C115">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1651</v>
+        <v>574</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3850,16 +3562,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46137.1875</v>
+        <v>46141.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="C116">
-        <v>1231</v>
+        <v>1018</v>
       </c>
       <c r="D116">
-        <v>1231</v>
+        <v>1595</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3870,16 +3582,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46137.19791666666</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="B117">
-        <v>430</v>
+        <v>584</v>
       </c>
       <c r="C117">
-        <v>1234</v>
+        <v>1025</v>
       </c>
       <c r="D117">
-        <v>1664</v>
+        <v>1609</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3890,16 +3602,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46137.20833333334</v>
+        <v>46141.20833333334</v>
       </c>
       <c r="B118">
-        <v>534</v>
+        <v>706</v>
       </c>
       <c r="C118">
-        <v>1348</v>
+        <v>1235</v>
       </c>
       <c r="D118">
-        <v>1882</v>
+        <v>1941</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3910,16 +3622,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46137.21875</v>
+        <v>46141.21875</v>
       </c>
       <c r="B119">
-        <v>543</v>
+        <v>718</v>
       </c>
       <c r="C119">
-        <v>1350</v>
+        <v>1243</v>
       </c>
       <c r="D119">
-        <v>1893</v>
+        <v>1961</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3930,16 +3642,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46137.22916666666</v>
+        <v>46141.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>1351</v>
+        <v>1244</v>
       </c>
       <c r="D120">
-        <v>1351</v>
+        <v>1244</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3950,16 +3662,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46137.23958333334</v>
+        <v>46141.23958333334</v>
       </c>
       <c r="B121">
-        <v>533</v>
+        <v>706</v>
       </c>
       <c r="C121">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1892</v>
+        <v>706</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3970,16 +3682,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46137.25</v>
+        <v>46141.25</v>
       </c>
       <c r="B122">
-        <v>460</v>
+        <v>605</v>
       </c>
       <c r="C122">
-        <v>1245</v>
+        <v>1211</v>
       </c>
       <c r="D122">
-        <v>1705</v>
+        <v>1816</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3990,16 +3702,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46137.26041666666</v>
+        <v>46141.26041666666</v>
       </c>
       <c r="B123">
-        <v>455</v>
+        <v>594</v>
       </c>
       <c r="C123">
-        <v>1243</v>
+        <v>1200</v>
       </c>
       <c r="D123">
-        <v>1698</v>
+        <v>1794</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -4010,16 +3722,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46137.27083333334</v>
+        <v>46141.27083333334</v>
       </c>
       <c r="B124">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1240</v>
+        <v>1205</v>
       </c>
       <c r="D124">
-        <v>1690</v>
+        <v>1205</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -4030,16 +3742,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46137.28125</v>
+        <v>46141.28125</v>
       </c>
       <c r="B125">
-        <v>451</v>
+        <v>616</v>
       </c>
       <c r="C125">
-        <v>1243</v>
+        <v>1204</v>
       </c>
       <c r="D125">
-        <v>1694</v>
+        <v>1820</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -4050,16 +3762,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46137.29166666666</v>
+        <v>46141.29166666666</v>
       </c>
       <c r="B126">
-        <v>329</v>
+        <v>871</v>
       </c>
       <c r="C126">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="D126">
-        <v>1487</v>
+        <v>2056</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -4070,16 +3782,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46137.30208333334</v>
+        <v>46141.30208333334</v>
       </c>
       <c r="B127">
-        <v>317</v>
+        <v>899</v>
       </c>
       <c r="C127">
-        <v>1161</v>
+        <v>1183</v>
       </c>
       <c r="D127">
-        <v>1478</v>
+        <v>2082</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -4090,16 +3802,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46137.3125</v>
+        <v>46141.3125</v>
       </c>
       <c r="B128">
-        <v>322</v>
+        <v>891</v>
       </c>
       <c r="C128">
-        <v>1162</v>
+        <v>1184</v>
       </c>
       <c r="D128">
-        <v>1484</v>
+        <v>2075</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -4110,16 +3822,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46137.32291666666</v>
+        <v>46141.32291666666</v>
       </c>
       <c r="B129">
-        <v>329</v>
+        <v>880</v>
       </c>
       <c r="C129">
-        <v>1163</v>
+        <v>1183</v>
       </c>
       <c r="D129">
-        <v>1492</v>
+        <v>2063</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -4130,16 +3842,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46137.33333333334</v>
+        <v>46141.33333333334</v>
       </c>
       <c r="B130">
-        <v>228</v>
+        <v>794</v>
       </c>
       <c r="C130">
-        <v>1054</v>
+        <v>930</v>
       </c>
       <c r="D130">
-        <v>1282</v>
+        <v>1724</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -4150,16 +3862,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46137.34375</v>
+        <v>46141.34375</v>
       </c>
       <c r="B131">
-        <v>220</v>
+        <v>574</v>
       </c>
       <c r="C131">
-        <v>1048</v>
+        <v>831</v>
       </c>
       <c r="D131">
-        <v>1268</v>
+        <v>1405</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -4170,16 +3882,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46137.35416666666</v>
+        <v>46141.35416666666</v>
       </c>
       <c r="B132">
-        <v>201</v>
+        <v>594</v>
       </c>
       <c r="C132">
-        <v>1046</v>
+        <v>830</v>
       </c>
       <c r="D132">
-        <v>1247</v>
+        <v>1424</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -4190,16 +3902,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46137.36458333334</v>
+        <v>46141.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="C133">
-        <v>1049</v>
+        <v>821</v>
       </c>
       <c r="D133">
-        <v>1049</v>
+        <v>1453</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -4210,16 +3922,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46137.375</v>
+        <v>46141.375</v>
       </c>
       <c r="B134">
-        <v>136</v>
+        <v>562</v>
       </c>
       <c r="C134">
-        <v>904</v>
+        <v>794</v>
       </c>
       <c r="D134">
-        <v>1040</v>
+        <v>1356</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -4230,16 +3942,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46137.38541666666</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="B135">
-        <v>133</v>
+        <v>594</v>
       </c>
       <c r="C135">
-        <v>891</v>
+        <v>871</v>
       </c>
       <c r="D135">
-        <v>1024</v>
+        <v>1465</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -4250,16 +3962,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46137.39583333334</v>
+        <v>46141.39583333334</v>
       </c>
       <c r="B136">
-        <v>130</v>
+        <v>575</v>
       </c>
       <c r="C136">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D136">
-        <v>1014</v>
+        <v>1460</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -4270,16 +3982,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46137.40625</v>
+        <v>46141.40625</v>
       </c>
       <c r="B137">
-        <v>133</v>
+        <v>578</v>
       </c>
       <c r="C137">
-        <v>713</v>
+        <v>888</v>
       </c>
       <c r="D137">
-        <v>846</v>
+        <v>1466</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -4290,16 +4002,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46137.41666666666</v>
+        <v>46141.41666666666</v>
       </c>
       <c r="B138">
-        <v>146</v>
+        <v>270</v>
       </c>
       <c r="C138">
-        <v>622</v>
+        <v>577</v>
       </c>
       <c r="D138">
-        <v>768</v>
+        <v>847</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -4310,16 +4022,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46137.42708333334</v>
+        <v>46141.42708333334</v>
       </c>
       <c r="B139">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="C139">
-        <v>616</v>
+        <v>508</v>
       </c>
       <c r="D139">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -4330,16 +4042,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46137.4375</v>
+        <v>46141.4375</v>
       </c>
       <c r="B140">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="C140">
-        <v>698</v>
+        <v>444</v>
       </c>
       <c r="D140">
-        <v>812</v>
+        <v>618</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -4350,16 +4062,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46137.44791666666</v>
+        <v>46141.44791666666</v>
       </c>
       <c r="B141">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="C141">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>826</v>
+        <v>180</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -4370,16 +4082,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46137.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="B142">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="C142">
-        <v>672</v>
+        <v>460</v>
       </c>
       <c r="D142">
-        <v>773</v>
+        <v>604</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -4390,16 +4102,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46137.46875</v>
+        <v>46141.46875</v>
       </c>
       <c r="B143">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C143">
-        <v>656</v>
+        <v>462</v>
       </c>
       <c r="D143">
-        <v>756</v>
+        <v>592</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -4410,16 +4122,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46137.47916666666</v>
+        <v>46141.47916666666</v>
       </c>
       <c r="B144">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C144">
-        <v>747</v>
+        <v>459</v>
       </c>
       <c r="D144">
-        <v>843</v>
+        <v>581</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -4430,16 +4142,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46137.48958333334</v>
+        <v>46141.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C145">
-        <v>754</v>
+        <v>458</v>
       </c>
       <c r="D145">
-        <v>754</v>
+        <v>579</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -4450,16 +4162,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46137.5</v>
+        <v>46141.5</v>
       </c>
       <c r="B146">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C146">
-        <v>737</v>
+        <v>456</v>
       </c>
       <c r="D146">
-        <v>839</v>
+        <v>566</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -4470,16 +4182,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46137.51041666666</v>
+        <v>46141.51041666666</v>
       </c>
       <c r="B147">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C147">
-        <v>740</v>
+        <v>449</v>
       </c>
       <c r="D147">
-        <v>848</v>
+        <v>556</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -4490,16 +4202,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46137.52083333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C148">
-        <v>738</v>
+        <v>418</v>
       </c>
       <c r="D148">
-        <v>738</v>
+        <v>528</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -4510,16 +4222,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46137.53125</v>
+        <v>46141.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="C149">
-        <v>737</v>
+        <v>417</v>
       </c>
       <c r="D149">
-        <v>737</v>
+        <v>526</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -4530,16 +4242,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46137.54166666666</v>
+        <v>46141.54166666666</v>
       </c>
       <c r="B150">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C150">
-        <v>748</v>
+        <v>413</v>
       </c>
       <c r="D150">
-        <v>842</v>
+        <v>521</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -4550,16 +4262,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46137.55208333334</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="B151">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="D151">
-        <v>93</v>
+        <v>528</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -4570,16 +4282,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46137.5625</v>
+        <v>46141.5625</v>
       </c>
       <c r="B152">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="D152">
-        <v>94</v>
+        <v>518</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4590,16 +4302,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46137.57291666666</v>
+        <v>46141.57291666666</v>
       </c>
       <c r="B153">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="D153">
-        <v>93</v>
+        <v>544</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4610,16 +4322,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46137.58333333334</v>
+        <v>46141.58333333334</v>
       </c>
       <c r="B154">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C154">
-        <v>735</v>
+        <v>427</v>
       </c>
       <c r="D154">
-        <v>826</v>
+        <v>540</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4630,16 +4342,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46137.59375</v>
+        <v>46141.59375</v>
       </c>
       <c r="B155">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="C155">
-        <v>738</v>
+        <v>426</v>
       </c>
       <c r="D155">
-        <v>827</v>
+        <v>577</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4650,16 +4362,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46137.60416666666</v>
+        <v>46141.60416666666</v>
       </c>
       <c r="B156">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="C156">
-        <v>603</v>
+        <v>485</v>
       </c>
       <c r="D156">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4670,16 +4382,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46137.61458333334</v>
+        <v>46141.61458333334</v>
       </c>
       <c r="B157">
-        <v>93</v>
+        <v>230</v>
       </c>
       <c r="C157">
-        <v>587</v>
+        <v>484</v>
       </c>
       <c r="D157">
-        <v>680</v>
+        <v>714</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4690,16 +4402,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46137.625</v>
+        <v>46141.625</v>
       </c>
       <c r="B158">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="C158">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="D158">
-        <v>691</v>
+        <v>840</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4710,16 +4422,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46137.63541666666</v>
+        <v>46141.63541666666</v>
       </c>
       <c r="B159">
-        <v>99</v>
+        <v>289</v>
       </c>
       <c r="C159">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="D159">
-        <v>692</v>
+        <v>853</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4730,16 +4442,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46137.64583333334</v>
+        <v>46141.64583333334</v>
       </c>
       <c r="B160">
-        <v>103</v>
+        <v>305</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="D160">
-        <v>103</v>
+        <v>859</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4750,16 +4462,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46137.65625</v>
+        <v>46141.65625</v>
       </c>
       <c r="B161">
-        <v>102</v>
+        <v>333</v>
       </c>
       <c r="C161">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="D161">
-        <v>700</v>
+        <v>922</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4770,16 +4482,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46137.66666666666</v>
+        <v>46141.66666666666</v>
       </c>
       <c r="B162">
-        <v>114</v>
+        <v>669</v>
       </c>
       <c r="C162">
-        <v>766</v>
+        <v>929</v>
       </c>
       <c r="D162">
-        <v>880</v>
+        <v>1598</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4790,16 +4502,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46137.67708333334</v>
+        <v>46141.67708333334</v>
       </c>
       <c r="B163">
-        <v>119</v>
+        <v>684</v>
       </c>
       <c r="C163">
-        <v>776</v>
+        <v>919</v>
       </c>
       <c r="D163">
-        <v>895</v>
+        <v>1603</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4810,16 +4522,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46137.6875</v>
+        <v>46141.6875</v>
       </c>
       <c r="B164">
-        <v>124</v>
+        <v>698</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>923</v>
       </c>
       <c r="D164">
-        <v>124</v>
+        <v>1621</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4830,16 +4542,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46137.69791666666</v>
+        <v>46141.69791666666</v>
       </c>
       <c r="B165">
-        <v>151</v>
+        <v>715</v>
       </c>
       <c r="C165">
-        <v>783</v>
+        <v>924</v>
       </c>
       <c r="D165">
-        <v>934</v>
+        <v>1639</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4850,16 +4562,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46137.70833333334</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="B166">
-        <v>329</v>
+        <v>742</v>
       </c>
       <c r="C166">
-        <v>1083</v>
+        <v>1050</v>
       </c>
       <c r="D166">
-        <v>1412</v>
+        <v>1792</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4870,16 +4582,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46137.71875</v>
+        <v>46141.71875</v>
       </c>
       <c r="B167">
-        <v>341</v>
+        <v>762</v>
       </c>
       <c r="C167">
-        <v>1116</v>
+        <v>1068</v>
       </c>
       <c r="D167">
-        <v>1457</v>
+        <v>1830</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4890,16 +4602,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46137.72916666666</v>
+        <v>46141.72916666666</v>
       </c>
       <c r="B168">
-        <v>349</v>
+        <v>760</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1083</v>
       </c>
       <c r="D168">
-        <v>349</v>
+        <v>1843</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4910,16 +4622,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46137.73958333334</v>
+        <v>46141.73958333334</v>
       </c>
       <c r="B169">
-        <v>377</v>
+        <v>797</v>
       </c>
       <c r="C169">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>1593</v>
+        <v>797</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4930,16 +4642,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46137.75</v>
+        <v>46141.75</v>
       </c>
       <c r="B170">
-        <v>795</v>
+        <v>1156</v>
       </c>
       <c r="C170">
-        <v>1381</v>
+        <v>1145</v>
       </c>
       <c r="D170">
-        <v>2176</v>
+        <v>2301</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4950,16 +4662,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46137.76041666666</v>
+        <v>46141.76041666666</v>
       </c>
       <c r="B171">
-        <v>800</v>
+        <v>1164</v>
       </c>
       <c r="C171">
-        <v>1406</v>
+        <v>1152</v>
       </c>
       <c r="D171">
-        <v>2206</v>
+        <v>2316</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4970,16 +4682,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46137.77083333334</v>
+        <v>46141.77083333334</v>
       </c>
       <c r="B172">
-        <v>793</v>
+        <v>1110</v>
       </c>
       <c r="C172">
-        <v>1401</v>
+        <v>1141</v>
       </c>
       <c r="D172">
-        <v>2194</v>
+        <v>2251</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4990,16 +4702,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46137.78125</v>
+        <v>46141.78125</v>
       </c>
       <c r="B173">
-        <v>812</v>
+        <v>1150</v>
       </c>
       <c r="C173">
-        <v>1400</v>
+        <v>1147</v>
       </c>
       <c r="D173">
-        <v>2212</v>
+        <v>2297</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -5010,16 +4722,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46137.79166666666</v>
+        <v>46141.79166666666</v>
       </c>
       <c r="B174">
-        <v>799</v>
+        <v>1173</v>
       </c>
       <c r="C174">
-        <v>1403</v>
+        <v>1140</v>
       </c>
       <c r="D174">
-        <v>2202</v>
+        <v>2313</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -5030,16 +4742,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46137.80208333334</v>
+        <v>46141.80208333334</v>
       </c>
       <c r="B175">
-        <v>810</v>
+        <v>1131</v>
       </c>
       <c r="C175">
-        <v>1415</v>
+        <v>1179</v>
       </c>
       <c r="D175">
-        <v>2225</v>
+        <v>2310</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -5050,16 +4762,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46137.8125</v>
+        <v>46141.8125</v>
       </c>
       <c r="B176">
-        <v>809</v>
+        <v>1119</v>
       </c>
       <c r="C176">
-        <v>1435</v>
+        <v>1196</v>
       </c>
       <c r="D176">
-        <v>2244</v>
+        <v>2315</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -5070,16 +4782,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46137.82291666666</v>
+        <v>46141.82291666666</v>
       </c>
       <c r="B177">
-        <v>826</v>
+        <v>1141</v>
       </c>
       <c r="C177">
-        <v>1434</v>
+        <v>1197</v>
       </c>
       <c r="D177">
-        <v>2260</v>
+        <v>2338</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -5090,16 +4802,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46137.83333333334</v>
+        <v>46141.83333333334</v>
       </c>
       <c r="B178">
-        <v>790</v>
+        <v>1056</v>
       </c>
       <c r="C178">
-        <v>1403</v>
+        <v>1150</v>
       </c>
       <c r="D178">
-        <v>2193</v>
+        <v>2206</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -5110,16 +4822,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46137.84375</v>
+        <v>46141.84375</v>
       </c>
       <c r="B179">
-        <v>775</v>
+        <v>1022</v>
       </c>
       <c r="C179">
-        <v>1398</v>
+        <v>1140</v>
       </c>
       <c r="D179">
-        <v>2173</v>
+        <v>2162</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -5130,16 +4842,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46137.85416666666</v>
+        <v>46141.85416666666</v>
       </c>
       <c r="B180">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="C180">
-        <v>1394</v>
+        <v>1141</v>
       </c>
       <c r="D180">
-        <v>2165</v>
+        <v>1141</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -5150,16 +4862,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46137.86458333334</v>
+        <v>46141.86458333334</v>
       </c>
       <c r="B181">
-        <v>769</v>
+        <v>1011</v>
       </c>
       <c r="C181">
-        <v>1396</v>
+        <v>1142</v>
       </c>
       <c r="D181">
-        <v>2165</v>
+        <v>2153</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -5170,16 +4882,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46137.875</v>
+        <v>46141.875</v>
       </c>
       <c r="B182">
-        <v>688</v>
+        <v>975</v>
       </c>
       <c r="C182">
-        <v>1414</v>
+        <v>1179</v>
       </c>
       <c r="D182">
-        <v>2102</v>
+        <v>2154</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -5190,16 +4902,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46137.88541666666</v>
+        <v>46141.88541666666</v>
       </c>
       <c r="B183">
-        <v>686</v>
+        <v>977</v>
       </c>
       <c r="C183">
-        <v>1430</v>
+        <v>1187</v>
       </c>
       <c r="D183">
-        <v>2116</v>
+        <v>2164</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -5210,16 +4922,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46137.89583333334</v>
+        <v>46141.89583333334</v>
       </c>
       <c r="B184">
-        <v>685</v>
+        <v>964</v>
       </c>
       <c r="C184">
-        <v>1428</v>
+        <v>1184</v>
       </c>
       <c r="D184">
-        <v>2113</v>
+        <v>2148</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -5230,16 +4942,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46137.90625</v>
+        <v>46141.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="C185">
-        <v>1432</v>
+        <v>1195</v>
       </c>
       <c r="D185">
-        <v>1432</v>
+        <v>2157</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -5250,16 +4962,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46137.91666666666</v>
+        <v>46141.91666666666</v>
       </c>
       <c r="B186">
-        <v>598</v>
+        <v>665</v>
       </c>
       <c r="C186">
-        <v>1436</v>
+        <v>1315</v>
       </c>
       <c r="D186">
-        <v>2034</v>
+        <v>1980</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -5270,16 +4982,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46137.92708333334</v>
+        <v>46141.92708333334</v>
       </c>
       <c r="B187">
-        <v>592</v>
+        <v>654</v>
       </c>
       <c r="C187">
-        <v>1433</v>
+        <v>1294</v>
       </c>
       <c r="D187">
-        <v>2025</v>
+        <v>1948</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -5290,16 +5002,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46137.9375</v>
+        <v>46141.9375</v>
       </c>
       <c r="B188">
-        <v>594</v>
+        <v>651</v>
       </c>
       <c r="C188">
-        <v>1445</v>
+        <v>1283</v>
       </c>
       <c r="D188">
-        <v>2039</v>
+        <v>1934</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -5310,16 +5022,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46137.94791666666</v>
+        <v>46141.94791666666</v>
       </c>
       <c r="B189">
-        <v>589</v>
+        <v>649</v>
       </c>
       <c r="C189">
-        <v>1442</v>
+        <v>1284</v>
       </c>
       <c r="D189">
-        <v>2031</v>
+        <v>1933</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -5330,16 +5042,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46137.95833333334</v>
+        <v>46141.95833333334</v>
       </c>
       <c r="B190">
-        <v>490</v>
+        <v>571</v>
       </c>
       <c r="C190">
-        <v>1494</v>
+        <v>1013</v>
       </c>
       <c r="D190">
-        <v>1984</v>
+        <v>1584</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -5350,16 +5062,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46137.96875</v>
+        <v>46141.96875</v>
       </c>
       <c r="B191">
-        <v>482</v>
+        <v>564</v>
       </c>
       <c r="C191">
-        <v>1497</v>
+        <v>971</v>
       </c>
       <c r="D191">
-        <v>1979</v>
+        <v>1535</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -5370,16 +5082,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46137.97916666666</v>
+        <v>46141.97916666666</v>
       </c>
       <c r="B192">
-        <v>478</v>
+        <v>565</v>
       </c>
       <c r="C192">
-        <v>1501</v>
+        <v>973</v>
       </c>
       <c r="D192">
-        <v>1979</v>
+        <v>1538</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -5390,16 +5102,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46137.98958333334</v>
+        <v>46141.98958333334</v>
       </c>
       <c r="B193">
-        <v>475</v>
+        <v>562</v>
       </c>
       <c r="C193">
-        <v>1496</v>
+        <v>0</v>
       </c>
       <c r="D193">
-        <v>1971</v>
+        <v>562</v>
       </c>
       <c r="E193">
         <v>96</v>
@@ -5410,16 +5122,16 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B194">
-        <v>320</v>
+        <v>628</v>
       </c>
       <c r="C194">
-        <v>1471</v>
+        <v>1000</v>
       </c>
       <c r="D194">
-        <v>1791</v>
+        <v>1628</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -5430,16 +5142,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2">
-        <v>46138.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B195">
-        <v>319</v>
+        <v>625</v>
       </c>
       <c r="C195">
-        <v>1465</v>
+        <v>995</v>
       </c>
       <c r="D195">
-        <v>1784</v>
+        <v>1620</v>
       </c>
       <c r="E195">
         <v>2</v>
@@ -5450,16 +5162,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2">
-        <v>46138.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B196">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -5470,16 +5182,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2">
-        <v>46138.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B197">
-        <v>317</v>
+        <v>623</v>
       </c>
       <c r="C197">
-        <v>1466</v>
+        <v>993</v>
       </c>
       <c r="D197">
-        <v>1783</v>
+        <v>1616</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -5490,16 +5202,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2">
-        <v>46138.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B198">
-        <v>173</v>
+        <v>648</v>
       </c>
       <c r="C198">
-        <v>1390</v>
+        <v>954</v>
       </c>
       <c r="D198">
-        <v>1563</v>
+        <v>1602</v>
       </c>
       <c r="E198">
         <v>5</v>
@@ -5510,16 +5222,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2">
-        <v>46138.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B199">
-        <v>162</v>
+        <v>644</v>
       </c>
       <c r="C199">
-        <v>1377</v>
+        <v>955</v>
       </c>
       <c r="D199">
-        <v>1539</v>
+        <v>1599</v>
       </c>
       <c r="E199">
         <v>6</v>
@@ -5530,16 +5242,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2">
-        <v>46138.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B200">
-        <v>174</v>
+        <v>645</v>
       </c>
       <c r="C200">
-        <v>1378</v>
+        <v>0</v>
       </c>
       <c r="D200">
-        <v>1552</v>
+        <v>645</v>
       </c>
       <c r="E200">
         <v>7</v>
@@ -5550,16 +5262,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2">
-        <v>46138.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B201">
-        <v>158</v>
+        <v>643</v>
       </c>
       <c r="C201">
-        <v>1377</v>
+        <v>954</v>
       </c>
       <c r="D201">
-        <v>1535</v>
+        <v>1597</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -5570,16 +5282,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2">
-        <v>46138.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B202">
-        <v>141</v>
+        <v>636</v>
       </c>
       <c r="C202">
-        <v>1230</v>
+        <v>955</v>
       </c>
       <c r="D202">
-        <v>1371</v>
+        <v>1591</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -5590,16 +5302,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2">
-        <v>46138.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B203">
-        <v>140</v>
+        <v>641</v>
       </c>
       <c r="C203">
-        <v>1184</v>
+        <v>956</v>
       </c>
       <c r="D203">
-        <v>1324</v>
+        <v>1597</v>
       </c>
       <c r="E203">
         <v>10</v>
@@ -5610,16 +5322,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2">
-        <v>46138.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B204">
-        <v>141</v>
+        <v>642</v>
       </c>
       <c r="C204">
-        <v>1188</v>
+        <v>969</v>
       </c>
       <c r="D204">
-        <v>1329</v>
+        <v>1611</v>
       </c>
       <c r="E204">
         <v>11</v>
@@ -5630,16 +5342,16 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="2">
-        <v>46138.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B205">
-        <v>139</v>
+        <v>634</v>
       </c>
       <c r="C205">
-        <v>1185</v>
+        <v>966</v>
       </c>
       <c r="D205">
-        <v>1324</v>
+        <v>1600</v>
       </c>
       <c r="E205">
         <v>12</v>
@@ -5650,16 +5362,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2">
-        <v>46138.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B206">
-        <v>138</v>
+        <v>637</v>
       </c>
       <c r="C206">
-        <v>1202</v>
+        <v>970</v>
       </c>
       <c r="D206">
-        <v>1340</v>
+        <v>1607</v>
       </c>
       <c r="E206">
         <v>13</v>
@@ -5670,16 +5382,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2">
-        <v>46138.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B207">
-        <v>128</v>
+        <v>646</v>
       </c>
       <c r="C207">
-        <v>1201</v>
+        <v>969</v>
       </c>
       <c r="D207">
-        <v>1329</v>
+        <v>1615</v>
       </c>
       <c r="E207">
         <v>14</v>
@@ -5690,16 +5402,16 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2">
-        <v>46138.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B208">
-        <v>118</v>
+        <v>652</v>
       </c>
       <c r="C208">
-        <v>1195</v>
+        <v>970</v>
       </c>
       <c r="D208">
-        <v>1313</v>
+        <v>1622</v>
       </c>
       <c r="E208">
         <v>15</v>
@@ -5710,16 +5422,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2">
-        <v>46138.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B209">
-        <v>125</v>
+        <v>646</v>
       </c>
       <c r="C209">
-        <v>1186</v>
+        <v>969</v>
       </c>
       <c r="D209">
-        <v>1311</v>
+        <v>1615</v>
       </c>
       <c r="E209">
         <v>16</v>
@@ -5730,16 +5442,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2">
-        <v>46138.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B210">
-        <v>121</v>
+        <v>657</v>
       </c>
       <c r="C210">
-        <v>1181</v>
+        <v>972</v>
       </c>
       <c r="D210">
-        <v>1302</v>
+        <v>1629</v>
       </c>
       <c r="E210">
         <v>17</v>
@@ -5750,16 +5462,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2">
-        <v>46138.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B211">
-        <v>120</v>
+        <v>658</v>
       </c>
       <c r="C211">
         <v>0</v>
       </c>
       <c r="D211">
-        <v>120</v>
+        <v>658</v>
       </c>
       <c r="E211">
         <v>18</v>
@@ -5770,16 +5482,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2">
-        <v>46138.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B212">
-        <v>119</v>
+        <v>669</v>
       </c>
       <c r="C212">
-        <v>1182</v>
+        <v>971</v>
       </c>
       <c r="D212">
-        <v>1301</v>
+        <v>1640</v>
       </c>
       <c r="E212">
         <v>19</v>
@@ -5790,16 +5502,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2">
-        <v>46138.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B213">
-        <v>123</v>
+        <v>674</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="D213">
-        <v>123</v>
+        <v>1649</v>
       </c>
       <c r="E213">
         <v>20</v>
@@ -5810,16 +5522,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2">
-        <v>46138.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B214">
-        <v>172</v>
+        <v>652</v>
       </c>
       <c r="C214">
-        <v>1141</v>
+        <v>1057</v>
       </c>
       <c r="D214">
-        <v>1313</v>
+        <v>1709</v>
       </c>
       <c r="E214">
         <v>21</v>
@@ -5830,16 +5542,16 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2">
-        <v>46138.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B215">
-        <v>178</v>
+        <v>668</v>
       </c>
       <c r="C215">
-        <v>1138</v>
+        <v>1067</v>
       </c>
       <c r="D215">
-        <v>1316</v>
+        <v>1735</v>
       </c>
       <c r="E215">
         <v>22</v>
@@ -5850,16 +5562,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2">
-        <v>46138.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B216">
-        <v>184</v>
+        <v>675</v>
       </c>
       <c r="C216">
-        <v>1140</v>
+        <v>1064</v>
       </c>
       <c r="D216">
-        <v>1324</v>
+        <v>1739</v>
       </c>
       <c r="E216">
         <v>23</v>
@@ -5870,16 +5582,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2">
-        <v>46138.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B217">
-        <v>185</v>
+        <v>680</v>
       </c>
       <c r="C217">
-        <v>1139</v>
+        <v>1069</v>
       </c>
       <c r="D217">
-        <v>1324</v>
+        <v>1749</v>
       </c>
       <c r="E217">
         <v>24</v>
@@ -5890,16 +5602,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="2">
-        <v>46138.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B218">
-        <v>191</v>
+        <v>735</v>
       </c>
       <c r="C218">
-        <v>1203</v>
+        <v>1132</v>
       </c>
       <c r="D218">
-        <v>1394</v>
+        <v>1867</v>
       </c>
       <c r="E218">
         <v>25</v>
@@ -5910,16 +5622,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="2">
-        <v>46138.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B219">
-        <v>189</v>
+        <v>821</v>
       </c>
       <c r="C219">
-        <v>1194</v>
+        <v>1138</v>
       </c>
       <c r="D219">
-        <v>1383</v>
+        <v>1959</v>
       </c>
       <c r="E219">
         <v>26</v>
@@ -5930,16 +5642,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2">
-        <v>46138.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B220">
-        <v>188</v>
+        <v>1052</v>
       </c>
       <c r="C220">
-        <v>1188</v>
+        <v>1137</v>
       </c>
       <c r="D220">
-        <v>1376</v>
+        <v>2189</v>
       </c>
       <c r="E220">
         <v>27</v>
@@ -5950,16 +5662,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2">
-        <v>46138.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B221">
-        <v>190</v>
+        <v>1110</v>
       </c>
       <c r="C221">
-        <v>1189</v>
+        <v>0</v>
       </c>
       <c r="D221">
-        <v>1379</v>
+        <v>1110</v>
       </c>
       <c r="E221">
         <v>28</v>
@@ -5970,16 +5682,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="2">
-        <v>46138.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B222">
-        <v>205</v>
+        <v>1034</v>
       </c>
       <c r="C222">
-        <v>1163</v>
+        <v>1138</v>
       </c>
       <c r="D222">
-        <v>1368</v>
+        <v>2172</v>
       </c>
       <c r="E222">
         <v>29</v>
@@ -5990,16 +5702,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2">
-        <v>46138.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B223">
-        <v>207</v>
+        <v>1089</v>
       </c>
       <c r="C223">
-        <v>1162</v>
+        <v>1148</v>
       </c>
       <c r="D223">
-        <v>1369</v>
+        <v>2237</v>
       </c>
       <c r="E223">
         <v>30</v>
@@ -6010,16 +5722,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="2">
-        <v>46138.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="C224">
-        <v>1165</v>
+        <v>1152</v>
       </c>
       <c r="D224">
-        <v>1165</v>
+        <v>2240</v>
       </c>
       <c r="E224">
         <v>31</v>
@@ -6030,16 +5742,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2">
-        <v>46138.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B225">
-        <v>205</v>
+        <v>1078</v>
       </c>
       <c r="C225">
-        <v>1180</v>
+        <v>0</v>
       </c>
       <c r="D225">
-        <v>1385</v>
+        <v>1078</v>
       </c>
       <c r="E225">
         <v>32</v>
@@ -6050,16 +5762,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2">
-        <v>46138.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B226">
-        <v>168</v>
+        <v>1113</v>
       </c>
       <c r="C226">
-        <v>904</v>
+        <v>936</v>
       </c>
       <c r="D226">
-        <v>1072</v>
+        <v>2049</v>
       </c>
       <c r="E226">
         <v>33</v>
@@ -6070,16 +5782,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2">
-        <v>46138.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B227">
-        <v>151</v>
+        <v>1087</v>
       </c>
       <c r="C227">
-        <v>844</v>
+        <v>916</v>
       </c>
       <c r="D227">
-        <v>995</v>
+        <v>2003</v>
       </c>
       <c r="E227">
         <v>34</v>
@@ -6090,16 +5802,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2">
-        <v>46138.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B228">
-        <v>131</v>
+        <v>1040</v>
       </c>
       <c r="C228">
-        <v>847</v>
+        <v>955</v>
       </c>
       <c r="D228">
-        <v>978</v>
+        <v>1995</v>
       </c>
       <c r="E228">
         <v>35</v>
@@ -6110,16 +5822,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2">
-        <v>46138.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B229">
-        <v>187</v>
+        <v>922</v>
       </c>
       <c r="C229">
-        <v>926</v>
+        <v>959</v>
       </c>
       <c r="D229">
-        <v>1113</v>
+        <v>1881</v>
       </c>
       <c r="E229">
         <v>36</v>
@@ -6130,16 +5842,16 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2">
-        <v>46138.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B230">
-        <v>198</v>
+        <v>920</v>
       </c>
       <c r="C230">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D230">
-        <v>1106</v>
+        <v>1824</v>
       </c>
       <c r="E230">
         <v>37</v>
@@ -6150,16 +5862,16 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2">
-        <v>46138.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B231">
-        <v>180</v>
+        <v>905</v>
       </c>
       <c r="C231">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="D231">
-        <v>1083</v>
+        <v>1804</v>
       </c>
       <c r="E231">
         <v>38</v>
@@ -6170,16 +5882,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2">
-        <v>46138.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B232">
-        <v>175</v>
+        <v>663</v>
       </c>
       <c r="C232">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="D232">
-        <v>1065</v>
+        <v>663</v>
       </c>
       <c r="E232">
         <v>39</v>
@@ -6190,16 +5902,16 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2">
-        <v>46138.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B233">
-        <v>112</v>
+        <v>581</v>
       </c>
       <c r="C233">
-        <v>861</v>
+        <v>898</v>
       </c>
       <c r="D233">
-        <v>973</v>
+        <v>1479</v>
       </c>
       <c r="E233">
         <v>40</v>
@@ -6210,16 +5922,16 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2">
-        <v>46138.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B234">
-        <v>110</v>
+        <v>303</v>
       </c>
       <c r="C234">
-        <v>767</v>
+        <v>658</v>
       </c>
       <c r="D234">
-        <v>877</v>
+        <v>961</v>
       </c>
       <c r="E234">
         <v>41</v>
@@ -6230,16 +5942,16 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2">
-        <v>46138.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B235">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="C235">
-        <v>750</v>
+        <v>643</v>
       </c>
       <c r="D235">
-        <v>858</v>
+        <v>926</v>
       </c>
       <c r="E235">
         <v>42</v>
@@ -6250,16 +5962,16 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2">
-        <v>46138.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B236">
-        <v>109</v>
+        <v>284</v>
       </c>
       <c r="C236">
-        <v>722</v>
+        <v>650</v>
       </c>
       <c r="D236">
-        <v>831</v>
+        <v>934</v>
       </c>
       <c r="E236">
         <v>43</v>
@@ -6270,16 +5982,16 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="2">
-        <v>46138.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B237">
-        <v>108</v>
+        <v>307</v>
       </c>
       <c r="C237">
-        <v>647</v>
+        <v>595</v>
       </c>
       <c r="D237">
-        <v>755</v>
+        <v>902</v>
       </c>
       <c r="E237">
         <v>44</v>
@@ -6290,16 +6002,16 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2">
-        <v>46138.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B238">
-        <v>98</v>
+        <v>260</v>
       </c>
       <c r="C238">
-        <v>614</v>
+        <v>563</v>
       </c>
       <c r="D238">
-        <v>712</v>
+        <v>823</v>
       </c>
       <c r="E238">
         <v>45</v>
@@ -6310,16 +6022,16 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2">
-        <v>46138.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B239">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C239">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="D239">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>46</v>
@@ -6330,16 +6042,16 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2">
-        <v>46138.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B240">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C240">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="D240">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>47</v>
@@ -6350,16 +6062,16 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2">
-        <v>46138.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B241">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C241">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="D241">
-        <v>704</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>48</v>
@@ -6370,16 +6082,16 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="2">
-        <v>46138.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B242">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="C242">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="D242">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="E242">
         <v>49</v>
@@ -6390,16 +6102,16 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="2">
-        <v>46138.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B243">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C243">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="D243">
-        <v>708</v>
+        <v>0</v>
       </c>
       <c r="E243">
         <v>50</v>
@@ -6410,16 +6122,16 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2">
-        <v>46138.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="D244">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="E244">
         <v>51</v>
@@ -6430,16 +6142,16 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2">
-        <v>46138.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
-        <v>466</v>
+        <v>0</v>
       </c>
       <c r="D245">
-        <v>466</v>
+        <v>0</v>
       </c>
       <c r="E245">
         <v>52</v>
@@ -6450,16 +6162,16 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2">
-        <v>46138.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B246">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="C246">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="D246">
-        <v>551</v>
+        <v>0</v>
       </c>
       <c r="E246">
         <v>53</v>
@@ -6470,16 +6182,16 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2">
-        <v>46138.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="D247">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>54</v>
@@ -6490,16 +6202,16 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2">
-        <v>46138.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B248">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C248">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="D248">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="E248">
         <v>55</v>
@@ -6510,16 +6222,16 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2">
-        <v>46138.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B249">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="C249">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>56</v>
@@ -6530,16 +6242,16 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2">
-        <v>46138.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B250">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C250">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="D250">
-        <v>569</v>
+        <v>0</v>
       </c>
       <c r="E250">
         <v>57</v>
@@ -6550,16 +6262,16 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2">
-        <v>46138.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B251">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="E251">
         <v>58</v>
@@ -6570,16 +6282,16 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2">
-        <v>46138.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B252">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C252">
         <v>0</v>
       </c>
       <c r="D252">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="E252">
         <v>59</v>
@@ -6590,16 +6302,16 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2">
-        <v>46138.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B253">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C253">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="D253">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -6610,16 +6322,16 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2">
-        <v>46138.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B254">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C254">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="D254">
-        <v>542</v>
+        <v>0</v>
       </c>
       <c r="E254">
         <v>61</v>
@@ -6630,16 +6342,16 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2">
-        <v>46138.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B255">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="C255">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="D255">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>62</v>
@@ -6650,16 +6362,16 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2">
-        <v>46138.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B256">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="C256">
-        <v>488</v>
+        <v>0</v>
       </c>
       <c r="D256">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="E256">
         <v>63</v>
@@ -6670,16 +6382,16 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2">
-        <v>46138.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B257">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="C257">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="D257">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="E257">
         <v>64</v>
@@ -6690,16 +6402,16 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2">
-        <v>46138.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B258">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="C258">
-        <v>536</v>
+        <v>0</v>
       </c>
       <c r="D258">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="E258">
         <v>65</v>
@@ -6710,16 +6422,16 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2">
-        <v>46138.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B259">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C259">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="D259">
-        <v>721</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>66</v>
@@ -6730,16 +6442,16 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="2">
-        <v>46138.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B260">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C260">
         <v>0</v>
       </c>
       <c r="D260">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="E260">
         <v>67</v>
@@ -6750,16 +6462,16 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="2">
-        <v>46138.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B261">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C261">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="D261">
-        <v>737</v>
+        <v>0</v>
       </c>
       <c r="E261">
         <v>68</v>
@@ -6770,16 +6482,16 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2">
-        <v>46138.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B262">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C262">
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="D262">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="E262">
         <v>69</v>
@@ -6790,16 +6502,16 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2">
-        <v>46138.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B263">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="C263">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="D263">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="E263">
         <v>70</v>
@@ -6810,16 +6522,16 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2">
-        <v>46138.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B264">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="C264">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="D264">
-        <v>1169</v>
+        <v>0</v>
       </c>
       <c r="E264">
         <v>71</v>
@@ -6830,16 +6542,16 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="2">
-        <v>46138.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B265">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="C265">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="D265">
-        <v>1294</v>
+        <v>0</v>
       </c>
       <c r="E265">
         <v>72</v>
@@ -6850,16 +6562,16 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2">
-        <v>46138.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B266">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="C266">
-        <v>1111</v>
+        <v>0</v>
       </c>
       <c r="D266">
-        <v>1501</v>
+        <v>0</v>
       </c>
       <c r="E266">
         <v>73</v>
@@ -6870,16 +6582,16 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2">
-        <v>46138.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B267">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="C267">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="D267">
-        <v>1569</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>74</v>
@@ -6890,16 +6602,16 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="2">
-        <v>46138.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B268">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="C268">
-        <v>1227</v>
+        <v>0</v>
       </c>
       <c r="D268">
-        <v>1630</v>
+        <v>0</v>
       </c>
       <c r="E268">
         <v>75</v>
@@ -6910,16 +6622,16 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2">
-        <v>46138.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B269">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="C269">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="D269">
-        <v>1654</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>76</v>
@@ -6930,16 +6642,16 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2">
-        <v>46138.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B270">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="C270">
-        <v>1372</v>
+        <v>0</v>
       </c>
       <c r="D270">
-        <v>1844</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>77</v>
@@ -6950,16 +6662,16 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2">
-        <v>46138.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B271">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="C271">
-        <v>1385</v>
+        <v>0</v>
       </c>
       <c r="D271">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>78</v>
@@ -6970,16 +6682,16 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="2">
-        <v>46138.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B272">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="C272">
         <v>0</v>
       </c>
       <c r="D272">
-        <v>491</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>79</v>
@@ -6990,16 +6702,16 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2">
-        <v>46138.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B273">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="C273">
-        <v>1392</v>
+        <v>0</v>
       </c>
       <c r="D273">
-        <v>1922</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>80</v>
@@ -7010,16 +6722,16 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="2">
-        <v>46138.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B274">
-        <v>747</v>
+        <v>0</v>
       </c>
       <c r="C274">
-        <v>1468</v>
+        <v>0</v>
       </c>
       <c r="D274">
-        <v>2215</v>
+        <v>0</v>
       </c>
       <c r="E274">
         <v>81</v>
@@ -7030,16 +6742,16 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2">
-        <v>46138.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B275">
-        <v>772</v>
+        <v>0</v>
       </c>
       <c r="C275">
-        <v>1474</v>
+        <v>0</v>
       </c>
       <c r="D275">
-        <v>2246</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>82</v>
@@ -7050,16 +6762,16 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="2">
-        <v>46138.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B276">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="C276">
         <v>0</v>
       </c>
       <c r="D276">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="E276">
         <v>83</v>
@@ -7070,16 +6782,16 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2">
-        <v>46138.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B277">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="C277">
         <v>0</v>
       </c>
       <c r="D277">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>84</v>
@@ -7090,16 +6802,16 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="2">
-        <v>46138.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B278">
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="C278">
-        <v>1481</v>
+        <v>0</v>
       </c>
       <c r="D278">
-        <v>2278</v>
+        <v>0</v>
       </c>
       <c r="E278">
         <v>85</v>
@@ -7110,16 +6822,16 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2">
-        <v>46138.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B279">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="C279">
-        <v>1484</v>
+        <v>0</v>
       </c>
       <c r="D279">
-        <v>2269</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>86</v>
@@ -7130,16 +6842,16 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="2">
-        <v>46138.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B280">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="C280">
         <v>0</v>
       </c>
       <c r="D280">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="E280">
         <v>87</v>
@@ -7150,16 +6862,16 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2">
-        <v>46138.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B281">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="C281">
         <v>0</v>
       </c>
       <c r="D281">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="E281">
         <v>88</v>
@@ -7170,16 +6882,16 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2">
-        <v>46138.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B282">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="C282">
-        <v>1507</v>
+        <v>0</v>
       </c>
       <c r="D282">
-        <v>2212</v>
+        <v>0</v>
       </c>
       <c r="E282">
         <v>89</v>
@@ -7190,16 +6902,16 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2">
-        <v>46138.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B283">
-        <v>711</v>
+        <v>0</v>
       </c>
       <c r="C283">
-        <v>1502</v>
+        <v>0</v>
       </c>
       <c r="D283">
-        <v>2213</v>
+        <v>0</v>
       </c>
       <c r="E283">
         <v>90</v>
@@ -7210,16 +6922,16 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2">
-        <v>46138.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B284">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="C284">
-        <v>1495</v>
+        <v>0</v>
       </c>
       <c r="D284">
-        <v>2202</v>
+        <v>0</v>
       </c>
       <c r="E284">
         <v>91</v>
@@ -7230,16 +6942,16 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2">
-        <v>46138.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B285">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="C285">
-        <v>1494</v>
+        <v>0</v>
       </c>
       <c r="D285">
-        <v>2175</v>
+        <v>0</v>
       </c>
       <c r="E285">
         <v>92</v>
@@ -7250,16 +6962,16 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2">
-        <v>46138.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B286">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="C286">
-        <v>1397</v>
+        <v>0</v>
       </c>
       <c r="D286">
-        <v>2083</v>
+        <v>0</v>
       </c>
       <c r="E286">
         <v>93</v>
@@ -7270,16 +6982,16 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="2">
-        <v>46138.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B287">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="C287">
-        <v>1374</v>
+        <v>0</v>
       </c>
       <c r="D287">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E287">
         <v>94</v>
@@ -7290,16 +7002,16 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="2">
-        <v>46138.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B288">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="C288">
-        <v>1407</v>
+        <v>0</v>
       </c>
       <c r="D288">
-        <v>2026</v>
+        <v>0</v>
       </c>
       <c r="E288">
         <v>95</v>
@@ -7310,1942 +7022,22 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2">
-        <v>46138.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B289">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="C289">
-        <v>1402</v>
+        <v>0</v>
       </c>
       <c r="D289">
-        <v>1970</v>
+        <v>0</v>
       </c>
       <c r="E289">
         <v>96</v>
       </c>
       <c r="F289" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
-      <c r="A290" s="2">
-        <v>46139</v>
-      </c>
-      <c r="B290">
-        <v>589</v>
-      </c>
-      <c r="C290">
-        <v>1215</v>
-      </c>
-      <c r="D290">
-        <v>1804</v>
-      </c>
-      <c r="E290">
-        <v>1</v>
-      </c>
-      <c r="F290" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
-      <c r="A291" s="2">
-        <v>46139.01041666666</v>
-      </c>
-      <c r="B291">
-        <v>593</v>
-      </c>
-      <c r="C291">
-        <v>1174</v>
-      </c>
-      <c r="D291">
-        <v>1767</v>
-      </c>
-      <c r="E291">
-        <v>2</v>
-      </c>
-      <c r="F291" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
-      <c r="A292" s="2">
-        <v>46139.02083333334</v>
-      </c>
-      <c r="B292">
-        <v>532</v>
-      </c>
-      <c r="C292">
-        <v>1173</v>
-      </c>
-      <c r="D292">
-        <v>1705</v>
-      </c>
-      <c r="E292">
-        <v>3</v>
-      </c>
-      <c r="F292" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
-      <c r="A293" s="2">
-        <v>46139.03125</v>
-      </c>
-      <c r="B293">
-        <v>524</v>
-      </c>
-      <c r="C293">
-        <v>1171</v>
-      </c>
-      <c r="D293">
-        <v>1695</v>
-      </c>
-      <c r="E293">
-        <v>4</v>
-      </c>
-      <c r="F293" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
-      <c r="A294" s="2">
-        <v>46139.04166666666</v>
-      </c>
-      <c r="B294">
-        <v>513</v>
-      </c>
-      <c r="C294">
-        <v>1158</v>
-      </c>
-      <c r="D294">
-        <v>1671</v>
-      </c>
-      <c r="E294">
-        <v>5</v>
-      </c>
-      <c r="F294" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
-      <c r="A295" s="2">
-        <v>46139.05208333334</v>
-      </c>
-      <c r="B295">
-        <v>505</v>
-      </c>
-      <c r="C295">
-        <v>1146</v>
-      </c>
-      <c r="D295">
-        <v>1651</v>
-      </c>
-      <c r="E295">
-        <v>6</v>
-      </c>
-      <c r="F295" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
-      <c r="A296" s="2">
-        <v>46139.0625</v>
-      </c>
-      <c r="B296">
-        <v>511</v>
-      </c>
-      <c r="C296">
-        <v>1134</v>
-      </c>
-      <c r="D296">
-        <v>1645</v>
-      </c>
-      <c r="E296">
-        <v>7</v>
-      </c>
-      <c r="F296" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
-      <c r="A297" s="2">
-        <v>46139.07291666666</v>
-      </c>
-      <c r="B297">
-        <v>497</v>
-      </c>
-      <c r="C297">
-        <v>1196</v>
-      </c>
-      <c r="D297">
-        <v>1693</v>
-      </c>
-      <c r="E297">
-        <v>8</v>
-      </c>
-      <c r="F297" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
-      <c r="A298" s="2">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="B298">
-        <v>512</v>
-      </c>
-      <c r="C298">
-        <v>1201</v>
-      </c>
-      <c r="D298">
-        <v>1713</v>
-      </c>
-      <c r="E298">
-        <v>9</v>
-      </c>
-      <c r="F298" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
-      <c r="A299" s="2">
-        <v>46139.09375</v>
-      </c>
-      <c r="B299">
-        <v>523</v>
-      </c>
-      <c r="C299">
-        <v>0</v>
-      </c>
-      <c r="D299">
-        <v>523</v>
-      </c>
-      <c r="E299">
-        <v>10</v>
-      </c>
-      <c r="F299" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
-      <c r="A300" s="2">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="B300">
-        <v>533</v>
-      </c>
-      <c r="C300">
-        <v>0</v>
-      </c>
-      <c r="D300">
-        <v>533</v>
-      </c>
-      <c r="E300">
-        <v>11</v>
-      </c>
-      <c r="F300" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
-      <c r="A301" s="2">
-        <v>46139.11458333334</v>
-      </c>
-      <c r="B301">
-        <v>523</v>
-      </c>
-      <c r="C301">
-        <v>1203</v>
-      </c>
-      <c r="D301">
-        <v>1726</v>
-      </c>
-      <c r="E301">
-        <v>12</v>
-      </c>
-      <c r="F301" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
-      <c r="A302" s="2">
-        <v>46139.125</v>
-      </c>
-      <c r="B302">
-        <v>534</v>
-      </c>
-      <c r="C302">
-        <v>1208</v>
-      </c>
-      <c r="D302">
-        <v>1742</v>
-      </c>
-      <c r="E302">
-        <v>13</v>
-      </c>
-      <c r="F302" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6">
-      <c r="A303" s="2">
-        <v>46139.13541666666</v>
-      </c>
-      <c r="B303">
-        <v>544</v>
-      </c>
-      <c r="C303">
-        <v>1206</v>
-      </c>
-      <c r="D303">
-        <v>1750</v>
-      </c>
-      <c r="E303">
-        <v>14</v>
-      </c>
-      <c r="F303" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
-      <c r="A304" s="2">
-        <v>46139.14583333334</v>
-      </c>
-      <c r="B304">
-        <v>548</v>
-      </c>
-      <c r="C304">
-        <v>0</v>
-      </c>
-      <c r="D304">
-        <v>548</v>
-      </c>
-      <c r="E304">
-        <v>15</v>
-      </c>
-      <c r="F304" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
-      <c r="A305" s="2">
-        <v>46139.15625</v>
-      </c>
-      <c r="B305">
-        <v>0</v>
-      </c>
-      <c r="C305">
-        <v>1229</v>
-      </c>
-      <c r="D305">
-        <v>1229</v>
-      </c>
-      <c r="E305">
-        <v>16</v>
-      </c>
-      <c r="F305" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6">
-      <c r="A306" s="2">
-        <v>46139.16666666666</v>
-      </c>
-      <c r="B306">
-        <v>509</v>
-      </c>
-      <c r="C306">
-        <v>1332</v>
-      </c>
-      <c r="D306">
-        <v>1841</v>
-      </c>
-      <c r="E306">
-        <v>17</v>
-      </c>
-      <c r="F306" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
-      <c r="A307" s="2">
-        <v>46139.17708333334</v>
-      </c>
-      <c r="B307">
-        <v>0</v>
-      </c>
-      <c r="C307">
-        <v>0</v>
-      </c>
-      <c r="D307">
-        <v>0</v>
-      </c>
-      <c r="E307">
-        <v>18</v>
-      </c>
-      <c r="F307" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
-      <c r="A308" s="2">
-        <v>46139.1875</v>
-      </c>
-      <c r="B308">
-        <v>512</v>
-      </c>
-      <c r="C308">
-        <v>0</v>
-      </c>
-      <c r="D308">
-        <v>512</v>
-      </c>
-      <c r="E308">
-        <v>19</v>
-      </c>
-      <c r="F308" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
-      <c r="A309" s="2">
-        <v>46139.19791666666</v>
-      </c>
-      <c r="B309">
-        <v>521</v>
-      </c>
-      <c r="C309">
-        <v>0</v>
-      </c>
-      <c r="D309">
-        <v>521</v>
-      </c>
-      <c r="E309">
-        <v>20</v>
-      </c>
-      <c r="F309" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
-      <c r="A310" s="2">
-        <v>46139.20833333334</v>
-      </c>
-      <c r="B310">
-        <v>454</v>
-      </c>
-      <c r="C310">
-        <v>1323</v>
-      </c>
-      <c r="D310">
-        <v>1777</v>
-      </c>
-      <c r="E310">
-        <v>21</v>
-      </c>
-      <c r="F310" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6">
-      <c r="A311" s="2">
-        <v>46139.21875</v>
-      </c>
-      <c r="B311">
-        <v>450</v>
-      </c>
-      <c r="C311">
-        <v>1329</v>
-      </c>
-      <c r="D311">
-        <v>1779</v>
-      </c>
-      <c r="E311">
-        <v>22</v>
-      </c>
-      <c r="F311" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
-      <c r="A312" s="2">
-        <v>46139.22916666666</v>
-      </c>
-      <c r="B312">
-        <v>455</v>
-      </c>
-      <c r="C312">
-        <v>1332</v>
-      </c>
-      <c r="D312">
-        <v>1787</v>
-      </c>
-      <c r="E312">
-        <v>23</v>
-      </c>
-      <c r="F312" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
-      <c r="A313" s="2">
-        <v>46139.23958333334</v>
-      </c>
-      <c r="B313">
-        <v>461</v>
-      </c>
-      <c r="C313">
-        <v>1331</v>
-      </c>
-      <c r="D313">
-        <v>1792</v>
-      </c>
-      <c r="E313">
-        <v>24</v>
-      </c>
-      <c r="F313" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6">
-      <c r="A314" s="2">
-        <v>46139.25</v>
-      </c>
-      <c r="B314">
-        <v>607</v>
-      </c>
-      <c r="C314">
-        <v>1369</v>
-      </c>
-      <c r="D314">
-        <v>1976</v>
-      </c>
-      <c r="E314">
-        <v>25</v>
-      </c>
-      <c r="F314" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
-      <c r="A315" s="2">
-        <v>46139.26041666666</v>
-      </c>
-      <c r="B315">
-        <v>620</v>
-      </c>
-      <c r="C315">
-        <v>1366</v>
-      </c>
-      <c r="D315">
-        <v>1986</v>
-      </c>
-      <c r="E315">
-        <v>26</v>
-      </c>
-      <c r="F315" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
-      <c r="A316" s="2">
-        <v>46139.27083333334</v>
-      </c>
-      <c r="B316">
-        <v>621</v>
-      </c>
-      <c r="C316">
-        <v>1362</v>
-      </c>
-      <c r="D316">
-        <v>1983</v>
-      </c>
-      <c r="E316">
-        <v>27</v>
-      </c>
-      <c r="F316" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6">
-      <c r="A317" s="2">
-        <v>46139.28125</v>
-      </c>
-      <c r="B317">
-        <v>611</v>
-      </c>
-      <c r="C317">
-        <v>1360</v>
-      </c>
-      <c r="D317">
-        <v>1971</v>
-      </c>
-      <c r="E317">
-        <v>28</v>
-      </c>
-      <c r="F317" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6">
-      <c r="A318" s="2">
-        <v>46139.29166666666</v>
-      </c>
-      <c r="B318">
-        <v>644</v>
-      </c>
-      <c r="C318">
-        <v>1324</v>
-      </c>
-      <c r="D318">
-        <v>1968</v>
-      </c>
-      <c r="E318">
-        <v>29</v>
-      </c>
-      <c r="F318" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6">
-      <c r="A319" s="2">
-        <v>46139.30208333334</v>
-      </c>
-      <c r="B319">
-        <v>630</v>
-      </c>
-      <c r="C319">
-        <v>1316</v>
-      </c>
-      <c r="D319">
-        <v>1946</v>
-      </c>
-      <c r="E319">
-        <v>30</v>
-      </c>
-      <c r="F319" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6">
-      <c r="A320" s="2">
-        <v>46139.3125</v>
-      </c>
-      <c r="B320">
-        <v>641</v>
-      </c>
-      <c r="C320">
-        <v>1309</v>
-      </c>
-      <c r="D320">
-        <v>1950</v>
-      </c>
-      <c r="E320">
-        <v>31</v>
-      </c>
-      <c r="F320" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6">
-      <c r="A321" s="2">
-        <v>46139.32291666666</v>
-      </c>
-      <c r="B321">
-        <v>629</v>
-      </c>
-      <c r="C321">
-        <v>1313</v>
-      </c>
-      <c r="D321">
-        <v>1942</v>
-      </c>
-      <c r="E321">
-        <v>32</v>
-      </c>
-      <c r="F321" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6">
-      <c r="A322" s="2">
-        <v>46139.33333333334</v>
-      </c>
-      <c r="B322">
-        <v>529</v>
-      </c>
-      <c r="C322">
-        <v>1311</v>
-      </c>
-      <c r="D322">
-        <v>1840</v>
-      </c>
-      <c r="E322">
-        <v>33</v>
-      </c>
-      <c r="F322" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6">
-      <c r="A323" s="2">
-        <v>46139.34375</v>
-      </c>
-      <c r="B323">
-        <v>527</v>
-      </c>
-      <c r="C323">
-        <v>1310</v>
-      </c>
-      <c r="D323">
-        <v>1837</v>
-      </c>
-      <c r="E323">
-        <v>34</v>
-      </c>
-      <c r="F323" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6">
-      <c r="A324" s="2">
-        <v>46139.35416666666</v>
-      </c>
-      <c r="B324">
-        <v>501</v>
-      </c>
-      <c r="C324">
-        <v>1255</v>
-      </c>
-      <c r="D324">
-        <v>1756</v>
-      </c>
-      <c r="E324">
-        <v>35</v>
-      </c>
-      <c r="F324" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6">
-      <c r="A325" s="2">
-        <v>46139.36458333334</v>
-      </c>
-      <c r="B325">
-        <v>492</v>
-      </c>
-      <c r="C325">
-        <v>1252</v>
-      </c>
-      <c r="D325">
-        <v>1744</v>
-      </c>
-      <c r="E325">
-        <v>36</v>
-      </c>
-      <c r="F325" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6">
-      <c r="A326" s="2">
-        <v>46139.375</v>
-      </c>
-      <c r="B326">
-        <v>346</v>
-      </c>
-      <c r="C326">
-        <v>1013</v>
-      </c>
-      <c r="D326">
-        <v>1359</v>
-      </c>
-      <c r="E326">
-        <v>37</v>
-      </c>
-      <c r="F326" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6">
-      <c r="A327" s="2">
-        <v>46139.38541666666</v>
-      </c>
-      <c r="B327">
-        <v>336</v>
-      </c>
-      <c r="C327">
-        <v>981</v>
-      </c>
-      <c r="D327">
-        <v>1317</v>
-      </c>
-      <c r="E327">
-        <v>38</v>
-      </c>
-      <c r="F327" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
-      <c r="A328" s="2">
-        <v>46139.39583333334</v>
-      </c>
-      <c r="B328">
-        <v>311</v>
-      </c>
-      <c r="C328">
-        <v>976</v>
-      </c>
-      <c r="D328">
-        <v>1287</v>
-      </c>
-      <c r="E328">
-        <v>39</v>
-      </c>
-      <c r="F328" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6">
-      <c r="A329" s="2">
-        <v>46139.40625</v>
-      </c>
-      <c r="B329">
-        <v>301</v>
-      </c>
-      <c r="C329">
-        <v>1007</v>
-      </c>
-      <c r="D329">
-        <v>1308</v>
-      </c>
-      <c r="E329">
-        <v>40</v>
-      </c>
-      <c r="F329" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6">
-      <c r="A330" s="2">
-        <v>46139.41666666666</v>
-      </c>
-      <c r="B330">
-        <v>137</v>
-      </c>
-      <c r="C330">
-        <v>641</v>
-      </c>
-      <c r="D330">
-        <v>778</v>
-      </c>
-      <c r="E330">
-        <v>41</v>
-      </c>
-      <c r="F330" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6">
-      <c r="A331" s="2">
-        <v>46139.42708333334</v>
-      </c>
-      <c r="B331">
-        <v>128</v>
-      </c>
-      <c r="C331">
-        <v>574</v>
-      </c>
-      <c r="D331">
-        <v>702</v>
-      </c>
-      <c r="E331">
-        <v>42</v>
-      </c>
-      <c r="F331" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6">
-      <c r="A332" s="2">
-        <v>46139.4375</v>
-      </c>
-      <c r="B332">
-        <v>130</v>
-      </c>
-      <c r="C332">
-        <v>573</v>
-      </c>
-      <c r="D332">
-        <v>703</v>
-      </c>
-      <c r="E332">
-        <v>43</v>
-      </c>
-      <c r="F332" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6">
-      <c r="A333" s="2">
-        <v>46139.44791666666</v>
-      </c>
-      <c r="B333">
-        <v>128</v>
-      </c>
-      <c r="C333">
-        <v>572</v>
-      </c>
-      <c r="D333">
-        <v>700</v>
-      </c>
-      <c r="E333">
-        <v>44</v>
-      </c>
-      <c r="F333" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6">
-      <c r="A334" s="2">
-        <v>46139.45833333334</v>
-      </c>
-      <c r="B334">
-        <v>145</v>
-      </c>
-      <c r="C334">
-        <v>569</v>
-      </c>
-      <c r="D334">
-        <v>714</v>
-      </c>
-      <c r="E334">
-        <v>45</v>
-      </c>
-      <c r="F334" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6">
-      <c r="A335" s="2">
-        <v>46139.46875</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-      <c r="C335">
-        <v>0</v>
-      </c>
-      <c r="D335">
-        <v>0</v>
-      </c>
-      <c r="E335">
-        <v>46</v>
-      </c>
-      <c r="F335" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6">
-      <c r="A336" s="2">
-        <v>46139.47916666666</v>
-      </c>
-      <c r="B336">
-        <v>0</v>
-      </c>
-      <c r="C336">
-        <v>0</v>
-      </c>
-      <c r="D336">
-        <v>0</v>
-      </c>
-      <c r="E336">
-        <v>47</v>
-      </c>
-      <c r="F336" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6">
-      <c r="A337" s="2">
-        <v>46139.48958333334</v>
-      </c>
-      <c r="B337">
-        <v>0</v>
-      </c>
-      <c r="C337">
-        <v>0</v>
-      </c>
-      <c r="D337">
-        <v>0</v>
-      </c>
-      <c r="E337">
-        <v>48</v>
-      </c>
-      <c r="F337" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6">
-      <c r="A338" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B338">
-        <v>0</v>
-      </c>
-      <c r="C338">
-        <v>0</v>
-      </c>
-      <c r="D338">
-        <v>0</v>
-      </c>
-      <c r="E338">
-        <v>49</v>
-      </c>
-      <c r="F338" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6">
-      <c r="A339" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B339">
-        <v>0</v>
-      </c>
-      <c r="C339">
-        <v>0</v>
-      </c>
-      <c r="D339">
-        <v>0</v>
-      </c>
-      <c r="E339">
-        <v>50</v>
-      </c>
-      <c r="F339" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6">
-      <c r="A340" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B340">
-        <v>0</v>
-      </c>
-      <c r="C340">
-        <v>0</v>
-      </c>
-      <c r="D340">
-        <v>0</v>
-      </c>
-      <c r="E340">
-        <v>51</v>
-      </c>
-      <c r="F340" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6">
-      <c r="A341" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B341">
-        <v>0</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
-      </c>
-      <c r="D341">
-        <v>0</v>
-      </c>
-      <c r="E341">
-        <v>52</v>
-      </c>
-      <c r="F341" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6">
-      <c r="A342" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B342">
-        <v>0</v>
-      </c>
-      <c r="C342">
-        <v>0</v>
-      </c>
-      <c r="D342">
-        <v>0</v>
-      </c>
-      <c r="E342">
-        <v>53</v>
-      </c>
-      <c r="F342" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6">
-      <c r="A343" s="2">
-        <v>46139.55208333334</v>
-      </c>
-      <c r="B343">
-        <v>0</v>
-      </c>
-      <c r="C343">
-        <v>0</v>
-      </c>
-      <c r="D343">
-        <v>0</v>
-      </c>
-      <c r="E343">
-        <v>54</v>
-      </c>
-      <c r="F343" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6">
-      <c r="A344" s="2">
-        <v>46139.5625</v>
-      </c>
-      <c r="B344">
-        <v>0</v>
-      </c>
-      <c r="C344">
-        <v>0</v>
-      </c>
-      <c r="D344">
-        <v>0</v>
-      </c>
-      <c r="E344">
-        <v>55</v>
-      </c>
-      <c r="F344" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6">
-      <c r="A345" s="2">
-        <v>46139.57291666666</v>
-      </c>
-      <c r="B345">
-        <v>0</v>
-      </c>
-      <c r="C345">
-        <v>0</v>
-      </c>
-      <c r="D345">
-        <v>0</v>
-      </c>
-      <c r="E345">
-        <v>56</v>
-      </c>
-      <c r="F345" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6">
-      <c r="A346" s="2">
-        <v>46139.58333333334</v>
-      </c>
-      <c r="B346">
-        <v>0</v>
-      </c>
-      <c r="C346">
-        <v>0</v>
-      </c>
-      <c r="D346">
-        <v>0</v>
-      </c>
-      <c r="E346">
-        <v>57</v>
-      </c>
-      <c r="F346" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6">
-      <c r="A347" s="2">
-        <v>46139.59375</v>
-      </c>
-      <c r="B347">
-        <v>0</v>
-      </c>
-      <c r="C347">
-        <v>0</v>
-      </c>
-      <c r="D347">
-        <v>0</v>
-      </c>
-      <c r="E347">
-        <v>58</v>
-      </c>
-      <c r="F347" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6">
-      <c r="A348" s="2">
-        <v>46139.60416666666</v>
-      </c>
-      <c r="B348">
-        <v>0</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-      <c r="D348">
-        <v>0</v>
-      </c>
-      <c r="E348">
-        <v>59</v>
-      </c>
-      <c r="F348" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6">
-      <c r="A349" s="2">
-        <v>46139.61458333334</v>
-      </c>
-      <c r="B349">
-        <v>0</v>
-      </c>
-      <c r="C349">
-        <v>0</v>
-      </c>
-      <c r="D349">
-        <v>0</v>
-      </c>
-      <c r="E349">
-        <v>60</v>
-      </c>
-      <c r="F349" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6">
-      <c r="A350" s="2">
-        <v>46139.625</v>
-      </c>
-      <c r="B350">
-        <v>0</v>
-      </c>
-      <c r="C350">
-        <v>0</v>
-      </c>
-      <c r="D350">
-        <v>0</v>
-      </c>
-      <c r="E350">
-        <v>61</v>
-      </c>
-      <c r="F350" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6">
-      <c r="A351" s="2">
-        <v>46139.63541666666</v>
-      </c>
-      <c r="B351">
-        <v>0</v>
-      </c>
-      <c r="C351">
-        <v>0</v>
-      </c>
-      <c r="D351">
-        <v>0</v>
-      </c>
-      <c r="E351">
-        <v>62</v>
-      </c>
-      <c r="F351" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6">
-      <c r="A352" s="2">
-        <v>46139.64583333334</v>
-      </c>
-      <c r="B352">
-        <v>0</v>
-      </c>
-      <c r="C352">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <v>0</v>
-      </c>
-      <c r="E352">
-        <v>63</v>
-      </c>
-      <c r="F352" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6">
-      <c r="A353" s="2">
-        <v>46139.65625</v>
-      </c>
-      <c r="B353">
-        <v>0</v>
-      </c>
-      <c r="C353">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <v>0</v>
-      </c>
-      <c r="E353">
-        <v>64</v>
-      </c>
-      <c r="F353" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6">
-      <c r="A354" s="2">
-        <v>46139.66666666666</v>
-      </c>
-      <c r="B354">
-        <v>0</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <v>0</v>
-      </c>
-      <c r="E354">
-        <v>65</v>
-      </c>
-      <c r="F354" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6">
-      <c r="A355" s="2">
-        <v>46139.67708333334</v>
-      </c>
-      <c r="B355">
-        <v>0</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <v>0</v>
-      </c>
-      <c r="E355">
-        <v>66</v>
-      </c>
-      <c r="F355" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6">
-      <c r="A356" s="2">
-        <v>46139.6875</v>
-      </c>
-      <c r="B356">
-        <v>0</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <v>0</v>
-      </c>
-      <c r="E356">
-        <v>67</v>
-      </c>
-      <c r="F356" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6">
-      <c r="A357" s="2">
-        <v>46139.69791666666</v>
-      </c>
-      <c r="B357">
-        <v>0</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
-      </c>
-      <c r="D357">
-        <v>0</v>
-      </c>
-      <c r="E357">
-        <v>68</v>
-      </c>
-      <c r="F357" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6">
-      <c r="A358" s="2">
-        <v>46139.70833333334</v>
-      </c>
-      <c r="B358">
-        <v>0</v>
-      </c>
-      <c r="C358">
-        <v>0</v>
-      </c>
-      <c r="D358">
-        <v>0</v>
-      </c>
-      <c r="E358">
-        <v>69</v>
-      </c>
-      <c r="F358" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6">
-      <c r="A359" s="2">
-        <v>46139.71875</v>
-      </c>
-      <c r="B359">
-        <v>0</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
-      </c>
-      <c r="D359">
-        <v>0</v>
-      </c>
-      <c r="E359">
-        <v>70</v>
-      </c>
-      <c r="F359" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6">
-      <c r="A360" s="2">
-        <v>46139.72916666666</v>
-      </c>
-      <c r="B360">
-        <v>0</v>
-      </c>
-      <c r="C360">
-        <v>0</v>
-      </c>
-      <c r="D360">
-        <v>0</v>
-      </c>
-      <c r="E360">
-        <v>71</v>
-      </c>
-      <c r="F360" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6">
-      <c r="A361" s="2">
-        <v>46139.73958333334</v>
-      </c>
-      <c r="B361">
-        <v>0</v>
-      </c>
-      <c r="C361">
-        <v>0</v>
-      </c>
-      <c r="D361">
-        <v>0</v>
-      </c>
-      <c r="E361">
-        <v>72</v>
-      </c>
-      <c r="F361" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6">
-      <c r="A362" s="2">
-        <v>46139.75</v>
-      </c>
-      <c r="B362">
-        <v>0</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-      <c r="D362">
-        <v>0</v>
-      </c>
-      <c r="E362">
-        <v>73</v>
-      </c>
-      <c r="F362" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6">
-      <c r="A363" s="2">
-        <v>46139.76041666666</v>
-      </c>
-      <c r="B363">
-        <v>0</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363">
-        <v>0</v>
-      </c>
-      <c r="E363">
-        <v>74</v>
-      </c>
-      <c r="F363" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6">
-      <c r="A364" s="2">
-        <v>46139.77083333334</v>
-      </c>
-      <c r="B364">
-        <v>0</v>
-      </c>
-      <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364">
-        <v>0</v>
-      </c>
-      <c r="E364">
-        <v>75</v>
-      </c>
-      <c r="F364" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6">
-      <c r="A365" s="2">
-        <v>46139.78125</v>
-      </c>
-      <c r="B365">
-        <v>0</v>
-      </c>
-      <c r="C365">
-        <v>0</v>
-      </c>
-      <c r="D365">
-        <v>0</v>
-      </c>
-      <c r="E365">
-        <v>76</v>
-      </c>
-      <c r="F365" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6">
-      <c r="A366" s="2">
-        <v>46139.79166666666</v>
-      </c>
-      <c r="B366">
-        <v>0</v>
-      </c>
-      <c r="C366">
-        <v>0</v>
-      </c>
-      <c r="D366">
-        <v>0</v>
-      </c>
-      <c r="E366">
-        <v>77</v>
-      </c>
-      <c r="F366" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="367" spans="1:6">
-      <c r="A367" s="2">
-        <v>46139.80208333334</v>
-      </c>
-      <c r="B367">
-        <v>0</v>
-      </c>
-      <c r="C367">
-        <v>0</v>
-      </c>
-      <c r="D367">
-        <v>0</v>
-      </c>
-      <c r="E367">
-        <v>78</v>
-      </c>
-      <c r="F367" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6">
-      <c r="A368" s="2">
-        <v>46139.8125</v>
-      </c>
-      <c r="B368">
-        <v>0</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368">
-        <v>0</v>
-      </c>
-      <c r="E368">
-        <v>79</v>
-      </c>
-      <c r="F368" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6">
-      <c r="A369" s="2">
-        <v>46139.82291666666</v>
-      </c>
-      <c r="B369">
-        <v>0</v>
-      </c>
-      <c r="C369">
-        <v>0</v>
-      </c>
-      <c r="D369">
-        <v>0</v>
-      </c>
-      <c r="E369">
-        <v>80</v>
-      </c>
-      <c r="F369" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6">
-      <c r="A370" s="2">
-        <v>46139.83333333334</v>
-      </c>
-      <c r="B370">
-        <v>0</v>
-      </c>
-      <c r="C370">
-        <v>0</v>
-      </c>
-      <c r="D370">
-        <v>0</v>
-      </c>
-      <c r="E370">
-        <v>81</v>
-      </c>
-      <c r="F370" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6">
-      <c r="A371" s="2">
-        <v>46139.84375</v>
-      </c>
-      <c r="B371">
-        <v>0</v>
-      </c>
-      <c r="C371">
-        <v>0</v>
-      </c>
-      <c r="D371">
-        <v>0</v>
-      </c>
-      <c r="E371">
-        <v>82</v>
-      </c>
-      <c r="F371" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6">
-      <c r="A372" s="2">
-        <v>46139.85416666666</v>
-      </c>
-      <c r="B372">
-        <v>0</v>
-      </c>
-      <c r="C372">
-        <v>0</v>
-      </c>
-      <c r="D372">
-        <v>0</v>
-      </c>
-      <c r="E372">
-        <v>83</v>
-      </c>
-      <c r="F372" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6">
-      <c r="A373" s="2">
-        <v>46139.86458333334</v>
-      </c>
-      <c r="B373">
-        <v>0</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373">
-        <v>0</v>
-      </c>
-      <c r="E373">
-        <v>84</v>
-      </c>
-      <c r="F373" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6">
-      <c r="A374" s="2">
-        <v>46139.875</v>
-      </c>
-      <c r="B374">
-        <v>0</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>0</v>
-      </c>
-      <c r="E374">
-        <v>85</v>
-      </c>
-      <c r="F374" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6">
-      <c r="A375" s="2">
-        <v>46139.88541666666</v>
-      </c>
-      <c r="B375">
-        <v>0</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
-      </c>
-      <c r="D375">
-        <v>0</v>
-      </c>
-      <c r="E375">
-        <v>86</v>
-      </c>
-      <c r="F375" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6">
-      <c r="A376" s="2">
-        <v>46139.89583333334</v>
-      </c>
-      <c r="B376">
-        <v>0</v>
-      </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376">
-        <v>0</v>
-      </c>
-      <c r="E376">
-        <v>87</v>
-      </c>
-      <c r="F376" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6">
-      <c r="A377" s="2">
-        <v>46139.90625</v>
-      </c>
-      <c r="B377">
-        <v>0</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>0</v>
-      </c>
-      <c r="E377">
-        <v>88</v>
-      </c>
-      <c r="F377" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6">
-      <c r="A378" s="2">
-        <v>46139.91666666666</v>
-      </c>
-      <c r="B378">
-        <v>0</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>0</v>
-      </c>
-      <c r="E378">
-        <v>89</v>
-      </c>
-      <c r="F378" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6">
-      <c r="A379" s="2">
-        <v>46139.92708333334</v>
-      </c>
-      <c r="B379">
-        <v>0</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379">
-        <v>0</v>
-      </c>
-      <c r="E379">
-        <v>90</v>
-      </c>
-      <c r="F379" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6">
-      <c r="A380" s="2">
-        <v>46139.9375</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380">
-        <v>0</v>
-      </c>
-      <c r="E380">
-        <v>91</v>
-      </c>
-      <c r="F380" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6">
-      <c r="A381" s="2">
-        <v>46139.94791666666</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381">
-        <v>0</v>
-      </c>
-      <c r="D381">
-        <v>0</v>
-      </c>
-      <c r="E381">
-        <v>92</v>
-      </c>
-      <c r="F381" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6">
-      <c r="A382" s="2">
-        <v>46139.95833333334</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382">
-        <v>0</v>
-      </c>
-      <c r="E382">
-        <v>93</v>
-      </c>
-      <c r="F382" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6">
-      <c r="A383" s="2">
-        <v>46139.96875</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-      <c r="C383">
-        <v>0</v>
-      </c>
-      <c r="D383">
-        <v>0</v>
-      </c>
-      <c r="E383">
-        <v>94</v>
-      </c>
-      <c r="F383" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6">
-      <c r="A384" s="2">
-        <v>46139.97916666666</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384">
-        <v>0</v>
-      </c>
-      <c r="D384">
-        <v>0</v>
-      </c>
-      <c r="E384">
-        <v>95</v>
-      </c>
-      <c r="F384" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6">
-      <c r="A385" s="2">
-        <v>46139.98958333334</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385">
-        <v>0</v>
-      </c>
-      <c r="E385">
-        <v>96</v>
-      </c>
-      <c r="F385" t="s">
-        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abbcgroup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/forecast_app/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_23F921ED81FB8C71D56540010921AC287D743F6D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C499C5EE-1B92-4B63-B7B9-46399F11C16D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,590 +53,590 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>05.05.202694</t>
-  </si>
-  <si>
-    <t>05.05.202695</t>
-  </si>
-  <si>
-    <t>05.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
+    <t>07.05.20261</t>
+  </si>
+  <si>
+    <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>07.05.202694</t>
+  </si>
+  <si>
+    <t>07.05.202695</t>
+  </si>
+  <si>
+    <t>07.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -681,13 +700,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -725,7 +752,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -759,6 +786,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -793,9 +821,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -968,11 +997,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F193"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,18 +1024,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
-        <v>890</v>
+        <v>719</v>
       </c>
       <c r="C2">
-        <v>1017</v>
+        <v>830</v>
       </c>
       <c r="D2">
-        <v>1907</v>
+        <v>1549</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1012,18 +1044,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.010416666657</v>
       </c>
       <c r="B3">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="C3">
-        <v>846</v>
+        <v>826</v>
       </c>
       <c r="D3">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1032,18 +1064,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.020833333343</v>
       </c>
       <c r="B4">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1443</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1052,18 +1084,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
-        <v>629</v>
+        <v>708</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="D5">
-        <v>629</v>
+        <v>1532</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1072,18 +1104,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.041666666657</v>
       </c>
       <c r="B6">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1508</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1092,18 +1124,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.052083333343</v>
       </c>
       <c r="B7">
-        <v>665</v>
+        <v>701</v>
       </c>
       <c r="C7">
-        <v>847</v>
+        <v>820</v>
       </c>
       <c r="D7">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1112,18 +1144,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>669</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1132,18 +1164,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.072916666657</v>
       </c>
       <c r="B9">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="C9">
-        <v>849</v>
+        <v>813</v>
       </c>
       <c r="D9">
-        <v>1523</v>
+        <v>1497</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1152,15 +1184,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.083333333343</v>
       </c>
       <c r="B10">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="C10">
-        <v>862</v>
+        <v>807</v>
       </c>
       <c r="D10">
         <v>1508</v>
@@ -1172,18 +1204,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
-        <v>641</v>
+        <v>702</v>
       </c>
       <c r="C11">
-        <v>863</v>
+        <v>806</v>
       </c>
       <c r="D11">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1192,18 +1224,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.104166666657</v>
       </c>
       <c r="B12">
-        <v>652</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="D12">
-        <v>652</v>
+        <v>805</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1212,18 +1244,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.114583333343</v>
       </c>
       <c r="B13">
-        <v>639</v>
+        <v>700</v>
       </c>
       <c r="C13">
-        <v>862</v>
+        <v>804</v>
       </c>
       <c r="D13">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1232,18 +1264,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="C14">
-        <v>863</v>
+        <v>796</v>
       </c>
       <c r="D14">
-        <v>1509</v>
+        <v>1490</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1252,18 +1284,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.135416666657</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1487</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1272,18 +1304,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.145833333343</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="C16">
-        <v>857</v>
+        <v>796</v>
       </c>
       <c r="D16">
-        <v>857</v>
+        <v>1492</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1292,18 +1324,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="C17">
-        <v>862</v>
+        <v>797</v>
       </c>
       <c r="D17">
-        <v>862</v>
+        <v>1497</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1312,18 +1344,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.166666666657</v>
       </c>
       <c r="B18">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C18">
-        <v>869</v>
+        <v>824</v>
       </c>
       <c r="D18">
-        <v>1567</v>
+        <v>1520</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1332,18 +1364,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.177083333343</v>
       </c>
       <c r="B19">
-        <v>819</v>
+        <v>680</v>
       </c>
       <c r="C19">
-        <v>908</v>
+        <v>825</v>
       </c>
       <c r="D19">
-        <v>1727</v>
+        <v>1505</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1352,18 +1384,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>835</v>
+        <v>681</v>
       </c>
       <c r="C20">
-        <v>912</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1747</v>
+        <v>681</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1372,18 +1404,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.197916666657</v>
       </c>
       <c r="B21">
-        <v>848</v>
+        <v>688</v>
       </c>
       <c r="C21">
-        <v>914</v>
+        <v>823</v>
       </c>
       <c r="D21">
-        <v>1762</v>
+        <v>1511</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1392,18 +1424,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.208333333343</v>
       </c>
       <c r="B22">
-        <v>894</v>
+        <v>747</v>
       </c>
       <c r="C22">
-        <v>920</v>
+        <v>840</v>
       </c>
       <c r="D22">
-        <v>1814</v>
+        <v>1587</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1412,18 +1444,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>900</v>
+        <v>748</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>844</v>
       </c>
       <c r="D23">
-        <v>900</v>
+        <v>1592</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1432,18 +1464,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.229166666657</v>
       </c>
       <c r="B24">
-        <v>960</v>
+        <v>754</v>
       </c>
       <c r="C24">
-        <v>923</v>
+        <v>850</v>
       </c>
       <c r="D24">
-        <v>1883</v>
+        <v>1604</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1452,18 +1484,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.239583333343</v>
       </c>
       <c r="B25">
-        <v>972</v>
+        <v>755</v>
       </c>
       <c r="C25">
-        <v>922</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1894</v>
+        <v>755</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1472,18 +1504,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>1082</v>
+        <v>790</v>
       </c>
       <c r="C26">
-        <v>937</v>
+        <v>836</v>
       </c>
       <c r="D26">
-        <v>2019</v>
+        <v>1626</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1492,18 +1524,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.260416666657</v>
       </c>
       <c r="B27">
-        <v>1137</v>
+        <v>788</v>
       </c>
       <c r="C27">
-        <v>938</v>
+        <v>839</v>
       </c>
       <c r="D27">
-        <v>2075</v>
+        <v>1627</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1512,18 +1544,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.270833333343</v>
       </c>
       <c r="B28">
-        <v>1252</v>
+        <v>783</v>
       </c>
       <c r="C28">
-        <v>934</v>
+        <v>836</v>
       </c>
       <c r="D28">
-        <v>2186</v>
+        <v>1619</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1532,18 +1564,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>1247</v>
+        <v>793</v>
       </c>
       <c r="C29">
-        <v>939</v>
+        <v>840</v>
       </c>
       <c r="D29">
-        <v>2186</v>
+        <v>1633</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1552,18 +1584,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.291666666657</v>
       </c>
       <c r="B30">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="C30">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="D30">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1572,18 +1604,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.302083333343</v>
       </c>
       <c r="B31">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="C31">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="D31">
-        <v>1576</v>
+        <v>1623</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1592,18 +1624,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>792</v>
+        <v>840</v>
       </c>
       <c r="C32">
-        <v>766</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1558</v>
+        <v>840</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1612,18 +1644,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.322916666657</v>
       </c>
       <c r="B33">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="C33">
-        <v>768</v>
+        <v>797</v>
       </c>
       <c r="D33">
-        <v>1576</v>
+        <v>1632</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1632,18 +1664,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.333333333343</v>
       </c>
       <c r="B34">
-        <v>794</v>
+        <v>759</v>
       </c>
       <c r="C34">
-        <v>744</v>
+        <v>790</v>
       </c>
       <c r="D34">
-        <v>1538</v>
+        <v>1549</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1652,18 +1684,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>792</v>
+        <v>763</v>
       </c>
       <c r="C35">
-        <v>746</v>
+        <v>784</v>
       </c>
       <c r="D35">
-        <v>1538</v>
+        <v>1547</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1672,18 +1704,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.354166666657</v>
       </c>
       <c r="B36">
-        <v>862</v>
+        <v>766</v>
       </c>
       <c r="C36">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="D36">
-        <v>1618</v>
+        <v>1552</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1692,18 +1724,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.364583333343</v>
       </c>
       <c r="B37">
-        <v>840</v>
+        <v>767</v>
       </c>
       <c r="C37">
-        <v>773</v>
+        <v>783</v>
       </c>
       <c r="D37">
-        <v>1613</v>
+        <v>1550</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1712,18 +1744,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>863</v>
+        <v>777</v>
       </c>
       <c r="C38">
-        <v>867</v>
+        <v>704</v>
       </c>
       <c r="D38">
-        <v>1730</v>
+        <v>1481</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1732,18 +1764,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.385416666657</v>
       </c>
       <c r="B39">
-        <v>860</v>
+        <v>770</v>
       </c>
       <c r="C39">
-        <v>862</v>
+        <v>684</v>
       </c>
       <c r="D39">
-        <v>1722</v>
+        <v>1454</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1752,18 +1784,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.395833333343</v>
       </c>
       <c r="B40">
-        <v>859</v>
+        <v>766</v>
       </c>
       <c r="C40">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1724</v>
+        <v>766</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1772,18 +1804,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>855</v>
+        <v>756</v>
       </c>
       <c r="C41">
-        <v>864</v>
+        <v>691</v>
       </c>
       <c r="D41">
-        <v>1719</v>
+        <v>1447</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1792,18 +1824,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.416666666657</v>
       </c>
       <c r="B42">
-        <v>642</v>
+        <v>814</v>
       </c>
       <c r="C42">
-        <v>666</v>
+        <v>562</v>
       </c>
       <c r="D42">
-        <v>1308</v>
+        <v>1376</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1812,18 +1844,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.427083333343</v>
       </c>
       <c r="B43">
-        <v>630</v>
+        <v>817</v>
       </c>
       <c r="C43">
-        <v>651</v>
+        <v>538</v>
       </c>
       <c r="D43">
-        <v>1281</v>
+        <v>1355</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1832,18 +1864,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>637</v>
+        <v>815</v>
       </c>
       <c r="C44">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1287</v>
+        <v>815</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1852,18 +1884,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.447916666657</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1872,18 +1904,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.458333333343</v>
       </c>
       <c r="B46">
-        <v>523</v>
+        <v>770</v>
       </c>
       <c r="C46">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="D46">
-        <v>1074</v>
+        <v>1309</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1892,18 +1924,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>515</v>
+        <v>765</v>
       </c>
       <c r="C47">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D47">
-        <v>1058</v>
+        <v>1303</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1912,18 +1944,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.479166666657</v>
       </c>
       <c r="B48">
-        <v>443</v>
+        <v>763</v>
       </c>
       <c r="C48">
-        <v>481</v>
+        <v>537</v>
       </c>
       <c r="D48">
-        <v>924</v>
+        <v>1300</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1932,18 +1964,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.489583333343</v>
       </c>
       <c r="B49">
-        <v>438</v>
+        <v>764</v>
       </c>
       <c r="C49">
-        <v>452</v>
+        <v>539</v>
       </c>
       <c r="D49">
-        <v>890</v>
+        <v>1303</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1952,18 +1984,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>320</v>
+        <v>745</v>
       </c>
       <c r="C50">
-        <v>473</v>
+        <v>576</v>
       </c>
       <c r="D50">
-        <v>793</v>
+        <v>1321</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1972,18 +2004,18 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.510416666657</v>
       </c>
       <c r="B51">
-        <v>167</v>
+        <v>744</v>
       </c>
       <c r="C51">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>641</v>
+        <v>744</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1992,18 +2024,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.520833333343</v>
       </c>
       <c r="B52">
-        <v>118</v>
+        <v>746</v>
       </c>
       <c r="C52">
-        <v>437</v>
+        <v>577</v>
       </c>
       <c r="D52">
-        <v>555</v>
+        <v>1323</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2012,18 +2044,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>75</v>
+        <v>741</v>
       </c>
       <c r="C53">
-        <v>388</v>
+        <v>575</v>
       </c>
       <c r="D53">
-        <v>463</v>
+        <v>1316</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2032,18 +2064,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.541666666657</v>
       </c>
       <c r="B54">
-        <v>74</v>
+        <v>750</v>
       </c>
       <c r="C54">
-        <v>382</v>
+        <v>579</v>
       </c>
       <c r="D54">
-        <v>456</v>
+        <v>1329</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2052,18 +2084,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.552083333343</v>
       </c>
       <c r="B55">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>380</v>
+        <v>573</v>
       </c>
       <c r="D55">
-        <v>456</v>
+        <v>573</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2072,18 +2104,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>75</v>
+        <v>751</v>
       </c>
       <c r="C56">
-        <v>369</v>
+        <v>574</v>
       </c>
       <c r="D56">
-        <v>444</v>
+        <v>1325</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2092,18 +2124,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.572916666657</v>
       </c>
       <c r="B57">
-        <v>82</v>
+        <v>749</v>
       </c>
       <c r="C57">
-        <v>360</v>
+        <v>575</v>
       </c>
       <c r="D57">
-        <v>442</v>
+        <v>1324</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2112,18 +2144,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.583333333343</v>
       </c>
       <c r="B58">
-        <v>105</v>
+        <v>771</v>
       </c>
       <c r="C58">
-        <v>359</v>
+        <v>600</v>
       </c>
       <c r="D58">
-        <v>464</v>
+        <v>1371</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2132,18 +2164,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>104</v>
+        <v>773</v>
       </c>
       <c r="C59">
-        <v>360</v>
+        <v>602</v>
       </c>
       <c r="D59">
-        <v>464</v>
+        <v>1375</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2152,18 +2184,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.604166666657</v>
       </c>
       <c r="B60">
-        <v>117</v>
+        <v>777</v>
       </c>
       <c r="C60">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>558</v>
+        <v>777</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2172,18 +2204,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.614583333343</v>
       </c>
       <c r="B61">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>470</v>
+        <v>604</v>
       </c>
       <c r="D61">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2192,18 +2224,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>829</v>
+        <v>758</v>
       </c>
       <c r="C62">
-        <v>538</v>
+        <v>669</v>
       </c>
       <c r="D62">
-        <v>1367</v>
+        <v>1427</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2212,18 +2244,18 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.635416666657</v>
       </c>
       <c r="B63">
-        <v>869</v>
+        <v>760</v>
       </c>
       <c r="C63">
-        <v>582</v>
+        <v>702</v>
       </c>
       <c r="D63">
-        <v>1451</v>
+        <v>1462</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2232,18 +2264,18 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.645833333343</v>
       </c>
       <c r="B64">
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>588</v>
+        <v>700</v>
       </c>
       <c r="D64">
-        <v>1465</v>
+        <v>700</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2252,18 +2284,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>979</v>
+        <v>814</v>
       </c>
       <c r="C65">
-        <v>506</v>
+        <v>658</v>
       </c>
       <c r="D65">
-        <v>1485</v>
+        <v>1472</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2272,18 +2304,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.666666666657</v>
       </c>
       <c r="B66">
-        <v>1029</v>
+        <v>874</v>
       </c>
       <c r="C66">
-        <v>656</v>
+        <v>690</v>
       </c>
       <c r="D66">
-        <v>1685</v>
+        <v>1564</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2292,18 +2324,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.677083333343</v>
       </c>
       <c r="B67">
-        <v>872</v>
+        <v>787</v>
       </c>
       <c r="C67">
-        <v>721</v>
+        <v>797</v>
       </c>
       <c r="D67">
-        <v>1593</v>
+        <v>1584</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2312,18 +2344,18 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>828</v>
+        <v>803</v>
       </c>
       <c r="C68">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="D68">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2332,18 +2364,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.697916666657</v>
       </c>
       <c r="B69">
-        <v>839</v>
+        <v>813</v>
       </c>
       <c r="C69">
-        <v>771</v>
+        <v>801</v>
       </c>
       <c r="D69">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2352,18 +2384,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.708333333343</v>
       </c>
       <c r="B70">
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="C70">
-        <v>895</v>
+        <v>877</v>
       </c>
       <c r="D70">
-        <v>1911</v>
+        <v>1899</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2372,18 +2404,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C71">
-        <v>916</v>
+        <v>889</v>
       </c>
       <c r="D71">
-        <v>1939</v>
+        <v>1916</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2392,18 +2424,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.729166666657</v>
       </c>
       <c r="B72">
-        <v>1003</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="D72">
-        <v>1865</v>
+        <v>884</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2412,18 +2444,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.739583333343</v>
       </c>
       <c r="B73">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="D73">
-        <v>1025</v>
+        <v>1938</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2432,18 +2464,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>978</v>
+        <v>1106</v>
       </c>
       <c r="C74">
-        <v>980</v>
+        <v>1075</v>
       </c>
       <c r="D74">
-        <v>1958</v>
+        <v>2181</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2452,18 +2484,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.760416666657</v>
       </c>
       <c r="B75">
-        <v>1016</v>
+        <v>1122</v>
       </c>
       <c r="C75">
-        <v>1036</v>
+        <v>1086</v>
       </c>
       <c r="D75">
-        <v>2052</v>
+        <v>2208</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2472,18 +2504,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.770833333343</v>
       </c>
       <c r="B76">
-        <v>1020</v>
+        <v>1113</v>
       </c>
       <c r="C76">
-        <v>1041</v>
+        <v>1083</v>
       </c>
       <c r="D76">
-        <v>2061</v>
+        <v>2196</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2492,18 +2524,18 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>1018</v>
+        <v>1115</v>
       </c>
       <c r="C77">
-        <v>1038</v>
+        <v>1084</v>
       </c>
       <c r="D77">
-        <v>2056</v>
+        <v>2199</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2512,18 +2544,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.791666666657</v>
       </c>
       <c r="B78">
-        <v>992</v>
+        <v>1134</v>
       </c>
       <c r="C78">
-        <v>1073</v>
+        <v>1059</v>
       </c>
       <c r="D78">
-        <v>2065</v>
+        <v>2193</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2532,18 +2564,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.802083333343</v>
       </c>
       <c r="B79">
-        <v>990</v>
+        <v>1135</v>
       </c>
       <c r="C79">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="D79">
-        <v>2065</v>
+        <v>2195</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2552,18 +2584,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>997</v>
+        <v>1140</v>
       </c>
       <c r="C80">
-        <v>1077</v>
+        <v>1061</v>
       </c>
       <c r="D80">
-        <v>2074</v>
+        <v>2201</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2572,18 +2604,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.822916666657</v>
       </c>
       <c r="B81">
-        <v>990</v>
+        <v>1152</v>
       </c>
       <c r="C81">
-        <v>1076</v>
+        <v>1066</v>
       </c>
       <c r="D81">
-        <v>2066</v>
+        <v>2218</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2592,18 +2624,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.833333333343</v>
       </c>
       <c r="B82">
-        <v>949</v>
+        <v>1083</v>
       </c>
       <c r="C82">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="D82">
-        <v>2029</v>
+        <v>2175</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2612,18 +2644,18 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>950</v>
+        <v>1078</v>
       </c>
       <c r="C83">
-        <v>1075</v>
+        <v>1093</v>
       </c>
       <c r="D83">
-        <v>2025</v>
+        <v>2171</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2632,18 +2664,18 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.854166666657</v>
       </c>
       <c r="B84">
-        <v>967</v>
+        <v>1081</v>
       </c>
       <c r="C84">
-        <v>1076</v>
+        <v>1092</v>
       </c>
       <c r="D84">
-        <v>2043</v>
+        <v>2173</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2652,18 +2684,18 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.864583333343</v>
       </c>
       <c r="B85">
-        <v>966</v>
+        <v>1078</v>
       </c>
       <c r="C85">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="D85">
-        <v>2043</v>
+        <v>2168</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2672,18 +2704,18 @@
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
-        <v>860</v>
+        <v>991</v>
       </c>
       <c r="C86">
-        <v>1093</v>
+        <v>1114</v>
       </c>
       <c r="D86">
-        <v>1953</v>
+        <v>2105</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2692,18 +2724,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.885416666657</v>
       </c>
       <c r="B87">
-        <v>853</v>
+        <v>982</v>
       </c>
       <c r="C87">
-        <v>1091</v>
+        <v>1110</v>
       </c>
       <c r="D87">
-        <v>1944</v>
+        <v>2092</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2712,18 +2744,18 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.895833333343</v>
       </c>
       <c r="B88">
-        <v>827</v>
+        <v>979</v>
       </c>
       <c r="C88">
-        <v>1019</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>1846</v>
+        <v>979</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2732,18 +2764,18 @@
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>829</v>
+        <v>967</v>
       </c>
       <c r="C89">
-        <v>1012</v>
+        <v>1105</v>
       </c>
       <c r="D89">
-        <v>1841</v>
+        <v>2072</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2752,18 +2784,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.916666666657</v>
       </c>
       <c r="B90">
-        <v>748</v>
+        <v>929</v>
       </c>
       <c r="C90">
-        <v>996</v>
+        <v>937</v>
       </c>
       <c r="D90">
-        <v>1744</v>
+        <v>1866</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2772,18 +2804,18 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.927083333343</v>
       </c>
       <c r="B91">
-        <v>752</v>
+        <v>920</v>
       </c>
       <c r="C91">
-        <v>977</v>
+        <v>920</v>
       </c>
       <c r="D91">
-        <v>1729</v>
+        <v>1840</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2792,18 +2824,18 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
-        <v>741</v>
+        <v>917</v>
       </c>
       <c r="C92">
-        <v>971</v>
+        <v>923</v>
       </c>
       <c r="D92">
-        <v>1712</v>
+        <v>1840</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2812,18 +2844,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.947916666657</v>
       </c>
       <c r="B93">
-        <v>758</v>
+        <v>923</v>
       </c>
       <c r="C93">
-        <v>988</v>
+        <v>921</v>
       </c>
       <c r="D93">
-        <v>1746</v>
+        <v>1844</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2832,18 +2864,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.958333333343</v>
       </c>
       <c r="B94">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="C94">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="D94">
-        <v>1456</v>
+        <v>1549</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2852,18 +2884,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
-        <v>567</v>
+        <v>627</v>
       </c>
       <c r="C95">
-        <v>868</v>
+        <v>898</v>
       </c>
       <c r="D95">
-        <v>1435</v>
+        <v>1525</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2872,18 +2904,18 @@
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.979166666657</v>
       </c>
       <c r="B96">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="C96">
-        <v>865</v>
+        <v>899</v>
       </c>
       <c r="D96">
-        <v>1430</v>
+        <v>1522</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2892,18 +2924,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.989583333343</v>
       </c>
       <c r="B97">
-        <v>562</v>
+        <v>616</v>
       </c>
       <c r="C97">
-        <v>863</v>
+        <v>897</v>
       </c>
       <c r="D97">
-        <v>1425</v>
+        <v>1513</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2912,18 +2944,18 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="C98">
-        <v>817</v>
+        <v>928</v>
       </c>
       <c r="D98">
-        <v>1456</v>
+        <v>1591</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2932,18 +2964,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.010416666657</v>
       </c>
       <c r="B99">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C99">
-        <v>816</v>
+        <v>922</v>
       </c>
       <c r="D99">
-        <v>1464</v>
+        <v>1578</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2952,18 +2984,18 @@
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.020833333343</v>
       </c>
       <c r="B100">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>636</v>
+        <v>655</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2972,18 +3004,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B101">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="D101">
-        <v>651</v>
+        <v>1565</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2992,18 +3024,18 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.041666666657</v>
       </c>
       <c r="B102">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C102">
-        <v>834</v>
+        <v>894</v>
       </c>
       <c r="D102">
-        <v>1479</v>
+        <v>1545</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3012,18 +3044,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.052083333343</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>647</v>
       </c>
       <c r="C103">
-        <v>835</v>
+        <v>888</v>
       </c>
       <c r="D103">
-        <v>835</v>
+        <v>1535</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3032,18 +3064,18 @@
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B104">
-        <v>644</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>834</v>
+        <v>889</v>
       </c>
       <c r="D104">
-        <v>1478</v>
+        <v>889</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3052,18 +3084,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.072916666657</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="C105">
-        <v>835</v>
+        <v>888</v>
       </c>
       <c r="D105">
-        <v>835</v>
+        <v>1541</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3072,18 +3104,18 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.083333333343</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>839</v>
+        <v>890</v>
       </c>
       <c r="D106">
-        <v>839</v>
+        <v>890</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3092,18 +3124,18 @@
         <v>110</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B107">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C107">
-        <v>837</v>
+        <v>888</v>
       </c>
       <c r="D107">
-        <v>1478</v>
+        <v>1534</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3112,18 +3144,18 @@
         <v>111</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.104166666657</v>
       </c>
       <c r="B108">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C108">
-        <v>836</v>
+        <v>890</v>
       </c>
       <c r="D108">
-        <v>1478</v>
+        <v>1538</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3132,18 +3164,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.114583333343</v>
       </c>
       <c r="B109">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="C109">
-        <v>838</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>1483</v>
+        <v>655</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3152,18 +3184,18 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B110">
-        <v>712</v>
+        <v>659</v>
       </c>
       <c r="C110">
-        <v>806</v>
+        <v>903</v>
       </c>
       <c r="D110">
-        <v>1518</v>
+        <v>1562</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3172,18 +3204,18 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.135416666657</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>805</v>
+        <v>904</v>
       </c>
       <c r="D111">
-        <v>805</v>
+        <v>904</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3192,18 +3224,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.145833333343</v>
       </c>
       <c r="B112">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="D112">
-        <v>713</v>
+        <v>903</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3212,18 +3244,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B113">
-        <v>714</v>
+        <v>660</v>
       </c>
       <c r="C113">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1521</v>
+        <v>660</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3232,18 +3264,18 @@
         <v>117</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.166666666657</v>
       </c>
       <c r="B114">
-        <v>735</v>
+        <v>693</v>
       </c>
       <c r="C114">
-        <v>817</v>
+        <v>907</v>
       </c>
       <c r="D114">
-        <v>1552</v>
+        <v>1600</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3252,18 +3284,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.177083333343</v>
       </c>
       <c r="B115">
-        <v>736</v>
+        <v>691</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="D115">
-        <v>736</v>
+        <v>1597</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3272,18 +3304,18 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B116">
-        <v>739</v>
+        <v>682</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="D116">
-        <v>739</v>
+        <v>1587</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3292,18 +3324,18 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.197916666657</v>
       </c>
       <c r="B117">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="C117">
-        <v>820</v>
+        <v>903</v>
       </c>
       <c r="D117">
-        <v>1565</v>
+        <v>1609</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3312,18 +3344,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.208333333343</v>
       </c>
       <c r="B118">
-        <v>817</v>
+        <v>756</v>
       </c>
       <c r="C118">
-        <v>809</v>
+        <v>925</v>
       </c>
       <c r="D118">
-        <v>1626</v>
+        <v>1681</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3332,18 +3364,18 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B119">
-        <v>820</v>
+        <v>759</v>
       </c>
       <c r="C119">
-        <v>810</v>
+        <v>928</v>
       </c>
       <c r="D119">
-        <v>1630</v>
+        <v>1687</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3352,18 +3384,18 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.229166666657</v>
       </c>
       <c r="B120">
-        <v>819</v>
+        <v>755</v>
       </c>
       <c r="C120">
-        <v>809</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>1628</v>
+        <v>755</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3372,18 +3404,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.239583333343</v>
       </c>
       <c r="B121">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="C121">
-        <v>807</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1627</v>
+        <v>750</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3392,18 +3424,18 @@
         <v>125</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B122">
-        <v>909</v>
+        <v>854</v>
       </c>
       <c r="C122">
-        <v>835</v>
+        <v>950</v>
       </c>
       <c r="D122">
-        <v>1744</v>
+        <v>1804</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3412,18 +3444,18 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.260416666657</v>
       </c>
       <c r="B123">
-        <v>893</v>
+        <v>860</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="D123">
-        <v>893</v>
+        <v>1807</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3432,18 +3464,18 @@
         <v>127</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.270833333343</v>
       </c>
       <c r="B124">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="C124">
-        <v>834</v>
+        <v>948</v>
       </c>
       <c r="D124">
-        <v>1709</v>
+        <v>1809</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3452,18 +3484,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B125">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="C125">
-        <v>835</v>
+        <v>953</v>
       </c>
       <c r="D125">
-        <v>1711</v>
+        <v>1815</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3472,18 +3504,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.291666666657</v>
       </c>
       <c r="B126">
-        <v>777</v>
+        <v>868</v>
       </c>
       <c r="C126">
-        <v>821</v>
+        <v>939</v>
       </c>
       <c r="D126">
-        <v>1598</v>
+        <v>1807</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3492,18 +3524,18 @@
         <v>130</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.302083333343</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>872</v>
       </c>
       <c r="C127">
-        <v>815</v>
+        <v>935</v>
       </c>
       <c r="D127">
-        <v>815</v>
+        <v>1807</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3512,18 +3544,18 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3532,9 +3564,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.322916666657</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3552,9 +3584,9 @@
         <v>133</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.333333333343</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3572,9 +3604,9 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3592,9 +3624,9 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.354166666657</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3612,9 +3644,9 @@
         <v>136</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.364583333343</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3632,9 +3664,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3652,9 +3684,9 @@
         <v>138</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.385416666657</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3672,9 +3704,9 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.395833333343</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3692,9 +3724,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3712,9 +3744,9 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.416666666657</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3732,9 +3764,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.427083333343</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3752,9 +3784,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3772,9 +3804,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.447916666657</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3792,9 +3824,9 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.458333333343</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3812,9 +3844,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3832,9 +3864,9 @@
         <v>147</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.479166666657</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3852,9 +3884,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.489583333343</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3872,9 +3904,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3892,9 +3924,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.510416666657</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3912,9 +3944,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.520833333343</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3932,9 +3964,9 @@
         <v>152</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3952,9 +3984,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.541666666657</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3972,9 +4004,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.552083333343</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3992,9 +4024,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4012,9 +4044,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.572916666657</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4032,9 +4064,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.583333333343</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4052,9 +4084,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4072,9 +4104,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.604166666657</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4092,9 +4124,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.614583333343</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4112,9 +4144,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4132,9 +4164,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.635416666657</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4152,9 +4184,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.645833333343</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4172,9 +4204,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4192,9 +4224,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.666666666657</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4212,9 +4244,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.677083333343</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4232,9 +4264,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4252,9 +4284,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.697916666657</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4272,9 +4304,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.708333333343</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4292,9 +4324,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4312,9 +4344,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.729166666657</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4332,9 +4364,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.739583333343</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4352,9 +4384,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4372,9 +4404,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.760416666657</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4392,9 +4424,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.770833333343</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4412,9 +4444,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4432,9 +4464,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.791666666657</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4452,9 +4484,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.802083333343</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4472,9 +4504,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4492,9 +4524,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.822916666657</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4512,9 +4544,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.833333333343</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4532,9 +4564,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4552,9 +4584,9 @@
         <v>183</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.854166666657</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4572,9 +4604,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.864583333343</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4592,9 +4624,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4612,9 +4644,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.885416666657</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4632,9 +4664,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.895833333343</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4652,9 +4684,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4672,9 +4704,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.916666666657</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4692,9 +4724,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.927083333343</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4712,9 +4744,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4732,9 +4764,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.947916666657</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4752,9 +4784,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.958333333343</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4772,9 +4804,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4792,9 +4824,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.979166666657</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4812,9 +4844,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.989583333343</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://abbcgroup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/forecast_app/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_23F921ED81FB8C71D56540010921AC287D743F6D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C499C5EE-1B92-4B63-B7B9-46399F11C16D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -53,590 +34,590 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202694</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>11.05.202694</t>
+  </si>
+  <si>
+    <t>11.05.202695</t>
+  </si>
+  <si>
+    <t>11.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,21 +681,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -752,7 +725,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -786,7 +759,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -821,10 +793,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -997,14 +968,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F193"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,18 +992,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>719</v>
+        <v>587</v>
       </c>
       <c r="C2">
-        <v>830</v>
+        <v>1033</v>
       </c>
       <c r="D2">
-        <v>1549</v>
+        <v>1620</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1044,18 +1012,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46149.010416666657</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>716</v>
+        <v>583</v>
       </c>
       <c r="C3">
-        <v>826</v>
+        <v>1032</v>
       </c>
       <c r="D3">
-        <v>1542</v>
+        <v>1615</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1064,18 +1032,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46149.020833333343</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1611</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1084,18 +1052,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>708</v>
+        <v>582</v>
       </c>
       <c r="C5">
-        <v>824</v>
+        <v>1028</v>
       </c>
       <c r="D5">
-        <v>1532</v>
+        <v>1610</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1104,18 +1072,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46149.041666666657</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1604</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1124,18 +1092,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46149.052083333343</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>701</v>
+        <v>581</v>
       </c>
       <c r="C7">
-        <v>820</v>
+        <v>1029</v>
       </c>
       <c r="D7">
-        <v>1521</v>
+        <v>1610</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1144,18 +1112,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1594</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1164,18 +1132,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46149.072916666657</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>684</v>
+        <v>568</v>
       </c>
       <c r="C9">
-        <v>813</v>
+        <v>1031</v>
       </c>
       <c r="D9">
-        <v>1497</v>
+        <v>1599</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1184,18 +1152,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46149.083333333343</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>701</v>
+        <v>505</v>
       </c>
       <c r="C10">
-        <v>807</v>
+        <v>1036</v>
       </c>
       <c r="D10">
-        <v>1508</v>
+        <v>1541</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1204,18 +1172,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>702</v>
+        <v>504</v>
       </c>
       <c r="C11">
-        <v>806</v>
+        <v>1033</v>
       </c>
       <c r="D11">
-        <v>1508</v>
+        <v>1537</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1224,18 +1192,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46149.104166666657</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>805</v>
+        <v>1035</v>
       </c>
       <c r="D12">
-        <v>805</v>
+        <v>1035</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1244,18 +1212,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46149.114583333343</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>700</v>
+        <v>503</v>
       </c>
       <c r="C13">
-        <v>804</v>
+        <v>1036</v>
       </c>
       <c r="D13">
-        <v>1504</v>
+        <v>1539</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1264,18 +1232,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>694</v>
+        <v>506</v>
       </c>
       <c r="C14">
-        <v>796</v>
+        <v>1039</v>
       </c>
       <c r="D14">
-        <v>1490</v>
+        <v>1545</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1284,18 +1252,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46149.135416666657</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>692</v>
+        <v>507</v>
       </c>
       <c r="C15">
-        <v>795</v>
+        <v>1040</v>
       </c>
       <c r="D15">
-        <v>1487</v>
+        <v>1547</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1304,18 +1272,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46149.145833333343</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>796</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1492</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1324,18 +1292,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>700</v>
+        <v>506</v>
       </c>
       <c r="C17">
-        <v>797</v>
+        <v>1038</v>
       </c>
       <c r="D17">
-        <v>1497</v>
+        <v>1544</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1344,18 +1312,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46149.166666666657</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>696</v>
+        <v>517</v>
       </c>
       <c r="C18">
-        <v>824</v>
+        <v>1048</v>
       </c>
       <c r="D18">
-        <v>1520</v>
+        <v>1565</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1364,18 +1332,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46149.177083333343</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1505</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1384,18 +1352,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>681</v>
+        <v>519</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="D20">
-        <v>681</v>
+        <v>1566</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1404,18 +1372,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46149.197916666657</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>688</v>
+        <v>530</v>
       </c>
       <c r="C21">
-        <v>823</v>
+        <v>1049</v>
       </c>
       <c r="D21">
-        <v>1511</v>
+        <v>1579</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1424,18 +1392,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46149.208333333343</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>747</v>
+        <v>577</v>
       </c>
       <c r="C22">
-        <v>840</v>
+        <v>1051</v>
       </c>
       <c r="D22">
-        <v>1587</v>
+        <v>1628</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1444,18 +1412,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>748</v>
+        <v>575</v>
       </c>
       <c r="C23">
-        <v>844</v>
+        <v>1053</v>
       </c>
       <c r="D23">
-        <v>1592</v>
+        <v>1628</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1464,18 +1432,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46149.229166666657</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>754</v>
+        <v>558</v>
       </c>
       <c r="C24">
-        <v>850</v>
+        <v>1050</v>
       </c>
       <c r="D24">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1484,18 +1452,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46149.239583333343</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>755</v>
+        <v>579</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1053</v>
       </c>
       <c r="D25">
-        <v>755</v>
+        <v>1632</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1504,18 +1472,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>790</v>
+        <v>711</v>
       </c>
       <c r="C26">
-        <v>836</v>
+        <v>1049</v>
       </c>
       <c r="D26">
-        <v>1626</v>
+        <v>1760</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1524,18 +1492,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46149.260416666657</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>788</v>
+        <v>706</v>
       </c>
       <c r="C27">
-        <v>839</v>
+        <v>1043</v>
       </c>
       <c r="D27">
-        <v>1627</v>
+        <v>1749</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1544,18 +1512,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46149.270833333343</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>783</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>836</v>
+        <v>1045</v>
       </c>
       <c r="D28">
-        <v>1619</v>
+        <v>1045</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1564,18 +1532,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>793</v>
+        <v>735</v>
       </c>
       <c r="C29">
-        <v>840</v>
+        <v>1013</v>
       </c>
       <c r="D29">
-        <v>1633</v>
+        <v>1748</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1584,18 +1552,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46149.291666666657</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>823</v>
+        <v>717</v>
       </c>
       <c r="C30">
-        <v>810</v>
+        <v>985</v>
       </c>
       <c r="D30">
-        <v>1633</v>
+        <v>1702</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1604,18 +1572,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46149.302083333343</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>824</v>
+        <v>718</v>
       </c>
       <c r="C31">
-        <v>799</v>
+        <v>980</v>
       </c>
       <c r="D31">
-        <v>1623</v>
+        <v>1698</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1624,18 +1592,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>840</v>
+        <v>728</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="D32">
-        <v>840</v>
+        <v>1709</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1644,18 +1612,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46149.322916666657</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>835</v>
+        <v>720</v>
       </c>
       <c r="C33">
-        <v>797</v>
+        <v>983</v>
       </c>
       <c r="D33">
-        <v>1632</v>
+        <v>1703</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1664,18 +1632,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46149.333333333343</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>759</v>
+        <v>640</v>
       </c>
       <c r="C34">
-        <v>790</v>
+        <v>967</v>
       </c>
       <c r="D34">
-        <v>1549</v>
+        <v>1607</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1684,18 +1652,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>763</v>
+        <v>629</v>
       </c>
       <c r="C35">
-        <v>784</v>
+        <v>964</v>
       </c>
       <c r="D35">
-        <v>1547</v>
+        <v>1593</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1704,18 +1672,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46149.354166666657</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>766</v>
+        <v>636</v>
       </c>
       <c r="C36">
-        <v>786</v>
+        <v>969</v>
       </c>
       <c r="D36">
-        <v>1552</v>
+        <v>1605</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1724,18 +1692,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46149.364583333343</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>767</v>
+        <v>633</v>
       </c>
       <c r="C37">
-        <v>783</v>
+        <v>965</v>
       </c>
       <c r="D37">
-        <v>1550</v>
+        <v>1598</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1744,18 +1712,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>777</v>
+        <v>611</v>
       </c>
       <c r="C38">
-        <v>704</v>
+        <v>893</v>
       </c>
       <c r="D38">
-        <v>1481</v>
+        <v>1504</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1764,18 +1732,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46149.385416666657</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>770</v>
+        <v>621</v>
       </c>
       <c r="C39">
-        <v>684</v>
+        <v>883</v>
       </c>
       <c r="D39">
-        <v>1454</v>
+        <v>1504</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1784,18 +1752,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46149.395833333343</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>766</v>
+        <v>606</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>886</v>
       </c>
       <c r="D40">
-        <v>766</v>
+        <v>1492</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1804,18 +1772,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>756</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>691</v>
+        <v>882</v>
       </c>
       <c r="D41">
-        <v>1447</v>
+        <v>882</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1824,18 +1792,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46149.416666666657</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>814</v>
+        <v>521</v>
       </c>
       <c r="C42">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1376</v>
+        <v>521</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1844,18 +1812,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46149.427083333343</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>817</v>
+        <v>522</v>
       </c>
       <c r="C43">
-        <v>538</v>
+        <v>881</v>
       </c>
       <c r="D43">
-        <v>1355</v>
+        <v>1403</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1864,18 +1832,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>815</v>
+        <v>523</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="D44">
-        <v>815</v>
+        <v>1487</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1884,18 +1852,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46149.447916666657</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="D45">
-        <v>818</v>
+        <v>968</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1904,18 +1872,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46149.458333333343</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>770</v>
+        <v>612</v>
       </c>
       <c r="C46">
-        <v>539</v>
+        <v>893</v>
       </c>
       <c r="D46">
-        <v>1309</v>
+        <v>1505</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1924,18 +1892,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>765</v>
+        <v>635</v>
       </c>
       <c r="C47">
-        <v>538</v>
+        <v>886</v>
       </c>
       <c r="D47">
-        <v>1303</v>
+        <v>1521</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1944,18 +1912,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46149.479166666657</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>763</v>
+        <v>641</v>
       </c>
       <c r="C48">
-        <v>537</v>
+        <v>927</v>
       </c>
       <c r="D48">
-        <v>1300</v>
+        <v>1568</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1964,18 +1932,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46149.489583333343</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>764</v>
+        <v>643</v>
       </c>
       <c r="C49">
-        <v>539</v>
+        <v>928</v>
       </c>
       <c r="D49">
-        <v>1303</v>
+        <v>1571</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1984,18 +1952,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>745</v>
+        <v>638</v>
       </c>
       <c r="C50">
-        <v>576</v>
+        <v>927</v>
       </c>
       <c r="D50">
-        <v>1321</v>
+        <v>1565</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2004,18 +1972,18 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46149.510416666657</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>744</v>
+        <v>636</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="D51">
-        <v>744</v>
+        <v>1561</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2024,18 +1992,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46149.520833333343</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>746</v>
+        <v>640</v>
       </c>
       <c r="C52">
-        <v>577</v>
+        <v>928</v>
       </c>
       <c r="D52">
-        <v>1323</v>
+        <v>1568</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2044,18 +2012,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>741</v>
+        <v>625</v>
       </c>
       <c r="C53">
-        <v>575</v>
+        <v>934</v>
       </c>
       <c r="D53">
-        <v>1316</v>
+        <v>1559</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2064,18 +2032,18 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46149.541666666657</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>750</v>
+        <v>616</v>
       </c>
       <c r="C54">
-        <v>579</v>
+        <v>972</v>
       </c>
       <c r="D54">
-        <v>1329</v>
+        <v>1588</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2084,18 +2052,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46149.552083333343</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>573</v>
+        <v>973</v>
       </c>
       <c r="D55">
-        <v>573</v>
+        <v>973</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2104,18 +2072,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>751</v>
+        <v>603</v>
       </c>
       <c r="C56">
-        <v>574</v>
+        <v>972</v>
       </c>
       <c r="D56">
-        <v>1325</v>
+        <v>1575</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2124,18 +2092,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46149.572916666657</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>749</v>
+        <v>596</v>
       </c>
       <c r="C57">
-        <v>575</v>
+        <v>970</v>
       </c>
       <c r="D57">
-        <v>1324</v>
+        <v>1566</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2144,18 +2112,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46149.583333333343</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>771</v>
+        <v>582</v>
       </c>
       <c r="C58">
-        <v>600</v>
+        <v>979</v>
       </c>
       <c r="D58">
-        <v>1371</v>
+        <v>1561</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2164,18 +2132,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>773</v>
+        <v>585</v>
       </c>
       <c r="C59">
-        <v>602</v>
+        <v>983</v>
       </c>
       <c r="D59">
-        <v>1375</v>
+        <v>1568</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2184,18 +2152,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46149.604166666657</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>777</v>
+        <v>566</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="D60">
-        <v>777</v>
+        <v>1482</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2204,18 +2172,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46149.614583333343</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="C61">
-        <v>604</v>
+        <v>914</v>
       </c>
       <c r="D61">
-        <v>604</v>
+        <v>1483</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2224,18 +2192,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>758</v>
+        <v>573</v>
       </c>
       <c r="C62">
-        <v>669</v>
+        <v>923</v>
       </c>
       <c r="D62">
-        <v>1427</v>
+        <v>1496</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2244,18 +2212,18 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46149.635416666657</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>760</v>
+        <v>583</v>
       </c>
       <c r="C63">
-        <v>702</v>
+        <v>912</v>
       </c>
       <c r="D63">
-        <v>1462</v>
+        <v>1495</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2264,18 +2232,18 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46149.645833333343</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="C64">
-        <v>700</v>
+        <v>902</v>
       </c>
       <c r="D64">
-        <v>700</v>
+        <v>1473</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2284,18 +2252,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>814</v>
+        <v>587</v>
       </c>
       <c r="C65">
-        <v>658</v>
+        <v>901</v>
       </c>
       <c r="D65">
-        <v>1472</v>
+        <v>1488</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2304,18 +2272,18 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46149.666666666657</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>874</v>
+        <v>545</v>
       </c>
       <c r="C66">
-        <v>690</v>
+        <v>934</v>
       </c>
       <c r="D66">
-        <v>1564</v>
+        <v>1479</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2324,18 +2292,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46149.677083333343</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>787</v>
+        <v>539</v>
       </c>
       <c r="C67">
-        <v>797</v>
+        <v>940</v>
       </c>
       <c r="D67">
-        <v>1584</v>
+        <v>1479</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2344,18 +2312,18 @@
         <v>71</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>803</v>
+        <v>547</v>
       </c>
       <c r="C68">
-        <v>796</v>
+        <v>941</v>
       </c>
       <c r="D68">
-        <v>1599</v>
+        <v>1488</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2364,18 +2332,18 @@
         <v>72</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46149.697916666657</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>813</v>
+        <v>558</v>
       </c>
       <c r="C69">
-        <v>801</v>
+        <v>950</v>
       </c>
       <c r="D69">
-        <v>1614</v>
+        <v>1508</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2384,18 +2352,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46149.708333333343</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>1022</v>
+        <v>771</v>
       </c>
       <c r="C70">
-        <v>877</v>
+        <v>1060</v>
       </c>
       <c r="D70">
-        <v>1899</v>
+        <v>1831</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2404,18 +2372,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>1027</v>
+        <v>815</v>
       </c>
       <c r="C71">
-        <v>889</v>
+        <v>1070</v>
       </c>
       <c r="D71">
-        <v>1916</v>
+        <v>1885</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2424,18 +2392,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46149.729166666657</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="C72">
-        <v>884</v>
+        <v>1101</v>
       </c>
       <c r="D72">
-        <v>884</v>
+        <v>1980</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2444,18 +2412,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46149.739583333343</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>1032</v>
+        <v>935</v>
       </c>
       <c r="C73">
-        <v>906</v>
+        <v>1109</v>
       </c>
       <c r="D73">
-        <v>1938</v>
+        <v>2044</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2464,18 +2432,18 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="C74">
-        <v>1075</v>
+        <v>1244</v>
       </c>
       <c r="D74">
-        <v>2181</v>
+        <v>2293</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2484,18 +2452,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46149.760416666657</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>1122</v>
+        <v>1052</v>
       </c>
       <c r="C75">
-        <v>1086</v>
+        <v>1252</v>
       </c>
       <c r="D75">
-        <v>2208</v>
+        <v>2304</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2504,18 +2472,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46149.770833333343</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>1113</v>
+        <v>1057</v>
       </c>
       <c r="C76">
-        <v>1083</v>
+        <v>1257</v>
       </c>
       <c r="D76">
-        <v>2196</v>
+        <v>2314</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2524,18 +2492,18 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>1115</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>1084</v>
+        <v>1259</v>
       </c>
       <c r="D77">
-        <v>2199</v>
+        <v>1259</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2544,18 +2512,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46149.791666666657</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>1134</v>
+        <v>1060</v>
       </c>
       <c r="C78">
-        <v>1059</v>
+        <v>1250</v>
       </c>
       <c r="D78">
-        <v>2193</v>
+        <v>2310</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2564,18 +2532,18 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46149.802083333343</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>1135</v>
+        <v>1066</v>
       </c>
       <c r="C79">
-        <v>1060</v>
+        <v>1258</v>
       </c>
       <c r="D79">
-        <v>2195</v>
+        <v>2324</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2584,18 +2552,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>1140</v>
+        <v>1062</v>
       </c>
       <c r="C80">
-        <v>1061</v>
+        <v>1254</v>
       </c>
       <c r="D80">
-        <v>2201</v>
+        <v>2316</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2604,18 +2572,18 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46149.822916666657</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>1152</v>
+        <v>1057</v>
       </c>
       <c r="C81">
-        <v>1066</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>2218</v>
+        <v>1057</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2624,18 +2592,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46149.833333333343</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>1083</v>
+        <v>1039</v>
       </c>
       <c r="C82">
-        <v>1092</v>
+        <v>1252</v>
       </c>
       <c r="D82">
-        <v>2175</v>
+        <v>2291</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2644,18 +2612,18 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>1078</v>
+        <v>1049</v>
       </c>
       <c r="C83">
-        <v>1093</v>
+        <v>1254</v>
       </c>
       <c r="D83">
-        <v>2171</v>
+        <v>2303</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2664,18 +2632,18 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46149.854166666657</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>1081</v>
+        <v>1046</v>
       </c>
       <c r="C84">
-        <v>1092</v>
+        <v>1253</v>
       </c>
       <c r="D84">
-        <v>2173</v>
+        <v>2299</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2684,18 +2652,18 @@
         <v>88</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46149.864583333343</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>1078</v>
+        <v>1045</v>
       </c>
       <c r="C85">
-        <v>1090</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>2168</v>
+        <v>1045</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2704,18 +2672,18 @@
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>991</v>
+        <v>970</v>
       </c>
       <c r="C86">
-        <v>1114</v>
+        <v>1235</v>
       </c>
       <c r="D86">
-        <v>2105</v>
+        <v>2205</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2724,18 +2692,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46149.885416666657</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>982</v>
+        <v>969</v>
       </c>
       <c r="C87">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2092</v>
+        <v>969</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2744,18 +2712,18 @@
         <v>91</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46149.895833333343</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>979</v>
+        <v>966</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1234</v>
       </c>
       <c r="D88">
-        <v>979</v>
+        <v>2200</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2764,18 +2732,18 @@
         <v>92</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="C89">
-        <v>1105</v>
+        <v>1230</v>
       </c>
       <c r="D89">
-        <v>2072</v>
+        <v>2183</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2784,18 +2752,18 @@
         <v>93</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46149.916666666657</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>929</v>
+        <v>906</v>
       </c>
       <c r="C90">
-        <v>937</v>
+        <v>1106</v>
       </c>
       <c r="D90">
-        <v>1866</v>
+        <v>2012</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2804,18 +2772,18 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46149.927083333343</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="C91">
-        <v>920</v>
+        <v>1079</v>
       </c>
       <c r="D91">
-        <v>1840</v>
+        <v>1986</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2824,18 +2792,18 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="C92">
-        <v>923</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1840</v>
+        <v>909</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2844,18 +2812,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46149.947916666657</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C93">
-        <v>921</v>
+        <v>1080</v>
       </c>
       <c r="D93">
-        <v>1844</v>
+        <v>1991</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2864,18 +2832,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46149.958333333343</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>643</v>
+        <v>746</v>
       </c>
       <c r="C94">
-        <v>906</v>
+        <v>972</v>
       </c>
       <c r="D94">
-        <v>1549</v>
+        <v>1718</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2884,18 +2852,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>627</v>
+        <v>732</v>
       </c>
       <c r="C95">
-        <v>898</v>
+        <v>964</v>
       </c>
       <c r="D95">
-        <v>1525</v>
+        <v>1696</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2904,18 +2872,18 @@
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46149.979166666657</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>623</v>
+        <v>751</v>
       </c>
       <c r="C96">
-        <v>899</v>
+        <v>965</v>
       </c>
       <c r="D96">
-        <v>1522</v>
+        <v>1716</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2924,18 +2892,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46149.989583333343</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>616</v>
+        <v>750</v>
       </c>
       <c r="C97">
-        <v>897</v>
+        <v>953</v>
       </c>
       <c r="D97">
-        <v>1513</v>
+        <v>1703</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2944,18 +2912,18 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
-        <v>663</v>
+        <v>604</v>
       </c>
       <c r="C98">
-        <v>928</v>
+        <v>965</v>
       </c>
       <c r="D98">
-        <v>1591</v>
+        <v>1569</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2964,18 +2932,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46150.010416666657</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B99">
-        <v>656</v>
+        <v>599</v>
       </c>
       <c r="C99">
-        <v>922</v>
+        <v>964</v>
       </c>
       <c r="D99">
-        <v>1578</v>
+        <v>1563</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2984,18 +2952,18 @@
         <v>103</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46150.020833333343</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B100">
-        <v>655</v>
+        <v>595</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="D100">
-        <v>655</v>
+        <v>1556</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3004,18 +2972,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B101">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>1565</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3024,18 +2992,18 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46150.041666666657</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B102">
-        <v>651</v>
+        <v>584</v>
       </c>
       <c r="C102">
-        <v>894</v>
+        <v>964</v>
       </c>
       <c r="D102">
-        <v>1545</v>
+        <v>1548</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3044,18 +3012,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46150.052083333343</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B103">
-        <v>647</v>
+        <v>581</v>
       </c>
       <c r="C103">
-        <v>888</v>
+        <v>960</v>
       </c>
       <c r="D103">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3064,18 +3032,18 @@
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="C104">
-        <v>889</v>
+        <v>961</v>
       </c>
       <c r="D104">
-        <v>889</v>
+        <v>1538</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3084,18 +3052,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46150.072916666657</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B105">
-        <v>653</v>
+        <v>566</v>
       </c>
       <c r="C105">
-        <v>888</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>1541</v>
+        <v>566</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3104,18 +3072,18 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46150.083333333343</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>572</v>
       </c>
       <c r="C106">
-        <v>890</v>
+        <v>957</v>
       </c>
       <c r="D106">
-        <v>890</v>
+        <v>1529</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3124,18 +3092,18 @@
         <v>110</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B107">
-        <v>646</v>
+        <v>570</v>
       </c>
       <c r="C107">
-        <v>888</v>
+        <v>954</v>
       </c>
       <c r="D107">
-        <v>1534</v>
+        <v>1524</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3144,18 +3112,18 @@
         <v>111</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46150.104166666657</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B108">
-        <v>648</v>
+        <v>564</v>
       </c>
       <c r="C108">
-        <v>890</v>
+        <v>956</v>
       </c>
       <c r="D108">
-        <v>1538</v>
+        <v>1520</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3164,18 +3132,18 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46150.114583333343</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B109">
-        <v>655</v>
+        <v>528</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>918</v>
       </c>
       <c r="D109">
-        <v>655</v>
+        <v>1446</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3184,18 +3152,18 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B110">
-        <v>659</v>
+        <v>530</v>
       </c>
       <c r="C110">
-        <v>903</v>
+        <v>945</v>
       </c>
       <c r="D110">
-        <v>1562</v>
+        <v>1475</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3204,18 +3172,18 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46150.135416666657</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3224,18 +3192,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46150.145833333343</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="C112">
-        <v>903</v>
+        <v>967</v>
       </c>
       <c r="D112">
-        <v>903</v>
+        <v>1526</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3244,18 +3212,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B113">
-        <v>660</v>
+        <v>581</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>660</v>
+        <v>581</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3264,18 +3232,18 @@
         <v>117</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46150.166666666657</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B114">
-        <v>693</v>
+        <v>637</v>
       </c>
       <c r="C114">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>1600</v>
+        <v>637</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3284,18 +3252,18 @@
         <v>118</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46150.177083333343</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B115">
-        <v>691</v>
+        <v>650</v>
       </c>
       <c r="C115">
-        <v>906</v>
+        <v>997</v>
       </c>
       <c r="D115">
-        <v>1597</v>
+        <v>1647</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3304,18 +3272,18 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B116">
-        <v>682</v>
+        <v>634</v>
       </c>
       <c r="C116">
-        <v>905</v>
+        <v>1022</v>
       </c>
       <c r="D116">
-        <v>1587</v>
+        <v>1656</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3324,18 +3292,18 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46150.197916666657</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B117">
-        <v>706</v>
+        <v>639</v>
       </c>
       <c r="C117">
-        <v>903</v>
+        <v>1025</v>
       </c>
       <c r="D117">
-        <v>1609</v>
+        <v>1664</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3344,18 +3312,18 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46150.208333333343</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B118">
-        <v>756</v>
+        <v>686</v>
       </c>
       <c r="C118">
-        <v>925</v>
+        <v>1041</v>
       </c>
       <c r="D118">
-        <v>1681</v>
+        <v>1727</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3364,18 +3332,18 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B119">
-        <v>759</v>
+        <v>688</v>
       </c>
       <c r="C119">
-        <v>928</v>
+        <v>1033</v>
       </c>
       <c r="D119">
-        <v>1687</v>
+        <v>1721</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3384,18 +3352,18 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46150.229166666657</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B120">
-        <v>755</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1042</v>
       </c>
       <c r="D120">
-        <v>755</v>
+        <v>1042</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3404,18 +3372,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46150.239583333343</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B121">
-        <v>750</v>
+        <v>691</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1043</v>
       </c>
       <c r="D121">
-        <v>750</v>
+        <v>1734</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3424,18 +3392,18 @@
         <v>125</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B122">
-        <v>854</v>
+        <v>711</v>
       </c>
       <c r="C122">
-        <v>950</v>
+        <v>1045</v>
       </c>
       <c r="D122">
-        <v>1804</v>
+        <v>1756</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3444,18 +3412,18 @@
         <v>126</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46150.260416666657</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B123">
-        <v>860</v>
+        <v>759</v>
       </c>
       <c r="C123">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>1807</v>
+        <v>759</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3464,18 +3432,18 @@
         <v>127</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46150.270833333343</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B124">
-        <v>861</v>
+        <v>750</v>
       </c>
       <c r="C124">
-        <v>948</v>
+        <v>1053</v>
       </c>
       <c r="D124">
-        <v>1809</v>
+        <v>1803</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3484,18 +3452,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B125">
-        <v>862</v>
+        <v>749</v>
       </c>
       <c r="C125">
-        <v>953</v>
+        <v>1054</v>
       </c>
       <c r="D125">
-        <v>1815</v>
+        <v>1803</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3504,18 +3472,18 @@
         <v>129</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46150.291666666657</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B126">
-        <v>868</v>
+        <v>745</v>
       </c>
       <c r="C126">
-        <v>939</v>
+        <v>1022</v>
       </c>
       <c r="D126">
-        <v>1807</v>
+        <v>1767</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3524,18 +3492,18 @@
         <v>130</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46150.302083333343</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B127">
-        <v>872</v>
+        <v>733</v>
       </c>
       <c r="C127">
-        <v>935</v>
+        <v>1014</v>
       </c>
       <c r="D127">
-        <v>1807</v>
+        <v>1747</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3544,18 +3512,18 @@
         <v>131</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B128">
-        <v>867</v>
+        <v>731</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="D128">
-        <v>867</v>
+        <v>1754</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3564,18 +3532,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46150.322916666657</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>974</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1708</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3584,18 +3552,18 @@
         <v>133</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46150.333333333343</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>863</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>1460</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3604,18 +3572,18 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3624,18 +3592,18 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46150.354166666657</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1675</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3644,18 +3612,18 @@
         <v>136</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46150.364583333343</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>748</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1723</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3664,18 +3632,18 @@
         <v>137</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1013</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1795</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3684,18 +3652,18 @@
         <v>138</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46150.385416666657</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>2048</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3704,18 +3672,18 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46150.395833333343</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1329</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>2133</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3724,18 +3692,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1342</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3744,18 +3712,18 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46150.416666666657</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>2084</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3764,18 +3732,18 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46150.427083333343</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>948</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3784,9 +3752,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3804,9 +3772,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46150.447916666657</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3824,9 +3792,9 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46150.458333333343</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3844,9 +3812,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3864,9 +3832,9 @@
         <v>147</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46150.479166666657</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3884,9 +3852,9 @@
         <v>148</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46150.489583333343</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3904,9 +3872,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3924,9 +3892,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46150.510416666657</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3944,9 +3912,9 @@
         <v>151</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46150.520833333343</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3964,9 +3932,9 @@
         <v>152</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3984,9 +3952,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46150.541666666657</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4004,9 +3972,9 @@
         <v>154</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46150.552083333343</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4024,9 +3992,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4044,9 +4012,9 @@
         <v>156</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46150.572916666657</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4064,9 +4032,9 @@
         <v>157</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46150.583333333343</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4084,9 +4052,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4104,9 +4072,9 @@
         <v>159</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46150.604166666657</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4124,9 +4092,9 @@
         <v>160</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46150.614583333343</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4144,9 +4112,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4164,9 +4132,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46150.635416666657</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4184,9 +4152,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46150.645833333343</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4204,9 +4172,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4224,9 +4192,9 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46150.666666666657</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4244,9 +4212,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46150.677083333343</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4264,9 +4232,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4284,9 +4252,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46150.697916666657</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4304,9 +4272,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46150.708333333343</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4324,9 +4292,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4344,9 +4312,9 @@
         <v>171</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46150.729166666657</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4364,9 +4332,9 @@
         <v>172</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46150.739583333343</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4384,9 +4352,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4404,9 +4372,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46150.760416666657</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4424,9 +4392,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46150.770833333343</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4444,9 +4412,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4464,9 +4432,9 @@
         <v>177</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46150.791666666657</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4484,9 +4452,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46150.802083333343</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4504,9 +4472,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4524,9 +4492,9 @@
         <v>180</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46150.822916666657</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4544,9 +4512,9 @@
         <v>181</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46150.833333333343</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4564,9 +4532,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4584,9 +4552,9 @@
         <v>183</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46150.854166666657</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4604,9 +4572,9 @@
         <v>184</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46150.864583333343</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4624,9 +4592,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4644,9 +4612,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46150.885416666657</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4664,9 +4632,9 @@
         <v>187</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46150.895833333343</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4684,9 +4652,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4704,9 +4672,9 @@
         <v>189</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46150.916666666657</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4724,9 +4692,9 @@
         <v>190</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46150.927083333343</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4744,9 +4712,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4764,9 +4732,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46150.947916666657</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4784,9 +4752,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46150.958333333343</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4804,9 +4772,9 @@
         <v>194</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4824,9 +4792,9 @@
         <v>195</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46150.979166666657</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4844,9 +4812,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46150.989583333343</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>11.05.202694</t>
-  </si>
-  <si>
-    <t>11.05.202695</t>
-  </si>
-  <si>
-    <t>11.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202694</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>587</v>
+        <v>634</v>
       </c>
       <c r="C2">
-        <v>1033</v>
+        <v>943</v>
       </c>
       <c r="D2">
-        <v>1620</v>
+        <v>1577</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>583</v>
+        <v>636</v>
       </c>
       <c r="C3">
-        <v>1032</v>
+        <v>933</v>
       </c>
       <c r="D3">
-        <v>1615</v>
+        <v>1569</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>581</v>
+        <v>639</v>
       </c>
       <c r="C4">
-        <v>1030</v>
+        <v>934</v>
       </c>
       <c r="D4">
-        <v>1611</v>
+        <v>1573</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>582</v>
+        <v>638</v>
       </c>
       <c r="C5">
-        <v>1028</v>
+        <v>932</v>
       </c>
       <c r="D5">
-        <v>1610</v>
+        <v>1570</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>572</v>
+        <v>639</v>
       </c>
       <c r="C6">
-        <v>1032</v>
+        <v>915</v>
       </c>
       <c r="D6">
-        <v>1604</v>
+        <v>1554</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>581</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1029</v>
+        <v>914</v>
       </c>
       <c r="D7">
-        <v>1610</v>
+        <v>914</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>567</v>
+        <v>640</v>
       </c>
       <c r="C8">
-        <v>1027</v>
+        <v>947</v>
       </c>
       <c r="D8">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>568</v>
+        <v>636</v>
       </c>
       <c r="C9">
-        <v>1031</v>
+        <v>946</v>
       </c>
       <c r="D9">
-        <v>1599</v>
+        <v>1582</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>505</v>
+        <v>640</v>
       </c>
       <c r="C10">
-        <v>1036</v>
+        <v>905</v>
       </c>
       <c r="D10">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>504</v>
+        <v>639</v>
       </c>
       <c r="C11">
-        <v>1033</v>
+        <v>903</v>
       </c>
       <c r="D11">
-        <v>1537</v>
+        <v>1542</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="C12">
-        <v>1035</v>
+        <v>901</v>
       </c>
       <c r="D12">
-        <v>1035</v>
+        <v>1538</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1036</v>
+        <v>916</v>
       </c>
       <c r="D13">
-        <v>1539</v>
+        <v>916</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>506</v>
+        <v>632</v>
       </c>
       <c r="C14">
-        <v>1039</v>
+        <v>928</v>
       </c>
       <c r="D14">
-        <v>1545</v>
+        <v>1560</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>507</v>
+        <v>624</v>
       </c>
       <c r="C15">
-        <v>1040</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1547</v>
+        <v>624</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1567</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>506</v>
+        <v>623</v>
       </c>
       <c r="C17">
-        <v>1038</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1544</v>
+        <v>623</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>517</v>
+        <v>645</v>
       </c>
       <c r="C18">
-        <v>1048</v>
+        <v>932</v>
       </c>
       <c r="D18">
-        <v>1565</v>
+        <v>1577</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>933</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1589</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>519</v>
+        <v>665</v>
       </c>
       <c r="C20">
-        <v>1047</v>
+        <v>938</v>
       </c>
       <c r="D20">
-        <v>1566</v>
+        <v>1603</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>530</v>
+        <v>668</v>
       </c>
       <c r="C21">
-        <v>1049</v>
+        <v>949</v>
       </c>
       <c r="D21">
-        <v>1579</v>
+        <v>1617</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>577</v>
+        <v>718</v>
       </c>
       <c r="C22">
-        <v>1051</v>
+        <v>937</v>
       </c>
       <c r="D22">
-        <v>1628</v>
+        <v>1655</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>575</v>
+        <v>713</v>
       </c>
       <c r="C23">
-        <v>1053</v>
+        <v>943</v>
       </c>
       <c r="D23">
-        <v>1628</v>
+        <v>1656</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>558</v>
+        <v>708</v>
       </c>
       <c r="C24">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1608</v>
+        <v>708</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>579</v>
+        <v>719</v>
       </c>
       <c r="C25">
-        <v>1053</v>
+        <v>946</v>
       </c>
       <c r="D25">
-        <v>1632</v>
+        <v>1665</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,13 +1474,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>711</v>
+        <v>782</v>
       </c>
       <c r="C26">
-        <v>1049</v>
+        <v>978</v>
       </c>
       <c r="D26">
         <v>1760</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>706</v>
+        <v>793</v>
       </c>
       <c r="C27">
-        <v>1043</v>
+        <v>973</v>
       </c>
       <c r="D27">
-        <v>1749</v>
+        <v>1766</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="C28">
-        <v>1045</v>
+        <v>968</v>
       </c>
       <c r="D28">
-        <v>1045</v>
+        <v>1760</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>735</v>
+        <v>795</v>
       </c>
       <c r="C29">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1748</v>
+        <v>795</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="C30">
-        <v>985</v>
+        <v>950</v>
       </c>
       <c r="D30">
-        <v>1702</v>
+        <v>1714</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>718</v>
+        <v>763</v>
       </c>
       <c r="C31">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1698</v>
+        <v>763</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>728</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>981</v>
+        <v>948</v>
       </c>
       <c r="D32">
-        <v>1709</v>
+        <v>948</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>720</v>
+        <v>761</v>
       </c>
       <c r="C33">
-        <v>983</v>
+        <v>949</v>
       </c>
       <c r="D33">
-        <v>1703</v>
+        <v>1710</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>640</v>
+        <v>738</v>
       </c>
       <c r="C34">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="D34">
-        <v>1607</v>
+        <v>1689</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>629</v>
+        <v>735</v>
       </c>
       <c r="C35">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="D35">
-        <v>1593</v>
+        <v>1685</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>636</v>
+        <v>732</v>
       </c>
       <c r="C36">
-        <v>969</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1605</v>
+        <v>732</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>633</v>
+        <v>721</v>
       </c>
       <c r="C37">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="D37">
-        <v>1598</v>
+        <v>1669</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>611</v>
+        <v>689</v>
       </c>
       <c r="C38">
-        <v>893</v>
+        <v>942</v>
       </c>
       <c r="D38">
-        <v>1504</v>
+        <v>1631</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>621</v>
+        <v>684</v>
       </c>
       <c r="C39">
-        <v>883</v>
+        <v>939</v>
       </c>
       <c r="D39">
-        <v>1504</v>
+        <v>1623</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>606</v>
+        <v>692</v>
       </c>
       <c r="C40">
-        <v>886</v>
+        <v>943</v>
       </c>
       <c r="D40">
-        <v>1492</v>
+        <v>1635</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="C41">
-        <v>882</v>
+        <v>942</v>
       </c>
       <c r="D41">
-        <v>882</v>
+        <v>1625</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>521</v>
+        <v>613</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="D42">
-        <v>521</v>
+        <v>1543</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>522</v>
+        <v>611</v>
       </c>
       <c r="C43">
-        <v>881</v>
+        <v>925</v>
       </c>
       <c r="D43">
-        <v>1403</v>
+        <v>1536</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>523</v>
+        <v>604</v>
       </c>
       <c r="C44">
-        <v>964</v>
+        <v>937</v>
       </c>
       <c r="D44">
-        <v>1487</v>
+        <v>1541</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="C45">
-        <v>968</v>
+        <v>940</v>
       </c>
       <c r="D45">
-        <v>968</v>
+        <v>1547</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C46">
-        <v>893</v>
+        <v>921</v>
       </c>
       <c r="D46">
-        <v>1505</v>
+        <v>1529</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="C47">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="D47">
-        <v>1521</v>
+        <v>1513</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>641</v>
+        <v>609</v>
       </c>
       <c r="C48">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="D48">
-        <v>1568</v>
+        <v>1530</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>643</v>
+        <v>595</v>
       </c>
       <c r="C49">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="D49">
-        <v>1571</v>
+        <v>1512</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>638</v>
+        <v>587</v>
       </c>
       <c r="C50">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D50">
-        <v>1565</v>
+        <v>1515</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="C51">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="D51">
-        <v>1561</v>
+        <v>1511</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="C52">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D52">
-        <v>1568</v>
+        <v>1508</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="C53">
-        <v>934</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1559</v>
+        <v>600</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="C54">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>1588</v>
+        <v>588</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="C55">
-        <v>973</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>973</v>
+        <v>583</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>603</v>
+        <v>579</v>
       </c>
       <c r="C56">
-        <v>972</v>
+        <v>927</v>
       </c>
       <c r="D56">
-        <v>1575</v>
+        <v>1506</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="C57">
-        <v>970</v>
+        <v>915</v>
       </c>
       <c r="D57">
-        <v>1566</v>
+        <v>1504</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>582</v>
+        <v>649</v>
       </c>
       <c r="C58">
-        <v>979</v>
+        <v>871</v>
       </c>
       <c r="D58">
-        <v>1561</v>
+        <v>1520</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>585</v>
+        <v>660</v>
       </c>
       <c r="C59">
-        <v>983</v>
+        <v>865</v>
       </c>
       <c r="D59">
-        <v>1568</v>
+        <v>1525</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>566</v>
+        <v>661</v>
       </c>
       <c r="C60">
-        <v>916</v>
+        <v>869</v>
       </c>
       <c r="D60">
-        <v>1482</v>
+        <v>1530</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>569</v>
+        <v>662</v>
       </c>
       <c r="C61">
-        <v>914</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1483</v>
+        <v>662</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>573</v>
+        <v>634</v>
       </c>
       <c r="C62">
-        <v>923</v>
+        <v>904</v>
       </c>
       <c r="D62">
-        <v>1496</v>
+        <v>1538</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>583</v>
+        <v>622</v>
       </c>
       <c r="C63">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="D63">
-        <v>1495</v>
+        <v>1529</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>571</v>
+        <v>625</v>
       </c>
       <c r="C64">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="D64">
-        <v>1473</v>
+        <v>1534</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>587</v>
+        <v>644</v>
       </c>
       <c r="C65">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D65">
-        <v>1488</v>
+        <v>1551</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>545</v>
+        <v>747</v>
       </c>
       <c r="C66">
-        <v>934</v>
+        <v>962</v>
       </c>
       <c r="D66">
-        <v>1479</v>
+        <v>1709</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>539</v>
+        <v>755</v>
       </c>
       <c r="C67">
-        <v>940</v>
+        <v>966</v>
       </c>
       <c r="D67">
-        <v>1479</v>
+        <v>1721</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>547</v>
+        <v>754</v>
       </c>
       <c r="C68">
-        <v>941</v>
+        <v>965</v>
       </c>
       <c r="D68">
-        <v>1488</v>
+        <v>1719</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>558</v>
+        <v>794</v>
       </c>
       <c r="C69">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>1508</v>
+        <v>794</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>771</v>
+        <v>1053</v>
       </c>
       <c r="C70">
-        <v>1060</v>
+        <v>1024</v>
       </c>
       <c r="D70">
-        <v>1831</v>
+        <v>2077</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>815</v>
+        <v>1045</v>
       </c>
       <c r="C71">
-        <v>1070</v>
+        <v>1032</v>
       </c>
       <c r="D71">
-        <v>1885</v>
+        <v>2077</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>879</v>
+        <v>1046</v>
       </c>
       <c r="C72">
-        <v>1101</v>
+        <v>1031</v>
       </c>
       <c r="D72">
-        <v>1980</v>
+        <v>2077</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>935</v>
+        <v>1047</v>
       </c>
       <c r="C73">
-        <v>1109</v>
+        <v>1046</v>
       </c>
       <c r="D73">
-        <v>2044</v>
+        <v>2093</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>1049</v>
+        <v>1080</v>
       </c>
       <c r="C74">
-        <v>1244</v>
+        <v>1180</v>
       </c>
       <c r="D74">
-        <v>2293</v>
+        <v>2260</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>1052</v>
+        <v>1096</v>
       </c>
       <c r="C75">
-        <v>1252</v>
+        <v>1189</v>
       </c>
       <c r="D75">
-        <v>2304</v>
+        <v>2285</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>1057</v>
+        <v>1098</v>
       </c>
       <c r="C76">
-        <v>1257</v>
+        <v>1206</v>
       </c>
       <c r="D76">
-        <v>2314</v>
+        <v>2304</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="C77">
-        <v>1259</v>
+        <v>1212</v>
       </c>
       <c r="D77">
-        <v>1259</v>
+        <v>2323</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>1060</v>
+        <v>1149</v>
       </c>
       <c r="C78">
-        <v>1250</v>
+        <v>1190</v>
       </c>
       <c r="D78">
-        <v>2310</v>
+        <v>2339</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>1066</v>
+        <v>1164</v>
       </c>
       <c r="C79">
-        <v>1258</v>
+        <v>1159</v>
       </c>
       <c r="D79">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>1062</v>
+        <v>1163</v>
       </c>
       <c r="C80">
-        <v>1254</v>
+        <v>1155</v>
       </c>
       <c r="D80">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>1057</v>
+        <v>1172</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="D81">
-        <v>1057</v>
+        <v>2329</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>1039</v>
+        <v>1150</v>
       </c>
       <c r="C82">
-        <v>1252</v>
+        <v>1181</v>
       </c>
       <c r="D82">
-        <v>2291</v>
+        <v>2331</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>1049</v>
+        <v>1148</v>
       </c>
       <c r="C83">
-        <v>1254</v>
+        <v>1170</v>
       </c>
       <c r="D83">
-        <v>2303</v>
+        <v>2318</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>1046</v>
+        <v>1145</v>
       </c>
       <c r="C84">
-        <v>1253</v>
+        <v>1115</v>
       </c>
       <c r="D84">
-        <v>2299</v>
+        <v>2260</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>1045</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="D85">
-        <v>1045</v>
+        <v>1102</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>970</v>
+        <v>1025</v>
       </c>
       <c r="C86">
-        <v>1235</v>
+        <v>1143</v>
       </c>
       <c r="D86">
-        <v>2205</v>
+        <v>2168</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>969</v>
+        <v>1019</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="D87">
-        <v>969</v>
+        <v>2159</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>966</v>
+        <v>1016</v>
       </c>
       <c r="C88">
-        <v>1234</v>
+        <v>1145</v>
       </c>
       <c r="D88">
-        <v>2200</v>
+        <v>2161</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>953</v>
+        <v>1014</v>
       </c>
       <c r="C89">
-        <v>1230</v>
+        <v>1141</v>
       </c>
       <c r="D89">
-        <v>2183</v>
+        <v>2155</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>906</v>
+        <v>828</v>
       </c>
       <c r="C90">
-        <v>1106</v>
+        <v>1154</v>
       </c>
       <c r="D90">
-        <v>2012</v>
+        <v>1982</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>907</v>
+        <v>801</v>
       </c>
       <c r="C91">
-        <v>1079</v>
+        <v>1149</v>
       </c>
       <c r="D91">
-        <v>1986</v>
+        <v>1950</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>909</v>
+        <v>804</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="D92">
-        <v>909</v>
+        <v>1956</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>911</v>
+        <v>786</v>
       </c>
       <c r="C93">
-        <v>1080</v>
+        <v>1148</v>
       </c>
       <c r="D93">
-        <v>1991</v>
+        <v>1934</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C94">
-        <v>972</v>
+        <v>1053</v>
       </c>
       <c r="D94">
-        <v>1718</v>
+        <v>1803</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C95">
-        <v>964</v>
+        <v>1035</v>
       </c>
       <c r="D95">
-        <v>1696</v>
+        <v>1768</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="C96">
-        <v>965</v>
+        <v>1038</v>
       </c>
       <c r="D96">
-        <v>1716</v>
+        <v>1780</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>953</v>
+        <v>1037</v>
       </c>
       <c r="D97">
-        <v>1703</v>
+        <v>1037</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
-        <v>604</v>
+        <v>672</v>
       </c>
       <c r="C98">
-        <v>965</v>
+        <v>1020</v>
       </c>
       <c r="D98">
-        <v>1569</v>
+        <v>1692</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
-        <v>599</v>
+        <v>653</v>
       </c>
       <c r="C99">
-        <v>964</v>
+        <v>1029</v>
       </c>
       <c r="D99">
-        <v>1563</v>
+        <v>1682</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
-        <v>595</v>
+        <v>649</v>
       </c>
       <c r="C100">
-        <v>961</v>
+        <v>1027</v>
       </c>
       <c r="D100">
-        <v>1556</v>
+        <v>1676</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1669</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
-        <v>584</v>
+        <v>618</v>
       </c>
       <c r="C102">
-        <v>964</v>
+        <v>1031</v>
       </c>
       <c r="D102">
-        <v>1548</v>
+        <v>1649</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
-        <v>581</v>
+        <v>614</v>
       </c>
       <c r="C103">
-        <v>960</v>
+        <v>1027</v>
       </c>
       <c r="D103">
-        <v>1541</v>
+        <v>1641</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
-        <v>577</v>
+        <v>615</v>
       </c>
       <c r="C104">
-        <v>961</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1538</v>
+        <v>615</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="C106">
-        <v>957</v>
+        <v>1032</v>
       </c>
       <c r="D106">
-        <v>1529</v>
+        <v>1635</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
-        <v>570</v>
+        <v>601</v>
       </c>
       <c r="C107">
-        <v>954</v>
+        <v>1013</v>
       </c>
       <c r="D107">
-        <v>1524</v>
+        <v>1614</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
-        <v>564</v>
+        <v>602</v>
       </c>
       <c r="C108">
-        <v>956</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>1520</v>
+        <v>602</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
-        <v>528</v>
+        <v>603</v>
       </c>
       <c r="C109">
-        <v>918</v>
+        <v>1015</v>
       </c>
       <c r="D109">
-        <v>1446</v>
+        <v>1618</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>530</v>
+        <v>612</v>
       </c>
       <c r="C110">
-        <v>945</v>
+        <v>1022</v>
       </c>
       <c r="D110">
-        <v>1475</v>
+        <v>1634</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
-        <v>559</v>
+        <v>613</v>
       </c>
       <c r="C112">
-        <v>967</v>
+        <v>1022</v>
       </c>
       <c r="D112">
-        <v>1526</v>
+        <v>1635</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>581</v>
+        <v>621</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1016</v>
       </c>
       <c r="D114">
-        <v>637</v>
+        <v>1681</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>997</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1647</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>634</v>
+        <v>667</v>
       </c>
       <c r="C116">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D116">
-        <v>1656</v>
+        <v>1688</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>639</v>
+        <v>679</v>
       </c>
       <c r="C117">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="D117">
-        <v>1664</v>
+        <v>1702</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>686</v>
+        <v>751</v>
       </c>
       <c r="C118">
-        <v>1041</v>
+        <v>1018</v>
       </c>
       <c r="D118">
-        <v>1727</v>
+        <v>1769</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>688</v>
+        <v>758</v>
       </c>
       <c r="C119">
-        <v>1033</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1721</v>
+        <v>758</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>1042</v>
+        <v>1014</v>
       </c>
       <c r="D120">
-        <v>1042</v>
+        <v>1014</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>691</v>
+        <v>762</v>
       </c>
       <c r="C121">
-        <v>1043</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1734</v>
+        <v>762</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>711</v>
+        <v>808</v>
       </c>
       <c r="C122">
-        <v>1045</v>
+        <v>1013</v>
       </c>
       <c r="D122">
-        <v>1756</v>
+        <v>1821</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>759</v>
+        <v>803</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="D123">
-        <v>759</v>
+        <v>1817</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="C124">
-        <v>1053</v>
+        <v>1009</v>
       </c>
       <c r="D124">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>749</v>
+        <v>803</v>
       </c>
       <c r="C125">
-        <v>1054</v>
+        <v>1011</v>
       </c>
       <c r="D125">
-        <v>1803</v>
+        <v>1814</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>745</v>
+        <v>793</v>
       </c>
       <c r="C126">
-        <v>1022</v>
+        <v>996</v>
       </c>
       <c r="D126">
-        <v>1767</v>
+        <v>1789</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>733</v>
+        <v>808</v>
       </c>
       <c r="C127">
-        <v>1014</v>
+        <v>976</v>
       </c>
       <c r="D127">
-        <v>1747</v>
+        <v>1784</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>731</v>
+        <v>798</v>
       </c>
       <c r="C128">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>1754</v>
+        <v>798</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>734</v>
+        <v>792</v>
       </c>
       <c r="C129">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D129">
-        <v>1708</v>
+        <v>1765</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>597</v>
+        <v>734</v>
       </c>
       <c r="C130">
-        <v>863</v>
+        <v>950</v>
       </c>
       <c r="D130">
-        <v>1460</v>
+        <v>1684</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>644</v>
+        <v>755</v>
       </c>
       <c r="C131">
-        <v>852</v>
+        <v>949</v>
       </c>
       <c r="D131">
-        <v>1496</v>
+        <v>1704</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>723</v>
+        <v>756</v>
       </c>
       <c r="C132">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="D132">
-        <v>1675</v>
+        <v>1703</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>748</v>
+        <v>713</v>
       </c>
       <c r="C133">
-        <v>975</v>
+        <v>918</v>
       </c>
       <c r="D133">
-        <v>1723</v>
+        <v>1631</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>782</v>
+        <v>625</v>
       </c>
       <c r="C134">
-        <v>1013</v>
+        <v>953</v>
       </c>
       <c r="D134">
-        <v>1795</v>
+        <v>1578</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>826</v>
+        <v>617</v>
       </c>
       <c r="C135">
-        <v>1222</v>
+        <v>950</v>
       </c>
       <c r="D135">
-        <v>2048</v>
+        <v>1567</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>804</v>
+        <v>619</v>
       </c>
       <c r="C136">
-        <v>1329</v>
+        <v>954</v>
       </c>
       <c r="D136">
-        <v>2133</v>
+        <v>1573</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="C137">
-        <v>1342</v>
+        <v>951</v>
       </c>
       <c r="D137">
-        <v>1342</v>
+        <v>1566</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>914</v>
+        <v>562</v>
       </c>
       <c r="C138">
-        <v>1170</v>
+        <v>950</v>
       </c>
       <c r="D138">
-        <v>2084</v>
+        <v>1512</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202694</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
-        <v>634</v>
+        <v>672</v>
       </c>
       <c r="C2">
-        <v>943</v>
+        <v>1020</v>
       </c>
       <c r="D2">
-        <v>1577</v>
+        <v>1692</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="C3">
-        <v>933</v>
+        <v>1029</v>
       </c>
       <c r="D3">
-        <v>1569</v>
+        <v>1682</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="C4">
-        <v>934</v>
+        <v>1027</v>
       </c>
       <c r="D4">
-        <v>1573</v>
+        <v>1676</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="C5">
-        <v>932</v>
+        <v>1026</v>
       </c>
       <c r="D5">
-        <v>1570</v>
+        <v>1669</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="C6">
-        <v>915</v>
+        <v>1031</v>
       </c>
       <c r="D6">
-        <v>1554</v>
+        <v>1649</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="C7">
-        <v>914</v>
+        <v>1027</v>
       </c>
       <c r="D7">
-        <v>914</v>
+        <v>1641</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
-        <v>640</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1587</v>
+        <v>615</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="C9">
-        <v>946</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1582</v>
+        <v>617</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
-        <v>640</v>
+        <v>603</v>
       </c>
       <c r="C10">
-        <v>905</v>
+        <v>1032</v>
       </c>
       <c r="D10">
-        <v>1545</v>
+        <v>1635</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
-        <v>639</v>
+        <v>601</v>
       </c>
       <c r="C11">
-        <v>903</v>
+        <v>1013</v>
       </c>
       <c r="D11">
-        <v>1542</v>
+        <v>1614</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
-        <v>637</v>
+        <v>602</v>
       </c>
       <c r="C12">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1538</v>
+        <v>602</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="C13">
-        <v>916</v>
+        <v>1015</v>
       </c>
       <c r="D13">
-        <v>916</v>
+        <v>1618</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="C14">
-        <v>928</v>
+        <v>1022</v>
       </c>
       <c r="D14">
-        <v>1560</v>
+        <v>1634</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
-        <v>624</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1021</v>
       </c>
       <c r="D15">
-        <v>624</v>
+        <v>1021</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
-        <v>638</v>
+        <v>613</v>
       </c>
       <c r="C16">
-        <v>929</v>
+        <v>1022</v>
       </c>
       <c r="D16">
-        <v>1567</v>
+        <v>1635</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="C18">
-        <v>932</v>
+        <v>1016</v>
       </c>
       <c r="D18">
-        <v>1577</v>
+        <v>1681</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>656</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>933</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1589</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C20">
-        <v>938</v>
+        <v>1021</v>
       </c>
       <c r="D20">
-        <v>1603</v>
+        <v>1688</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="C21">
-        <v>949</v>
+        <v>1023</v>
       </c>
       <c r="D21">
-        <v>1617</v>
+        <v>1702</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>718</v>
+        <v>751</v>
       </c>
       <c r="C22">
-        <v>937</v>
+        <v>1018</v>
       </c>
       <c r="D22">
-        <v>1655</v>
+        <v>1769</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>713</v>
+        <v>758</v>
       </c>
       <c r="C23">
-        <v>943</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1656</v>
+        <v>758</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>708</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1014</v>
       </c>
       <c r="D24">
-        <v>708</v>
+        <v>1014</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>719</v>
+        <v>762</v>
       </c>
       <c r="C25">
-        <v>946</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1665</v>
+        <v>762</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>782</v>
+        <v>808</v>
       </c>
       <c r="C26">
-        <v>978</v>
+        <v>1013</v>
       </c>
       <c r="D26">
-        <v>1760</v>
+        <v>1821</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="C27">
-        <v>973</v>
+        <v>1014</v>
       </c>
       <c r="D27">
-        <v>1766</v>
+        <v>1817</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="C28">
-        <v>968</v>
+        <v>1009</v>
       </c>
       <c r="D28">
-        <v>1760</v>
+        <v>1808</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="D29">
-        <v>795</v>
+        <v>1814</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="C30">
-        <v>950</v>
+        <v>996</v>
       </c>
       <c r="D30">
-        <v>1714</v>
+        <v>1789</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>763</v>
+        <v>808</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>976</v>
       </c>
       <c r="D31">
-        <v>763</v>
+        <v>1784</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="C32">
-        <v>948</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>948</v>
+        <v>798</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>761</v>
+        <v>792</v>
       </c>
       <c r="C33">
-        <v>949</v>
+        <v>973</v>
       </c>
       <c r="D33">
-        <v>1710</v>
+        <v>1765</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C34">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D34">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="C35">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D35">
-        <v>1685</v>
+        <v>1704</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>732</v>
+        <v>756</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="D36">
-        <v>732</v>
+        <v>1703</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="C37">
-        <v>948</v>
+        <v>918</v>
       </c>
       <c r="D37">
-        <v>1669</v>
+        <v>1631</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
-        <v>689</v>
+        <v>625</v>
       </c>
       <c r="C38">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="D38">
-        <v>1631</v>
+        <v>1578</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
-        <v>684</v>
+        <v>617</v>
       </c>
       <c r="C39">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="D39">
-        <v>1623</v>
+        <v>1567</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
-        <v>692</v>
+        <v>619</v>
       </c>
       <c r="C40">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="D40">
-        <v>1635</v>
+        <v>1573</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>683</v>
+        <v>615</v>
       </c>
       <c r="C41">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="D41">
-        <v>1625</v>
+        <v>1566</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>613</v>
+        <v>562</v>
       </c>
       <c r="C42">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="D42">
-        <v>1543</v>
+        <v>1512</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="C43">
-        <v>925</v>
+        <v>931</v>
       </c>
       <c r="D43">
-        <v>1536</v>
+        <v>1488</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="C44">
-        <v>937</v>
+        <v>970</v>
       </c>
       <c r="D44">
-        <v>1541</v>
+        <v>1552</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="C45">
-        <v>940</v>
+        <v>957</v>
       </c>
       <c r="D45">
-        <v>1547</v>
+        <v>1532</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>608</v>
+        <v>476</v>
       </c>
       <c r="C46">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="D46">
-        <v>1529</v>
+        <v>1390</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>595</v>
+        <v>479</v>
       </c>
       <c r="C47">
-        <v>918</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1513</v>
+        <v>479</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>609</v>
+        <v>505</v>
       </c>
       <c r="C48">
-        <v>921</v>
+        <v>869</v>
       </c>
       <c r="D48">
-        <v>1530</v>
+        <v>1374</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
-        <v>595</v>
+        <v>527</v>
       </c>
       <c r="C49">
-        <v>917</v>
+        <v>865</v>
       </c>
       <c r="D49">
-        <v>1512</v>
+        <v>1392</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>587</v>
+        <v>295</v>
       </c>
       <c r="C50">
-        <v>928</v>
+        <v>793</v>
       </c>
       <c r="D50">
-        <v>1515</v>
+        <v>1088</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
-        <v>582</v>
+        <v>330</v>
       </c>
       <c r="C51">
-        <v>929</v>
+        <v>745</v>
       </c>
       <c r="D51">
-        <v>1511</v>
+        <v>1075</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>578</v>
+        <v>276</v>
       </c>
       <c r="C52">
-        <v>930</v>
+        <v>790</v>
       </c>
       <c r="D52">
-        <v>1508</v>
+        <v>1066</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>600</v>
+        <v>288</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>791</v>
       </c>
       <c r="D53">
-        <v>600</v>
+        <v>1079</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>588</v>
+        <v>301</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="D54">
-        <v>588</v>
+        <v>1110</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>583</v>
+        <v>296</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>583</v>
+        <v>296</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>579</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>927</v>
+        <v>853</v>
       </c>
       <c r="D56">
-        <v>1506</v>
+        <v>853</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>589</v>
+        <v>285</v>
       </c>
       <c r="C57">
-        <v>915</v>
+        <v>858</v>
       </c>
       <c r="D57">
-        <v>1504</v>
+        <v>1143</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
-        <v>649</v>
+        <v>269</v>
       </c>
       <c r="C58">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="D58">
-        <v>1520</v>
+        <v>1152</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>660</v>
+        <v>275</v>
       </c>
       <c r="C59">
-        <v>865</v>
+        <v>908</v>
       </c>
       <c r="D59">
-        <v>1525</v>
+        <v>1183</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>661</v>
+        <v>284</v>
       </c>
       <c r="C60">
-        <v>869</v>
+        <v>914</v>
       </c>
       <c r="D60">
-        <v>1530</v>
+        <v>1198</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>662</v>
+        <v>287</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="D61">
-        <v>662</v>
+        <v>1202</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
-        <v>634</v>
+        <v>367</v>
       </c>
       <c r="C62">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="D62">
-        <v>1538</v>
+        <v>1267</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
-        <v>622</v>
+        <v>382</v>
       </c>
       <c r="C63">
-        <v>907</v>
+        <v>823</v>
       </c>
       <c r="D63">
-        <v>1529</v>
+        <v>1205</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>909</v>
+        <v>822</v>
       </c>
       <c r="D64">
-        <v>1534</v>
+        <v>822</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>644</v>
+        <v>391</v>
       </c>
       <c r="C65">
-        <v>907</v>
+        <v>824</v>
       </c>
       <c r="D65">
-        <v>1551</v>
+        <v>1215</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>747</v>
+        <v>591</v>
       </c>
       <c r="C66">
-        <v>962</v>
+        <v>1015</v>
       </c>
       <c r="D66">
-        <v>1709</v>
+        <v>1606</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>755</v>
+        <v>592</v>
       </c>
       <c r="C67">
-        <v>966</v>
+        <v>1030</v>
       </c>
       <c r="D67">
-        <v>1721</v>
+        <v>1622</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>754</v>
+        <v>581</v>
       </c>
       <c r="C68">
-        <v>965</v>
+        <v>945</v>
       </c>
       <c r="D68">
-        <v>1719</v>
+        <v>1526</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>794</v>
+        <v>564</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="D69">
-        <v>794</v>
+        <v>1480</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>1053</v>
+        <v>792</v>
       </c>
       <c r="C70">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="D70">
-        <v>2077</v>
+        <v>1809</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>1045</v>
+        <v>888</v>
       </c>
       <c r="C71">
-        <v>1032</v>
+        <v>1042</v>
       </c>
       <c r="D71">
-        <v>2077</v>
+        <v>1930</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>1046</v>
+        <v>940</v>
       </c>
       <c r="C72">
-        <v>1031</v>
+        <v>1075</v>
       </c>
       <c r="D72">
-        <v>2077</v>
+        <v>2015</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>1047</v>
+        <v>952</v>
       </c>
       <c r="C73">
-        <v>1046</v>
+        <v>1108</v>
       </c>
       <c r="D73">
-        <v>2093</v>
+        <v>2060</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>1080</v>
+        <v>1045</v>
       </c>
       <c r="C74">
-        <v>1180</v>
+        <v>1397</v>
       </c>
       <c r="D74">
-        <v>2260</v>
+        <v>2442</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>1096</v>
+        <v>1052</v>
       </c>
       <c r="C75">
-        <v>1189</v>
+        <v>1420</v>
       </c>
       <c r="D75">
-        <v>2285</v>
+        <v>2472</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>1098</v>
+        <v>1050</v>
       </c>
       <c r="C76">
-        <v>1206</v>
+        <v>1416</v>
       </c>
       <c r="D76">
-        <v>2304</v>
+        <v>2466</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>1111</v>
+        <v>1069</v>
       </c>
       <c r="C77">
-        <v>1212</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>2323</v>
+        <v>1069</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>1149</v>
+        <v>1070</v>
       </c>
       <c r="C78">
-        <v>1190</v>
+        <v>1398</v>
       </c>
       <c r="D78">
-        <v>2339</v>
+        <v>2468</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>1164</v>
+        <v>1069</v>
       </c>
       <c r="C79">
-        <v>1159</v>
+        <v>1399</v>
       </c>
       <c r="D79">
-        <v>2323</v>
+        <v>2468</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>1163</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>1155</v>
+        <v>1396</v>
       </c>
       <c r="D80">
-        <v>2318</v>
+        <v>1396</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>1172</v>
+        <v>1078</v>
       </c>
       <c r="C81">
-        <v>1157</v>
+        <v>1394</v>
       </c>
       <c r="D81">
-        <v>2329</v>
+        <v>2472</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>1150</v>
+        <v>1104</v>
       </c>
       <c r="C82">
-        <v>1181</v>
+        <v>1406</v>
       </c>
       <c r="D82">
-        <v>2331</v>
+        <v>2510</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>1148</v>
+        <v>1103</v>
       </c>
       <c r="C83">
-        <v>1170</v>
+        <v>1407</v>
       </c>
       <c r="D83">
-        <v>2318</v>
+        <v>2510</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>1145</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>1115</v>
+        <v>1405</v>
       </c>
       <c r="D84">
-        <v>2260</v>
+        <v>1405</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="C85">
-        <v>1102</v>
+        <v>1406</v>
       </c>
       <c r="D85">
-        <v>1102</v>
+        <v>2498</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>1025</v>
+        <v>1052</v>
       </c>
       <c r="C86">
-        <v>1143</v>
+        <v>1254</v>
       </c>
       <c r="D86">
-        <v>2168</v>
+        <v>2306</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>1019</v>
+        <v>1050</v>
       </c>
       <c r="C87">
-        <v>1140</v>
+        <v>1235</v>
       </c>
       <c r="D87">
-        <v>2159</v>
+        <v>2285</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>1016</v>
+        <v>1167</v>
       </c>
       <c r="C88">
-        <v>1145</v>
+        <v>1286</v>
       </c>
       <c r="D88">
-        <v>2161</v>
+        <v>2453</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>1014</v>
+        <v>1161</v>
       </c>
       <c r="C89">
-        <v>1141</v>
+        <v>1288</v>
       </c>
       <c r="D89">
-        <v>2155</v>
+        <v>2449</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>828</v>
+        <v>1055</v>
       </c>
       <c r="C90">
-        <v>1154</v>
+        <v>1117</v>
       </c>
       <c r="D90">
-        <v>1982</v>
+        <v>2172</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
-        <v>801</v>
+        <v>1050</v>
       </c>
       <c r="C91">
-        <v>1149</v>
+        <v>1103</v>
       </c>
       <c r="D91">
-        <v>1950</v>
+        <v>2153</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
-        <v>804</v>
+        <v>917</v>
       </c>
       <c r="C92">
-        <v>1152</v>
+        <v>1069</v>
       </c>
       <c r="D92">
-        <v>1956</v>
+        <v>1986</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
-        <v>786</v>
+        <v>903</v>
       </c>
       <c r="C93">
-        <v>1148</v>
+        <v>1059</v>
       </c>
       <c r="D93">
-        <v>1934</v>
+        <v>1962</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
-        <v>750</v>
+        <v>701</v>
       </c>
       <c r="C94">
-        <v>1053</v>
+        <v>1079</v>
       </c>
       <c r="D94">
-        <v>1803</v>
+        <v>1780</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
-        <v>733</v>
+        <v>697</v>
       </c>
       <c r="C95">
-        <v>1035</v>
+        <v>1072</v>
       </c>
       <c r="D95">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
-        <v>742</v>
+        <v>698</v>
       </c>
       <c r="C96">
-        <v>1038</v>
+        <v>1078</v>
       </c>
       <c r="D96">
-        <v>1780</v>
+        <v>1776</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="C97">
-        <v>1037</v>
+        <v>1075</v>
       </c>
       <c r="D97">
-        <v>1037</v>
+        <v>1771</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="C98">
-        <v>1020</v>
+        <v>1051</v>
       </c>
       <c r="D98">
-        <v>1692</v>
+        <v>1716</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B99">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C99">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="D99">
-        <v>1682</v>
+        <v>1703</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B100">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="C100">
-        <v>1027</v>
+        <v>1045</v>
       </c>
       <c r="D100">
-        <v>1676</v>
+        <v>1706</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B101">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="C101">
-        <v>1026</v>
+        <v>1044</v>
       </c>
       <c r="D101">
-        <v>1669</v>
+        <v>1698</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B102">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="C102">
-        <v>1031</v>
+        <v>1048</v>
       </c>
       <c r="D102">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B103">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>1027</v>
+        <v>1045</v>
       </c>
       <c r="D103">
-        <v>1641</v>
+        <v>1045</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B104">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1046</v>
       </c>
       <c r="D104">
-        <v>615</v>
+        <v>1640</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B105">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1042</v>
       </c>
       <c r="D105">
-        <v>617</v>
+        <v>1640</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B106">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="C106">
-        <v>1032</v>
+        <v>1048</v>
       </c>
       <c r="D106">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B107">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="C107">
-        <v>1013</v>
+        <v>1044</v>
       </c>
       <c r="D107">
-        <v>1614</v>
+        <v>1630</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B108">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="D108">
-        <v>602</v>
+        <v>1636</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B109">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>1015</v>
+        <v>1044</v>
       </c>
       <c r="D109">
-        <v>1618</v>
+        <v>1044</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B110">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="C110">
-        <v>1022</v>
+        <v>1047</v>
       </c>
       <c r="D110">
-        <v>1634</v>
+        <v>1680</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="C111">
-        <v>1021</v>
+        <v>1044</v>
       </c>
       <c r="D111">
-        <v>1021</v>
+        <v>1676</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B112">
-        <v>613</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>1022</v>
+        <v>1043</v>
       </c>
       <c r="D112">
-        <v>1635</v>
+        <v>1043</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B113">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="D113">
-        <v>621</v>
+        <v>1680</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B114">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C114">
-        <v>1016</v>
+        <v>1048</v>
       </c>
       <c r="D114">
-        <v>1681</v>
+        <v>1708</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B116">
-        <v>667</v>
+        <v>647</v>
       </c>
       <c r="C116">
-        <v>1021</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1688</v>
+        <v>647</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B117">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="C117">
-        <v>1023</v>
+        <v>1040</v>
       </c>
       <c r="D117">
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B118">
-        <v>751</v>
+        <v>722</v>
       </c>
       <c r="C118">
-        <v>1018</v>
+        <v>1050</v>
       </c>
       <c r="D118">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B119">
-        <v>758</v>
+        <v>726</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="D119">
-        <v>758</v>
+        <v>1777</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="C120">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="D120">
-        <v>1014</v>
+        <v>1777</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B121">
-        <v>762</v>
+        <v>727</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>762</v>
+        <v>727</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B122">
-        <v>808</v>
+        <v>722</v>
       </c>
       <c r="C122">
-        <v>1013</v>
+        <v>1049</v>
       </c>
       <c r="D122">
-        <v>1821</v>
+        <v>1771</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B123">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1014</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>1817</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B124">
-        <v>799</v>
+        <v>715</v>
       </c>
       <c r="C124">
-        <v>1009</v>
+        <v>1048</v>
       </c>
       <c r="D124">
-        <v>1808</v>
+        <v>1763</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B125">
-        <v>803</v>
+        <v>706</v>
       </c>
       <c r="C125">
-        <v>1011</v>
+        <v>1047</v>
       </c>
       <c r="D125">
-        <v>1814</v>
+        <v>1753</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B126">
-        <v>793</v>
+        <v>698</v>
       </c>
       <c r="C126">
-        <v>996</v>
+        <v>1052</v>
       </c>
       <c r="D126">
-        <v>1789</v>
+        <v>1750</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B127">
-        <v>808</v>
+        <v>680</v>
       </c>
       <c r="C127">
-        <v>976</v>
+        <v>1051</v>
       </c>
       <c r="D127">
-        <v>1784</v>
+        <v>1731</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B128">
-        <v>798</v>
+        <v>686</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="D128">
-        <v>798</v>
+        <v>1733</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B129">
-        <v>792</v>
+        <v>675</v>
       </c>
       <c r="C129">
-        <v>973</v>
+        <v>1046</v>
       </c>
       <c r="D129">
-        <v>1765</v>
+        <v>1721</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B130">
-        <v>734</v>
+        <v>611</v>
       </c>
       <c r="C130">
-        <v>950</v>
+        <v>1069</v>
       </c>
       <c r="D130">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B131">
-        <v>755</v>
+        <v>573</v>
       </c>
       <c r="C131">
-        <v>949</v>
+        <v>1061</v>
       </c>
       <c r="D131">
-        <v>1704</v>
+        <v>1634</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B132">
-        <v>756</v>
+        <v>574</v>
       </c>
       <c r="C132">
-        <v>947</v>
+        <v>1060</v>
       </c>
       <c r="D132">
-        <v>1703</v>
+        <v>1634</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B133">
-        <v>713</v>
+        <v>572</v>
       </c>
       <c r="C133">
-        <v>918</v>
+        <v>1054</v>
       </c>
       <c r="D133">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B134">
-        <v>625</v>
+        <v>576</v>
       </c>
       <c r="C134">
-        <v>953</v>
+        <v>974</v>
       </c>
       <c r="D134">
-        <v>1578</v>
+        <v>1550</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B135">
-        <v>617</v>
+        <v>551</v>
       </c>
       <c r="C135">
-        <v>950</v>
+        <v>969</v>
       </c>
       <c r="D135">
-        <v>1567</v>
+        <v>1520</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B136">
-        <v>619</v>
+        <v>562</v>
       </c>
       <c r="C136">
-        <v>954</v>
+        <v>968</v>
       </c>
       <c r="D136">
-        <v>1573</v>
+        <v>1530</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B137">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="C137">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="D137">
-        <v>1566</v>
+        <v>1524</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B138">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="C138">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="D138">
-        <v>1512</v>
+        <v>1475</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1459</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1457</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>20.05.202694</t>
+  </si>
+  <si>
+    <t>20.05.202695</t>
+  </si>
+  <si>
+    <t>20.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
-        <v>672</v>
+        <v>503</v>
       </c>
       <c r="C2">
-        <v>1020</v>
+        <v>1200</v>
       </c>
       <c r="D2">
-        <v>1692</v>
+        <v>1703</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
-        <v>653</v>
+        <v>505</v>
       </c>
       <c r="C3">
-        <v>1029</v>
+        <v>1199</v>
       </c>
       <c r="D3">
-        <v>1682</v>
+        <v>1704</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
-        <v>649</v>
+        <v>503</v>
       </c>
       <c r="C4">
-        <v>1027</v>
+        <v>1208</v>
       </c>
       <c r="D4">
-        <v>1676</v>
+        <v>1711</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
-        <v>643</v>
+        <v>504</v>
       </c>
       <c r="C5">
-        <v>1026</v>
+        <v>1206</v>
       </c>
       <c r="D5">
-        <v>1669</v>
+        <v>1710</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
-        <v>618</v>
+        <v>446</v>
       </c>
       <c r="C6">
-        <v>1031</v>
+        <v>1216</v>
       </c>
       <c r="D6">
-        <v>1649</v>
+        <v>1662</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
-        <v>614</v>
+        <v>447</v>
       </c>
       <c r="C7">
-        <v>1027</v>
+        <v>1212</v>
       </c>
       <c r="D7">
-        <v>1641</v>
+        <v>1659</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
-        <v>615</v>
+        <v>448</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="D8">
-        <v>615</v>
+        <v>1661</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
-        <v>617</v>
+        <v>422</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="D9">
-        <v>617</v>
+        <v>1636</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
-        <v>603</v>
+        <v>391</v>
       </c>
       <c r="C10">
-        <v>1032</v>
+        <v>1222</v>
       </c>
       <c r="D10">
-        <v>1635</v>
+        <v>1613</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
-        <v>601</v>
+        <v>390</v>
       </c>
       <c r="C11">
-        <v>1013</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1614</v>
+        <v>390</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="D12">
-        <v>602</v>
+        <v>1224</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
-        <v>603</v>
+        <v>389</v>
       </c>
       <c r="C13">
-        <v>1015</v>
+        <v>1223</v>
       </c>
       <c r="D13">
-        <v>1618</v>
+        <v>1612</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>612</v>
+        <v>477</v>
       </c>
       <c r="C14">
-        <v>1022</v>
+        <v>1211</v>
       </c>
       <c r="D14">
-        <v>1634</v>
+        <v>1688</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="C15">
-        <v>1021</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1021</v>
+        <v>446</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>613</v>
+        <v>470</v>
       </c>
       <c r="C16">
-        <v>1022</v>
+        <v>1192</v>
       </c>
       <c r="D16">
-        <v>1635</v>
+        <v>1662</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>621</v>
+        <v>479</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>621</v>
+        <v>479</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>665</v>
+        <v>503</v>
       </c>
       <c r="C18">
-        <v>1016</v>
+        <v>1198</v>
       </c>
       <c r="D18">
-        <v>1681</v>
+        <v>1701</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1197</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1699</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>667</v>
+        <v>494</v>
       </c>
       <c r="C20">
-        <v>1021</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1688</v>
+        <v>494</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>679</v>
+        <v>481</v>
       </c>
       <c r="C21">
-        <v>1023</v>
+        <v>1194</v>
       </c>
       <c r="D21">
-        <v>1702</v>
+        <v>1675</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>751</v>
+        <v>569</v>
       </c>
       <c r="C22">
-        <v>1018</v>
+        <v>1160</v>
       </c>
       <c r="D22">
-        <v>1769</v>
+        <v>1729</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>758</v>
+        <v>572</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1155</v>
       </c>
       <c r="D23">
-        <v>758</v>
+        <v>1727</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="C24">
-        <v>1014</v>
+        <v>1162</v>
       </c>
       <c r="D24">
-        <v>1014</v>
+        <v>1736</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>762</v>
+        <v>607</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="D25">
-        <v>762</v>
+        <v>1774</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>808</v>
+        <v>627</v>
       </c>
       <c r="C26">
-        <v>1013</v>
+        <v>1186</v>
       </c>
       <c r="D26">
-        <v>1821</v>
+        <v>1813</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>803</v>
+        <v>618</v>
       </c>
       <c r="C27">
-        <v>1014</v>
+        <v>1171</v>
       </c>
       <c r="D27">
-        <v>1817</v>
+        <v>1789</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>799</v>
+        <v>631</v>
       </c>
       <c r="C28">
-        <v>1009</v>
+        <v>1170</v>
       </c>
       <c r="D28">
-        <v>1808</v>
+        <v>1801</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>803</v>
+        <v>630</v>
       </c>
       <c r="C29">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1814</v>
+        <v>630</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>793</v>
+        <v>602</v>
       </c>
       <c r="C30">
-        <v>996</v>
+        <v>1180</v>
       </c>
       <c r="D30">
-        <v>1789</v>
+        <v>1782</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>808</v>
+        <v>612</v>
       </c>
       <c r="C31">
-        <v>976</v>
+        <v>1183</v>
       </c>
       <c r="D31">
-        <v>1784</v>
+        <v>1795</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>798</v>
+        <v>652</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="D32">
-        <v>798</v>
+        <v>1865</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>792</v>
+        <v>621</v>
       </c>
       <c r="C33">
-        <v>973</v>
+        <v>1235</v>
       </c>
       <c r="D33">
-        <v>1765</v>
+        <v>1856</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>734</v>
+        <v>601</v>
       </c>
       <c r="C34">
-        <v>950</v>
+        <v>1213</v>
       </c>
       <c r="D34">
-        <v>1684</v>
+        <v>1814</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>755</v>
+        <v>592</v>
       </c>
       <c r="C35">
-        <v>949</v>
+        <v>1208</v>
       </c>
       <c r="D35">
-        <v>1704</v>
+        <v>1800</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>756</v>
+        <v>664</v>
       </c>
       <c r="C36">
-        <v>947</v>
+        <v>1209</v>
       </c>
       <c r="D36">
-        <v>1703</v>
+        <v>1873</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>713</v>
+        <v>660</v>
       </c>
       <c r="C37">
-        <v>918</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1631</v>
+        <v>660</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>625</v>
+        <v>461</v>
       </c>
       <c r="C38">
-        <v>953</v>
+        <v>1099</v>
       </c>
       <c r="D38">
-        <v>1578</v>
+        <v>1560</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>617</v>
+        <v>449</v>
       </c>
       <c r="C39">
-        <v>950</v>
+        <v>1083</v>
       </c>
       <c r="D39">
-        <v>1567</v>
+        <v>1532</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
-        <v>619</v>
+        <v>430</v>
       </c>
       <c r="C40">
-        <v>954</v>
+        <v>1070</v>
       </c>
       <c r="D40">
-        <v>1573</v>
+        <v>1500</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>615</v>
+        <v>321</v>
       </c>
       <c r="C41">
-        <v>951</v>
+        <v>1053</v>
       </c>
       <c r="D41">
-        <v>1566</v>
+        <v>1374</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>562</v>
+        <v>226</v>
       </c>
       <c r="C42">
-        <v>950</v>
+        <v>1024</v>
       </c>
       <c r="D42">
-        <v>1512</v>
+        <v>1250</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>557</v>
+        <v>209</v>
       </c>
       <c r="C43">
-        <v>931</v>
+        <v>1018</v>
       </c>
       <c r="D43">
-        <v>1488</v>
+        <v>1227</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>582</v>
+        <v>199</v>
       </c>
       <c r="C44">
-        <v>970</v>
+        <v>1006</v>
       </c>
       <c r="D44">
-        <v>1552</v>
+        <v>1205</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
-        <v>575</v>
+        <v>190</v>
       </c>
       <c r="C45">
-        <v>957</v>
+        <v>1004</v>
       </c>
       <c r="D45">
-        <v>1532</v>
+        <v>1194</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>476</v>
+        <v>214</v>
       </c>
       <c r="C46">
-        <v>914</v>
+        <v>1005</v>
       </c>
       <c r="D46">
-        <v>1390</v>
+        <v>1219</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>479</v>
+        <v>217</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="D47">
-        <v>479</v>
+        <v>1221</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>505</v>
+        <v>216</v>
       </c>
       <c r="C48">
-        <v>869</v>
+        <v>1005</v>
       </c>
       <c r="D48">
-        <v>1374</v>
+        <v>1221</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>527</v>
+        <v>309</v>
       </c>
       <c r="C49">
-        <v>865</v>
+        <v>1026</v>
       </c>
       <c r="D49">
-        <v>1392</v>
+        <v>1335</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C50">
-        <v>793</v>
+        <v>1046</v>
       </c>
       <c r="D50">
-        <v>1088</v>
+        <v>1350</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="C51">
-        <v>745</v>
+        <v>1043</v>
       </c>
       <c r="D51">
-        <v>1075</v>
+        <v>1340</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C52">
-        <v>790</v>
+        <v>1037</v>
       </c>
       <c r="D52">
-        <v>1066</v>
+        <v>1319</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C53">
-        <v>791</v>
+        <v>1049</v>
       </c>
       <c r="D53">
-        <v>1079</v>
+        <v>1342</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>301</v>
+        <v>429</v>
       </c>
       <c r="C54">
-        <v>809</v>
+        <v>1108</v>
       </c>
       <c r="D54">
-        <v>1110</v>
+        <v>1537</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>296</v>
+        <v>430</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1111</v>
       </c>
       <c r="D55">
-        <v>296</v>
+        <v>1541</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
         <v>0</v>
       </c>
       <c r="C56">
-        <v>853</v>
+        <v>1112</v>
       </c>
       <c r="D56">
-        <v>853</v>
+        <v>1112</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>285</v>
+        <v>431</v>
       </c>
       <c r="C57">
-        <v>858</v>
+        <v>1120</v>
       </c>
       <c r="D57">
-        <v>1143</v>
+        <v>1551</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="C58">
-        <v>883</v>
+        <v>1111</v>
       </c>
       <c r="D58">
-        <v>1152</v>
+        <v>1443</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="C59">
-        <v>908</v>
+        <v>1113</v>
       </c>
       <c r="D59">
-        <v>1183</v>
+        <v>1434</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C60">
-        <v>914</v>
+        <v>1094</v>
       </c>
       <c r="D60">
-        <v>1198</v>
+        <v>1385</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="C61">
-        <v>915</v>
+        <v>1092</v>
       </c>
       <c r="D61">
-        <v>1202</v>
+        <v>1356</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>367</v>
+        <v>444</v>
       </c>
       <c r="C62">
-        <v>900</v>
+        <v>1095</v>
       </c>
       <c r="D62">
-        <v>1267</v>
+        <v>1539</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>382</v>
+        <v>474</v>
       </c>
       <c r="C63">
-        <v>823</v>
+        <v>1094</v>
       </c>
       <c r="D63">
-        <v>1205</v>
+        <v>1568</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="C64">
-        <v>822</v>
+        <v>1091</v>
       </c>
       <c r="D64">
-        <v>822</v>
+        <v>1531</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="C65">
-        <v>824</v>
+        <v>1095</v>
       </c>
       <c r="D65">
-        <v>1215</v>
+        <v>1546</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>591</v>
+        <v>478</v>
       </c>
       <c r="C66">
-        <v>1015</v>
+        <v>1150</v>
       </c>
       <c r="D66">
-        <v>1606</v>
+        <v>1628</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>592</v>
+        <v>488</v>
       </c>
       <c r="C67">
-        <v>1030</v>
+        <v>1151</v>
       </c>
       <c r="D67">
-        <v>1622</v>
+        <v>1639</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>581</v>
+        <v>493</v>
       </c>
       <c r="C68">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>1526</v>
+        <v>493</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>564</v>
+        <v>522</v>
       </c>
       <c r="C69">
-        <v>916</v>
+        <v>1157</v>
       </c>
       <c r="D69">
-        <v>1480</v>
+        <v>1679</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>792</v>
+        <v>942</v>
       </c>
       <c r="C70">
-        <v>1017</v>
+        <v>1227</v>
       </c>
       <c r="D70">
-        <v>1809</v>
+        <v>2169</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="C71">
-        <v>1042</v>
+        <v>1177</v>
       </c>
       <c r="D71">
-        <v>1930</v>
+        <v>2080</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>940</v>
+        <v>889</v>
       </c>
       <c r="C72">
-        <v>1075</v>
+        <v>1180</v>
       </c>
       <c r="D72">
-        <v>2015</v>
+        <v>2069</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>952</v>
+        <v>925</v>
       </c>
       <c r="C73">
-        <v>1108</v>
+        <v>1181</v>
       </c>
       <c r="D73">
-        <v>2060</v>
+        <v>2106</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>1045</v>
+        <v>1197</v>
       </c>
       <c r="C74">
-        <v>1397</v>
+        <v>1172</v>
       </c>
       <c r="D74">
-        <v>2442</v>
+        <v>2369</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>1052</v>
+        <v>1211</v>
       </c>
       <c r="C75">
-        <v>1420</v>
+        <v>1181</v>
       </c>
       <c r="D75">
-        <v>2472</v>
+        <v>2392</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>1050</v>
+        <v>1208</v>
       </c>
       <c r="C76">
-        <v>1416</v>
+        <v>1177</v>
       </c>
       <c r="D76">
-        <v>2466</v>
+        <v>2385</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>1069</v>
+        <v>1239</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1069</v>
+        <v>1239</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>1070</v>
+        <v>1275</v>
       </c>
       <c r="C78">
-        <v>1398</v>
+        <v>1242</v>
       </c>
       <c r="D78">
-        <v>2468</v>
+        <v>2517</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>1069</v>
+        <v>1283</v>
       </c>
       <c r="C79">
-        <v>1399</v>
+        <v>1245</v>
       </c>
       <c r="D79">
-        <v>2468</v>
+        <v>2528</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1281</v>
       </c>
       <c r="C80">
-        <v>1396</v>
+        <v>1243</v>
       </c>
       <c r="D80">
-        <v>1396</v>
+        <v>2524</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>1078</v>
+        <v>1276</v>
       </c>
       <c r="C81">
-        <v>1394</v>
+        <v>1271</v>
       </c>
       <c r="D81">
-        <v>2472</v>
+        <v>2547</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,13 +2594,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="C82">
-        <v>1406</v>
+        <v>1413</v>
       </c>
       <c r="D82">
         <v>2510</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>1103</v>
+        <v>1089</v>
       </c>
       <c r="C83">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="D83">
-        <v>2510</v>
+        <v>2503</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1075</v>
       </c>
       <c r="C84">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="D84">
-        <v>1405</v>
+        <v>2491</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>1092</v>
+        <v>1072</v>
       </c>
       <c r="C85">
-        <v>1406</v>
+        <v>1415</v>
       </c>
       <c r="D85">
-        <v>2498</v>
+        <v>2487</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>1052</v>
+        <v>880</v>
       </c>
       <c r="C86">
-        <v>1254</v>
+        <v>1422</v>
       </c>
       <c r="D86">
-        <v>2306</v>
+        <v>2302</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>1050</v>
+        <v>878</v>
       </c>
       <c r="C87">
-        <v>1235</v>
+        <v>1423</v>
       </c>
       <c r="D87">
-        <v>2285</v>
+        <v>2301</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>1167</v>
+        <v>876</v>
       </c>
       <c r="C88">
-        <v>1286</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>2453</v>
+        <v>876</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>1161</v>
+        <v>858</v>
       </c>
       <c r="C89">
-        <v>1288</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>2449</v>
+        <v>858</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>1055</v>
+        <v>617</v>
       </c>
       <c r="C90">
-        <v>1117</v>
+        <v>1409</v>
       </c>
       <c r="D90">
-        <v>2172</v>
+        <v>2026</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>1050</v>
+        <v>615</v>
       </c>
       <c r="C91">
-        <v>1103</v>
+        <v>1405</v>
       </c>
       <c r="D91">
-        <v>2153</v>
+        <v>2020</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
-        <v>917</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1069</v>
+        <v>1402</v>
       </c>
       <c r="D92">
-        <v>1986</v>
+        <v>1402</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
-        <v>903</v>
+        <v>609</v>
       </c>
       <c r="C93">
-        <v>1059</v>
+        <v>1406</v>
       </c>
       <c r="D93">
-        <v>1962</v>
+        <v>2015</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
-        <v>701</v>
+        <v>412</v>
       </c>
       <c r="C94">
-        <v>1079</v>
+        <v>1310</v>
       </c>
       <c r="D94">
-        <v>1780</v>
+        <v>1722</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
-        <v>697</v>
+        <v>402</v>
       </c>
       <c r="C95">
-        <v>1072</v>
+        <v>1290</v>
       </c>
       <c r="D95">
-        <v>1769</v>
+        <v>1692</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1078</v>
+        <v>1287</v>
       </c>
       <c r="D96">
-        <v>1776</v>
+        <v>1287</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
-        <v>696</v>
+        <v>399</v>
       </c>
       <c r="C97">
-        <v>1075</v>
+        <v>1286</v>
       </c>
       <c r="D97">
-        <v>1771</v>
+        <v>1685</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>665</v>
+        <v>448</v>
       </c>
       <c r="C98">
-        <v>1051</v>
+        <v>1279</v>
       </c>
       <c r="D98">
-        <v>1716</v>
+        <v>1727</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B99">
-        <v>662</v>
+        <v>447</v>
       </c>
       <c r="C99">
-        <v>1041</v>
+        <v>1274</v>
       </c>
       <c r="D99">
-        <v>1703</v>
+        <v>1721</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B100">
-        <v>661</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>1045</v>
+        <v>1273</v>
       </c>
       <c r="D100">
-        <v>1706</v>
+        <v>1273</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B101">
-        <v>654</v>
+        <v>446</v>
       </c>
       <c r="C101">
-        <v>1044</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>1698</v>
+        <v>446</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B102">
-        <v>600</v>
+        <v>418</v>
       </c>
       <c r="C102">
-        <v>1048</v>
+        <v>1212</v>
       </c>
       <c r="D102">
-        <v>1648</v>
+        <v>1630</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="C103">
-        <v>1045</v>
+        <v>1206</v>
       </c>
       <c r="D103">
-        <v>1045</v>
+        <v>1622</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B104">
-        <v>594</v>
+        <v>415</v>
       </c>
       <c r="C104">
-        <v>1046</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1640</v>
+        <v>415</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B105">
-        <v>598</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>1042</v>
+        <v>1207</v>
       </c>
       <c r="D105">
-        <v>1640</v>
+        <v>1207</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B106">
-        <v>590</v>
+        <v>399</v>
       </c>
       <c r="C106">
-        <v>1048</v>
+        <v>1210</v>
       </c>
       <c r="D106">
-        <v>1638</v>
+        <v>1609</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B107">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="C107">
-        <v>1044</v>
+        <v>1209</v>
       </c>
       <c r="D107">
-        <v>1630</v>
+        <v>1601</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B108">
-        <v>588</v>
+        <v>397</v>
       </c>
       <c r="C108">
-        <v>1048</v>
+        <v>1216</v>
       </c>
       <c r="D108">
-        <v>1636</v>
+        <v>1613</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="C109">
-        <v>1044</v>
+        <v>1217</v>
       </c>
       <c r="D109">
-        <v>1044</v>
+        <v>1615</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B110">
-        <v>633</v>
+        <v>392</v>
       </c>
       <c r="C110">
-        <v>1047</v>
+        <v>1223</v>
       </c>
       <c r="D110">
-        <v>1680</v>
+        <v>1615</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B111">
-        <v>632</v>
+        <v>390</v>
       </c>
       <c r="C111">
-        <v>1044</v>
+        <v>1220</v>
       </c>
       <c r="D111">
-        <v>1676</v>
+        <v>1610</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="C112">
-        <v>1043</v>
+        <v>1218</v>
       </c>
       <c r="D112">
-        <v>1043</v>
+        <v>1609</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B113">
-        <v>633</v>
+        <v>390</v>
       </c>
       <c r="C113">
-        <v>1047</v>
+        <v>1221</v>
       </c>
       <c r="D113">
-        <v>1680</v>
+        <v>1611</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B114">
-        <v>660</v>
+        <v>395</v>
       </c>
       <c r="C114">
-        <v>1048</v>
+        <v>1239</v>
       </c>
       <c r="D114">
-        <v>1708</v>
+        <v>1634</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B115">
-        <v>645</v>
+        <v>393</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1238</v>
       </c>
       <c r="D115">
-        <v>645</v>
+        <v>1631</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B116">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B117">
-        <v>669</v>
+        <v>404</v>
       </c>
       <c r="C117">
-        <v>1040</v>
+        <v>1239</v>
       </c>
       <c r="D117">
-        <v>1709</v>
+        <v>1643</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B118">
-        <v>722</v>
+        <v>507</v>
       </c>
       <c r="C118">
-        <v>1050</v>
+        <v>1206</v>
       </c>
       <c r="D118">
-        <v>1772</v>
+        <v>1713</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B119">
-        <v>726</v>
+        <v>505</v>
       </c>
       <c r="C119">
-        <v>1051</v>
+        <v>1199</v>
       </c>
       <c r="D119">
-        <v>1777</v>
+        <v>1704</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B120">
-        <v>724</v>
+        <v>506</v>
       </c>
       <c r="C120">
-        <v>1053</v>
+        <v>1201</v>
       </c>
       <c r="D120">
-        <v>1777</v>
+        <v>1707</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B121">
-        <v>727</v>
+        <v>520</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="D121">
-        <v>727</v>
+        <v>1720</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B122">
-        <v>722</v>
+        <v>615</v>
       </c>
       <c r="C122">
-        <v>1049</v>
+        <v>1181</v>
       </c>
       <c r="D122">
-        <v>1771</v>
+        <v>1796</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>638</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1180</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1818</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B124">
-        <v>715</v>
+        <v>635</v>
       </c>
       <c r="C124">
-        <v>1048</v>
+        <v>1181</v>
       </c>
       <c r="D124">
-        <v>1763</v>
+        <v>1816</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B125">
-        <v>706</v>
+        <v>600</v>
       </c>
       <c r="C125">
-        <v>1047</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>1753</v>
+        <v>600</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B126">
-        <v>698</v>
+        <v>571</v>
       </c>
       <c r="C126">
-        <v>1052</v>
+        <v>1164</v>
       </c>
       <c r="D126">
-        <v>1750</v>
+        <v>1735</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B127">
-        <v>680</v>
+        <v>578</v>
       </c>
       <c r="C127">
-        <v>1051</v>
+        <v>1160</v>
       </c>
       <c r="D127">
-        <v>1731</v>
+        <v>1738</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B128">
-        <v>686</v>
+        <v>585</v>
       </c>
       <c r="C128">
-        <v>1047</v>
+        <v>1161</v>
       </c>
       <c r="D128">
-        <v>1733</v>
+        <v>1746</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B129">
-        <v>675</v>
+        <v>605</v>
       </c>
       <c r="C129">
-        <v>1046</v>
+        <v>1164</v>
       </c>
       <c r="D129">
-        <v>1721</v>
+        <v>1769</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B130">
-        <v>611</v>
+        <v>467</v>
       </c>
       <c r="C130">
-        <v>1069</v>
+        <v>1118</v>
       </c>
       <c r="D130">
-        <v>1680</v>
+        <v>1585</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B131">
-        <v>573</v>
+        <v>456</v>
       </c>
       <c r="C131">
-        <v>1061</v>
+        <v>1107</v>
       </c>
       <c r="D131">
-        <v>1634</v>
+        <v>1563</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B132">
-        <v>574</v>
+        <v>468</v>
       </c>
       <c r="C132">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="D132">
-        <v>1634</v>
+        <v>1574</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B133">
-        <v>572</v>
+        <v>464</v>
       </c>
       <c r="C133">
-        <v>1054</v>
+        <v>1104</v>
       </c>
       <c r="D133">
-        <v>1626</v>
+        <v>1568</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B134">
-        <v>576</v>
+        <v>416</v>
       </c>
       <c r="C134">
-        <v>974</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>1550</v>
+        <v>416</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B135">
-        <v>551</v>
+        <v>421</v>
       </c>
       <c r="C135">
-        <v>969</v>
+        <v>1105</v>
       </c>
       <c r="D135">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B136">
-        <v>562</v>
+        <v>457</v>
       </c>
       <c r="C136">
-        <v>968</v>
+        <v>1109</v>
       </c>
       <c r="D136">
-        <v>1530</v>
+        <v>1566</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B137">
-        <v>595</v>
+        <v>451</v>
       </c>
       <c r="C137">
-        <v>929</v>
+        <v>1104</v>
       </c>
       <c r="D137">
-        <v>1524</v>
+        <v>1555</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B138">
-        <v>544</v>
+        <v>190</v>
       </c>
       <c r="C138">
-        <v>931</v>
+        <v>998</v>
       </c>
       <c r="D138">
-        <v>1475</v>
+        <v>1188</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B139">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="C139">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="D139">
-        <v>1459</v>
+        <v>1258</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B140">
-        <v>477</v>
+        <v>276</v>
       </c>
       <c r="C140">
-        <v>980</v>
+        <v>1036</v>
       </c>
       <c r="D140">
-        <v>1457</v>
+        <v>1312</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1049</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1238</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1036</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1198</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>1165</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>908</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>20.05.202694</t>
-  </si>
-  <si>
-    <t>20.05.202695</t>
-  </si>
-  <si>
-    <t>20.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
-        <v>503</v>
+        <v>448</v>
       </c>
       <c r="C2">
-        <v>1200</v>
+        <v>1279</v>
       </c>
       <c r="D2">
-        <v>1703</v>
+        <v>1727</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
-        <v>505</v>
+        <v>447</v>
       </c>
       <c r="C3">
-        <v>1199</v>
+        <v>1274</v>
       </c>
       <c r="D3">
-        <v>1704</v>
+        <v>1721</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1208</v>
+        <v>1273</v>
       </c>
       <c r="D4">
-        <v>1711</v>
+        <v>1273</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
-        <v>504</v>
+        <v>446</v>
       </c>
       <c r="C5">
-        <v>1206</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1710</v>
+        <v>446</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>446</v>
+        <v>418</v>
       </c>
       <c r="C6">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D6">
-        <v>1662</v>
+        <v>1630</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="C7">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="D7">
-        <v>1659</v>
+        <v>1622</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>448</v>
+        <v>415</v>
       </c>
       <c r="C8">
-        <v>1213</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1661</v>
+        <v>415</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1214</v>
+        <v>1207</v>
       </c>
       <c r="D9">
-        <v>1636</v>
+        <v>1207</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C10">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="D10">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1209</v>
       </c>
       <c r="D11">
-        <v>390</v>
+        <v>1601</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="C12">
-        <v>1224</v>
+        <v>1216</v>
       </c>
       <c r="D12">
-        <v>1224</v>
+        <v>1613</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C13">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="D13">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>477</v>
+        <v>392</v>
       </c>
       <c r="C14">
-        <v>1211</v>
+        <v>1223</v>
       </c>
       <c r="D14">
-        <v>1688</v>
+        <v>1615</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
-        <v>446</v>
+        <v>390</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="D15">
-        <v>446</v>
+        <v>1610</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>470</v>
+        <v>391</v>
       </c>
       <c r="C16">
-        <v>1192</v>
+        <v>1218</v>
       </c>
       <c r="D16">
-        <v>1662</v>
+        <v>1609</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>479</v>
+        <v>390</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1221</v>
       </c>
       <c r="D17">
-        <v>479</v>
+        <v>1611</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>503</v>
+        <v>395</v>
       </c>
       <c r="C18">
-        <v>1198</v>
+        <v>1239</v>
       </c>
       <c r="D18">
-        <v>1701</v>
+        <v>1634</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>502</v>
+        <v>393</v>
       </c>
       <c r="C19">
-        <v>1197</v>
+        <v>1238</v>
       </c>
       <c r="D19">
-        <v>1699</v>
+        <v>1631</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>481</v>
+        <v>404</v>
       </c>
       <c r="C21">
-        <v>1194</v>
+        <v>1239</v>
       </c>
       <c r="D21">
-        <v>1675</v>
+        <v>1643</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>569</v>
+        <v>507</v>
       </c>
       <c r="C22">
-        <v>1160</v>
+        <v>1206</v>
       </c>
       <c r="D22">
-        <v>1729</v>
+        <v>1713</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>572</v>
+        <v>505</v>
       </c>
       <c r="C23">
-        <v>1155</v>
+        <v>1199</v>
       </c>
       <c r="D23">
-        <v>1727</v>
+        <v>1704</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>574</v>
+        <v>506</v>
       </c>
       <c r="C24">
-        <v>1162</v>
+        <v>1201</v>
       </c>
       <c r="D24">
-        <v>1736</v>
+        <v>1707</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>607</v>
+        <v>520</v>
       </c>
       <c r="C25">
-        <v>1167</v>
+        <v>1200</v>
       </c>
       <c r="D25">
-        <v>1774</v>
+        <v>1720</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="C26">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="D26">
-        <v>1813</v>
+        <v>1796</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="C27">
-        <v>1171</v>
+        <v>1180</v>
       </c>
       <c r="D27">
-        <v>1789</v>
+        <v>1818</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C28">
-        <v>1170</v>
+        <v>1181</v>
       </c>
       <c r="D28">
-        <v>1801</v>
+        <v>1816</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>602</v>
+        <v>571</v>
       </c>
       <c r="C30">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="D30">
-        <v>1782</v>
+        <v>1735</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="C31">
-        <v>1183</v>
+        <v>1160</v>
       </c>
       <c r="D31">
-        <v>1795</v>
+        <v>1738</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>652</v>
+        <v>585</v>
       </c>
       <c r="C32">
-        <v>1213</v>
+        <v>1161</v>
       </c>
       <c r="D32">
-        <v>1865</v>
+        <v>1746</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="C33">
-        <v>1235</v>
+        <v>1164</v>
       </c>
       <c r="D33">
-        <v>1856</v>
+        <v>1769</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>601</v>
+        <v>467</v>
       </c>
       <c r="C34">
-        <v>1213</v>
+        <v>1118</v>
       </c>
       <c r="D34">
-        <v>1814</v>
+        <v>1585</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>592</v>
+        <v>456</v>
       </c>
       <c r="C35">
-        <v>1208</v>
+        <v>1107</v>
       </c>
       <c r="D35">
-        <v>1800</v>
+        <v>1563</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>664</v>
+        <v>468</v>
       </c>
       <c r="C36">
-        <v>1209</v>
+        <v>1106</v>
       </c>
       <c r="D36">
-        <v>1873</v>
+        <v>1574</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>660</v>
+        <v>464</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="D37">
-        <v>660</v>
+        <v>1568</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="C38">
-        <v>1099</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1560</v>
+        <v>416</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="C39">
-        <v>1083</v>
+        <v>1105</v>
       </c>
       <c r="D39">
-        <v>1532</v>
+        <v>1526</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="C40">
-        <v>1070</v>
+        <v>1109</v>
       </c>
       <c r="D40">
-        <v>1500</v>
+        <v>1566</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>321</v>
+        <v>451</v>
       </c>
       <c r="C41">
-        <v>1053</v>
+        <v>1104</v>
       </c>
       <c r="D41">
-        <v>1374</v>
+        <v>1555</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="C42">
-        <v>1024</v>
+        <v>998</v>
       </c>
       <c r="D42">
-        <v>1250</v>
+        <v>1188</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>209</v>
+        <v>288</v>
       </c>
       <c r="C43">
-        <v>1018</v>
+        <v>970</v>
       </c>
       <c r="D43">
-        <v>1227</v>
+        <v>1258</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>199</v>
+        <v>276</v>
       </c>
       <c r="C44">
-        <v>1006</v>
+        <v>1036</v>
       </c>
       <c r="D44">
-        <v>1205</v>
+        <v>1312</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C45">
-        <v>1004</v>
+        <v>1049</v>
       </c>
       <c r="D45">
-        <v>1194</v>
+        <v>1238</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="C46">
-        <v>1005</v>
+        <v>1036</v>
       </c>
       <c r="D46">
-        <v>1219</v>
+        <v>1198</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="D47">
-        <v>1221</v>
+        <v>1015</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="C48">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="D48">
-        <v>1221</v>
+        <v>1163</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>309</v>
+        <v>160</v>
       </c>
       <c r="C49">
-        <v>1026</v>
+        <v>1005</v>
       </c>
       <c r="D49">
-        <v>1335</v>
+        <v>1165</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="C50">
-        <v>1046</v>
+        <v>914</v>
       </c>
       <c r="D50">
-        <v>1350</v>
+        <v>1070</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>297</v>
+        <v>160</v>
       </c>
       <c r="C51">
-        <v>1043</v>
+        <v>908</v>
       </c>
       <c r="D51">
-        <v>1340</v>
+        <v>1068</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>282</v>
+        <v>175</v>
       </c>
       <c r="C52">
-        <v>1037</v>
+        <v>910</v>
       </c>
       <c r="D52">
-        <v>1319</v>
+        <v>1085</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="C53">
-        <v>1049</v>
+        <v>902</v>
       </c>
       <c r="D53">
-        <v>1342</v>
+        <v>1106</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>429</v>
+        <v>207</v>
       </c>
       <c r="C54">
-        <v>1108</v>
+        <v>928</v>
       </c>
       <c r="D54">
-        <v>1537</v>
+        <v>1135</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>430</v>
+        <v>223</v>
       </c>
       <c r="C55">
-        <v>1111</v>
+        <v>929</v>
       </c>
       <c r="D55">
-        <v>1541</v>
+        <v>1152</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="C56">
-        <v>1112</v>
+        <v>948</v>
       </c>
       <c r="D56">
-        <v>1112</v>
+        <v>1282</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>431</v>
+        <v>322</v>
       </c>
       <c r="C57">
-        <v>1120</v>
+        <v>952</v>
       </c>
       <c r="D57">
-        <v>1551</v>
+        <v>1274</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="C58">
-        <v>1111</v>
+        <v>1041</v>
       </c>
       <c r="D58">
-        <v>1443</v>
+        <v>1428</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="C59">
-        <v>1113</v>
+        <v>1052</v>
       </c>
       <c r="D59">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>291</v>
+        <v>181</v>
       </c>
       <c r="C60">
-        <v>1094</v>
+        <v>1015</v>
       </c>
       <c r="D60">
-        <v>1385</v>
+        <v>1196</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="C61">
-        <v>1092</v>
+        <v>987</v>
       </c>
       <c r="D61">
-        <v>1356</v>
+        <v>1202</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>444</v>
+        <v>269</v>
       </c>
       <c r="C62">
-        <v>1095</v>
+        <v>999</v>
       </c>
       <c r="D62">
-        <v>1539</v>
+        <v>1268</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>474</v>
+        <v>260</v>
       </c>
       <c r="C63">
-        <v>1094</v>
+        <v>1009</v>
       </c>
       <c r="D63">
-        <v>1568</v>
+        <v>1269</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>440</v>
+        <v>266</v>
       </c>
       <c r="C64">
-        <v>1091</v>
+        <v>920</v>
       </c>
       <c r="D64">
-        <v>1531</v>
+        <v>1186</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>451</v>
+        <v>296</v>
       </c>
       <c r="C65">
-        <v>1095</v>
+        <v>889</v>
       </c>
       <c r="D65">
-        <v>1546</v>
+        <v>1185</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="C66">
-        <v>1150</v>
+        <v>949</v>
       </c>
       <c r="D66">
-        <v>1628</v>
+        <v>1406</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="C67">
-        <v>1151</v>
+        <v>947</v>
       </c>
       <c r="D67">
-        <v>1639</v>
+        <v>1409</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="D68">
-        <v>493</v>
+        <v>1406</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>522</v>
+        <v>484</v>
       </c>
       <c r="C69">
-        <v>1157</v>
+        <v>952</v>
       </c>
       <c r="D69">
-        <v>1679</v>
+        <v>1436</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>942</v>
+        <v>688</v>
       </c>
       <c r="C70">
-        <v>1227</v>
+        <v>1183</v>
       </c>
       <c r="D70">
-        <v>2169</v>
+        <v>1871</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>903</v>
+        <v>680</v>
       </c>
       <c r="C71">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D71">
-        <v>2080</v>
+        <v>1865</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>889</v>
+        <v>681</v>
       </c>
       <c r="C72">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="D72">
-        <v>2069</v>
+        <v>1871</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>925</v>
+        <v>701</v>
       </c>
       <c r="C73">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="D73">
-        <v>2106</v>
+        <v>1886</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>1197</v>
+        <v>1005</v>
       </c>
       <c r="C74">
-        <v>1172</v>
+        <v>1334</v>
       </c>
       <c r="D74">
-        <v>2369</v>
+        <v>2339</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>1211</v>
+        <v>941</v>
       </c>
       <c r="C75">
-        <v>1181</v>
+        <v>1363</v>
       </c>
       <c r="D75">
-        <v>2392</v>
+        <v>2304</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>1208</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>1177</v>
+        <v>1367</v>
       </c>
       <c r="D76">
-        <v>2385</v>
+        <v>1367</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>1239</v>
+        <v>949</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1363</v>
       </c>
       <c r="D77">
-        <v>1239</v>
+        <v>2312</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>1275</v>
+        <v>1101</v>
       </c>
       <c r="C78">
-        <v>1242</v>
+        <v>1461</v>
       </c>
       <c r="D78">
-        <v>2517</v>
+        <v>2562</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>1283</v>
+        <v>1105</v>
       </c>
       <c r="C79">
-        <v>1245</v>
+        <v>1479</v>
       </c>
       <c r="D79">
-        <v>2528</v>
+        <v>2584</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>1281</v>
+        <v>1107</v>
       </c>
       <c r="C80">
-        <v>1243</v>
+        <v>1499</v>
       </c>
       <c r="D80">
-        <v>2524</v>
+        <v>2606</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>1276</v>
+        <v>1104</v>
       </c>
       <c r="C81">
-        <v>1271</v>
+        <v>1498</v>
       </c>
       <c r="D81">
-        <v>2547</v>
+        <v>2602</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="C82">
-        <v>1413</v>
+        <v>1490</v>
       </c>
       <c r="D82">
-        <v>2510</v>
+        <v>2571</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="C83">
-        <v>1414</v>
+        <v>1503</v>
       </c>
       <c r="D83">
-        <v>2503</v>
+        <v>2580</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>1075</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>1416</v>
+        <v>1505</v>
       </c>
       <c r="D84">
-        <v>2491</v>
+        <v>1505</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="C85">
-        <v>1415</v>
+        <v>1495</v>
       </c>
       <c r="D85">
-        <v>2487</v>
+        <v>2579</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>880</v>
+        <v>918</v>
       </c>
       <c r="C86">
-        <v>1422</v>
+        <v>1490</v>
       </c>
       <c r="D86">
-        <v>2302</v>
+        <v>2408</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>878</v>
+        <v>909</v>
       </c>
       <c r="C87">
-        <v>1423</v>
+        <v>1493</v>
       </c>
       <c r="D87">
-        <v>2301</v>
+        <v>2402</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1494</v>
       </c>
       <c r="D88">
-        <v>876</v>
+        <v>1494</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>858</v>
+        <v>906</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="D89">
-        <v>858</v>
+        <v>2409</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>617</v>
+        <v>713</v>
       </c>
       <c r="C90">
-        <v>1409</v>
+        <v>1453</v>
       </c>
       <c r="D90">
-        <v>2026</v>
+        <v>2166</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>615</v>
+        <v>705</v>
       </c>
       <c r="C91">
-        <v>1405</v>
+        <v>1446</v>
       </c>
       <c r="D91">
-        <v>2020</v>
+        <v>2151</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="C92">
-        <v>1402</v>
+        <v>1470</v>
       </c>
       <c r="D92">
-        <v>1402</v>
+        <v>2186</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>609</v>
+        <v>710</v>
       </c>
       <c r="C93">
-        <v>1406</v>
+        <v>1475</v>
       </c>
       <c r="D93">
-        <v>2015</v>
+        <v>2185</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="C94">
-        <v>1310</v>
+        <v>1392</v>
       </c>
       <c r="D94">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="C95">
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="D95">
-        <v>1692</v>
+        <v>1830</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>1287</v>
+        <v>1391</v>
       </c>
       <c r="D96">
-        <v>1287</v>
+        <v>1391</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="C97">
-        <v>1286</v>
+        <v>1387</v>
       </c>
       <c r="D97">
-        <v>1685</v>
+        <v>1825</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
-        <v>448</v>
+        <v>328</v>
       </c>
       <c r="C98">
-        <v>1279</v>
+        <v>1401</v>
       </c>
       <c r="D98">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B99">
-        <v>447</v>
+        <v>320</v>
       </c>
       <c r="C99">
-        <v>1274</v>
+        <v>1392</v>
       </c>
       <c r="D99">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>1273</v>
+        <v>1391</v>
       </c>
       <c r="D100">
-        <v>1273</v>
+        <v>1391</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B101">
-        <v>446</v>
+        <v>321</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="D101">
-        <v>446</v>
+        <v>1713</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B102">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="C102">
-        <v>1212</v>
+        <v>1246</v>
       </c>
       <c r="D102">
-        <v>1630</v>
+        <v>1703</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B103">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="C103">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="D103">
-        <v>1622</v>
+        <v>1682</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B104">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D104">
-        <v>415</v>
+        <v>1223</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C105">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="D105">
-        <v>1207</v>
+        <v>1683</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B106">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="C106">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="D106">
-        <v>1609</v>
+        <v>1683</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B107">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="C107">
-        <v>1209</v>
+        <v>1225</v>
       </c>
       <c r="D107">
-        <v>1601</v>
+        <v>1676</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B108">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>1613</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B109">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="C109">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="D109">
-        <v>1615</v>
+        <v>1681</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B110">
-        <v>392</v>
+        <v>468</v>
       </c>
       <c r="C110">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="D110">
-        <v>1615</v>
+        <v>1698</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B111">
-        <v>390</v>
+        <v>469</v>
       </c>
       <c r="C111">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="D111">
-        <v>1610</v>
+        <v>1698</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B112">
-        <v>391</v>
+        <v>476</v>
       </c>
       <c r="C112">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1609</v>
+        <v>476</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B113">
-        <v>390</v>
+        <v>478</v>
       </c>
       <c r="C113">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1611</v>
+        <v>478</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B114">
-        <v>395</v>
+        <v>515</v>
       </c>
       <c r="C114">
-        <v>1239</v>
+        <v>1225</v>
       </c>
       <c r="D114">
-        <v>1634</v>
+        <v>1740</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B115">
-        <v>393</v>
+        <v>513</v>
       </c>
       <c r="C115">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="D115">
-        <v>1631</v>
+        <v>1737</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B117">
-        <v>404</v>
+        <v>527</v>
       </c>
       <c r="C117">
-        <v>1239</v>
+        <v>1218</v>
       </c>
       <c r="D117">
-        <v>1643</v>
+        <v>1745</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B118">
-        <v>507</v>
+        <v>595</v>
       </c>
       <c r="C118">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="D118">
-        <v>1713</v>
+        <v>1820</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B119">
-        <v>505</v>
+        <v>592</v>
       </c>
       <c r="C119">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="D119">
-        <v>1704</v>
+        <v>1816</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B120">
-        <v>506</v>
+        <v>591</v>
       </c>
       <c r="C120">
-        <v>1201</v>
+        <v>1222</v>
       </c>
       <c r="D120">
-        <v>1707</v>
+        <v>1813</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B121">
-        <v>520</v>
+        <v>619</v>
       </c>
       <c r="C121">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="D121">
-        <v>1720</v>
+        <v>1842</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B122">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="C122">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>1796</v>
+        <v>717</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B123">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="C123">
-        <v>1180</v>
+        <v>1218</v>
       </c>
       <c r="D123">
-        <v>1818</v>
+        <v>1942</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B124">
-        <v>635</v>
+        <v>725</v>
       </c>
       <c r="C124">
-        <v>1181</v>
+        <v>1222</v>
       </c>
       <c r="D124">
-        <v>1816</v>
+        <v>1947</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B125">
-        <v>600</v>
+        <v>732</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D125">
-        <v>600</v>
+        <v>1955</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B126">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C126">
-        <v>1164</v>
+        <v>1269</v>
       </c>
       <c r="D126">
-        <v>1735</v>
+        <v>1844</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B127">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C127">
-        <v>1160</v>
+        <v>1277</v>
       </c>
       <c r="D127">
-        <v>1738</v>
+        <v>1843</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B128">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="C128">
-        <v>1161</v>
+        <v>1279</v>
       </c>
       <c r="D128">
-        <v>1746</v>
+        <v>1848</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B129">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="C129">
-        <v>1164</v>
+        <v>1309</v>
       </c>
       <c r="D129">
-        <v>1769</v>
+        <v>1947</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B130">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="C130">
-        <v>1118</v>
+        <v>1276</v>
       </c>
       <c r="D130">
-        <v>1585</v>
+        <v>1819</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B131">
-        <v>456</v>
+        <v>541</v>
       </c>
       <c r="C131">
-        <v>1107</v>
+        <v>1272</v>
       </c>
       <c r="D131">
-        <v>1563</v>
+        <v>1813</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B132">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="C132">
-        <v>1106</v>
+        <v>1248</v>
       </c>
       <c r="D132">
-        <v>1574</v>
+        <v>1740</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B133">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C133">
-        <v>1104</v>
+        <v>1247</v>
       </c>
       <c r="D133">
-        <v>1568</v>
+        <v>1725</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B134">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="D134">
-        <v>416</v>
+        <v>1634</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B135">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C135">
-        <v>1105</v>
+        <v>1197</v>
       </c>
       <c r="D135">
-        <v>1526</v>
+        <v>1626</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B136">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="C136">
-        <v>1109</v>
+        <v>1182</v>
       </c>
       <c r="D136">
-        <v>1566</v>
+        <v>1607</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B137">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="C137">
-        <v>1104</v>
+        <v>1183</v>
       </c>
       <c r="D137">
-        <v>1555</v>
+        <v>1183</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B138">
-        <v>190</v>
+        <v>413</v>
       </c>
       <c r="C138">
-        <v>998</v>
+        <v>1184</v>
       </c>
       <c r="D138">
-        <v>1188</v>
+        <v>1597</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B139">
-        <v>288</v>
+        <v>411</v>
       </c>
       <c r="C139">
-        <v>970</v>
+        <v>1185</v>
       </c>
       <c r="D139">
-        <v>1258</v>
+        <v>1596</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B140">
-        <v>276</v>
+        <v>414</v>
       </c>
       <c r="C140">
-        <v>1036</v>
+        <v>1182</v>
       </c>
       <c r="D140">
-        <v>1312</v>
+        <v>1596</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B141">
-        <v>189</v>
+        <v>411</v>
       </c>
       <c r="C141">
-        <v>1049</v>
+        <v>1184</v>
       </c>
       <c r="D141">
-        <v>1238</v>
+        <v>1595</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B142">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C142">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="D142">
-        <v>1198</v>
+        <v>1230</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C143">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D143">
-        <v>1015</v>
+        <v>1227</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B144">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="C144">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="D144">
-        <v>1163</v>
+        <v>1208</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B145">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="C145">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="D145">
-        <v>1165</v>
+        <v>1205</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B146">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C146">
-        <v>914</v>
+        <v>998</v>
       </c>
       <c r="D146">
-        <v>1070</v>
+        <v>1181</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B147">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>908</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>1068</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B148">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>1085</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,870 @@
   </si>
   <si>
     <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,16 +1570,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
-        <v>448</v>
+        <v>328</v>
       </c>
       <c r="C2">
-        <v>1279</v>
+        <v>1401</v>
       </c>
       <c r="D2">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1590,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
-        <v>447</v>
+        <v>320</v>
       </c>
       <c r="C3">
-        <v>1274</v>
+        <v>1392</v>
       </c>
       <c r="D3">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1610,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1273</v>
+        <v>1391</v>
       </c>
       <c r="D4">
-        <v>1273</v>
+        <v>1391</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1630,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
-        <v>446</v>
+        <v>321</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="D5">
-        <v>446</v>
+        <v>1713</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="C6">
-        <v>1212</v>
+        <v>1246</v>
       </c>
       <c r="D6">
-        <v>1630</v>
+        <v>1703</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="C7">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="D7">
-        <v>1622</v>
+        <v>1682</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D8">
-        <v>415</v>
+        <v>1223</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C9">
-        <v>1207</v>
+        <v>1224</v>
       </c>
       <c r="D9">
-        <v>1207</v>
+        <v>1683</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="C10">
-        <v>1210</v>
+        <v>1229</v>
       </c>
       <c r="D10">
-        <v>1609</v>
+        <v>1683</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="C11">
-        <v>1209</v>
+        <v>1225</v>
       </c>
       <c r="D11">
-        <v>1601</v>
+        <v>1676</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1613</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="C13">
-        <v>1217</v>
+        <v>1229</v>
       </c>
       <c r="D13">
-        <v>1615</v>
+        <v>1681</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>392</v>
+        <v>468</v>
       </c>
       <c r="C14">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="D14">
-        <v>1615</v>
+        <v>1698</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>390</v>
+        <v>469</v>
       </c>
       <c r="C15">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="D15">
-        <v>1610</v>
+        <v>1698</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>391</v>
+        <v>476</v>
       </c>
       <c r="C16">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1609</v>
+        <v>476</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>390</v>
+        <v>478</v>
       </c>
       <c r="C17">
-        <v>1221</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1611</v>
+        <v>478</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>395</v>
+        <v>515</v>
       </c>
       <c r="C18">
-        <v>1239</v>
+        <v>1225</v>
       </c>
       <c r="D18">
-        <v>1634</v>
+        <v>1740</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>393</v>
+        <v>513</v>
       </c>
       <c r="C19">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="D19">
-        <v>1631</v>
+        <v>1737</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>404</v>
+        <v>527</v>
       </c>
       <c r="C21">
-        <v>1239</v>
+        <v>1218</v>
       </c>
       <c r="D21">
-        <v>1643</v>
+        <v>1745</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>507</v>
+        <v>595</v>
       </c>
       <c r="C22">
-        <v>1206</v>
+        <v>1225</v>
       </c>
       <c r="D22">
-        <v>1713</v>
+        <v>1820</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>505</v>
+        <v>592</v>
       </c>
       <c r="C23">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="D23">
-        <v>1704</v>
+        <v>1816</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>506</v>
+        <v>591</v>
       </c>
       <c r="C24">
-        <v>1201</v>
+        <v>1222</v>
       </c>
       <c r="D24">
-        <v>1707</v>
+        <v>1813</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>520</v>
+        <v>619</v>
       </c>
       <c r="C25">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="D25">
-        <v>1720</v>
+        <v>1842</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>615</v>
+        <v>717</v>
       </c>
       <c r="C26">
-        <v>1181</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1796</v>
+        <v>717</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="C27">
-        <v>1180</v>
+        <v>1218</v>
       </c>
       <c r="D27">
-        <v>1818</v>
+        <v>1942</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>635</v>
+        <v>725</v>
       </c>
       <c r="C28">
-        <v>1181</v>
+        <v>1222</v>
       </c>
       <c r="D28">
-        <v>1816</v>
+        <v>1947</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>600</v>
+        <v>732</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1223</v>
       </c>
       <c r="D29">
-        <v>600</v>
+        <v>1955</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C30">
-        <v>1164</v>
+        <v>1269</v>
       </c>
       <c r="D30">
-        <v>1735</v>
+        <v>1844</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="C31">
-        <v>1160</v>
+        <v>1277</v>
       </c>
       <c r="D31">
-        <v>1738</v>
+        <v>1843</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="C32">
-        <v>1161</v>
+        <v>1279</v>
       </c>
       <c r="D32">
-        <v>1746</v>
+        <v>1848</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="C33">
-        <v>1164</v>
+        <v>1309</v>
       </c>
       <c r="D33">
-        <v>1769</v>
+        <v>1947</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="C34">
-        <v>1118</v>
+        <v>1276</v>
       </c>
       <c r="D34">
-        <v>1585</v>
+        <v>1819</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>456</v>
+        <v>541</v>
       </c>
       <c r="C35">
-        <v>1107</v>
+        <v>1272</v>
       </c>
       <c r="D35">
-        <v>1563</v>
+        <v>1813</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="C36">
-        <v>1106</v>
+        <v>1248</v>
       </c>
       <c r="D36">
-        <v>1574</v>
+        <v>1740</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="C37">
-        <v>1104</v>
+        <v>1247</v>
       </c>
       <c r="D37">
-        <v>1568</v>
+        <v>1725</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="D38">
-        <v>416</v>
+        <v>1634</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C39">
-        <v>1105</v>
+        <v>1197</v>
       </c>
       <c r="D39">
-        <v>1526</v>
+        <v>1626</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="C40">
-        <v>1109</v>
+        <v>1182</v>
       </c>
       <c r="D40">
-        <v>1566</v>
+        <v>1607</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1104</v>
+        <v>1183</v>
       </c>
       <c r="D41">
-        <v>1555</v>
+        <v>1183</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>190</v>
+        <v>413</v>
       </c>
       <c r="C42">
-        <v>998</v>
+        <v>1184</v>
       </c>
       <c r="D42">
-        <v>1188</v>
+        <v>1597</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>288</v>
+        <v>411</v>
       </c>
       <c r="C43">
-        <v>970</v>
+        <v>1185</v>
       </c>
       <c r="D43">
-        <v>1258</v>
+        <v>1596</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>276</v>
+        <v>414</v>
       </c>
       <c r="C44">
-        <v>1036</v>
+        <v>1182</v>
       </c>
       <c r="D44">
-        <v>1312</v>
+        <v>1596</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>189</v>
+        <v>411</v>
       </c>
       <c r="C45">
-        <v>1049</v>
+        <v>1184</v>
       </c>
       <c r="D45">
-        <v>1238</v>
+        <v>1595</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C46">
-        <v>1036</v>
+        <v>1006</v>
       </c>
       <c r="D46">
-        <v>1198</v>
+        <v>1230</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C47">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D47">
-        <v>1015</v>
+        <v>1227</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="C48">
-        <v>1002</v>
+        <v>1014</v>
       </c>
       <c r="D48">
-        <v>1163</v>
+        <v>1208</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="C49">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="D49">
-        <v>1165</v>
+        <v>1205</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C50">
-        <v>914</v>
+        <v>998</v>
       </c>
       <c r="D50">
-        <v>1070</v>
+        <v>1181</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C51">
-        <v>908</v>
+        <v>1001</v>
       </c>
       <c r="D51">
-        <v>1068</v>
+        <v>1176</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C52">
-        <v>910</v>
+        <v>1005</v>
       </c>
       <c r="D52">
-        <v>1085</v>
+        <v>1179</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="C53">
-        <v>902</v>
+        <v>1004</v>
       </c>
       <c r="D53">
-        <v>1106</v>
+        <v>1192</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="C54">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D54">
-        <v>1135</v>
+        <v>1101</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="C55">
-        <v>929</v>
+        <v>813</v>
       </c>
       <c r="D55">
-        <v>1152</v>
+        <v>993</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>334</v>
+        <v>176</v>
       </c>
       <c r="C56">
-        <v>948</v>
+        <v>807</v>
       </c>
       <c r="D56">
-        <v>1282</v>
+        <v>983</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>322</v>
+        <v>178</v>
       </c>
       <c r="C57">
-        <v>952</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>1274</v>
+        <v>178</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>387</v>
+        <v>231</v>
       </c>
       <c r="C58">
-        <v>1041</v>
+        <v>843</v>
       </c>
       <c r="D58">
-        <v>1428</v>
+        <v>1074</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>386</v>
+        <v>236</v>
       </c>
       <c r="C59">
-        <v>1052</v>
+        <v>839</v>
       </c>
       <c r="D59">
-        <v>1438</v>
+        <v>1075</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="C60">
-        <v>1015</v>
+        <v>941</v>
       </c>
       <c r="D60">
-        <v>1196</v>
+        <v>1156</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C61">
-        <v>987</v>
+        <v>948</v>
       </c>
       <c r="D61">
-        <v>1202</v>
+        <v>1172</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="C62">
-        <v>999</v>
+        <v>1036</v>
       </c>
       <c r="D62">
-        <v>1268</v>
+        <v>1290</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C63">
-        <v>1009</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1269</v>
+        <v>256</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C64">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1186</v>
+        <v>257</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="C65">
-        <v>889</v>
+        <v>921</v>
       </c>
       <c r="D65">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="C66">
-        <v>949</v>
+        <v>1078</v>
       </c>
       <c r="D66">
-        <v>1406</v>
+        <v>1501</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="C67">
-        <v>947</v>
+        <v>1092</v>
       </c>
       <c r="D67">
-        <v>1409</v>
+        <v>1520</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="C68">
-        <v>939</v>
+        <v>1095</v>
       </c>
       <c r="D68">
-        <v>1406</v>
+        <v>1529</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="C69">
-        <v>952</v>
+        <v>1119</v>
       </c>
       <c r="D69">
-        <v>1436</v>
+        <v>1571</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>688</v>
+        <v>819</v>
       </c>
       <c r="C70">
-        <v>1183</v>
+        <v>1387</v>
       </c>
       <c r="D70">
-        <v>1871</v>
+        <v>2206</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>680</v>
+        <v>850</v>
       </c>
       <c r="C71">
-        <v>1185</v>
+        <v>1396</v>
       </c>
       <c r="D71">
-        <v>1865</v>
+        <v>2246</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>681</v>
+        <v>851</v>
       </c>
       <c r="C72">
-        <v>1190</v>
+        <v>1392</v>
       </c>
       <c r="D72">
-        <v>1871</v>
+        <v>2243</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>701</v>
+        <v>868</v>
       </c>
       <c r="C73">
-        <v>1185</v>
+        <v>1428</v>
       </c>
       <c r="D73">
-        <v>1886</v>
+        <v>2296</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>1005</v>
+        <v>1110</v>
       </c>
       <c r="C74">
-        <v>1334</v>
+        <v>1429</v>
       </c>
       <c r="D74">
-        <v>2339</v>
+        <v>2539</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>941</v>
+        <v>1135</v>
       </c>
       <c r="C75">
-        <v>1363</v>
+        <v>1430</v>
       </c>
       <c r="D75">
-        <v>2304</v>
+        <v>2565</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="C76">
-        <v>1367</v>
+        <v>1433</v>
       </c>
       <c r="D76">
-        <v>1367</v>
+        <v>2593</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>949</v>
+        <v>1157</v>
       </c>
       <c r="C77">
-        <v>1363</v>
+        <v>1413</v>
       </c>
       <c r="D77">
-        <v>2312</v>
+        <v>2570</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="C78">
-        <v>1461</v>
+        <v>1444</v>
       </c>
       <c r="D78">
-        <v>2562</v>
+        <v>2552</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C79">
-        <v>1479</v>
+        <v>1451</v>
       </c>
       <c r="D79">
-        <v>2584</v>
+        <v>2557</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C80">
-        <v>1499</v>
+        <v>1448</v>
       </c>
       <c r="D80">
-        <v>2606</v>
+        <v>2556</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C81">
-        <v>1498</v>
+        <v>1463</v>
       </c>
       <c r="D81">
-        <v>2602</v>
+        <v>2575</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>1081</v>
+        <v>1125</v>
       </c>
       <c r="C82">
-        <v>1490</v>
+        <v>1443</v>
       </c>
       <c r="D82">
-        <v>2571</v>
+        <v>2568</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>1077</v>
+        <v>1111</v>
       </c>
       <c r="C83">
-        <v>1503</v>
+        <v>1445</v>
       </c>
       <c r="D83">
-        <v>2580</v>
+        <v>2556</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>1505</v>
+        <v>1442</v>
       </c>
       <c r="D84">
-        <v>1505</v>
+        <v>1442</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>1084</v>
+        <v>1106</v>
       </c>
       <c r="C85">
-        <v>1495</v>
+        <v>1440</v>
       </c>
       <c r="D85">
-        <v>2579</v>
+        <v>2546</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C86">
-        <v>1490</v>
+        <v>1462</v>
       </c>
       <c r="D86">
-        <v>2408</v>
+        <v>2382</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C87">
-        <v>1493</v>
+        <v>1466</v>
       </c>
       <c r="D87">
-        <v>2402</v>
+        <v>2376</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="C88">
-        <v>1494</v>
+        <v>1467</v>
       </c>
       <c r="D88">
-        <v>1494</v>
+        <v>2376</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C89">
-        <v>1503</v>
+        <v>1465</v>
       </c>
       <c r="D89">
-        <v>2409</v>
+        <v>2372</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>713</v>
+        <v>775</v>
       </c>
       <c r="C90">
-        <v>1453</v>
+        <v>1462</v>
       </c>
       <c r="D90">
-        <v>2166</v>
+        <v>2237</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="C91">
-        <v>1446</v>
+        <v>1459</v>
       </c>
       <c r="D91">
-        <v>2151</v>
+        <v>2224</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>716</v>
+        <v>779</v>
       </c>
       <c r="C92">
-        <v>1470</v>
+        <v>1456</v>
       </c>
       <c r="D92">
-        <v>2186</v>
+        <v>2235</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>710</v>
+        <v>760</v>
       </c>
       <c r="C93">
-        <v>1475</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>2185</v>
+        <v>760</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="C94">
-        <v>1392</v>
+        <v>1418</v>
       </c>
       <c r="D94">
-        <v>1839</v>
+        <v>1927</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="C95">
-        <v>1390</v>
+        <v>1413</v>
       </c>
       <c r="D95">
-        <v>1830</v>
+        <v>1905</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="C96">
-        <v>1391</v>
+        <v>1410</v>
       </c>
       <c r="D96">
-        <v>1391</v>
+        <v>1909</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>438</v>
+        <v>491</v>
       </c>
       <c r="C97">
-        <v>1387</v>
+        <v>1400</v>
       </c>
       <c r="D97">
-        <v>1825</v>
+        <v>1891</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>328</v>
+        <v>414</v>
       </c>
       <c r="C98">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="D98">
-        <v>1729</v>
+        <v>1812</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B99">
-        <v>320</v>
+        <v>397</v>
       </c>
       <c r="C99">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="D99">
-        <v>1712</v>
+        <v>1791</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="C100">
-        <v>1391</v>
+        <v>1409</v>
       </c>
       <c r="D100">
-        <v>1391</v>
+        <v>1782</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B101">
-        <v>321</v>
+        <v>387</v>
       </c>
       <c r="C101">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="D101">
-        <v>1713</v>
+        <v>1797</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B102">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="C102">
-        <v>1246</v>
+        <v>1267</v>
       </c>
       <c r="D102">
-        <v>1703</v>
+        <v>1735</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B103">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C103">
-        <v>1222</v>
+        <v>1254</v>
       </c>
       <c r="D103">
-        <v>1682</v>
+        <v>1715</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>1223</v>
+        <v>1258</v>
       </c>
       <c r="D104">
-        <v>1223</v>
+        <v>1258</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B105">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C105">
-        <v>1224</v>
+        <v>1261</v>
       </c>
       <c r="D105">
-        <v>1683</v>
+        <v>1723</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B106">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C106">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D106">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B107">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>1225</v>
+        <v>1262</v>
       </c>
       <c r="D107">
-        <v>1676</v>
+        <v>1262</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1232</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1682</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B109">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C109">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="D109">
-        <v>1681</v>
+        <v>1674</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B110">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C110">
-        <v>1230</v>
+        <v>1260</v>
       </c>
       <c r="D110">
-        <v>1698</v>
+        <v>1723</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B111">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1229</v>
+        <v>1262</v>
       </c>
       <c r="D111">
-        <v>1698</v>
+        <v>1262</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B112">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1261</v>
       </c>
       <c r="D112">
-        <v>476</v>
+        <v>1261</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B113">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B114">
-        <v>515</v>
+        <v>450</v>
       </c>
       <c r="C114">
-        <v>1225</v>
+        <v>1276</v>
       </c>
       <c r="D114">
-        <v>1740</v>
+        <v>1726</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B115">
-        <v>513</v>
+        <v>448</v>
       </c>
       <c r="C115">
-        <v>1224</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1737</v>
+        <v>448</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B116">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="D116">
-        <v>512</v>
+        <v>1277</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B117">
-        <v>527</v>
+        <v>459</v>
       </c>
       <c r="C117">
-        <v>1218</v>
+        <v>1276</v>
       </c>
       <c r="D117">
-        <v>1745</v>
+        <v>1735</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B118">
-        <v>595</v>
+        <v>463</v>
       </c>
       <c r="C118">
-        <v>1225</v>
+        <v>1273</v>
       </c>
       <c r="D118">
-        <v>1820</v>
+        <v>1736</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B119">
-        <v>592</v>
+        <v>461</v>
       </c>
       <c r="C119">
-        <v>1224</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1816</v>
+        <v>461</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B120">
-        <v>591</v>
+        <v>465</v>
       </c>
       <c r="C120">
-        <v>1222</v>
+        <v>1272</v>
       </c>
       <c r="D120">
-        <v>1813</v>
+        <v>1737</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B121">
-        <v>619</v>
+        <v>469</v>
       </c>
       <c r="C121">
-        <v>1223</v>
+        <v>1275</v>
       </c>
       <c r="D121">
-        <v>1842</v>
+        <v>1744</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B122">
-        <v>717</v>
+        <v>505</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1263</v>
       </c>
       <c r="D122">
-        <v>717</v>
+        <v>1768</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B123">
-        <v>724</v>
+        <v>504</v>
       </c>
       <c r="C123">
-        <v>1218</v>
+        <v>1278</v>
       </c>
       <c r="D123">
-        <v>1942</v>
+        <v>1782</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B124">
-        <v>725</v>
+        <v>510</v>
       </c>
       <c r="C124">
-        <v>1222</v>
+        <v>1286</v>
       </c>
       <c r="D124">
-        <v>1947</v>
+        <v>1796</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B125">
-        <v>732</v>
+        <v>541</v>
       </c>
       <c r="C125">
-        <v>1223</v>
+        <v>1288</v>
       </c>
       <c r="D125">
-        <v>1955</v>
+        <v>1829</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B126">
-        <v>575</v>
+        <v>428</v>
       </c>
       <c r="C126">
-        <v>1269</v>
+        <v>1283</v>
       </c>
       <c r="D126">
-        <v>1844</v>
+        <v>1711</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B127">
-        <v>566</v>
+        <v>450</v>
       </c>
       <c r="C127">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="D127">
-        <v>1843</v>
+        <v>1732</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B128">
-        <v>569</v>
+        <v>503</v>
       </c>
       <c r="C128">
-        <v>1279</v>
+        <v>1319</v>
       </c>
       <c r="D128">
-        <v>1848</v>
+        <v>1822</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B129">
-        <v>638</v>
+        <v>496</v>
       </c>
       <c r="C129">
-        <v>1309</v>
+        <v>1329</v>
       </c>
       <c r="D129">
-        <v>1947</v>
+        <v>1825</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B130">
-        <v>543</v>
+        <v>403</v>
       </c>
       <c r="C130">
-        <v>1276</v>
+        <v>1267</v>
       </c>
       <c r="D130">
-        <v>1819</v>
+        <v>1670</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B131">
-        <v>541</v>
+        <v>391</v>
       </c>
       <c r="C131">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="D131">
-        <v>1813</v>
+        <v>1656</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B132">
-        <v>492</v>
+        <v>390</v>
       </c>
       <c r="C132">
-        <v>1248</v>
+        <v>1262</v>
       </c>
       <c r="D132">
-        <v>1740</v>
+        <v>1652</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B133">
-        <v>478</v>
+        <v>388</v>
       </c>
       <c r="C133">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D133">
-        <v>1725</v>
+        <v>1643</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B134">
-        <v>432</v>
+        <v>334</v>
       </c>
       <c r="C134">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="D134">
-        <v>1634</v>
+        <v>1534</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B135">
-        <v>429</v>
+        <v>340</v>
       </c>
       <c r="C135">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D135">
-        <v>1626</v>
+        <v>1539</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B136">
-        <v>425</v>
+        <v>284</v>
       </c>
       <c r="C136">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="D136">
-        <v>1607</v>
+        <v>1473</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C137">
-        <v>1183</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>1183</v>
+        <v>280</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B138">
-        <v>413</v>
+        <v>147</v>
       </c>
       <c r="C138">
-        <v>1184</v>
+        <v>1047</v>
       </c>
       <c r="D138">
-        <v>1597</v>
+        <v>1194</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B139">
-        <v>411</v>
+        <v>141</v>
       </c>
       <c r="C139">
-        <v>1185</v>
+        <v>1026</v>
       </c>
       <c r="D139">
-        <v>1596</v>
+        <v>1167</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B140">
-        <v>414</v>
+        <v>143</v>
       </c>
       <c r="C140">
-        <v>1182</v>
+        <v>1038</v>
       </c>
       <c r="D140">
-        <v>1596</v>
+        <v>1181</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B141">
-        <v>411</v>
+        <v>144</v>
       </c>
       <c r="C141">
+        <v>1040</v>
+      </c>
+      <c r="D141">
         <v>1184</v>
-      </c>
-      <c r="D141">
-        <v>1595</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B142">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C142">
-        <v>1006</v>
+        <v>996</v>
       </c>
       <c r="D142">
-        <v>1230</v>
+        <v>1211</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +4390,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B143">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="C143">
-        <v>1011</v>
+        <v>954</v>
       </c>
       <c r="D143">
-        <v>1227</v>
+        <v>1145</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B144">
-        <v>194</v>
+        <v>149</v>
       </c>
       <c r="C144">
-        <v>1014</v>
+        <v>951</v>
       </c>
       <c r="D144">
-        <v>1208</v>
+        <v>1100</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B145">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="C145">
-        <v>1013</v>
+        <v>952</v>
       </c>
       <c r="D145">
-        <v>1205</v>
+        <v>1089</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B146">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="C146">
-        <v>998</v>
+        <v>938</v>
       </c>
       <c r="D146">
-        <v>1181</v>
+        <v>1097</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1076</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>946</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>1067</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4610,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4630,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,16 +4650,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4094,16 +4670,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>939</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>1091</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>935</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>1122</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1346</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="C164">
         <v>0</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1139</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1659</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1294</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1688</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,16 +4890,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1293</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1697</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4334,16 +4910,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1811</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1459</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>2384</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>2430</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>971</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1469</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>2435</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1449</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>2370</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>917</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1444</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>2361</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>924</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1451</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>2375</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>2372</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1492</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>2349</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>881</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1491</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>2372</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1493</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>2382</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1478</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>2259</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1538</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>2618</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>2633</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="C185">
         <v>0</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>934</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1543</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>2477</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>1039</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1551</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>2590</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1554</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>2518</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1558</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>2527</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1131</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1673</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>2804</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1042</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1698</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>2740</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1699</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>2661</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,22 +5390,3862 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>874</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1697</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>2571</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B194">
+        <v>682</v>
+      </c>
+      <c r="C194">
+        <v>1447</v>
+      </c>
+      <c r="D194">
+        <v>2129</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>493</v>
+      </c>
+      <c r="C195">
+        <v>1372</v>
+      </c>
+      <c r="D195">
+        <v>1865</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>429</v>
+      </c>
+      <c r="C196">
+        <v>1297</v>
+      </c>
+      <c r="D196">
+        <v>1726</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B197">
+        <v>425</v>
+      </c>
+      <c r="C197">
+        <v>1299</v>
+      </c>
+      <c r="D197">
+        <v>1724</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>364</v>
+      </c>
+      <c r="C198">
+        <v>1283</v>
+      </c>
+      <c r="D198">
+        <v>1647</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>357</v>
+      </c>
+      <c r="C199">
+        <v>1279</v>
+      </c>
+      <c r="D199">
+        <v>1636</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B200">
+        <v>358</v>
+      </c>
+      <c r="C200">
+        <v>1280</v>
+      </c>
+      <c r="D200">
+        <v>1638</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>354</v>
+      </c>
+      <c r="C201">
+        <v>1278</v>
+      </c>
+      <c r="D201">
+        <v>1632</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>363</v>
+      </c>
+      <c r="C202">
+        <v>1270</v>
+      </c>
+      <c r="D202">
+        <v>1633</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B203">
+        <v>354</v>
+      </c>
+      <c r="C203">
+        <v>1265</v>
+      </c>
+      <c r="D203">
+        <v>1619</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>361</v>
+      </c>
+      <c r="C204">
+        <v>1273</v>
+      </c>
+      <c r="D204">
+        <v>1634</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>362</v>
+      </c>
+      <c r="C205">
+        <v>1274</v>
+      </c>
+      <c r="D205">
+        <v>1636</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B206">
+        <v>359</v>
+      </c>
+      <c r="C206">
+        <v>1282</v>
+      </c>
+      <c r="D206">
+        <v>1641</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>1281</v>
+      </c>
+      <c r="D207">
+        <v>1281</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>1282</v>
+      </c>
+      <c r="D208">
+        <v>1282</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B209">
+        <v>363</v>
+      </c>
+      <c r="C209">
+        <v>1285</v>
+      </c>
+      <c r="D209">
+        <v>1648</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>375</v>
+      </c>
+      <c r="C210">
+        <v>1288</v>
+      </c>
+      <c r="D210">
+        <v>1663</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>372</v>
+      </c>
+      <c r="C211">
+        <v>1290</v>
+      </c>
+      <c r="D211">
+        <v>1662</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B212">
+        <v>374</v>
+      </c>
+      <c r="C212">
+        <v>1289</v>
+      </c>
+      <c r="D212">
+        <v>1663</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>403</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>403</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>406</v>
+      </c>
+      <c r="C214">
+        <v>1445</v>
+      </c>
+      <c r="D214">
+        <v>1851</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B215">
+        <v>401</v>
+      </c>
+      <c r="C215">
+        <v>1483</v>
+      </c>
+      <c r="D215">
+        <v>1884</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>400</v>
+      </c>
+      <c r="C216">
+        <v>1492</v>
+      </c>
+      <c r="D216">
+        <v>1892</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>404</v>
+      </c>
+      <c r="C217">
+        <v>1517</v>
+      </c>
+      <c r="D217">
+        <v>1921</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B218">
+        <v>421</v>
+      </c>
+      <c r="C218">
+        <v>1498</v>
+      </c>
+      <c r="D218">
+        <v>1919</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>1497</v>
+      </c>
+      <c r="D219">
+        <v>1497</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>449</v>
+      </c>
+      <c r="C220">
+        <v>1503</v>
+      </c>
+      <c r="D220">
+        <v>1952</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B221">
+        <v>411</v>
+      </c>
+      <c r="C221">
+        <v>1509</v>
+      </c>
+      <c r="D221">
+        <v>1920</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>254</v>
+      </c>
+      <c r="C222">
+        <v>1251</v>
+      </c>
+      <c r="D222">
+        <v>1505</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>280</v>
+      </c>
+      <c r="C223">
+        <v>1239</v>
+      </c>
+      <c r="D223">
+        <v>1519</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B224">
+        <v>251</v>
+      </c>
+      <c r="C224">
+        <v>1224</v>
+      </c>
+      <c r="D224">
+        <v>1475</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>1223</v>
+      </c>
+      <c r="D225">
+        <v>1223</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>209</v>
+      </c>
+      <c r="C226">
+        <v>1159</v>
+      </c>
+      <c r="D226">
+        <v>1368</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B227">
+        <v>202</v>
+      </c>
+      <c r="C227">
+        <v>1148</v>
+      </c>
+      <c r="D227">
+        <v>1350</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>201</v>
+      </c>
+      <c r="C228">
+        <v>1149</v>
+      </c>
+      <c r="D228">
+        <v>1350</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>197</v>
+      </c>
+      <c r="C229">
+        <v>1125</v>
+      </c>
+      <c r="D229">
+        <v>1322</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B230">
+        <v>161</v>
+      </c>
+      <c r="C230">
+        <v>935</v>
+      </c>
+      <c r="D230">
+        <v>1096</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>156</v>
+      </c>
+      <c r="C231">
+        <v>924</v>
+      </c>
+      <c r="D231">
+        <v>1080</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>157</v>
+      </c>
+      <c r="C232">
+        <v>923</v>
+      </c>
+      <c r="D232">
+        <v>1080</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B233">
+        <v>158</v>
+      </c>
+      <c r="C233">
+        <v>922</v>
+      </c>
+      <c r="D233">
+        <v>1080</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>122</v>
+      </c>
+      <c r="C234">
+        <v>928</v>
+      </c>
+      <c r="D234">
+        <v>1050</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>120</v>
+      </c>
+      <c r="C235">
+        <v>932</v>
+      </c>
+      <c r="D235">
+        <v>1052</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B236">
+        <v>121</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>121</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>120</v>
+      </c>
+      <c r="C237">
+        <v>935</v>
+      </c>
+      <c r="D237">
+        <v>1055</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>150</v>
+      </c>
+      <c r="C238">
+        <v>939</v>
+      </c>
+      <c r="D238">
+        <v>1089</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B239">
+        <v>156</v>
+      </c>
+      <c r="C239">
+        <v>938</v>
+      </c>
+      <c r="D239">
+        <v>1094</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>145</v>
+      </c>
+      <c r="C240">
+        <v>917</v>
+      </c>
+      <c r="D240">
+        <v>1062</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>109</v>
+      </c>
+      <c r="C241">
+        <v>916</v>
+      </c>
+      <c r="D241">
+        <v>1025</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B242">
+        <v>152</v>
+      </c>
+      <c r="C242">
+        <v>927</v>
+      </c>
+      <c r="D242">
+        <v>1079</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>150</v>
+      </c>
+      <c r="C243">
+        <v>902</v>
+      </c>
+      <c r="D243">
+        <v>1052</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>114</v>
+      </c>
+      <c r="C244">
+        <v>890</v>
+      </c>
+      <c r="D244">
+        <v>1004</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B245">
+        <v>107</v>
+      </c>
+      <c r="C245">
+        <v>891</v>
+      </c>
+      <c r="D245">
+        <v>998</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>120</v>
+      </c>
+      <c r="C246">
+        <v>908</v>
+      </c>
+      <c r="D246">
+        <v>1028</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>110</v>
+      </c>
+      <c r="C247">
+        <v>891</v>
+      </c>
+      <c r="D247">
+        <v>1001</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B248">
+        <v>114</v>
+      </c>
+      <c r="C248">
+        <v>872</v>
+      </c>
+      <c r="D248">
+        <v>986</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>109</v>
+      </c>
+      <c r="C249">
+        <v>871</v>
+      </c>
+      <c r="D249">
+        <v>980</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>168</v>
+      </c>
+      <c r="C250">
+        <v>882</v>
+      </c>
+      <c r="D250">
+        <v>1050</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B251">
+        <v>134</v>
+      </c>
+      <c r="C251">
+        <v>880</v>
+      </c>
+      <c r="D251">
+        <v>1014</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>129</v>
+      </c>
+      <c r="C252">
+        <v>881</v>
+      </c>
+      <c r="D252">
+        <v>1010</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>145</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>145</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B254">
+        <v>187</v>
+      </c>
+      <c r="C254">
+        <v>896</v>
+      </c>
+      <c r="D254">
+        <v>1083</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>188</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>188</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>895</v>
+      </c>
+      <c r="D256">
+        <v>895</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B257">
+        <v>198</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>198</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>256</v>
+      </c>
+      <c r="C258">
+        <v>907</v>
+      </c>
+      <c r="D258">
+        <v>1163</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>268</v>
+      </c>
+      <c r="C259">
+        <v>915</v>
+      </c>
+      <c r="D259">
+        <v>1183</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B260">
+        <v>266</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>266</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>300</v>
+      </c>
+      <c r="C261">
+        <v>929</v>
+      </c>
+      <c r="D261">
+        <v>1229</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>332</v>
+      </c>
+      <c r="C262">
+        <v>1240</v>
+      </c>
+      <c r="D262">
+        <v>1572</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B263">
+        <v>337</v>
+      </c>
+      <c r="C263">
+        <v>1256</v>
+      </c>
+      <c r="D263">
+        <v>1593</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>1255</v>
+      </c>
+      <c r="D264">
+        <v>1255</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>392</v>
+      </c>
+      <c r="C265">
+        <v>1258</v>
+      </c>
+      <c r="D265">
+        <v>1650</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B266">
+        <v>935</v>
+      </c>
+      <c r="C266">
+        <v>1380</v>
+      </c>
+      <c r="D266">
+        <v>2315</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>943</v>
+      </c>
+      <c r="C267">
+        <v>1411</v>
+      </c>
+      <c r="D267">
+        <v>2354</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>963</v>
+      </c>
+      <c r="C268">
+        <v>1423</v>
+      </c>
+      <c r="D268">
+        <v>2386</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B269">
+        <v>987</v>
+      </c>
+      <c r="C269">
+        <v>1420</v>
+      </c>
+      <c r="D269">
+        <v>2407</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>991</v>
+      </c>
+      <c r="C270">
+        <v>1412</v>
+      </c>
+      <c r="D270">
+        <v>2403</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>1009</v>
+      </c>
+      <c r="C271">
+        <v>1421</v>
+      </c>
+      <c r="D271">
+        <v>2430</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>1452</v>
+      </c>
+      <c r="D272">
+        <v>1452</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>1008</v>
+      </c>
+      <c r="C273">
+        <v>1451</v>
+      </c>
+      <c r="D273">
+        <v>2459</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>979</v>
+      </c>
+      <c r="C274">
+        <v>1466</v>
+      </c>
+      <c r="D274">
+        <v>2445</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B275">
+        <v>982</v>
+      </c>
+      <c r="C275">
+        <v>1465</v>
+      </c>
+      <c r="D275">
+        <v>2447</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>976</v>
+      </c>
+      <c r="C276">
+        <v>1461</v>
+      </c>
+      <c r="D276">
+        <v>2437</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>1450</v>
+      </c>
+      <c r="D277">
+        <v>1450</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B278">
+        <v>875</v>
+      </c>
+      <c r="C278">
+        <v>1446</v>
+      </c>
+      <c r="D278">
+        <v>2321</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>866</v>
+      </c>
+      <c r="C279">
+        <v>1449</v>
+      </c>
+      <c r="D279">
+        <v>2315</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>853</v>
+      </c>
+      <c r="C280">
+        <v>1450</v>
+      </c>
+      <c r="D280">
+        <v>2303</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B281">
+        <v>842</v>
+      </c>
+      <c r="C281">
+        <v>1444</v>
+      </c>
+      <c r="D281">
+        <v>2286</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>721</v>
+      </c>
+      <c r="C282">
+        <v>1445</v>
+      </c>
+      <c r="D282">
+        <v>2166</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>712</v>
+      </c>
+      <c r="C283">
+        <v>1446</v>
+      </c>
+      <c r="D283">
+        <v>2158</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B284">
+        <v>719</v>
+      </c>
+      <c r="C284">
+        <v>1450</v>
+      </c>
+      <c r="D284">
+        <v>2169</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>721</v>
+      </c>
+      <c r="C285">
+        <v>1449</v>
+      </c>
+      <c r="D285">
+        <v>2170</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>565</v>
+      </c>
+      <c r="C286">
+        <v>1388</v>
+      </c>
+      <c r="D286">
+        <v>1953</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B287">
+        <v>554</v>
+      </c>
+      <c r="C287">
+        <v>1390</v>
+      </c>
+      <c r="D287">
+        <v>1944</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>556</v>
+      </c>
+      <c r="C288">
+        <v>1392</v>
+      </c>
+      <c r="D288">
+        <v>1948</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>554</v>
+      </c>
+      <c r="C289">
+        <v>1391</v>
+      </c>
+      <c r="D289">
+        <v>1945</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B290">
+        <v>489</v>
+      </c>
+      <c r="C290">
+        <v>1423</v>
+      </c>
+      <c r="D290">
+        <v>1912</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>499</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>499</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>483</v>
+      </c>
+      <c r="C292">
+        <v>1421</v>
+      </c>
+      <c r="D292">
+        <v>1904</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B293">
+        <v>482</v>
+      </c>
+      <c r="C293">
+        <v>1420</v>
+      </c>
+      <c r="D293">
+        <v>1902</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>513</v>
+      </c>
+      <c r="C294">
+        <v>1376</v>
+      </c>
+      <c r="D294">
+        <v>1889</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>518</v>
+      </c>
+      <c r="C295">
+        <v>1371</v>
+      </c>
+      <c r="D295">
+        <v>1889</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B296">
+        <v>520</v>
+      </c>
+      <c r="C296">
+        <v>1373</v>
+      </c>
+      <c r="D296">
+        <v>1893</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>512</v>
+      </c>
+      <c r="C297">
+        <v>1368</v>
+      </c>
+      <c r="D297">
+        <v>1880</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>475</v>
+      </c>
+      <c r="C298">
+        <v>1369</v>
+      </c>
+      <c r="D298">
+        <v>1844</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>476</v>
+      </c>
+      <c r="C300">
+        <v>1363</v>
+      </c>
+      <c r="D300">
+        <v>1839</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>475</v>
+      </c>
+      <c r="C301">
+        <v>1326</v>
+      </c>
+      <c r="D301">
+        <v>1801</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B302">
+        <v>478</v>
+      </c>
+      <c r="C302">
+        <v>1361</v>
+      </c>
+      <c r="D302">
+        <v>1839</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>458</v>
+      </c>
+      <c r="C303">
+        <v>1362</v>
+      </c>
+      <c r="D303">
+        <v>1820</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>440</v>
+      </c>
+      <c r="C304">
+        <v>1363</v>
+      </c>
+      <c r="D304">
+        <v>1803</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B305">
+        <v>479</v>
+      </c>
+      <c r="C305">
+        <v>1364</v>
+      </c>
+      <c r="D305">
+        <v>1843</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>493</v>
+      </c>
+      <c r="C306">
+        <v>1395</v>
+      </c>
+      <c r="D306">
+        <v>1888</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B308">
+        <v>492</v>
+      </c>
+      <c r="C308">
+        <v>1397</v>
+      </c>
+      <c r="D308">
+        <v>1889</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>501</v>
+      </c>
+      <c r="C309">
+        <v>1421</v>
+      </c>
+      <c r="D309">
+        <v>1922</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>525</v>
+      </c>
+      <c r="C310">
+        <v>1420</v>
+      </c>
+      <c r="D310">
+        <v>1945</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B311">
+        <v>517</v>
+      </c>
+      <c r="C311">
+        <v>1422</v>
+      </c>
+      <c r="D311">
+        <v>1939</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>514</v>
+      </c>
+      <c r="C312">
+        <v>1424</v>
+      </c>
+      <c r="D312">
+        <v>1938</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>528</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>528</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B314">
+        <v>614</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>614</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>619</v>
+      </c>
+      <c r="C315">
+        <v>1428</v>
+      </c>
+      <c r="D315">
+        <v>2047</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>609</v>
+      </c>
+      <c r="C316">
+        <v>1426</v>
+      </c>
+      <c r="D316">
+        <v>2035</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B317">
+        <v>594</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>594</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>537</v>
+      </c>
+      <c r="C318">
+        <v>1396</v>
+      </c>
+      <c r="D318">
+        <v>1933</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>504</v>
+      </c>
+      <c r="C319">
+        <v>1342</v>
+      </c>
+      <c r="D319">
+        <v>1846</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>1336</v>
+      </c>
+      <c r="D320">
+        <v>1336</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>505</v>
+      </c>
+      <c r="C321">
+        <v>1346</v>
+      </c>
+      <c r="D321">
+        <v>1851</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>235</v>
+      </c>
+      <c r="C322">
+        <v>1288</v>
+      </c>
+      <c r="D322">
+        <v>1523</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B323">
+        <v>203</v>
+      </c>
+      <c r="C323">
+        <v>1282</v>
+      </c>
+      <c r="D323">
+        <v>1485</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>198</v>
+      </c>
+      <c r="C324">
+        <v>1278</v>
+      </c>
+      <c r="D324">
+        <v>1476</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>195</v>
+      </c>
+      <c r="C325">
+        <v>1279</v>
+      </c>
+      <c r="D325">
+        <v>1474</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B326">
+        <v>141</v>
+      </c>
+      <c r="C326">
+        <v>1229</v>
+      </c>
+      <c r="D326">
+        <v>1370</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>170</v>
+      </c>
+      <c r="C327">
+        <v>1336</v>
+      </c>
+      <c r="D327">
+        <v>1506</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>174</v>
+      </c>
+      <c r="C328">
+        <v>1345</v>
+      </c>
+      <c r="D328">
+        <v>1519</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B329">
+        <v>173</v>
+      </c>
+      <c r="C329">
+        <v>1237</v>
+      </c>
+      <c r="D329">
+        <v>1410</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>107</v>
+      </c>
+      <c r="C330">
+        <v>938</v>
+      </c>
+      <c r="D330">
+        <v>1045</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>106</v>
+      </c>
+      <c r="C331">
+        <v>894</v>
+      </c>
+      <c r="D331">
+        <v>1000</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>1028</v>
+      </c>
+      <c r="D332">
+        <v>1028</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>25.05.202694</t>
-  </si>
-  <si>
-    <t>25.05.202695</t>
-  </si>
-  <si>
-    <t>25.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>26.05.202696</t>
+  </si>
+  <si>
+    <t>27.05.20261</t>
+  </si>
+  <si>
+    <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
+    <t>27.05.202695</t>
+  </si>
+  <si>
+    <t>27.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
-        <v>489</v>
+        <v>671</v>
       </c>
       <c r="C2">
-        <v>1423</v>
+        <v>1290</v>
       </c>
       <c r="D2">
-        <v>1912</v>
+        <v>1961</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
-        <v>499</v>
+        <v>669</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>499</v>
+        <v>669</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1421</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1904</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
-        <v>482</v>
+        <v>666</v>
       </c>
       <c r="C5">
-        <v>1420</v>
+        <v>1288</v>
       </c>
       <c r="D5">
-        <v>1902</v>
+        <v>1954</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>513</v>
+        <v>609</v>
       </c>
       <c r="C6">
-        <v>1376</v>
+        <v>1297</v>
       </c>
       <c r="D6">
-        <v>1889</v>
+        <v>1906</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>518</v>
+        <v>612</v>
       </c>
       <c r="C7">
-        <v>1371</v>
+        <v>1284</v>
       </c>
       <c r="D7">
-        <v>1889</v>
+        <v>1896</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,13 +1114,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>520</v>
+        <v>611</v>
       </c>
       <c r="C8">
-        <v>1373</v>
+        <v>1282</v>
       </c>
       <c r="D8">
         <v>1893</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>512</v>
+        <v>612</v>
       </c>
       <c r="C9">
-        <v>1368</v>
+        <v>1281</v>
       </c>
       <c r="D9">
-        <v>1880</v>
+        <v>1893</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>475</v>
+        <v>594</v>
       </c>
       <c r="C10">
-        <v>1369</v>
+        <v>1286</v>
       </c>
       <c r="D10">
-        <v>1844</v>
+        <v>1880</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1877</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1363</v>
+        <v>1260</v>
       </c>
       <c r="D12">
-        <v>1839</v>
+        <v>1260</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
-        <v>475</v>
+        <v>582</v>
       </c>
       <c r="C13">
-        <v>1326</v>
+        <v>1211</v>
       </c>
       <c r="D13">
-        <v>1801</v>
+        <v>1793</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>478</v>
+        <v>608</v>
       </c>
       <c r="C14">
-        <v>1361</v>
+        <v>1216</v>
       </c>
       <c r="D14">
-        <v>1839</v>
+        <v>1824</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>458</v>
+        <v>607</v>
       </c>
       <c r="C15">
-        <v>1362</v>
+        <v>1201</v>
       </c>
       <c r="D15">
-        <v>1820</v>
+        <v>1808</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>440</v>
+        <v>609</v>
       </c>
       <c r="C16">
-        <v>1363</v>
+        <v>1196</v>
       </c>
       <c r="D16">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>479</v>
+        <v>630</v>
       </c>
       <c r="C17">
-        <v>1364</v>
+        <v>1204</v>
       </c>
       <c r="D17">
-        <v>1843</v>
+        <v>1834</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>493</v>
+        <v>674</v>
       </c>
       <c r="C18">
-        <v>1395</v>
+        <v>1207</v>
       </c>
       <c r="D18">
-        <v>1888</v>
+        <v>1881</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="C20">
-        <v>1397</v>
+        <v>1205</v>
       </c>
       <c r="D20">
-        <v>1889</v>
+        <v>1724</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="C21">
-        <v>1421</v>
+        <v>1204</v>
       </c>
       <c r="D21">
-        <v>1922</v>
+        <v>1737</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="C22">
-        <v>1420</v>
+        <v>1238</v>
       </c>
       <c r="D22">
-        <v>1945</v>
+        <v>1808</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>517</v>
+        <v>581</v>
       </c>
       <c r="C23">
-        <v>1422</v>
+        <v>1239</v>
       </c>
       <c r="D23">
-        <v>1939</v>
+        <v>1820</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>514</v>
+        <v>723</v>
       </c>
       <c r="C24">
-        <v>1424</v>
+        <v>1264</v>
       </c>
       <c r="D24">
-        <v>1938</v>
+        <v>1987</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>528</v>
+        <v>735</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1265</v>
       </c>
       <c r="D25">
-        <v>528</v>
+        <v>2000</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>614</v>
+        <v>709</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1287</v>
       </c>
       <c r="D26">
-        <v>614</v>
+        <v>1996</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>619</v>
+        <v>706</v>
       </c>
       <c r="C27">
-        <v>1428</v>
+        <v>1291</v>
       </c>
       <c r="D27">
-        <v>2047</v>
+        <v>1997</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>609</v>
+        <v>708</v>
       </c>
       <c r="C28">
-        <v>1426</v>
+        <v>1298</v>
       </c>
       <c r="D28">
-        <v>2035</v>
+        <v>2006</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>594</v>
+        <v>712</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1296</v>
       </c>
       <c r="D29">
-        <v>594</v>
+        <v>2008</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>537</v>
+        <v>655</v>
       </c>
       <c r="C30">
-        <v>1396</v>
+        <v>1254</v>
       </c>
       <c r="D30">
-        <v>1933</v>
+        <v>1909</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>504</v>
+        <v>658</v>
       </c>
       <c r="C31">
-        <v>1342</v>
+        <v>1255</v>
       </c>
       <c r="D31">
-        <v>1846</v>
+        <v>1913</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="C32">
-        <v>1336</v>
+        <v>1266</v>
       </c>
       <c r="D32">
-        <v>1336</v>
+        <v>1947</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>505</v>
+        <v>668</v>
       </c>
       <c r="C33">
-        <v>1346</v>
+        <v>1293</v>
       </c>
       <c r="D33">
-        <v>1851</v>
+        <v>1961</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>235</v>
+        <v>410</v>
       </c>
       <c r="C34">
-        <v>1288</v>
+        <v>1278</v>
       </c>
       <c r="D34">
-        <v>1523</v>
+        <v>1688</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>203</v>
+        <v>402</v>
       </c>
       <c r="C35">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D35">
-        <v>1485</v>
+        <v>1679</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="C36">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D36">
-        <v>1476</v>
+        <v>1683</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>195</v>
+        <v>407</v>
       </c>
       <c r="C37">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="D37">
-        <v>1474</v>
+        <v>1683</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>141</v>
+        <v>363</v>
       </c>
       <c r="C38">
-        <v>1229</v>
+        <v>1208</v>
       </c>
       <c r="D38">
-        <v>1370</v>
+        <v>1571</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>170</v>
+        <v>351</v>
       </c>
       <c r="C39">
-        <v>1336</v>
+        <v>1199</v>
       </c>
       <c r="D39">
-        <v>1506</v>
+        <v>1550</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>174</v>
+        <v>348</v>
       </c>
       <c r="C40">
-        <v>1345</v>
+        <v>1202</v>
       </c>
       <c r="D40">
-        <v>1519</v>
+        <v>1550</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>173</v>
+        <v>347</v>
       </c>
       <c r="C41">
-        <v>1237</v>
+        <v>1203</v>
       </c>
       <c r="D41">
-        <v>1410</v>
+        <v>1550</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="C42">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="D42">
-        <v>1045</v>
+        <v>1097</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="C43">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="D43">
-        <v>1000</v>
+        <v>1063</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="C44">
-        <v>1028</v>
+        <v>895</v>
       </c>
       <c r="D44">
-        <v>1028</v>
+        <v>1069</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="C45">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1140</v>
+        <v>173</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C46">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="D46">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C47">
-        <v>852</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>976</v>
+        <v>152</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C48">
-        <v>854</v>
+        <v>880</v>
       </c>
       <c r="D48">
-        <v>1016</v>
+        <v>1034</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C49">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="D49">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C50">
-        <v>830</v>
+        <v>861</v>
       </c>
       <c r="D50">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="C51">
-        <v>826</v>
+        <v>859</v>
       </c>
       <c r="D51">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>235</v>
+        <v>147</v>
       </c>
       <c r="C52">
-        <v>970</v>
+        <v>860</v>
       </c>
       <c r="D52">
-        <v>1205</v>
+        <v>1007</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="C53">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1237</v>
+        <v>145</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>279</v>
+        <v>125</v>
       </c>
       <c r="C54">
-        <v>967</v>
+        <v>861</v>
       </c>
       <c r="D54">
-        <v>1246</v>
+        <v>986</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>259</v>
+        <v>132</v>
       </c>
       <c r="C55">
-        <v>988</v>
+        <v>860</v>
       </c>
       <c r="D55">
-        <v>1247</v>
+        <v>992</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>234</v>
+        <v>149</v>
       </c>
       <c r="C56">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>1224</v>
+        <v>149</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>247</v>
+        <v>150</v>
       </c>
       <c r="C57">
-        <v>993</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>1240</v>
+        <v>150</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="C58">
-        <v>1027</v>
+        <v>829</v>
       </c>
       <c r="D58">
-        <v>1279</v>
+        <v>998</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="C59">
-        <v>1015</v>
+        <v>826</v>
       </c>
       <c r="D59">
-        <v>1269</v>
+        <v>998</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="C61">
-        <v>1014</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1251</v>
+        <v>183</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="C62">
-        <v>1025</v>
+        <v>817</v>
       </c>
       <c r="D62">
-        <v>1204</v>
+        <v>1082</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="C63">
-        <v>1024</v>
+        <v>807</v>
       </c>
       <c r="D63">
-        <v>1243</v>
+        <v>1084</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>198</v>
+        <v>269</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>819</v>
       </c>
       <c r="D64">
-        <v>198</v>
+        <v>1088</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>210</v>
+        <v>273</v>
       </c>
       <c r="C65">
-        <v>1022</v>
+        <v>818</v>
       </c>
       <c r="D65">
-        <v>1232</v>
+        <v>1091</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>314</v>
+        <v>416</v>
       </c>
       <c r="C66">
-        <v>1180</v>
+        <v>840</v>
       </c>
       <c r="D66">
-        <v>1494</v>
+        <v>1256</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>336</v>
+        <v>427</v>
       </c>
       <c r="C67">
-        <v>1196</v>
+        <v>850</v>
       </c>
       <c r="D67">
-        <v>1532</v>
+        <v>1277</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>337</v>
+        <v>430</v>
       </c>
       <c r="C68">
-        <v>1198</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>1535</v>
+        <v>430</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>361</v>
+        <v>471</v>
       </c>
       <c r="C69">
-        <v>1205</v>
+        <v>856</v>
       </c>
       <c r="D69">
-        <v>1566</v>
+        <v>1327</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>495</v>
+        <v>892</v>
       </c>
       <c r="C70">
-        <v>1348</v>
+        <v>1246</v>
       </c>
       <c r="D70">
-        <v>1843</v>
+        <v>2138</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>498</v>
+        <v>905</v>
       </c>
       <c r="C71">
-        <v>1356</v>
+        <v>1259</v>
       </c>
       <c r="D71">
-        <v>1854</v>
+        <v>2164</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>502</v>
+        <v>906</v>
       </c>
       <c r="C72">
-        <v>1362</v>
+        <v>1261</v>
       </c>
       <c r="D72">
-        <v>1864</v>
+        <v>2167</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>533</v>
+        <v>928</v>
       </c>
       <c r="C73">
-        <v>1314</v>
+        <v>1240</v>
       </c>
       <c r="D73">
-        <v>1847</v>
+        <v>2168</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>1066</v>
+        <v>1211</v>
       </c>
       <c r="C74">
-        <v>1345</v>
+        <v>1266</v>
       </c>
       <c r="D74">
-        <v>2411</v>
+        <v>2477</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>1029</v>
+        <v>1210</v>
       </c>
       <c r="C75">
-        <v>1317</v>
+        <v>1278</v>
       </c>
       <c r="D75">
-        <v>2346</v>
+        <v>2488</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>1047</v>
+        <v>1225</v>
       </c>
       <c r="C76">
-        <v>1323</v>
+        <v>1284</v>
       </c>
       <c r="D76">
-        <v>2370</v>
+        <v>2509</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>1079</v>
+        <v>1223</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="D77">
-        <v>1079</v>
+        <v>2503</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>1076</v>
+        <v>1256</v>
       </c>
       <c r="C78">
-        <v>1305</v>
+        <v>1278</v>
       </c>
       <c r="D78">
-        <v>2381</v>
+        <v>2534</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>1083</v>
+        <v>1272</v>
       </c>
       <c r="C79">
-        <v>1300</v>
+        <v>1290</v>
       </c>
       <c r="D79">
-        <v>2383</v>
+        <v>2562</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>1104</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>1339</v>
+        <v>1277</v>
       </c>
       <c r="D80">
-        <v>2443</v>
+        <v>1277</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>1118</v>
+        <v>1271</v>
       </c>
       <c r="C81">
-        <v>1343</v>
+        <v>1278</v>
       </c>
       <c r="D81">
-        <v>2461</v>
+        <v>2549</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>1106</v>
+        <v>1240</v>
       </c>
       <c r="C82">
-        <v>1353</v>
+        <v>1256</v>
       </c>
       <c r="D82">
-        <v>2459</v>
+        <v>2496</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>1116</v>
+        <v>1237</v>
       </c>
       <c r="C83">
-        <v>1357</v>
+        <v>1267</v>
       </c>
       <c r="D83">
-        <v>2473</v>
+        <v>2504</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>1118</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>1358</v>
+        <v>1266</v>
       </c>
       <c r="D84">
-        <v>2476</v>
+        <v>1266</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>1115</v>
+        <v>1239</v>
       </c>
       <c r="C85">
-        <v>1356</v>
+        <v>1265</v>
       </c>
       <c r="D85">
-        <v>2471</v>
+        <v>2504</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>984</v>
+        <v>1141</v>
       </c>
       <c r="C86">
-        <v>1376</v>
+        <v>1251</v>
       </c>
       <c r="D86">
-        <v>2360</v>
+        <v>2392</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>977</v>
+        <v>1136</v>
       </c>
       <c r="C87">
-        <v>1378</v>
+        <v>1253</v>
       </c>
       <c r="D87">
-        <v>2355</v>
+        <v>2389</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>979</v>
+        <v>1132</v>
       </c>
       <c r="C88">
-        <v>1374</v>
+        <v>1268</v>
       </c>
       <c r="D88">
-        <v>2353</v>
+        <v>2400</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>969</v>
+        <v>1155</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1365</v>
       </c>
       <c r="D89">
-        <v>969</v>
+        <v>2520</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>750</v>
+        <v>1081</v>
       </c>
       <c r="C90">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="D90">
-        <v>2109</v>
+        <v>2397</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>727</v>
+        <v>1085</v>
       </c>
       <c r="C91">
-        <v>1353</v>
+        <v>1313</v>
       </c>
       <c r="D91">
-        <v>2080</v>
+        <v>2398</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>724</v>
+        <v>1023</v>
       </c>
       <c r="C92">
-        <v>1351</v>
+        <v>1297</v>
       </c>
       <c r="D92">
-        <v>2075</v>
+        <v>2320</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>729</v>
+        <v>1025</v>
       </c>
       <c r="C93">
-        <v>1354</v>
+        <v>1295</v>
       </c>
       <c r="D93">
-        <v>2083</v>
+        <v>2320</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>667</v>
+        <v>773</v>
       </c>
       <c r="C94">
-        <v>1311</v>
+        <v>1237</v>
       </c>
       <c r="D94">
-        <v>1978</v>
+        <v>2010</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>659</v>
+        <v>767</v>
       </c>
       <c r="C95">
-        <v>1301</v>
+        <v>1234</v>
       </c>
       <c r="D95">
-        <v>1960</v>
+        <v>2001</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>662</v>
+        <v>766</v>
       </c>
       <c r="C96">
-        <v>1306</v>
+        <v>1233</v>
       </c>
       <c r="D96">
-        <v>1968</v>
+        <v>1999</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="C97">
-        <v>1300</v>
+        <v>1231</v>
       </c>
       <c r="D97">
-        <v>1300</v>
+        <v>1994</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="C98">
-        <v>1290</v>
+        <v>1203</v>
       </c>
       <c r="D98">
-        <v>1961</v>
+        <v>1857</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B99">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="D99">
-        <v>669</v>
+        <v>1853</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1199</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1845</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B101">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="C101">
-        <v>1288</v>
+        <v>1208</v>
       </c>
       <c r="D101">
-        <v>1954</v>
+        <v>1857</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B102">
-        <v>609</v>
+        <v>669</v>
       </c>
       <c r="C102">
-        <v>1297</v>
+        <v>1220</v>
       </c>
       <c r="D102">
-        <v>1906</v>
+        <v>1889</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B103">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>1284</v>
+        <v>1228</v>
       </c>
       <c r="D103">
-        <v>1896</v>
+        <v>1228</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B104">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>1282</v>
+        <v>1227</v>
       </c>
       <c r="D104">
-        <v>1893</v>
+        <v>1227</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B105">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>1281</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>1893</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B106">
-        <v>594</v>
+        <v>671</v>
       </c>
       <c r="C106">
-        <v>1286</v>
+        <v>1225</v>
       </c>
       <c r="D106">
-        <v>1880</v>
+        <v>1896</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B107">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>1877</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="C108">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>1260</v>
+        <v>666</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B109">
-        <v>582</v>
+        <v>668</v>
       </c>
       <c r="C109">
-        <v>1211</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>1793</v>
+        <v>668</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B110">
-        <v>608</v>
+        <v>673</v>
       </c>
       <c r="C110">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="D110">
-        <v>1824</v>
+        <v>1876</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B111">
-        <v>607</v>
+        <v>672</v>
       </c>
       <c r="C111">
-        <v>1201</v>
+        <v>1193</v>
       </c>
       <c r="D111">
-        <v>1808</v>
+        <v>1865</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B112">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D112">
-        <v>1805</v>
+        <v>1192</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B113">
-        <v>630</v>
+        <v>673</v>
       </c>
       <c r="C113">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="D113">
-        <v>1834</v>
+        <v>1867</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B114">
         <v>674</v>
       </c>
       <c r="C114">
-        <v>1207</v>
+        <v>1227</v>
       </c>
       <c r="D114">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B115">
-        <v>534</v>
+        <v>673</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>534</v>
+        <v>673</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B116">
-        <v>519</v>
+        <v>670</v>
       </c>
       <c r="C116">
-        <v>1205</v>
+        <v>1229</v>
       </c>
       <c r="D116">
-        <v>1724</v>
+        <v>1899</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B117">
-        <v>533</v>
+        <v>684</v>
       </c>
       <c r="C117">
-        <v>1204</v>
+        <v>1231</v>
       </c>
       <c r="D117">
-        <v>1737</v>
+        <v>1915</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B118">
-        <v>570</v>
+        <v>774</v>
       </c>
       <c r="C118">
-        <v>1238</v>
+        <v>1215</v>
       </c>
       <c r="D118">
-        <v>1808</v>
+        <v>1989</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B119">
-        <v>581</v>
+        <v>777</v>
       </c>
       <c r="C119">
-        <v>1239</v>
+        <v>1208</v>
       </c>
       <c r="D119">
-        <v>1820</v>
+        <v>1985</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B120">
-        <v>723</v>
+        <v>773</v>
       </c>
       <c r="C120">
-        <v>1264</v>
+        <v>1210</v>
       </c>
       <c r="D120">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B121">
-        <v>735</v>
+        <v>777</v>
       </c>
       <c r="C121">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>2000</v>
+        <v>777</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B122">
-        <v>709</v>
+        <v>865</v>
       </c>
       <c r="C122">
-        <v>1287</v>
+        <v>1215</v>
       </c>
       <c r="D122">
-        <v>1996</v>
+        <v>2080</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B123">
-        <v>706</v>
+        <v>868</v>
       </c>
       <c r="C123">
-        <v>1291</v>
+        <v>1211</v>
       </c>
       <c r="D123">
-        <v>1997</v>
+        <v>2079</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B124">
-        <v>708</v>
+        <v>869</v>
       </c>
       <c r="C124">
-        <v>1298</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>2006</v>
+        <v>869</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B125">
-        <v>712</v>
+        <v>871</v>
       </c>
       <c r="C125">
-        <v>1296</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>2008</v>
+        <v>871</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B126">
-        <v>655</v>
+        <v>559</v>
       </c>
       <c r="C126">
-        <v>1254</v>
+        <v>1193</v>
       </c>
       <c r="D126">
-        <v>1909</v>
+        <v>1752</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B127">
-        <v>658</v>
+        <v>531</v>
       </c>
       <c r="C127">
-        <v>1255</v>
+        <v>1183</v>
       </c>
       <c r="D127">
-        <v>1913</v>
+        <v>1714</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B128">
-        <v>681</v>
+        <v>528</v>
       </c>
       <c r="C128">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>1947</v>
+        <v>528</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B129">
-        <v>668</v>
+        <v>531</v>
       </c>
       <c r="C129">
-        <v>1293</v>
+        <v>1187</v>
       </c>
       <c r="D129">
-        <v>1961</v>
+        <v>1718</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B130">
-        <v>410</v>
+        <v>574</v>
       </c>
       <c r="C130">
-        <v>1278</v>
+        <v>1086</v>
       </c>
       <c r="D130">
-        <v>1688</v>
+        <v>1660</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B131">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1277</v>
+        <v>1064</v>
       </c>
       <c r="D131">
-        <v>1679</v>
+        <v>1064</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B132">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>1683</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B133">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>1276</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>1683</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>27.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="C2">
-        <v>1290</v>
+        <v>1203</v>
       </c>
       <c r="D2">
-        <v>1961</v>
+        <v>1857</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="D3">
-        <v>669</v>
+        <v>1853</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1199</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1845</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="C5">
-        <v>1288</v>
+        <v>1208</v>
       </c>
       <c r="D5">
-        <v>1954</v>
+        <v>1857</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>609</v>
+        <v>669</v>
       </c>
       <c r="C6">
-        <v>1297</v>
+        <v>1220</v>
       </c>
       <c r="D6">
-        <v>1906</v>
+        <v>1889</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1284</v>
+        <v>1228</v>
       </c>
       <c r="D7">
-        <v>1896</v>
+        <v>1228</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>611</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1282</v>
+        <v>1227</v>
       </c>
       <c r="D8">
-        <v>1893</v>
+        <v>1227</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1281</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1893</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>594</v>
+        <v>671</v>
       </c>
       <c r="C10">
-        <v>1286</v>
+        <v>1225</v>
       </c>
       <c r="D10">
-        <v>1880</v>
+        <v>1896</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>1284</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1877</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="C12">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1260</v>
+        <v>666</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>582</v>
+        <v>668</v>
       </c>
       <c r="C13">
-        <v>1211</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1793</v>
+        <v>668</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>608</v>
+        <v>673</v>
       </c>
       <c r="C14">
-        <v>1216</v>
+        <v>1203</v>
       </c>
       <c r="D14">
-        <v>1824</v>
+        <v>1876</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>607</v>
+        <v>672</v>
       </c>
       <c r="C15">
-        <v>1201</v>
+        <v>1193</v>
       </c>
       <c r="D15">
-        <v>1808</v>
+        <v>1865</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D16">
-        <v>1805</v>
+        <v>1192</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>630</v>
+        <v>673</v>
       </c>
       <c r="C17">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="D17">
-        <v>1834</v>
+        <v>1867</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
         <v>674</v>
       </c>
       <c r="C18">
-        <v>1207</v>
+        <v>1227</v>
       </c>
       <c r="D18">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>534</v>
+        <v>673</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>534</v>
+        <v>673</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>519</v>
+        <v>670</v>
       </c>
       <c r="C20">
-        <v>1205</v>
+        <v>1229</v>
       </c>
       <c r="D20">
-        <v>1724</v>
+        <v>1899</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>533</v>
+        <v>684</v>
       </c>
       <c r="C21">
-        <v>1204</v>
+        <v>1231</v>
       </c>
       <c r="D21">
-        <v>1737</v>
+        <v>1915</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>570</v>
+        <v>774</v>
       </c>
       <c r="C22">
-        <v>1238</v>
+        <v>1215</v>
       </c>
       <c r="D22">
-        <v>1808</v>
+        <v>1989</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>581</v>
+        <v>777</v>
       </c>
       <c r="C23">
-        <v>1239</v>
+        <v>1208</v>
       </c>
       <c r="D23">
-        <v>1820</v>
+        <v>1985</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>723</v>
+        <v>773</v>
       </c>
       <c r="C24">
-        <v>1264</v>
+        <v>1210</v>
       </c>
       <c r="D24">
-        <v>1987</v>
+        <v>1983</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>735</v>
+        <v>777</v>
       </c>
       <c r="C25">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>2000</v>
+        <v>777</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>709</v>
+        <v>865</v>
       </c>
       <c r="C26">
-        <v>1287</v>
+        <v>1215</v>
       </c>
       <c r="D26">
-        <v>1996</v>
+        <v>2080</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>706</v>
+        <v>868</v>
       </c>
       <c r="C27">
-        <v>1291</v>
+        <v>1211</v>
       </c>
       <c r="D27">
-        <v>1997</v>
+        <v>2079</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>708</v>
+        <v>869</v>
       </c>
       <c r="C28">
-        <v>1298</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>2006</v>
+        <v>869</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>712</v>
+        <v>871</v>
       </c>
       <c r="C29">
-        <v>1296</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2008</v>
+        <v>871</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>655</v>
+        <v>559</v>
       </c>
       <c r="C30">
-        <v>1254</v>
+        <v>1193</v>
       </c>
       <c r="D30">
-        <v>1909</v>
+        <v>1752</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>658</v>
+        <v>531</v>
       </c>
       <c r="C31">
-        <v>1255</v>
+        <v>1183</v>
       </c>
       <c r="D31">
-        <v>1913</v>
+        <v>1714</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>681</v>
+        <v>528</v>
       </c>
       <c r="C32">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1947</v>
+        <v>528</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>668</v>
+        <v>531</v>
       </c>
       <c r="C33">
-        <v>1293</v>
+        <v>1187</v>
       </c>
       <c r="D33">
-        <v>1961</v>
+        <v>1718</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>410</v>
+        <v>574</v>
       </c>
       <c r="C34">
-        <v>1278</v>
+        <v>1086</v>
       </c>
       <c r="D34">
-        <v>1688</v>
+        <v>1660</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>1277</v>
+        <v>1064</v>
       </c>
       <c r="D35">
-        <v>1679</v>
+        <v>1064</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>408</v>
+        <v>558</v>
       </c>
       <c r="C36">
-        <v>1275</v>
+        <v>1059</v>
       </c>
       <c r="D36">
-        <v>1683</v>
+        <v>1617</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>407</v>
+        <v>559</v>
       </c>
       <c r="C37">
-        <v>1276</v>
+        <v>1058</v>
       </c>
       <c r="D37">
-        <v>1683</v>
+        <v>1617</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>363</v>
+        <v>502</v>
       </c>
       <c r="C38">
-        <v>1208</v>
+        <v>994</v>
       </c>
       <c r="D38">
-        <v>1571</v>
+        <v>1496</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>351</v>
+        <v>500</v>
       </c>
       <c r="C39">
-        <v>1199</v>
+        <v>988</v>
       </c>
       <c r="D39">
-        <v>1550</v>
+        <v>1488</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>348</v>
+        <v>493</v>
       </c>
       <c r="C40">
-        <v>1202</v>
+        <v>983</v>
       </c>
       <c r="D40">
-        <v>1550</v>
+        <v>1476</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>347</v>
+        <v>489</v>
       </c>
       <c r="C41">
-        <v>1203</v>
+        <v>985</v>
       </c>
       <c r="D41">
-        <v>1550</v>
+        <v>1474</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C42">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="D42">
         <v>1097</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C43">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="D43">
-        <v>1063</v>
+        <v>1080</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="C44">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="D44">
-        <v>1069</v>
+        <v>1191</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="D45">
-        <v>173</v>
+        <v>1200</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="C46">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="D46">
-        <v>1021</v>
+        <v>1172</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C48">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D48">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C49">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="D49">
-        <v>1013</v>
+        <v>1051</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="C50">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="D50">
-        <v>1028</v>
+        <v>998</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C51">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="D51">
-        <v>1012</v>
+        <v>995</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1007</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C54">
         <v>861</v>
       </c>
       <c r="D54">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>860</v>
       </c>
       <c r="D55">
-        <v>992</v>
+        <v>860</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>859</v>
       </c>
       <c r="D56">
-        <v>149</v>
+        <v>994</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="D57">
-        <v>150</v>
+        <v>990</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C58">
-        <v>829</v>
+        <v>855</v>
       </c>
       <c r="D58">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C59">
-        <v>826</v>
+        <v>852</v>
       </c>
       <c r="D59">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="D61">
-        <v>183</v>
+        <v>1015</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>265</v>
+        <v>184</v>
       </c>
       <c r="C62">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="D62">
-        <v>1082</v>
+        <v>990</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>277</v>
+        <v>178</v>
       </c>
       <c r="C63">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D63">
-        <v>1084</v>
+        <v>980</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>269</v>
+        <v>175</v>
       </c>
       <c r="C64">
-        <v>819</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1088</v>
+        <v>175</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="C65">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="D65">
-        <v>1091</v>
+        <v>994</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>416</v>
+        <v>370</v>
       </c>
       <c r="C66">
-        <v>840</v>
+        <v>1150</v>
       </c>
       <c r="D66">
-        <v>1256</v>
+        <v>1520</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>427</v>
+        <v>378</v>
       </c>
       <c r="C67">
-        <v>850</v>
+        <v>1193</v>
       </c>
       <c r="D67">
-        <v>1277</v>
+        <v>1571</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1173</v>
       </c>
       <c r="D68">
-        <v>430</v>
+        <v>1553</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="C69">
-        <v>856</v>
+        <v>1182</v>
       </c>
       <c r="D69">
-        <v>1327</v>
+        <v>1641</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>892</v>
+        <v>1090</v>
       </c>
       <c r="C70">
-        <v>1246</v>
+        <v>1323</v>
       </c>
       <c r="D70">
-        <v>2138</v>
+        <v>2413</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>905</v>
+        <v>1117</v>
       </c>
       <c r="C71">
-        <v>1259</v>
+        <v>1337</v>
       </c>
       <c r="D71">
-        <v>2164</v>
+        <v>2454</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>906</v>
+        <v>1127</v>
       </c>
       <c r="C72">
-        <v>1261</v>
+        <v>1342</v>
       </c>
       <c r="D72">
-        <v>2167</v>
+        <v>2469</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>928</v>
+        <v>1150</v>
       </c>
       <c r="C73">
-        <v>1240</v>
+        <v>1339</v>
       </c>
       <c r="D73">
-        <v>2168</v>
+        <v>2489</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>1211</v>
+        <v>1246</v>
       </c>
       <c r="C74">
-        <v>1266</v>
+        <v>1341</v>
       </c>
       <c r="D74">
-        <v>2477</v>
+        <v>2587</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="C75">
-        <v>1278</v>
+        <v>1349</v>
       </c>
       <c r="D75">
-        <v>2488</v>
+        <v>2609</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="C76">
-        <v>1284</v>
+        <v>1352</v>
       </c>
       <c r="D76">
-        <v>2509</v>
+        <v>2602</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>1223</v>
+        <v>1246</v>
       </c>
       <c r="C77">
-        <v>1280</v>
+        <v>1348</v>
       </c>
       <c r="D77">
-        <v>2503</v>
+        <v>2594</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>1256</v>
+        <v>1294</v>
       </c>
       <c r="C78">
-        <v>1278</v>
+        <v>1383</v>
       </c>
       <c r="D78">
-        <v>2534</v>
+        <v>2677</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>1272</v>
+        <v>1306</v>
       </c>
       <c r="C79">
-        <v>1290</v>
+        <v>1391</v>
       </c>
       <c r="D79">
-        <v>2562</v>
+        <v>2697</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1317</v>
       </c>
       <c r="C80">
-        <v>1277</v>
+        <v>1371</v>
       </c>
       <c r="D80">
-        <v>1277</v>
+        <v>2688</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>1271</v>
+        <v>1315</v>
       </c>
       <c r="C81">
-        <v>1278</v>
+        <v>1368</v>
       </c>
       <c r="D81">
-        <v>2549</v>
+        <v>2683</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>1240</v>
+        <v>1263</v>
       </c>
       <c r="C82">
-        <v>1256</v>
+        <v>1312</v>
       </c>
       <c r="D82">
-        <v>2496</v>
+        <v>2575</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>1237</v>
+        <v>1256</v>
       </c>
       <c r="C83">
-        <v>1267</v>
+        <v>1302</v>
       </c>
       <c r="D83">
-        <v>2504</v>
+        <v>2558</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1251</v>
       </c>
       <c r="C84">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>1266</v>
+        <v>1251</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>1239</v>
+        <v>1254</v>
       </c>
       <c r="C85">
-        <v>1265</v>
+        <v>1292</v>
       </c>
       <c r="D85">
-        <v>2504</v>
+        <v>2546</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>1141</v>
+        <v>1105</v>
       </c>
       <c r="C86">
-        <v>1251</v>
+        <v>1339</v>
       </c>
       <c r="D86">
-        <v>2392</v>
+        <v>2444</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>1136</v>
+        <v>1099</v>
       </c>
       <c r="C87">
-        <v>1253</v>
+        <v>1341</v>
       </c>
       <c r="D87">
-        <v>2389</v>
+        <v>2440</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>1132</v>
+        <v>1102</v>
       </c>
       <c r="C88">
-        <v>1268</v>
+        <v>1339</v>
       </c>
       <c r="D88">
-        <v>2400</v>
+        <v>2441</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>1155</v>
+        <v>1094</v>
       </c>
       <c r="C89">
-        <v>1365</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>2520</v>
+        <v>1094</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>1081</v>
+        <v>977</v>
       </c>
       <c r="C90">
-        <v>1316</v>
+        <v>1369</v>
       </c>
       <c r="D90">
-        <v>2397</v>
+        <v>2346</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>1085</v>
+        <v>973</v>
       </c>
       <c r="C91">
-        <v>1313</v>
+        <v>1354</v>
       </c>
       <c r="D91">
-        <v>2398</v>
+        <v>2327</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>1023</v>
+        <v>971</v>
       </c>
       <c r="C92">
-        <v>1297</v>
+        <v>1338</v>
       </c>
       <c r="D92">
-        <v>2320</v>
+        <v>2309</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>1025</v>
+        <v>977</v>
       </c>
       <c r="C93">
-        <v>1295</v>
+        <v>1347</v>
       </c>
       <c r="D93">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>773</v>
+        <v>660</v>
       </c>
       <c r="C94">
         <v>1237</v>
       </c>
       <c r="D94">
-        <v>2010</v>
+        <v>1897</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>767</v>
+        <v>650</v>
       </c>
       <c r="C95">
-        <v>1234</v>
+        <v>1222</v>
       </c>
       <c r="D95">
-        <v>2001</v>
+        <v>1872</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>766</v>
+        <v>648</v>
       </c>
       <c r="C96">
-        <v>1233</v>
+        <v>1213</v>
       </c>
       <c r="D96">
-        <v>1999</v>
+        <v>1861</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>763</v>
+        <v>650</v>
       </c>
       <c r="C97">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="D97">
-        <v>1994</v>
+        <v>1865</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>654</v>
+        <v>544</v>
       </c>
       <c r="C98">
-        <v>1203</v>
+        <v>1173</v>
       </c>
       <c r="D98">
-        <v>1857</v>
+        <v>1717</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>651</v>
+        <v>542</v>
       </c>
       <c r="C99">
-        <v>1202</v>
+        <v>1168</v>
       </c>
       <c r="D99">
-        <v>1853</v>
+        <v>1710</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
-        <v>646</v>
+        <v>546</v>
       </c>
       <c r="C100">
-        <v>1199</v>
+        <v>1167</v>
       </c>
       <c r="D100">
-        <v>1845</v>
+        <v>1713</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>649</v>
+        <v>553</v>
       </c>
       <c r="C101">
-        <v>1208</v>
+        <v>1162</v>
       </c>
       <c r="D101">
-        <v>1857</v>
+        <v>1715</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C102">
-        <v>1220</v>
+        <v>1080</v>
       </c>
       <c r="D102">
-        <v>1889</v>
+        <v>1743</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="C103">
-        <v>1228</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>1228</v>
+        <v>660</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="C104">
-        <v>1227</v>
+        <v>1090</v>
       </c>
       <c r="D104">
-        <v>1227</v>
+        <v>1955</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
-        <v>671</v>
+        <v>926</v>
       </c>
       <c r="C106">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>1896</v>
+        <v>926</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
-        <v>666</v>
+        <v>956</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="D108">
-        <v>666</v>
+        <v>2091</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
-        <v>668</v>
+        <v>976</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="D109">
-        <v>668</v>
+        <v>2122</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>673</v>
+        <v>959</v>
       </c>
       <c r="C110">
-        <v>1203</v>
+        <v>1307</v>
       </c>
       <c r="D110">
-        <v>1876</v>
+        <v>2266</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1193</v>
+        <v>1315</v>
       </c>
       <c r="D111">
-        <v>1865</v>
+        <v>1315</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>957</v>
       </c>
       <c r="C112">
-        <v>1192</v>
+        <v>1314</v>
       </c>
       <c r="D112">
-        <v>1192</v>
+        <v>2271</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>673</v>
+        <v>955</v>
       </c>
       <c r="C113">
-        <v>1194</v>
+        <v>1309</v>
       </c>
       <c r="D113">
-        <v>1867</v>
+        <v>2264</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>674</v>
+        <v>966</v>
       </c>
       <c r="C114">
-        <v>1227</v>
+        <v>1290</v>
       </c>
       <c r="D114">
-        <v>1901</v>
+        <v>2256</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>673</v>
+        <v>978</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="D115">
-        <v>673</v>
+        <v>2128</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>670</v>
+        <v>839</v>
       </c>
       <c r="C116">
-        <v>1229</v>
+        <v>1143</v>
       </c>
       <c r="D116">
-        <v>1899</v>
+        <v>1982</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>684</v>
+        <v>706</v>
       </c>
       <c r="C117">
-        <v>1231</v>
+        <v>1128</v>
       </c>
       <c r="D117">
-        <v>1915</v>
+        <v>1834</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>774</v>
+        <v>746</v>
       </c>
       <c r="C118">
-        <v>1215</v>
+        <v>1116</v>
       </c>
       <c r="D118">
-        <v>1989</v>
+        <v>1862</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="C119">
-        <v>1208</v>
+        <v>1113</v>
       </c>
       <c r="D119">
-        <v>1985</v>
+        <v>1854</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>773</v>
+        <v>745</v>
       </c>
       <c r="C120">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="D120">
-        <v>1983</v>
+        <v>1846</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D121">
-        <v>777</v>
+        <v>1852</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>865</v>
+        <v>696</v>
       </c>
       <c r="C122">
-        <v>1215</v>
+        <v>1065</v>
       </c>
       <c r="D122">
-        <v>2080</v>
+        <v>1761</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>868</v>
+        <v>695</v>
       </c>
       <c r="C123">
-        <v>1211</v>
+        <v>1058</v>
       </c>
       <c r="D123">
-        <v>2079</v>
+        <v>1753</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1075</v>
       </c>
       <c r="D124">
-        <v>869</v>
+        <v>1951</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="D125">
-        <v>871</v>
+        <v>1963</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>559</v>
+        <v>877</v>
       </c>
       <c r="C126">
-        <v>1193</v>
+        <v>1072</v>
       </c>
       <c r="D126">
-        <v>1752</v>
+        <v>1949</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>531</v>
+        <v>864</v>
       </c>
       <c r="C127">
-        <v>1183</v>
+        <v>1069</v>
       </c>
       <c r="D127">
-        <v>1714</v>
+        <v>1933</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>528</v>
+        <v>703</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="D128">
-        <v>528</v>
+        <v>1754</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>531</v>
+        <v>668</v>
       </c>
       <c r="C129">
-        <v>1187</v>
+        <v>1049</v>
       </c>
       <c r="D129">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>574</v>
+        <v>653</v>
       </c>
       <c r="C130">
-        <v>1086</v>
+        <v>1024</v>
       </c>
       <c r="D130">
-        <v>1660</v>
+        <v>1677</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="C131">
-        <v>1064</v>
+        <v>1020</v>
       </c>
       <c r="D131">
-        <v>1064</v>
+        <v>1665</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1626</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>654</v>
+        <v>544</v>
       </c>
       <c r="C2">
-        <v>1203</v>
+        <v>1173</v>
       </c>
       <c r="D2">
-        <v>1857</v>
+        <v>1717</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>651</v>
+        <v>542</v>
       </c>
       <c r="C3">
-        <v>1202</v>
+        <v>1168</v>
       </c>
       <c r="D3">
-        <v>1853</v>
+        <v>1710</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
-        <v>646</v>
+        <v>546</v>
       </c>
       <c r="C4">
-        <v>1199</v>
+        <v>1167</v>
       </c>
       <c r="D4">
-        <v>1845</v>
+        <v>1713</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>649</v>
+        <v>553</v>
       </c>
       <c r="C5">
-        <v>1208</v>
+        <v>1162</v>
       </c>
       <c r="D5">
-        <v>1857</v>
+        <v>1715</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C6">
-        <v>1220</v>
+        <v>1080</v>
       </c>
       <c r="D6">
-        <v>1889</v>
+        <v>1743</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="C7">
-        <v>1228</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1228</v>
+        <v>660</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="C8">
-        <v>1227</v>
+        <v>1090</v>
       </c>
       <c r="D8">
-        <v>1227</v>
+        <v>1955</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>671</v>
+        <v>926</v>
       </c>
       <c r="C10">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1896</v>
+        <v>926</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2050</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>666</v>
+        <v>956</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="D12">
-        <v>666</v>
+        <v>2091</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>668</v>
+        <v>976</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="D13">
-        <v>668</v>
+        <v>2122</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>673</v>
+        <v>959</v>
       </c>
       <c r="C14">
-        <v>1203</v>
+        <v>1307</v>
       </c>
       <c r="D14">
-        <v>1876</v>
+        <v>2266</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>1193</v>
+        <v>1315</v>
       </c>
       <c r="D15">
-        <v>1865</v>
+        <v>1315</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>957</v>
       </c>
       <c r="C16">
-        <v>1192</v>
+        <v>1314</v>
       </c>
       <c r="D16">
-        <v>1192</v>
+        <v>2271</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>673</v>
+        <v>955</v>
       </c>
       <c r="C17">
-        <v>1194</v>
+        <v>1309</v>
       </c>
       <c r="D17">
-        <v>1867</v>
+        <v>2264</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>674</v>
+        <v>966</v>
       </c>
       <c r="C18">
-        <v>1227</v>
+        <v>1290</v>
       </c>
       <c r="D18">
-        <v>1901</v>
+        <v>2256</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>673</v>
+        <v>978</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1150</v>
       </c>
       <c r="D19">
-        <v>673</v>
+        <v>2128</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>670</v>
+        <v>839</v>
       </c>
       <c r="C20">
-        <v>1229</v>
+        <v>1143</v>
       </c>
       <c r="D20">
-        <v>1899</v>
+        <v>1982</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>684</v>
+        <v>706</v>
       </c>
       <c r="C21">
-        <v>1231</v>
+        <v>1128</v>
       </c>
       <c r="D21">
-        <v>1915</v>
+        <v>1834</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>774</v>
+        <v>746</v>
       </c>
       <c r="C22">
-        <v>1215</v>
+        <v>1116</v>
       </c>
       <c r="D22">
-        <v>1989</v>
+        <v>1862</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>777</v>
+        <v>741</v>
       </c>
       <c r="C23">
-        <v>1208</v>
+        <v>1113</v>
       </c>
       <c r="D23">
-        <v>1985</v>
+        <v>1854</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>773</v>
+        <v>745</v>
       </c>
       <c r="C24">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="D24">
-        <v>1983</v>
+        <v>1846</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="D25">
-        <v>777</v>
+        <v>1852</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>865</v>
+        <v>696</v>
       </c>
       <c r="C26">
-        <v>1215</v>
+        <v>1065</v>
       </c>
       <c r="D26">
-        <v>2080</v>
+        <v>1761</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>868</v>
+        <v>695</v>
       </c>
       <c r="C27">
-        <v>1211</v>
+        <v>1058</v>
       </c>
       <c r="D27">
-        <v>2079</v>
+        <v>1753</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1075</v>
       </c>
       <c r="D28">
-        <v>869</v>
+        <v>1951</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="D29">
-        <v>871</v>
+        <v>1963</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>559</v>
+        <v>877</v>
       </c>
       <c r="C30">
-        <v>1193</v>
+        <v>1072</v>
       </c>
       <c r="D30">
-        <v>1752</v>
+        <v>1949</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>531</v>
+        <v>864</v>
       </c>
       <c r="C31">
-        <v>1183</v>
+        <v>1069</v>
       </c>
       <c r="D31">
-        <v>1714</v>
+        <v>1933</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>528</v>
+        <v>703</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="D32">
-        <v>528</v>
+        <v>1754</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>531</v>
+        <v>668</v>
       </c>
       <c r="C33">
-        <v>1187</v>
+        <v>1049</v>
       </c>
       <c r="D33">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>574</v>
+        <v>653</v>
       </c>
       <c r="C34">
-        <v>1086</v>
+        <v>1024</v>
       </c>
       <c r="D34">
-        <v>1660</v>
+        <v>1677</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="C35">
-        <v>1064</v>
+        <v>1020</v>
       </c>
       <c r="D35">
-        <v>1064</v>
+        <v>1665</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>558</v>
+        <v>639</v>
       </c>
       <c r="C36">
-        <v>1059</v>
+        <v>987</v>
       </c>
       <c r="D36">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>559</v>
+        <v>640</v>
       </c>
       <c r="C37">
-        <v>1058</v>
+        <v>981</v>
       </c>
       <c r="D37">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>502</v>
+        <v>557</v>
       </c>
       <c r="C38">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="D38">
-        <v>1496</v>
+        <v>1566</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>500</v>
+        <v>553</v>
       </c>
       <c r="C39">
-        <v>988</v>
+        <v>1007</v>
       </c>
       <c r="D39">
-        <v>1488</v>
+        <v>1560</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>493</v>
+        <v>548</v>
       </c>
       <c r="C40">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="D40">
-        <v>1476</v>
+        <v>1558</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>489</v>
+        <v>549</v>
       </c>
       <c r="C41">
-        <v>985</v>
+        <v>896</v>
       </c>
       <c r="D41">
-        <v>1474</v>
+        <v>1445</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="C42">
-        <v>928</v>
+        <v>956</v>
       </c>
       <c r="D42">
-        <v>1097</v>
+        <v>1168</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C43">
-        <v>900</v>
+        <v>969</v>
       </c>
       <c r="D43">
-        <v>1080</v>
+        <v>1156</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="C44">
-        <v>917</v>
+        <v>966</v>
       </c>
       <c r="D44">
-        <v>1191</v>
+        <v>1168</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>279</v>
+        <v>204</v>
       </c>
       <c r="C45">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="D45">
-        <v>1200</v>
+        <v>1112</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>275</v>
+        <v>148</v>
       </c>
       <c r="C46">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="D46">
-        <v>1172</v>
+        <v>1072</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>265</v>
+        <v>145</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="D47">
-        <v>265</v>
+        <v>1061</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C48">
-        <v>878</v>
+        <v>959</v>
       </c>
       <c r="D48">
-        <v>1047</v>
+        <v>1106</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>876</v>
+        <v>960</v>
       </c>
       <c r="D49">
-        <v>1051</v>
+        <v>960</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C50">
-        <v>866</v>
+        <v>952</v>
       </c>
       <c r="D50">
-        <v>998</v>
+        <v>1094</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C51">
-        <v>864</v>
+        <v>954</v>
       </c>
       <c r="D51">
-        <v>995</v>
+        <v>1097</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>955</v>
       </c>
       <c r="D53">
-        <v>130</v>
+        <v>1097</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C54">
-        <v>861</v>
+        <v>947</v>
       </c>
       <c r="D54">
-        <v>984</v>
+        <v>1068</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C55">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>860</v>
+        <v>120</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C56">
-        <v>859</v>
+        <v>946</v>
       </c>
       <c r="D56">
-        <v>994</v>
+        <v>1076</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C57">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>990</v>
+        <v>138</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C58">
-        <v>855</v>
+        <v>911</v>
       </c>
       <c r="D58">
-        <v>1011</v>
+        <v>1093</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="C59">
-        <v>852</v>
+        <v>913</v>
       </c>
       <c r="D59">
-        <v>1006</v>
+        <v>1119</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="D60">
-        <v>160</v>
+        <v>1100</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C61">
-        <v>850</v>
+        <v>933</v>
       </c>
       <c r="D61">
-        <v>1015</v>
+        <v>1110</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="C62">
-        <v>806</v>
+        <v>957</v>
       </c>
       <c r="D62">
-        <v>990</v>
+        <v>1202</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C63">
-        <v>802</v>
+        <v>971</v>
       </c>
       <c r="D63">
-        <v>980</v>
+        <v>1220</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>175</v>
+        <v>253</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="D64">
-        <v>175</v>
+        <v>1221</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="C65">
-        <v>813</v>
+        <v>983</v>
       </c>
       <c r="D65">
-        <v>994</v>
+        <v>1242</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>370</v>
+        <v>419</v>
       </c>
       <c r="C66">
-        <v>1150</v>
+        <v>1282</v>
       </c>
       <c r="D66">
-        <v>1520</v>
+        <v>1701</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="C67">
-        <v>1193</v>
+        <v>1292</v>
       </c>
       <c r="D67">
-        <v>1571</v>
+        <v>1726</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>380</v>
+        <v>539</v>
       </c>
       <c r="C68">
-        <v>1173</v>
+        <v>1295</v>
       </c>
       <c r="D68">
-        <v>1553</v>
+        <v>1834</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>459</v>
+        <v>641</v>
       </c>
       <c r="C69">
-        <v>1182</v>
+        <v>1294</v>
       </c>
       <c r="D69">
-        <v>1641</v>
+        <v>1935</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>1090</v>
+        <v>1159</v>
       </c>
       <c r="C70">
-        <v>1323</v>
+        <v>1350</v>
       </c>
       <c r="D70">
-        <v>2413</v>
+        <v>2509</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>1117</v>
+        <v>1186</v>
       </c>
       <c r="C71">
-        <v>1337</v>
+        <v>1360</v>
       </c>
       <c r="D71">
-        <v>2454</v>
+        <v>2546</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>1127</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1342</v>
+        <v>1358</v>
       </c>
       <c r="D72">
-        <v>2469</v>
+        <v>1358</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1339</v>
+        <v>1274</v>
       </c>
       <c r="D73">
-        <v>2489</v>
+        <v>1274</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>1246</v>
+        <v>1328</v>
       </c>
       <c r="C74">
-        <v>1341</v>
+        <v>1327</v>
       </c>
       <c r="D74">
-        <v>2587</v>
+        <v>2655</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>1260</v>
+        <v>1353</v>
       </c>
       <c r="C75">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="D75">
-        <v>2609</v>
+        <v>2697</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>1250</v>
+        <v>1356</v>
       </c>
       <c r="C76">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D76">
-        <v>2602</v>
+        <v>2706</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>1246</v>
+        <v>1364</v>
       </c>
       <c r="C77">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D77">
-        <v>2594</v>
+        <v>2710</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>1294</v>
+        <v>1428</v>
       </c>
       <c r="C78">
-        <v>1383</v>
+        <v>1333</v>
       </c>
       <c r="D78">
-        <v>2677</v>
+        <v>2761</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>1306</v>
+        <v>1443</v>
       </c>
       <c r="C79">
-        <v>1391</v>
+        <v>1341</v>
       </c>
       <c r="D79">
-        <v>2697</v>
+        <v>2784</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>1317</v>
+        <v>1441</v>
       </c>
       <c r="C80">
-        <v>1371</v>
+        <v>1340</v>
       </c>
       <c r="D80">
-        <v>2688</v>
+        <v>2781</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>1315</v>
+        <v>1448</v>
       </c>
       <c r="C81">
-        <v>1368</v>
+        <v>1325</v>
       </c>
       <c r="D81">
-        <v>2683</v>
+        <v>2773</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>1263</v>
+        <v>1370</v>
       </c>
       <c r="C82">
-        <v>1312</v>
+        <v>1336</v>
       </c>
       <c r="D82">
-        <v>2575</v>
+        <v>2706</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>1256</v>
+        <v>1401</v>
       </c>
       <c r="C83">
-        <v>1302</v>
+        <v>1354</v>
       </c>
       <c r="D83">
-        <v>2558</v>
+        <v>2755</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>1251</v>
+        <v>1408</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1341</v>
       </c>
       <c r="D84">
-        <v>1251</v>
+        <v>2749</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>1254</v>
+        <v>1406</v>
       </c>
       <c r="C85">
-        <v>1292</v>
+        <v>1343</v>
       </c>
       <c r="D85">
-        <v>2546</v>
+        <v>2749</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>1105</v>
+        <v>1335</v>
       </c>
       <c r="C86">
-        <v>1339</v>
+        <v>1324</v>
       </c>
       <c r="D86">
-        <v>2444</v>
+        <v>2659</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>1099</v>
+        <v>1312</v>
       </c>
       <c r="C87">
-        <v>1341</v>
+        <v>1320</v>
       </c>
       <c r="D87">
-        <v>2440</v>
+        <v>2632</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>1102</v>
+        <v>1305</v>
       </c>
       <c r="C88">
-        <v>1339</v>
+        <v>1274</v>
       </c>
       <c r="D88">
-        <v>2441</v>
+        <v>2579</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>1094</v>
+        <v>1309</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="D89">
-        <v>1094</v>
+        <v>2581</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>977</v>
+        <v>1060</v>
       </c>
       <c r="C90">
-        <v>1369</v>
+        <v>1240</v>
       </c>
       <c r="D90">
-        <v>2346</v>
+        <v>2300</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>973</v>
+        <v>1044</v>
       </c>
       <c r="C91">
-        <v>1354</v>
+        <v>1237</v>
       </c>
       <c r="D91">
-        <v>2327</v>
+        <v>2281</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>971</v>
+        <v>1034</v>
       </c>
       <c r="C92">
-        <v>1338</v>
+        <v>1280</v>
       </c>
       <c r="D92">
-        <v>2309</v>
+        <v>2314</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>977</v>
+        <v>1029</v>
       </c>
       <c r="C93">
-        <v>1347</v>
+        <v>1267</v>
       </c>
       <c r="D93">
-        <v>2324</v>
+        <v>2296</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
         <v>660</v>
       </c>
       <c r="C94">
-        <v>1237</v>
+        <v>1189</v>
       </c>
       <c r="D94">
-        <v>1897</v>
+        <v>1849</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C95">
-        <v>1222</v>
+        <v>1195</v>
       </c>
       <c r="D95">
-        <v>1872</v>
+        <v>1842</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C96">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D96">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="C97">
-        <v>1215</v>
+        <v>1235</v>
       </c>
       <c r="D97">
-        <v>1865</v>
+        <v>1896</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>544</v>
+        <v>624</v>
       </c>
       <c r="C98">
-        <v>1173</v>
+        <v>1097</v>
       </c>
       <c r="D98">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
-        <v>542</v>
+        <v>625</v>
       </c>
       <c r="C99">
-        <v>1168</v>
+        <v>1059</v>
       </c>
       <c r="D99">
-        <v>1710</v>
+        <v>1684</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
-        <v>546</v>
+        <v>630</v>
       </c>
       <c r="C100">
-        <v>1167</v>
+        <v>1058</v>
       </c>
       <c r="D100">
-        <v>1713</v>
+        <v>1688</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
-        <v>553</v>
+        <v>623</v>
       </c>
       <c r="C101">
-        <v>1162</v>
+        <v>1057</v>
       </c>
       <c r="D101">
-        <v>1715</v>
+        <v>1680</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="D102">
-        <v>1743</v>
+        <v>1073</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="D103">
-        <v>660</v>
+        <v>1070</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
-        <v>865</v>
+        <v>622</v>
       </c>
       <c r="C104">
-        <v>1090</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1955</v>
+        <v>622</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
-        <v>940</v>
+        <v>603</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="D105">
-        <v>940</v>
+        <v>1672</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
-        <v>926</v>
+        <v>585</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1046</v>
       </c>
       <c r="D106">
-        <v>926</v>
+        <v>1631</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
-        <v>950</v>
+        <v>577</v>
       </c>
       <c r="C107">
-        <v>1100</v>
+        <v>1041</v>
       </c>
       <c r="D107">
-        <v>2050</v>
+        <v>1618</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
-        <v>956</v>
+        <v>578</v>
       </c>
       <c r="C108">
-        <v>1135</v>
+        <v>1042</v>
       </c>
       <c r="D108">
-        <v>2091</v>
+        <v>1620</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
-        <v>976</v>
+        <v>601</v>
       </c>
       <c r="C109">
-        <v>1146</v>
+        <v>1043</v>
       </c>
       <c r="D109">
-        <v>2122</v>
+        <v>1644</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>959</v>
+        <v>620</v>
       </c>
       <c r="C110">
-        <v>1307</v>
+        <v>1046</v>
       </c>
       <c r="D110">
-        <v>2266</v>
+        <v>1666</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="C111">
-        <v>1315</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1315</v>
+        <v>608</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>957</v>
+        <v>602</v>
       </c>
       <c r="C112">
-        <v>1314</v>
+        <v>1045</v>
       </c>
       <c r="D112">
-        <v>2271</v>
+        <v>1647</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>955</v>
+        <v>617</v>
       </c>
       <c r="C113">
-        <v>1309</v>
+        <v>1046</v>
       </c>
       <c r="D113">
-        <v>2264</v>
+        <v>1663</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>966</v>
+        <v>643</v>
       </c>
       <c r="C114">
-        <v>1290</v>
+        <v>1037</v>
       </c>
       <c r="D114">
-        <v>2256</v>
+        <v>1680</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>978</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>2128</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>839</v>
+        <v>641</v>
       </c>
       <c r="C116">
-        <v>1143</v>
+        <v>1036</v>
       </c>
       <c r="D116">
-        <v>1982</v>
+        <v>1677</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>706</v>
+        <v>644</v>
       </c>
       <c r="C117">
-        <v>1128</v>
+        <v>1037</v>
       </c>
       <c r="D117">
-        <v>1834</v>
+        <v>1681</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>746</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1116</v>
+        <v>1041</v>
       </c>
       <c r="D118">
-        <v>1862</v>
+        <v>1041</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>741</v>
+        <v>635</v>
       </c>
       <c r="C119">
-        <v>1113</v>
+        <v>1037</v>
       </c>
       <c r="D119">
-        <v>1854</v>
+        <v>1672</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>745</v>
+        <v>638</v>
       </c>
       <c r="C120">
-        <v>1101</v>
+        <v>1034</v>
       </c>
       <c r="D120">
-        <v>1846</v>
+        <v>1672</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>752</v>
+        <v>642</v>
       </c>
       <c r="C121">
-        <v>1100</v>
+        <v>1029</v>
       </c>
       <c r="D121">
-        <v>1852</v>
+        <v>1671</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C122">
-        <v>1065</v>
+        <v>1035</v>
       </c>
       <c r="D122">
-        <v>1761</v>
+        <v>1727</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C123">
-        <v>1058</v>
+        <v>1041</v>
       </c>
       <c r="D123">
-        <v>1753</v>
+        <v>1740</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>876</v>
+        <v>698</v>
       </c>
       <c r="C124">
-        <v>1075</v>
+        <v>1048</v>
       </c>
       <c r="D124">
-        <v>1951</v>
+        <v>1746</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>885</v>
+        <v>692</v>
       </c>
       <c r="C125">
-        <v>1078</v>
+        <v>1047</v>
       </c>
       <c r="D125">
-        <v>1963</v>
+        <v>1739</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>877</v>
+        <v>653</v>
       </c>
       <c r="C126">
-        <v>1072</v>
+        <v>1027</v>
       </c>
       <c r="D126">
-        <v>1949</v>
+        <v>1680</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>864</v>
+        <v>645</v>
       </c>
       <c r="C127">
-        <v>1069</v>
+        <v>1023</v>
       </c>
       <c r="D127">
-        <v>1933</v>
+        <v>1668</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>703</v>
+        <v>643</v>
       </c>
       <c r="C128">
-        <v>1051</v>
+        <v>1034</v>
       </c>
       <c r="D128">
-        <v>1754</v>
+        <v>1677</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="C129">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="D129">
-        <v>1717</v>
+        <v>1672</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>653</v>
+        <v>508</v>
       </c>
       <c r="C130">
-        <v>1024</v>
+        <v>1044</v>
       </c>
       <c r="D130">
-        <v>1677</v>
+        <v>1552</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>645</v>
+        <v>491</v>
       </c>
       <c r="C131">
-        <v>1020</v>
+        <v>1034</v>
       </c>
       <c r="D131">
-        <v>1665</v>
+        <v>1525</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>639</v>
+        <v>488</v>
       </c>
       <c r="C132">
-        <v>987</v>
+        <v>1039</v>
       </c>
       <c r="D132">
-        <v>1626</v>
+        <v>1527</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>03.06.202694</t>
-  </si>
-  <si>
-    <t>03.06.202695</t>
-  </si>
-  <si>
-    <t>03.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>11.06.202694</t>
+  </si>
+  <si>
+    <t>11.06.202695</t>
+  </si>
+  <si>
+    <t>11.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
-        <v>711</v>
+        <v>500</v>
       </c>
       <c r="C2">
-        <v>923</v>
+        <v>1060</v>
       </c>
       <c r="D2">
-        <v>1634</v>
+        <v>1560</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
-        <v>667</v>
+        <v>503</v>
       </c>
       <c r="C3">
-        <v>921</v>
+        <v>1044</v>
       </c>
       <c r="D3">
-        <v>1588</v>
+        <v>1547</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
-        <v>636</v>
+        <v>502</v>
       </c>
       <c r="C4">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1556</v>
+        <v>502</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
-        <v>638</v>
+        <v>499</v>
       </c>
       <c r="C5">
-        <v>921</v>
+        <v>1041</v>
       </c>
       <c r="D5">
-        <v>1559</v>
+        <v>1540</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
-        <v>659</v>
+        <v>486</v>
       </c>
       <c r="C6">
-        <v>908</v>
+        <v>1045</v>
       </c>
       <c r="D6">
-        <v>1567</v>
+        <v>1531</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
-        <v>650</v>
+        <v>477</v>
       </c>
       <c r="C7">
-        <v>907</v>
+        <v>1043</v>
       </c>
       <c r="D7">
-        <v>1557</v>
+        <v>1520</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
-        <v>647</v>
+        <v>478</v>
       </c>
       <c r="C8">
-        <v>908</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1555</v>
+        <v>478</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
-        <v>635</v>
+        <v>475</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>635</v>
+        <v>475</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
-        <v>650</v>
+        <v>465</v>
       </c>
       <c r="C10">
-        <v>894</v>
+        <v>1033</v>
       </c>
       <c r="D10">
-        <v>1544</v>
+        <v>1498</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
-        <v>664</v>
+        <v>468</v>
       </c>
       <c r="C11">
-        <v>890</v>
+        <v>1032</v>
       </c>
       <c r="D11">
-        <v>1554</v>
+        <v>1500</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
-        <v>642</v>
+        <v>469</v>
       </c>
       <c r="C12">
-        <v>891</v>
+        <v>1034</v>
       </c>
       <c r="D12">
-        <v>1533</v>
+        <v>1503</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
-        <v>640</v>
+        <v>468</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="D13">
-        <v>640</v>
+        <v>1501</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>643</v>
+        <v>465</v>
       </c>
       <c r="C14">
-        <v>895</v>
+        <v>1032</v>
       </c>
       <c r="D14">
-        <v>1538</v>
+        <v>1497</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>655</v>
+        <v>470</v>
       </c>
       <c r="C15">
-        <v>894</v>
+        <v>1034</v>
       </c>
       <c r="D15">
-        <v>1549</v>
+        <v>1504</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>640</v>
+        <v>468</v>
       </c>
       <c r="C16">
-        <v>892</v>
+        <v>1033</v>
       </c>
       <c r="D16">
-        <v>1532</v>
+        <v>1501</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>634</v>
+        <v>467</v>
       </c>
       <c r="C17">
-        <v>891</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1525</v>
+        <v>467</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>667</v>
+        <v>475</v>
       </c>
       <c r="C18">
-        <v>894</v>
+        <v>1042</v>
       </c>
       <c r="D18">
-        <v>1561</v>
+        <v>1517</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>668</v>
+        <v>473</v>
       </c>
       <c r="C19">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1563</v>
+        <v>473</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="C20">
-        <v>894</v>
+        <v>1043</v>
       </c>
       <c r="D20">
-        <v>894</v>
+        <v>1514</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>695</v>
+        <v>485</v>
       </c>
       <c r="C21">
-        <v>895</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1590</v>
+        <v>485</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>687</v>
+        <v>510</v>
       </c>
       <c r="C22">
-        <v>915</v>
+        <v>1049</v>
       </c>
       <c r="D22">
-        <v>1602</v>
+        <v>1559</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>683</v>
+        <v>516</v>
       </c>
       <c r="C23">
-        <v>916</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1599</v>
+        <v>516</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>679</v>
+        <v>514</v>
       </c>
       <c r="C24">
-        <v>917</v>
+        <v>1046</v>
       </c>
       <c r="D24">
-        <v>1596</v>
+        <v>1560</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>686</v>
+        <v>520</v>
       </c>
       <c r="C25">
-        <v>915</v>
+        <v>1048</v>
       </c>
       <c r="D25">
-        <v>1601</v>
+        <v>1568</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>699</v>
+        <v>593</v>
       </c>
       <c r="C26">
-        <v>937</v>
+        <v>1065</v>
       </c>
       <c r="D26">
-        <v>1636</v>
+        <v>1658</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>749</v>
+        <v>594</v>
       </c>
       <c r="C27">
-        <v>938</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1687</v>
+        <v>594</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>781</v>
+        <v>591</v>
       </c>
       <c r="C28">
-        <v>936</v>
+        <v>1058</v>
       </c>
       <c r="D28">
-        <v>1717</v>
+        <v>1649</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>780</v>
+        <v>595</v>
       </c>
       <c r="C29">
-        <v>929</v>
+        <v>1064</v>
       </c>
       <c r="D29">
-        <v>1709</v>
+        <v>1659</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>779</v>
+        <v>630</v>
       </c>
       <c r="C30">
-        <v>922</v>
+        <v>1036</v>
       </c>
       <c r="D30">
-        <v>1701</v>
+        <v>1666</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>786</v>
+        <v>622</v>
       </c>
       <c r="C31">
-        <v>923</v>
+        <v>1030</v>
       </c>
       <c r="D31">
-        <v>1709</v>
+        <v>1652</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>782</v>
+        <v>624</v>
       </c>
       <c r="C32">
-        <v>926</v>
+        <v>1031</v>
       </c>
       <c r="D32">
-        <v>1708</v>
+        <v>1655</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>777</v>
+        <v>619</v>
       </c>
       <c r="C33">
-        <v>923</v>
+        <v>1030</v>
       </c>
       <c r="D33">
-        <v>1700</v>
+        <v>1649</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
-        <v>732</v>
+        <v>589</v>
       </c>
       <c r="C34">
-        <v>942</v>
+        <v>1038</v>
       </c>
       <c r="D34">
-        <v>1674</v>
+        <v>1627</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>728</v>
+        <v>570</v>
       </c>
       <c r="C35">
-        <v>943</v>
+        <v>1035</v>
       </c>
       <c r="D35">
-        <v>1671</v>
+        <v>1605</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>713</v>
+        <v>581</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="D36">
-        <v>713</v>
+        <v>1612</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>857</v>
+        <v>1021</v>
       </c>
       <c r="D37">
-        <v>1562</v>
+        <v>1021</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>633</v>
+        <v>586</v>
       </c>
       <c r="C38">
-        <v>875</v>
+        <v>995</v>
       </c>
       <c r="D38">
-        <v>1508</v>
+        <v>1581</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>611</v>
+        <v>579</v>
       </c>
       <c r="C39">
-        <v>862</v>
+        <v>986</v>
       </c>
       <c r="D39">
-        <v>1473</v>
+        <v>1565</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
-        <v>537</v>
+        <v>673</v>
       </c>
       <c r="C40">
-        <v>872</v>
+        <v>993</v>
       </c>
       <c r="D40">
-        <v>1409</v>
+        <v>1666</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>502</v>
+        <v>660</v>
       </c>
       <c r="C41">
-        <v>875</v>
+        <v>991</v>
       </c>
       <c r="D41">
-        <v>1377</v>
+        <v>1651</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="C42">
-        <v>743</v>
+        <v>943</v>
       </c>
       <c r="D42">
-        <v>1208</v>
+        <v>1456</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>446</v>
+        <v>508</v>
       </c>
       <c r="C43">
-        <v>758</v>
+        <v>934</v>
       </c>
       <c r="D43">
-        <v>1204</v>
+        <v>1442</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C44">
-        <v>764</v>
+        <v>938</v>
       </c>
       <c r="D44">
-        <v>1263</v>
+        <v>1445</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C45">
-        <v>762</v>
+        <v>941</v>
       </c>
       <c r="D45">
-        <v>1258</v>
+        <v>1446</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>453</v>
+        <v>138</v>
       </c>
       <c r="C46">
-        <v>755</v>
+        <v>812</v>
       </c>
       <c r="D46">
-        <v>1208</v>
+        <v>950</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>472</v>
+        <v>128</v>
       </c>
       <c r="C47">
-        <v>753</v>
+        <v>803</v>
       </c>
       <c r="D47">
-        <v>1225</v>
+        <v>931</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>502</v>
+        <v>131</v>
       </c>
       <c r="C48">
-        <v>754</v>
+        <v>806</v>
       </c>
       <c r="D48">
-        <v>1256</v>
+        <v>937</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>590</v>
+        <v>126</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>590</v>
+        <v>126</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>589</v>
+        <v>178</v>
       </c>
       <c r="C50">
-        <v>746</v>
+        <v>799</v>
       </c>
       <c r="D50">
-        <v>1335</v>
+        <v>977</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>654</v>
+        <v>173</v>
       </c>
       <c r="C51">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D51">
-        <v>1448</v>
+        <v>966</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>615</v>
+        <v>130</v>
       </c>
       <c r="C52">
-        <v>824</v>
+        <v>792</v>
       </c>
       <c r="D52">
-        <v>1439</v>
+        <v>922</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>618</v>
+        <v>137</v>
       </c>
       <c r="C53">
-        <v>827</v>
+        <v>745</v>
       </c>
       <c r="D53">
-        <v>1445</v>
+        <v>882</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>634</v>
+        <v>175</v>
       </c>
       <c r="C54">
-        <v>812</v>
+        <v>767</v>
       </c>
       <c r="D54">
-        <v>1446</v>
+        <v>942</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>803</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>1446</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>654</v>
+        <v>173</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>752</v>
       </c>
       <c r="D56">
-        <v>654</v>
+        <v>925</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>660</v>
+        <v>119</v>
       </c>
       <c r="C57">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="D57">
-        <v>1458</v>
+        <v>929</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>673</v>
+        <v>158</v>
       </c>
       <c r="C58">
         <v>820</v>
       </c>
       <c r="D58">
-        <v>1493</v>
+        <v>978</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>671</v>
+        <v>130</v>
       </c>
       <c r="C59">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D59">
-        <v>1493</v>
+        <v>955</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="C60">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D60">
-        <v>821</v>
+        <v>980</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>669</v>
+        <v>184</v>
       </c>
       <c r="C61">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D61">
-        <v>1491</v>
+        <v>1004</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
-        <v>729</v>
+        <v>424</v>
       </c>
       <c r="C62">
-        <v>811</v>
+        <v>973</v>
       </c>
       <c r="D62">
-        <v>1540</v>
+        <v>1397</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>744</v>
+        <v>555</v>
       </c>
       <c r="C63">
-        <v>807</v>
+        <v>1009</v>
       </c>
       <c r="D63">
-        <v>1551</v>
+        <v>1564</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>754</v>
+        <v>567</v>
       </c>
       <c r="C64">
-        <v>811</v>
+        <v>1012</v>
       </c>
       <c r="D64">
-        <v>1565</v>
+        <v>1579</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="C65">
-        <v>825</v>
+        <v>1054</v>
       </c>
       <c r="D65">
-        <v>1592</v>
+        <v>1800</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>715</v>
+        <v>785</v>
       </c>
       <c r="C66">
-        <v>928</v>
+        <v>1049</v>
       </c>
       <c r="D66">
-        <v>1643</v>
+        <v>1834</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>719</v>
+        <v>789</v>
       </c>
       <c r="C67">
-        <v>936</v>
+        <v>1050</v>
       </c>
       <c r="D67">
-        <v>1655</v>
+        <v>1839</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="C68">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>937</v>
+        <v>784</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C69">
-        <v>940</v>
+        <v>1017</v>
       </c>
       <c r="D69">
-        <v>1652</v>
+        <v>1726</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="C70">
-        <v>997</v>
+        <v>1084</v>
       </c>
       <c r="D70">
-        <v>1785</v>
+        <v>1886</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>814</v>
+        <v>869</v>
       </c>
       <c r="C71">
-        <v>1005</v>
+        <v>1092</v>
       </c>
       <c r="D71">
-        <v>1819</v>
+        <v>1961</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>817</v>
+        <v>871</v>
       </c>
       <c r="C72">
-        <v>1001</v>
+        <v>1096</v>
       </c>
       <c r="D72">
-        <v>1818</v>
+        <v>1967</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>844</v>
+        <v>892</v>
       </c>
       <c r="C73">
-        <v>1002</v>
+        <v>1077</v>
       </c>
       <c r="D73">
-        <v>1846</v>
+        <v>1969</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>1080</v>
+        <v>896</v>
       </c>
       <c r="C74">
-        <v>1151</v>
+        <v>1222</v>
       </c>
       <c r="D74">
-        <v>2231</v>
+        <v>2118</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>1087</v>
+        <v>907</v>
       </c>
       <c r="C75">
-        <v>1176</v>
+        <v>1237</v>
       </c>
       <c r="D75">
-        <v>2263</v>
+        <v>2144</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>1079</v>
+        <v>1009</v>
       </c>
       <c r="C76">
-        <v>1166</v>
+        <v>1238</v>
       </c>
       <c r="D76">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>1076</v>
+        <v>1007</v>
       </c>
       <c r="C77">
-        <v>1167</v>
+        <v>1227</v>
       </c>
       <c r="D77">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>1091</v>
+        <v>1276</v>
       </c>
       <c r="C78">
-        <v>1210</v>
+        <v>1233</v>
       </c>
       <c r="D78">
-        <v>2301</v>
+        <v>2509</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>1095</v>
+        <v>1285</v>
       </c>
       <c r="C79">
-        <v>1211</v>
+        <v>1240</v>
       </c>
       <c r="D79">
-        <v>2306</v>
+        <v>2525</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>1089</v>
+        <v>1133</v>
       </c>
       <c r="C80">
-        <v>1207</v>
+        <v>1239</v>
       </c>
       <c r="D80">
-        <v>2296</v>
+        <v>2372</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1122</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1225</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>2347</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>1066</v>
+        <v>1125</v>
       </c>
       <c r="C82">
-        <v>1216</v>
+        <v>1236</v>
       </c>
       <c r="D82">
-        <v>2282</v>
+        <v>2361</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>1069</v>
+        <v>1114</v>
       </c>
       <c r="C83">
-        <v>1218</v>
+        <v>1233</v>
       </c>
       <c r="D83">
-        <v>2287</v>
+        <v>2347</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>1077</v>
+        <v>1103</v>
       </c>
       <c r="C84">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="D84">
-        <v>2297</v>
+        <v>2333</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>1080</v>
+        <v>1098</v>
       </c>
       <c r="C85">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="D85">
-        <v>2301</v>
+        <v>2329</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>1048</v>
+        <v>823</v>
       </c>
       <c r="C86">
-        <v>1177</v>
+        <v>1192</v>
       </c>
       <c r="D86">
-        <v>2225</v>
+        <v>2015</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>1041</v>
+        <v>786</v>
       </c>
       <c r="C87">
-        <v>1170</v>
+        <v>1191</v>
       </c>
       <c r="D87">
-        <v>2211</v>
+        <v>1977</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>1049</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1172</v>
+        <v>1188</v>
       </c>
       <c r="D88">
-        <v>2221</v>
+        <v>1188</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>1083</v>
+        <v>779</v>
       </c>
       <c r="C89">
-        <v>1198</v>
+        <v>1189</v>
       </c>
       <c r="D89">
-        <v>2281</v>
+        <v>1968</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>739</v>
+        <v>666</v>
       </c>
       <c r="C90">
-        <v>1160</v>
+        <v>1217</v>
       </c>
       <c r="D90">
-        <v>1899</v>
+        <v>1883</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>719</v>
+        <v>611</v>
       </c>
       <c r="C91">
-        <v>1149</v>
+        <v>1211</v>
       </c>
       <c r="D91">
-        <v>1868</v>
+        <v>1822</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>734</v>
+        <v>628</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1216</v>
       </c>
       <c r="D92">
-        <v>734</v>
+        <v>1844</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
-        <v>718</v>
+        <v>621</v>
       </c>
       <c r="C93">
-        <v>1148</v>
+        <v>1211</v>
       </c>
       <c r="D93">
-        <v>1866</v>
+        <v>1832</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>635</v>
+        <v>362</v>
       </c>
       <c r="C94">
-        <v>1012</v>
+        <v>1203</v>
       </c>
       <c r="D94">
-        <v>1647</v>
+        <v>1565</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
-        <v>632</v>
+        <v>352</v>
       </c>
       <c r="C95">
-        <v>999</v>
+        <v>1201</v>
       </c>
       <c r="D95">
-        <v>1631</v>
+        <v>1553</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
-        <v>634</v>
+        <v>355</v>
       </c>
       <c r="C96">
-        <v>1004</v>
+        <v>1211</v>
       </c>
       <c r="D96">
-        <v>1638</v>
+        <v>1566</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
-        <v>602</v>
+        <v>350</v>
       </c>
       <c r="C97">
-        <v>998</v>
+        <v>1202</v>
       </c>
       <c r="D97">
-        <v>1600</v>
+        <v>1552</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="C98">
-        <v>1017</v>
+        <v>1048</v>
       </c>
       <c r="D98">
-        <v>1494</v>
+        <v>1503</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B99">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C99">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="D99">
-        <v>1484</v>
+        <v>1493</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B100">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="C100">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="D100">
-        <v>1489</v>
+        <v>1477</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B101">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C101">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="D101">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B102">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="C102">
-        <v>996</v>
+        <v>1032</v>
       </c>
       <c r="D102">
-        <v>1465</v>
+        <v>1476</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B103">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C103">
-        <v>992</v>
+        <v>1037</v>
       </c>
       <c r="D103">
-        <v>1458</v>
+        <v>1479</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B104">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1036</v>
       </c>
       <c r="D104">
-        <v>467</v>
+        <v>1036</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B106">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="C106">
-        <v>957</v>
+        <v>1039</v>
       </c>
       <c r="D106">
-        <v>1451</v>
+        <v>1473</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B107">
-        <v>490</v>
+        <v>429</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1036</v>
       </c>
       <c r="D107">
-        <v>490</v>
+        <v>1465</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B108">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="C108">
-        <v>959</v>
+        <v>1038</v>
       </c>
       <c r="D108">
-        <v>1453</v>
+        <v>1473</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B109">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="C109">
-        <v>958</v>
+        <v>1037</v>
       </c>
       <c r="D109">
-        <v>1442</v>
+        <v>1475</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B110">
-        <v>493</v>
+        <v>443</v>
       </c>
       <c r="C110">
-        <v>964</v>
+        <v>1045</v>
       </c>
       <c r="D110">
-        <v>1457</v>
+        <v>1488</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B112">
-        <v>489</v>
+        <v>445</v>
       </c>
       <c r="C112">
-        <v>963</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1452</v>
+        <v>445</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B113">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="C113">
-        <v>962</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1428</v>
+        <v>450</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B114">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="C114">
-        <v>1005</v>
+        <v>1041</v>
       </c>
       <c r="D114">
-        <v>1491</v>
+        <v>1519</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B115">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="D115">
-        <v>1491</v>
+        <v>1040</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B116">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C116">
-        <v>1008</v>
+        <v>1039</v>
       </c>
       <c r="D116">
-        <v>1484</v>
+        <v>1514</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B117">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C117">
-        <v>1007</v>
+        <v>1041</v>
       </c>
       <c r="D117">
-        <v>1485</v>
+        <v>1525</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B118">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="C118">
-        <v>1028</v>
+        <v>1046</v>
       </c>
       <c r="D118">
-        <v>1548</v>
+        <v>1591</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B119">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="C119">
-        <v>1025</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1542</v>
+        <v>548</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B120">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="C120">
-        <v>1026</v>
+        <v>1042</v>
       </c>
       <c r="D120">
-        <v>1545</v>
+        <v>1592</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B121">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1043</v>
       </c>
       <c r="D121">
-        <v>523</v>
+        <v>1623</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B122">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="C122">
-        <v>999</v>
+        <v>1056</v>
       </c>
       <c r="D122">
-        <v>1643</v>
+        <v>1717</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B123">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="C123">
-        <v>944</v>
+        <v>1058</v>
       </c>
       <c r="D123">
-        <v>1591</v>
+        <v>1712</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B124">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C124">
-        <v>939</v>
+        <v>1056</v>
       </c>
       <c r="D124">
-        <v>1591</v>
+        <v>1711</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B125">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C125">
-        <v>855</v>
+        <v>1057</v>
       </c>
       <c r="D125">
-        <v>1514</v>
+        <v>1714</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B126">
-        <v>656</v>
+        <v>678</v>
       </c>
       <c r="C126">
-        <v>952</v>
+        <v>1058</v>
       </c>
       <c r="D126">
-        <v>1608</v>
+        <v>1736</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B127">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="C127">
-        <v>956</v>
+        <v>1061</v>
       </c>
       <c r="D127">
-        <v>1620</v>
+        <v>1741</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B128">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="C128">
-        <v>955</v>
+        <v>1052</v>
       </c>
       <c r="D128">
-        <v>1626</v>
+        <v>1737</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B129">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="C129">
-        <v>954</v>
+        <v>1042</v>
       </c>
       <c r="D129">
-        <v>1628</v>
+        <v>1723</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B130">
-        <v>589</v>
+        <v>640</v>
       </c>
       <c r="C130">
-        <v>951</v>
+        <v>1043</v>
       </c>
       <c r="D130">
-        <v>1540</v>
+        <v>1683</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B131">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="C131">
-        <v>946</v>
+        <v>1050</v>
       </c>
       <c r="D131">
-        <v>1519</v>
+        <v>1679</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B132">
-        <v>668</v>
+        <v>633</v>
       </c>
       <c r="C132">
-        <v>998</v>
+        <v>1054</v>
       </c>
       <c r="D132">
-        <v>1666</v>
+        <v>1687</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1705</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1717</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1684</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1617</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>756</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1595</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>749</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1573</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1577</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1558</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>734</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1558</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>719</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1544</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>1545</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1565</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1552</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>673</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,580 +34,424 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>11.06.202694</t>
-  </si>
-  <si>
-    <t>11.06.202695</t>
-  </si>
-  <si>
-    <t>11.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
   </si>
 </sst>
 </file>
@@ -969,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,16 +838,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>500</v>
+        <v>736</v>
       </c>
       <c r="C2">
-        <v>1060</v>
+        <v>589</v>
       </c>
       <c r="D2">
-        <v>1560</v>
+        <v>1325</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +858,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>503</v>
+        <v>730</v>
       </c>
       <c r="C3">
-        <v>1044</v>
+        <v>587</v>
       </c>
       <c r="D3">
-        <v>1547</v>
+        <v>1317</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +878,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>502</v>
+        <v>730</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="D4">
-        <v>502</v>
+        <v>1317</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +898,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>499</v>
+        <v>728</v>
       </c>
       <c r="C5">
-        <v>1041</v>
+        <v>586</v>
       </c>
       <c r="D5">
-        <v>1540</v>
+        <v>1314</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +918,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>486</v>
+        <v>728</v>
       </c>
       <c r="C6">
-        <v>1045</v>
+        <v>557</v>
       </c>
       <c r="D6">
-        <v>1531</v>
+        <v>1285</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +938,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>477</v>
+        <v>701</v>
       </c>
       <c r="C7">
-        <v>1043</v>
+        <v>554</v>
       </c>
       <c r="D7">
-        <v>1520</v>
+        <v>1255</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +958,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>478</v>
+        <v>679</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="D8">
-        <v>478</v>
+        <v>1233</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +978,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>475</v>
+        <v>688</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="D9">
-        <v>475</v>
+        <v>1242</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +998,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>465</v>
+        <v>741</v>
       </c>
       <c r="C10">
-        <v>1033</v>
+        <v>499</v>
       </c>
       <c r="D10">
-        <v>1498</v>
+        <v>1240</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1018,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>468</v>
+        <v>747</v>
       </c>
       <c r="C11">
-        <v>1032</v>
+        <v>494</v>
       </c>
       <c r="D11">
-        <v>1500</v>
+        <v>1241</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1038,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>469</v>
+        <v>735</v>
       </c>
       <c r="C12">
-        <v>1034</v>
+        <v>493</v>
       </c>
       <c r="D12">
-        <v>1503</v>
+        <v>1228</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1058,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>468</v>
+        <v>723</v>
       </c>
       <c r="C13">
-        <v>1033</v>
+        <v>493</v>
       </c>
       <c r="D13">
-        <v>1501</v>
+        <v>1216</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1078,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>465</v>
+        <v>723</v>
       </c>
       <c r="C14">
-        <v>1032</v>
+        <v>464</v>
       </c>
       <c r="D14">
-        <v>1497</v>
+        <v>1187</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1098,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>470</v>
+        <v>729</v>
       </c>
       <c r="C15">
-        <v>1034</v>
+        <v>473</v>
       </c>
       <c r="D15">
-        <v>1504</v>
+        <v>1202</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1118,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>468</v>
+        <v>727</v>
       </c>
       <c r="C16">
-        <v>1033</v>
+        <v>472</v>
       </c>
       <c r="D16">
-        <v>1501</v>
+        <v>1199</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1138,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>467</v>
+        <v>744</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="D17">
-        <v>467</v>
+        <v>1217</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1158,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>475</v>
+        <v>746</v>
       </c>
       <c r="C18">
-        <v>1042</v>
+        <v>512</v>
       </c>
       <c r="D18">
-        <v>1517</v>
+        <v>1258</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1178,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
-        <v>473</v>
+        <v>741</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="D19">
-        <v>473</v>
+        <v>1255</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1198,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
-        <v>471</v>
+        <v>725</v>
       </c>
       <c r="C20">
-        <v>1043</v>
+        <v>513</v>
       </c>
       <c r="D20">
-        <v>1514</v>
+        <v>1238</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1218,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>485</v>
+        <v>750</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="D21">
-        <v>485</v>
+        <v>1266</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1238,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>510</v>
+        <v>716</v>
       </c>
       <c r="C22">
-        <v>1049</v>
+        <v>584</v>
       </c>
       <c r="D22">
-        <v>1559</v>
+        <v>1300</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1258,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>516</v>
+        <v>709</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="D23">
-        <v>516</v>
+        <v>1301</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1278,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>514</v>
+        <v>721</v>
       </c>
       <c r="C24">
-        <v>1046</v>
+        <v>600</v>
       </c>
       <c r="D24">
-        <v>1560</v>
+        <v>1321</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1298,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>520</v>
+        <v>734</v>
       </c>
       <c r="C25">
-        <v>1048</v>
+        <v>602</v>
       </c>
       <c r="D25">
-        <v>1568</v>
+        <v>1336</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1318,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>593</v>
+        <v>689</v>
       </c>
       <c r="C26">
-        <v>1065</v>
+        <v>724</v>
       </c>
       <c r="D26">
-        <v>1658</v>
+        <v>1413</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1338,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>594</v>
+        <v>685</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>729</v>
       </c>
       <c r="D27">
-        <v>594</v>
+        <v>1414</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1358,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>591</v>
+        <v>692</v>
       </c>
       <c r="C28">
-        <v>1058</v>
+        <v>729</v>
       </c>
       <c r="D28">
-        <v>1649</v>
+        <v>1421</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1378,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>595</v>
+        <v>690</v>
       </c>
       <c r="C29">
-        <v>1064</v>
+        <v>729</v>
       </c>
       <c r="D29">
-        <v>1659</v>
+        <v>1419</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1398,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>630</v>
+        <v>708</v>
       </c>
       <c r="C30">
-        <v>1036</v>
+        <v>712</v>
       </c>
       <c r="D30">
-        <v>1666</v>
+        <v>1420</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1418,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>622</v>
+        <v>690</v>
       </c>
       <c r="C31">
-        <v>1030</v>
+        <v>711</v>
       </c>
       <c r="D31">
-        <v>1652</v>
+        <v>1401</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1438,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>624</v>
+        <v>703</v>
       </c>
       <c r="C32">
-        <v>1031</v>
+        <v>703</v>
       </c>
       <c r="D32">
-        <v>1655</v>
+        <v>1406</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1458,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>619</v>
+        <v>730</v>
       </c>
       <c r="C33">
-        <v>1030</v>
+        <v>701</v>
       </c>
       <c r="D33">
-        <v>1649</v>
+        <v>1431</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1478,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>589</v>
+        <v>657</v>
       </c>
       <c r="C34">
-        <v>1038</v>
+        <v>717</v>
       </c>
       <c r="D34">
-        <v>1627</v>
+        <v>1374</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1498,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>570</v>
+        <v>625</v>
       </c>
       <c r="C35">
-        <v>1035</v>
+        <v>718</v>
       </c>
       <c r="D35">
-        <v>1605</v>
+        <v>1343</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1518,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="C36">
-        <v>1031</v>
+        <v>706</v>
       </c>
       <c r="D36">
-        <v>1612</v>
+        <v>1313</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1538,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="C37">
-        <v>1021</v>
+        <v>705</v>
       </c>
       <c r="D37">
-        <v>1021</v>
+        <v>1301</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1558,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>586</v>
+        <v>557</v>
       </c>
       <c r="C38">
-        <v>995</v>
+        <v>713</v>
       </c>
       <c r="D38">
-        <v>1581</v>
+        <v>1270</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1578,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>579</v>
+        <v>551</v>
       </c>
       <c r="C39">
-        <v>986</v>
+        <v>686</v>
       </c>
       <c r="D39">
-        <v>1565</v>
+        <v>1237</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1598,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
-        <v>673</v>
+        <v>367</v>
       </c>
       <c r="C40">
-        <v>993</v>
+        <v>729</v>
       </c>
       <c r="D40">
-        <v>1666</v>
+        <v>1096</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1618,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>660</v>
+        <v>364</v>
       </c>
       <c r="C41">
-        <v>991</v>
+        <v>734</v>
       </c>
       <c r="D41">
-        <v>1651</v>
+        <v>1098</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1638,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>513</v>
+        <v>191</v>
       </c>
       <c r="C42">
-        <v>943</v>
+        <v>579</v>
       </c>
       <c r="D42">
-        <v>1456</v>
+        <v>770</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1658,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>508</v>
+        <v>181</v>
       </c>
       <c r="C43">
-        <v>934</v>
+        <v>603</v>
       </c>
       <c r="D43">
-        <v>1442</v>
+        <v>784</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1678,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>507</v>
+        <v>182</v>
       </c>
       <c r="C44">
-        <v>938</v>
+        <v>614</v>
       </c>
       <c r="D44">
-        <v>1445</v>
+        <v>796</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1698,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>505</v>
+        <v>189</v>
       </c>
       <c r="C45">
-        <v>941</v>
+        <v>611</v>
       </c>
       <c r="D45">
-        <v>1446</v>
+        <v>800</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1718,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>138</v>
+        <v>285</v>
       </c>
       <c r="C46">
-        <v>812</v>
+        <v>653</v>
       </c>
       <c r="D46">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1738,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="C47">
-        <v>803</v>
+        <v>640</v>
       </c>
       <c r="D47">
-        <v>931</v>
+        <v>1000</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1758,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="C48">
-        <v>806</v>
+        <v>630</v>
       </c>
       <c r="D48">
-        <v>937</v>
+        <v>997</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1778,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>126</v>
+        <v>364</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="D49">
-        <v>126</v>
+        <v>1007</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1798,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="C50">
-        <v>799</v>
+        <v>551</v>
       </c>
       <c r="D50">
-        <v>977</v>
+        <v>902</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1818,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>173</v>
+        <v>364</v>
       </c>
       <c r="C51">
-        <v>793</v>
+        <v>545</v>
       </c>
       <c r="D51">
-        <v>966</v>
+        <v>909</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1838,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>130</v>
+        <v>381</v>
       </c>
       <c r="C52">
-        <v>792</v>
+        <v>536</v>
       </c>
       <c r="D52">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +1858,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>137</v>
+        <v>371</v>
       </c>
       <c r="C53">
-        <v>745</v>
+        <v>541</v>
       </c>
       <c r="D53">
-        <v>882</v>
+        <v>912</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +1878,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="C54">
-        <v>767</v>
+        <v>362</v>
       </c>
       <c r="D54">
-        <v>942</v>
+        <v>503</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +1898,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +1918,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="C56">
-        <v>752</v>
+        <v>350</v>
       </c>
       <c r="D56">
-        <v>925</v>
+        <v>479</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +1938,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
         <v>119</v>
       </c>
       <c r="C57">
-        <v>810</v>
+        <v>356</v>
       </c>
       <c r="D57">
-        <v>929</v>
+        <v>475</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +1958,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46184.58333333334</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>158</v>
+        <v>94</v>
       </c>
       <c r="C58">
-        <v>820</v>
+        <v>367</v>
       </c>
       <c r="D58">
-        <v>978</v>
+        <v>461</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +1978,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46184.59375</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="C59">
-        <v>825</v>
+        <v>367</v>
       </c>
       <c r="D59">
-        <v>955</v>
+        <v>460</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +1998,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46184.60416666666</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="C60">
-        <v>818</v>
+        <v>367</v>
       </c>
       <c r="D60">
-        <v>980</v>
+        <v>455</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2018,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46184.61458333334</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="C61">
-        <v>820</v>
+        <v>376</v>
       </c>
       <c r="D61">
-        <v>1004</v>
+        <v>500</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2038,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46184.625</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C62">
-        <v>973</v>
+        <v>574</v>
       </c>
       <c r="D62">
-        <v>1397</v>
+        <v>1006</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2058,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46184.63541666666</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
-        <v>555</v>
+        <v>435</v>
       </c>
       <c r="C63">
-        <v>1009</v>
+        <v>578</v>
       </c>
       <c r="D63">
-        <v>1564</v>
+        <v>1013</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2078,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46184.64583333334</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
-        <v>567</v>
+        <v>430</v>
       </c>
       <c r="C64">
+        <v>582</v>
+      </c>
+      <c r="D64">
         <v>1012</v>
-      </c>
-      <c r="D64">
-        <v>1579</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2098,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46184.65625</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>746</v>
+        <v>446</v>
       </c>
       <c r="C65">
-        <v>1054</v>
+        <v>583</v>
       </c>
       <c r="D65">
-        <v>1800</v>
+        <v>1029</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2118,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46184.66666666666</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
-        <v>785</v>
+        <v>669</v>
       </c>
       <c r="C66">
-        <v>1049</v>
+        <v>751</v>
       </c>
       <c r="D66">
-        <v>1834</v>
+        <v>1420</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2138,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46184.67708333334</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
-        <v>789</v>
+        <v>680</v>
       </c>
       <c r="C67">
-        <v>1050</v>
+        <v>810</v>
       </c>
       <c r="D67">
-        <v>1839</v>
+        <v>1490</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2158,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46184.6875</v>
+        <v>46212.6875</v>
       </c>
       <c r="B68">
-        <v>784</v>
+        <v>688</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>798</v>
       </c>
       <c r="D68">
-        <v>784</v>
+        <v>1486</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2178,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46184.69791666666</v>
+        <v>46212.69791666666</v>
       </c>
       <c r="B69">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="C69">
-        <v>1017</v>
+        <v>816</v>
       </c>
       <c r="D69">
-        <v>1726</v>
+        <v>1514</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2198,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46184.70833333334</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="B70">
-        <v>802</v>
+        <v>735</v>
       </c>
       <c r="C70">
-        <v>1084</v>
+        <v>847</v>
       </c>
       <c r="D70">
-        <v>1886</v>
+        <v>1582</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2218,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46184.71875</v>
+        <v>46212.71875</v>
       </c>
       <c r="B71">
-        <v>869</v>
+        <v>660</v>
       </c>
       <c r="C71">
-        <v>1092</v>
+        <v>891</v>
       </c>
       <c r="D71">
-        <v>1961</v>
+        <v>1551</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2238,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46184.72916666666</v>
+        <v>46212.72916666666</v>
       </c>
       <c r="B72">
-        <v>871</v>
+        <v>634</v>
       </c>
       <c r="C72">
-        <v>1096</v>
+        <v>915</v>
       </c>
       <c r="D72">
-        <v>1967</v>
+        <v>1549</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2258,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46184.73958333334</v>
+        <v>46212.73958333334</v>
       </c>
       <c r="B73">
-        <v>892</v>
+        <v>639</v>
       </c>
       <c r="C73">
-        <v>1077</v>
+        <v>915</v>
       </c>
       <c r="D73">
-        <v>1969</v>
+        <v>1554</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2278,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46184.75</v>
+        <v>46212.75</v>
       </c>
       <c r="B74">
-        <v>896</v>
+        <v>670</v>
       </c>
       <c r="C74">
-        <v>1222</v>
+        <v>917</v>
       </c>
       <c r="D74">
-        <v>2118</v>
+        <v>1587</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2298,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46184.76041666666</v>
+        <v>46212.76041666666</v>
       </c>
       <c r="B75">
-        <v>907</v>
+        <v>674</v>
       </c>
       <c r="C75">
-        <v>1237</v>
+        <v>896</v>
       </c>
       <c r="D75">
-        <v>2144</v>
+        <v>1570</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2318,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46184.77083333334</v>
+        <v>46212.77083333334</v>
       </c>
       <c r="B76">
-        <v>1009</v>
+        <v>585</v>
       </c>
       <c r="C76">
-        <v>1238</v>
+        <v>895</v>
       </c>
       <c r="D76">
-        <v>2247</v>
+        <v>1480</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2338,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46184.78125</v>
+        <v>46212.78125</v>
       </c>
       <c r="B77">
-        <v>1007</v>
+        <v>601</v>
       </c>
       <c r="C77">
-        <v>1227</v>
+        <v>898</v>
       </c>
       <c r="D77">
-        <v>2234</v>
+        <v>1499</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2358,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46184.79166666666</v>
+        <v>46212.79166666666</v>
       </c>
       <c r="B78">
-        <v>1276</v>
+        <v>794</v>
       </c>
       <c r="C78">
-        <v>1233</v>
+        <v>802</v>
       </c>
       <c r="D78">
-        <v>2509</v>
+        <v>1596</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2378,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46184.80208333334</v>
+        <v>46212.80208333334</v>
       </c>
       <c r="B79">
-        <v>1285</v>
+        <v>810</v>
       </c>
       <c r="C79">
-        <v>1240</v>
+        <v>797</v>
       </c>
       <c r="D79">
-        <v>2525</v>
+        <v>1607</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2398,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46184.8125</v>
+        <v>46212.8125</v>
       </c>
       <c r="B80">
-        <v>1133</v>
+        <v>813</v>
       </c>
       <c r="C80">
-        <v>1239</v>
+        <v>802</v>
       </c>
       <c r="D80">
-        <v>2372</v>
+        <v>1615</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2418,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46184.82291666666</v>
+        <v>46212.82291666666</v>
       </c>
       <c r="B81">
-        <v>1122</v>
+        <v>896</v>
       </c>
       <c r="C81">
-        <v>1225</v>
+        <v>803</v>
       </c>
       <c r="D81">
-        <v>2347</v>
+        <v>1699</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2438,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46184.83333333334</v>
+        <v>46212.83333333334</v>
       </c>
       <c r="B82">
-        <v>1125</v>
+        <v>957</v>
       </c>
       <c r="C82">
-        <v>1236</v>
+        <v>794</v>
       </c>
       <c r="D82">
-        <v>2361</v>
+        <v>1751</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2458,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46184.84375</v>
+        <v>46212.84375</v>
       </c>
       <c r="B83">
-        <v>1114</v>
+        <v>961</v>
       </c>
       <c r="C83">
-        <v>1233</v>
+        <v>794</v>
       </c>
       <c r="D83">
-        <v>2347</v>
+        <v>1755</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2478,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46184.85416666666</v>
+        <v>46212.85416666666</v>
       </c>
       <c r="B84">
-        <v>1103</v>
+        <v>958</v>
       </c>
       <c r="C84">
-        <v>1230</v>
+        <v>791</v>
       </c>
       <c r="D84">
-        <v>2333</v>
+        <v>1749</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2498,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46184.86458333334</v>
+        <v>46212.86458333334</v>
       </c>
       <c r="B85">
-        <v>1098</v>
+        <v>956</v>
       </c>
       <c r="C85">
-        <v>1231</v>
+        <v>788</v>
       </c>
       <c r="D85">
-        <v>2329</v>
+        <v>1744</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2518,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46184.875</v>
+        <v>46212.875</v>
       </c>
       <c r="B86">
-        <v>823</v>
+        <v>880</v>
       </c>
       <c r="C86">
-        <v>1192</v>
+        <v>758</v>
       </c>
       <c r="D86">
-        <v>2015</v>
+        <v>1638</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2538,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46184.88541666666</v>
+        <v>46212.88541666666</v>
       </c>
       <c r="B87">
+        <v>799</v>
+      </c>
+      <c r="C87">
         <v>786</v>
       </c>
-      <c r="C87">
-        <v>1191</v>
-      </c>
       <c r="D87">
-        <v>1977</v>
+        <v>1585</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2558,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46184.89583333334</v>
+        <v>46212.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>753</v>
       </c>
       <c r="C88">
-        <v>1188</v>
+        <v>806</v>
       </c>
       <c r="D88">
-        <v>1188</v>
+        <v>1559</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2578,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46184.90625</v>
+        <v>46212.90625</v>
       </c>
       <c r="B89">
-        <v>779</v>
+        <v>543</v>
       </c>
       <c r="C89">
-        <v>1189</v>
+        <v>791</v>
       </c>
       <c r="D89">
-        <v>1968</v>
+        <v>1334</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2598,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46184.91666666666</v>
+        <v>46212.91666666666</v>
       </c>
       <c r="B90">
-        <v>666</v>
+        <v>380</v>
       </c>
       <c r="C90">
-        <v>1217</v>
+        <v>771</v>
       </c>
       <c r="D90">
-        <v>1883</v>
+        <v>1151</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2618,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46184.92708333334</v>
+        <v>46212.92708333334</v>
       </c>
       <c r="B91">
-        <v>611</v>
+        <v>384</v>
       </c>
       <c r="C91">
-        <v>1211</v>
+        <v>780</v>
       </c>
       <c r="D91">
-        <v>1822</v>
+        <v>1164</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2638,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46184.9375</v>
+        <v>46212.9375</v>
       </c>
       <c r="B92">
-        <v>628</v>
+        <v>437</v>
       </c>
       <c r="C92">
-        <v>1216</v>
+        <v>777</v>
       </c>
       <c r="D92">
-        <v>1844</v>
+        <v>1214</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2658,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46184.94791666666</v>
+        <v>46212.94791666666</v>
       </c>
       <c r="B93">
-        <v>621</v>
+        <v>453</v>
       </c>
       <c r="C93">
-        <v>1211</v>
+        <v>780</v>
       </c>
       <c r="D93">
-        <v>1832</v>
+        <v>1233</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2678,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46184.95833333334</v>
+        <v>46212.95833333334</v>
       </c>
       <c r="B94">
-        <v>362</v>
+        <v>482</v>
       </c>
       <c r="C94">
-        <v>1203</v>
+        <v>744</v>
       </c>
       <c r="D94">
-        <v>1565</v>
+        <v>1226</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2698,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46184.96875</v>
+        <v>46212.96875</v>
       </c>
       <c r="B95">
-        <v>352</v>
+        <v>489</v>
       </c>
       <c r="C95">
-        <v>1201</v>
+        <v>746</v>
       </c>
       <c r="D95">
-        <v>1553</v>
+        <v>1235</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2718,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46184.97916666666</v>
+        <v>46212.97916666666</v>
       </c>
       <c r="B96">
-        <v>355</v>
+        <v>546</v>
       </c>
       <c r="C96">
-        <v>1211</v>
+        <v>753</v>
       </c>
       <c r="D96">
-        <v>1566</v>
+        <v>1299</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2738,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46184.98958333334</v>
+        <v>46212.98958333334</v>
       </c>
       <c r="B97">
-        <v>350</v>
+        <v>552</v>
       </c>
       <c r="C97">
-        <v>1202</v>
+        <v>755</v>
       </c>
       <c r="D97">
-        <v>1552</v>
+        <v>1307</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2758,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="B98">
-        <v>455</v>
+        <v>626</v>
       </c>
       <c r="C98">
-        <v>1048</v>
+        <v>625</v>
       </c>
       <c r="D98">
-        <v>1503</v>
+        <v>1251</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2778,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46185.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B99">
-        <v>462</v>
+        <v>617</v>
       </c>
       <c r="C99">
-        <v>1031</v>
+        <v>617</v>
       </c>
       <c r="D99">
-        <v>1493</v>
+        <v>1234</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2798,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B100">
-        <v>450</v>
+        <v>699</v>
       </c>
       <c r="C100">
-        <v>1027</v>
+        <v>616</v>
       </c>
       <c r="D100">
-        <v>1477</v>
+        <v>1315</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2818,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46185.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B101">
-        <v>460</v>
+        <v>719</v>
       </c>
       <c r="C101">
-        <v>1029</v>
+        <v>615</v>
       </c>
       <c r="D101">
-        <v>1489</v>
+        <v>1334</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2838,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B102">
-        <v>444</v>
+        <v>766</v>
       </c>
       <c r="C102">
-        <v>1032</v>
+        <v>536</v>
       </c>
       <c r="D102">
-        <v>1476</v>
+        <v>1302</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +2858,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B103">
-        <v>442</v>
+        <v>749</v>
       </c>
       <c r="C103">
-        <v>1037</v>
+        <v>532</v>
       </c>
       <c r="D103">
-        <v>1479</v>
+        <v>1281</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +2878,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46185.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="C104">
-        <v>1036</v>
+        <v>532</v>
       </c>
       <c r="D104">
-        <v>1036</v>
+        <v>1275</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +2898,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B105">
-        <v>444</v>
+        <v>660</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="D105">
-        <v>444</v>
+        <v>1170</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +2918,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B106">
-        <v>434</v>
+        <v>630</v>
       </c>
       <c r="C106">
-        <v>1039</v>
+        <v>491</v>
       </c>
       <c r="D106">
-        <v>1473</v>
+        <v>1121</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +2938,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46185.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B107">
-        <v>429</v>
+        <v>648</v>
       </c>
       <c r="C107">
-        <v>1036</v>
+        <v>493</v>
       </c>
       <c r="D107">
-        <v>1465</v>
+        <v>1141</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +2958,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B108">
-        <v>435</v>
+        <v>583</v>
       </c>
       <c r="C108">
-        <v>1038</v>
+        <v>493</v>
       </c>
       <c r="D108">
-        <v>1473</v>
+        <v>1076</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +2978,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B109">
-        <v>438</v>
+        <v>573</v>
       </c>
       <c r="C109">
-        <v>1037</v>
+        <v>493</v>
       </c>
       <c r="D109">
-        <v>1475</v>
+        <v>1066</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +2998,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46185.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B110">
-        <v>443</v>
+        <v>581</v>
       </c>
       <c r="C110">
-        <v>1045</v>
+        <v>478</v>
       </c>
       <c r="D110">
-        <v>1488</v>
+        <v>1059</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3018,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1072</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3038,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B112">
-        <v>445</v>
+        <v>596</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="D112">
-        <v>445</v>
+        <v>1074</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3058,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46185.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B113">
-        <v>450</v>
+        <v>653</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="D113">
-        <v>450</v>
+        <v>1131</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3078,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B114">
-        <v>478</v>
+        <v>659</v>
       </c>
       <c r="C114">
-        <v>1041</v>
+        <v>505</v>
       </c>
       <c r="D114">
-        <v>1519</v>
+        <v>1164</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3098,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="C115">
-        <v>1040</v>
+        <v>509</v>
       </c>
       <c r="D115">
-        <v>1040</v>
+        <v>1168</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3118,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46185.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B116">
-        <v>475</v>
+        <v>675</v>
       </c>
       <c r="C116">
-        <v>1039</v>
+        <v>509</v>
       </c>
       <c r="D116">
-        <v>1514</v>
+        <v>1184</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3138,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B117">
-        <v>484</v>
+        <v>674</v>
       </c>
       <c r="C117">
-        <v>1041</v>
+        <v>513</v>
       </c>
       <c r="D117">
-        <v>1525</v>
+        <v>1187</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3158,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B118">
-        <v>545</v>
+        <v>642</v>
       </c>
       <c r="C118">
-        <v>1046</v>
+        <v>604</v>
       </c>
       <c r="D118">
-        <v>1591</v>
+        <v>1246</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3178,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46185.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B119">
-        <v>548</v>
+        <v>731</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>613</v>
       </c>
       <c r="D119">
-        <v>548</v>
+        <v>1344</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3198,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B120">
-        <v>550</v>
+        <v>748</v>
       </c>
       <c r="C120">
-        <v>1042</v>
+        <v>609</v>
       </c>
       <c r="D120">
-        <v>1592</v>
+        <v>1357</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3218,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B121">
-        <v>580</v>
+        <v>747</v>
       </c>
       <c r="C121">
-        <v>1043</v>
+        <v>615</v>
       </c>
       <c r="D121">
-        <v>1623</v>
+        <v>1362</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3238,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46185.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B122">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="C122">
-        <v>1056</v>
+        <v>788</v>
       </c>
       <c r="D122">
-        <v>1717</v>
+        <v>1421</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3258,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B123">
-        <v>654</v>
+        <v>618</v>
       </c>
       <c r="C123">
-        <v>1058</v>
+        <v>810</v>
       </c>
       <c r="D123">
-        <v>1712</v>
+        <v>1428</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3278,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B124">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="C124">
-        <v>1056</v>
+        <v>812</v>
       </c>
       <c r="D124">
-        <v>1711</v>
+        <v>1434</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3298,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46185.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B125">
-        <v>657</v>
+        <v>630</v>
       </c>
       <c r="C125">
-        <v>1057</v>
+        <v>812</v>
       </c>
       <c r="D125">
-        <v>1714</v>
+        <v>1442</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3318,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B126">
-        <v>678</v>
+        <v>575</v>
       </c>
       <c r="C126">
-        <v>1058</v>
+        <v>840</v>
       </c>
       <c r="D126">
-        <v>1736</v>
+        <v>1415</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3338,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B127">
-        <v>680</v>
+        <v>571</v>
       </c>
       <c r="C127">
-        <v>1061</v>
+        <v>841</v>
       </c>
       <c r="D127">
-        <v>1741</v>
+        <v>1412</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3358,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46185.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B128">
-        <v>685</v>
+        <v>550</v>
       </c>
       <c r="C128">
-        <v>1052</v>
+        <v>852</v>
       </c>
       <c r="D128">
-        <v>1737</v>
+        <v>1402</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3378,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B129">
-        <v>681</v>
+        <v>532</v>
       </c>
       <c r="C129">
-        <v>1042</v>
+        <v>848</v>
       </c>
       <c r="D129">
-        <v>1723</v>
+        <v>1380</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3398,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B130">
-        <v>640</v>
+        <v>532</v>
       </c>
       <c r="C130">
-        <v>1043</v>
+        <v>812</v>
       </c>
       <c r="D130">
-        <v>1683</v>
+        <v>1344</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3418,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46185.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B131">
-        <v>629</v>
+        <v>540</v>
       </c>
       <c r="C131">
-        <v>1050</v>
+        <v>813</v>
       </c>
       <c r="D131">
-        <v>1679</v>
+        <v>1353</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3438,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B132">
-        <v>633</v>
+        <v>556</v>
       </c>
       <c r="C132">
-        <v>1054</v>
+        <v>807</v>
       </c>
       <c r="D132">
-        <v>1687</v>
+        <v>1363</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3458,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B133">
-        <v>654</v>
+        <v>551</v>
       </c>
       <c r="C133">
-        <v>1051</v>
+        <v>811</v>
       </c>
       <c r="D133">
-        <v>1705</v>
+        <v>1362</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3478,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46185.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B134">
-        <v>757</v>
+        <v>120</v>
       </c>
       <c r="C134">
-        <v>960</v>
+        <v>669</v>
       </c>
       <c r="D134">
-        <v>1717</v>
+        <v>789</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3498,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B135">
-        <v>746</v>
+        <v>90</v>
       </c>
       <c r="C135">
-        <v>938</v>
+        <v>661</v>
       </c>
       <c r="D135">
-        <v>1684</v>
+        <v>751</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3518,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B136">
-        <v>751</v>
+        <v>88</v>
       </c>
       <c r="C136">
-        <v>866</v>
+        <v>660</v>
       </c>
       <c r="D136">
-        <v>1617</v>
+        <v>748</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3538,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46185.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B137">
-        <v>756</v>
+        <v>86</v>
       </c>
       <c r="C137">
-        <v>839</v>
+        <v>661</v>
       </c>
       <c r="D137">
-        <v>1595</v>
+        <v>747</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3558,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B138">
-        <v>755</v>
+        <v>96</v>
       </c>
       <c r="C138">
-        <v>802</v>
+        <v>652</v>
       </c>
       <c r="D138">
-        <v>1557</v>
+        <v>748</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3578,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B139">
-        <v>749</v>
+        <v>64</v>
       </c>
       <c r="C139">
-        <v>824</v>
+        <v>614</v>
       </c>
       <c r="D139">
-        <v>1573</v>
+        <v>678</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3598,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46185.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B140">
-        <v>750</v>
+        <v>58</v>
       </c>
       <c r="C140">
-        <v>827</v>
+        <v>618</v>
       </c>
       <c r="D140">
-        <v>1577</v>
+        <v>676</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,1062 +3618,22 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B141">
-        <v>733</v>
+        <v>66</v>
       </c>
       <c r="C141">
-        <v>825</v>
+        <v>615</v>
       </c>
       <c r="D141">
-        <v>1558</v>
+        <v>681</v>
       </c>
       <c r="E141">
         <v>44</v>
       </c>
       <c r="F141" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142" s="2">
-        <v>46185.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>734</v>
-      </c>
-      <c r="C142">
-        <v>824</v>
-      </c>
-      <c r="D142">
-        <v>1558</v>
-      </c>
-      <c r="E142">
-        <v>45</v>
-      </c>
-      <c r="F142" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143" s="2">
-        <v>46185.46875</v>
-      </c>
-      <c r="B143">
-        <v>719</v>
-      </c>
-      <c r="C143">
-        <v>825</v>
-      </c>
-      <c r="D143">
-        <v>1544</v>
-      </c>
-      <c r="E143">
-        <v>46</v>
-      </c>
-      <c r="F143" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144" s="2">
-        <v>46185.47916666666</v>
-      </c>
-      <c r="B144">
-        <v>716</v>
-      </c>
-      <c r="C144">
-        <v>829</v>
-      </c>
-      <c r="D144">
-        <v>1545</v>
-      </c>
-      <c r="E144">
-        <v>47</v>
-      </c>
-      <c r="F144" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" s="2">
-        <v>46185.48958333334</v>
-      </c>
-      <c r="B145">
-        <v>730</v>
-      </c>
-      <c r="C145">
-        <v>827</v>
-      </c>
-      <c r="D145">
-        <v>1557</v>
-      </c>
-      <c r="E145">
-        <v>48</v>
-      </c>
-      <c r="F145" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" s="2">
-        <v>46185.5</v>
-      </c>
-      <c r="B146">
-        <v>685</v>
-      </c>
-      <c r="C146">
-        <v>880</v>
-      </c>
-      <c r="D146">
-        <v>1565</v>
-      </c>
-      <c r="E146">
-        <v>49</v>
-      </c>
-      <c r="F146" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" s="2">
-        <v>46185.51041666666</v>
-      </c>
-      <c r="B147">
-        <v>675</v>
-      </c>
-      <c r="C147">
-        <v>877</v>
-      </c>
-      <c r="D147">
-        <v>1552</v>
-      </c>
-      <c r="E147">
-        <v>50</v>
-      </c>
-      <c r="F147" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" s="2">
-        <v>46185.52083333334</v>
-      </c>
-      <c r="B148">
-        <v>678</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>678</v>
-      </c>
-      <c r="E148">
-        <v>51</v>
-      </c>
-      <c r="F148" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" s="2">
-        <v>46185.53125</v>
-      </c>
-      <c r="B149">
-        <v>673</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>673</v>
-      </c>
-      <c r="E149">
-        <v>52</v>
-      </c>
-      <c r="F149" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" s="2">
-        <v>46185.54166666666</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="E150">
-        <v>53</v>
-      </c>
-      <c r="F150" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" s="2">
-        <v>46185.55208333334</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="E151">
-        <v>54</v>
-      </c>
-      <c r="F151" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" s="2">
-        <v>46185.5625</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="E152">
-        <v>55</v>
-      </c>
-      <c r="F152" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" s="2">
-        <v>46185.57291666666</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="E153">
-        <v>56</v>
-      </c>
-      <c r="F153" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" s="2">
-        <v>46185.58333333334</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-      <c r="E154">
-        <v>57</v>
-      </c>
-      <c r="F154" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" s="2">
-        <v>46185.59375</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="E155">
-        <v>58</v>
-      </c>
-      <c r="F155" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" s="2">
-        <v>46185.60416666666</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="E156">
-        <v>59</v>
-      </c>
-      <c r="F156" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" s="2">
-        <v>46185.61458333334</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="E157">
-        <v>60</v>
-      </c>
-      <c r="F157" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" s="2">
-        <v>46185.625</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-      <c r="E158">
-        <v>61</v>
-      </c>
-      <c r="F158" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" s="2">
-        <v>46185.63541666666</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="E159">
-        <v>62</v>
-      </c>
-      <c r="F159" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" s="2">
-        <v>46185.64583333334</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="E160">
-        <v>63</v>
-      </c>
-      <c r="F160" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161" s="2">
-        <v>46185.65625</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="E161">
-        <v>64</v>
-      </c>
-      <c r="F161" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162" s="2">
-        <v>46185.66666666666</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-      <c r="C162">
-        <v>0</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="E162">
-        <v>65</v>
-      </c>
-      <c r="F162" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163" s="2">
-        <v>46185.67708333334</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="E163">
-        <v>66</v>
-      </c>
-      <c r="F163" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164" s="2">
-        <v>46185.6875</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="E164">
-        <v>67</v>
-      </c>
-      <c r="F164" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165" s="2">
-        <v>46185.69791666666</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-      <c r="C165">
-        <v>0</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="E165">
-        <v>68</v>
-      </c>
-      <c r="F165" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166" s="2">
-        <v>46185.70833333334</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="E166">
-        <v>69</v>
-      </c>
-      <c r="F166" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" s="2">
-        <v>46185.71875</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167">
-        <v>70</v>
-      </c>
-      <c r="F167" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6">
-      <c r="A168" s="2">
-        <v>46185.72916666666</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="E168">
-        <v>71</v>
-      </c>
-      <c r="F168" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="A169" s="2">
-        <v>46185.73958333334</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-      <c r="C169">
-        <v>0</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-      <c r="E169">
-        <v>72</v>
-      </c>
-      <c r="F169" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6">
-      <c r="A170" s="2">
-        <v>46185.75</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-      <c r="C170">
-        <v>0</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-      <c r="E170">
-        <v>73</v>
-      </c>
-      <c r="F170" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="A171" s="2">
-        <v>46185.76041666666</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-      <c r="E171">
-        <v>74</v>
-      </c>
-      <c r="F171" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="A172" s="2">
-        <v>46185.77083333334</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-      <c r="C172">
-        <v>0</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-      <c r="E172">
-        <v>75</v>
-      </c>
-      <c r="F172" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="A173" s="2">
-        <v>46185.78125</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-      <c r="E173">
-        <v>76</v>
-      </c>
-      <c r="F173" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="A174" s="2">
-        <v>46185.79166666666</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-      <c r="C174">
-        <v>0</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-      <c r="E174">
-        <v>77</v>
-      </c>
-      <c r="F174" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="A175" s="2">
-        <v>46185.80208333334</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
-      </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
-      <c r="E175">
-        <v>78</v>
-      </c>
-      <c r="F175" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6">
-      <c r="A176" s="2">
-        <v>46185.8125</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-      <c r="C176">
-        <v>0</v>
-      </c>
-      <c r="D176">
-        <v>0</v>
-      </c>
-      <c r="E176">
-        <v>79</v>
-      </c>
-      <c r="F176" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6">
-      <c r="A177" s="2">
-        <v>46185.82291666666</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-      <c r="C177">
-        <v>0</v>
-      </c>
-      <c r="D177">
-        <v>0</v>
-      </c>
-      <c r="E177">
-        <v>80</v>
-      </c>
-      <c r="F177" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6">
-      <c r="A178" s="2">
-        <v>46185.83333333334</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-      <c r="C178">
-        <v>0</v>
-      </c>
-      <c r="D178">
-        <v>0</v>
-      </c>
-      <c r="E178">
-        <v>81</v>
-      </c>
-      <c r="F178" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6">
-      <c r="A179" s="2">
-        <v>46185.84375</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-      <c r="C179">
-        <v>0</v>
-      </c>
-      <c r="D179">
-        <v>0</v>
-      </c>
-      <c r="E179">
-        <v>82</v>
-      </c>
-      <c r="F179" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6">
-      <c r="A180" s="2">
-        <v>46185.85416666666</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
-      </c>
-      <c r="D180">
-        <v>0</v>
-      </c>
-      <c r="E180">
-        <v>83</v>
-      </c>
-      <c r="F180" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181" s="2">
-        <v>46185.86458333334</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
-      <c r="D181">
-        <v>0</v>
-      </c>
-      <c r="E181">
-        <v>84</v>
-      </c>
-      <c r="F181" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" s="2">
-        <v>46185.875</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
-      <c r="D182">
-        <v>0</v>
-      </c>
-      <c r="E182">
-        <v>85</v>
-      </c>
-      <c r="F182" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6">
-      <c r="A183" s="2">
-        <v>46185.88541666666</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
-      <c r="D183">
-        <v>0</v>
-      </c>
-      <c r="E183">
-        <v>86</v>
-      </c>
-      <c r="F183" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184" s="2">
-        <v>46185.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
-      </c>
-      <c r="D184">
-        <v>0</v>
-      </c>
-      <c r="E184">
-        <v>87</v>
-      </c>
-      <c r="F184" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185" s="2">
-        <v>46185.90625</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
-      </c>
-      <c r="D185">
-        <v>0</v>
-      </c>
-      <c r="E185">
-        <v>88</v>
-      </c>
-      <c r="F185" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="A186" s="2">
-        <v>46185.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-      <c r="C186">
-        <v>0</v>
-      </c>
-      <c r="D186">
-        <v>0</v>
-      </c>
-      <c r="E186">
-        <v>89</v>
-      </c>
-      <c r="F186" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6">
-      <c r="A187" s="2">
-        <v>46185.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
-      </c>
-      <c r="D187">
-        <v>0</v>
-      </c>
-      <c r="E187">
-        <v>90</v>
-      </c>
-      <c r="F187" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="A188" s="2">
-        <v>46185.9375</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-      <c r="D188">
-        <v>0</v>
-      </c>
-      <c r="E188">
-        <v>91</v>
-      </c>
-      <c r="F188" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6">
-      <c r="A189" s="2">
-        <v>46185.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
-      <c r="D189">
-        <v>0</v>
-      </c>
-      <c r="E189">
-        <v>92</v>
-      </c>
-      <c r="F189" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" s="2">
-        <v>46185.95833333334</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
-      <c r="D190">
-        <v>0</v>
-      </c>
-      <c r="E190">
-        <v>93</v>
-      </c>
-      <c r="F190" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
-      <c r="D191">
-        <v>0</v>
-      </c>
-      <c r="E191">
-        <v>94</v>
-      </c>
-      <c r="F191" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
-      <c r="D192">
-        <v>0</v>
-      </c>
-      <c r="E192">
-        <v>95</v>
-      </c>
-      <c r="F192" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B193">
-        <v>0</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
-      </c>
-      <c r="D193">
-        <v>0</v>
-      </c>
-      <c r="E193">
-        <v>96</v>
-      </c>
-      <c r="F193" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
+++ b/data_fetching/Entsoe/Hydro_Production_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.07.20261</t>
-  </si>
-  <si>
-    <t>09.07.20262</t>
-  </si>
-  <si>
-    <t>09.07.20263</t>
-  </si>
-  <si>
-    <t>09.07.20264</t>
-  </si>
-  <si>
-    <t>09.07.20265</t>
-  </si>
-  <si>
-    <t>09.07.20266</t>
-  </si>
-  <si>
-    <t>09.07.20267</t>
-  </si>
-  <si>
-    <t>09.07.20268</t>
-  </si>
-  <si>
-    <t>09.07.20269</t>
-  </si>
-  <si>
-    <t>09.07.202610</t>
-  </si>
-  <si>
-    <t>09.07.202611</t>
-  </si>
-  <si>
-    <t>09.07.202612</t>
-  </si>
-  <si>
-    <t>09.07.202613</t>
-  </si>
-  <si>
-    <t>09.07.202614</t>
-  </si>
-  <si>
-    <t>09.07.202615</t>
-  </si>
-  <si>
-    <t>09.07.202616</t>
-  </si>
-  <si>
-    <t>09.07.202617</t>
-  </si>
-  <si>
-    <t>09.07.202618</t>
-  </si>
-  <si>
-    <t>09.07.202619</t>
-  </si>
-  <si>
-    <t>09.07.202620</t>
-  </si>
-  <si>
-    <t>09.07.202621</t>
-  </si>
-  <si>
-    <t>09.07.202622</t>
-  </si>
-  <si>
-    <t>09.07.202623</t>
-  </si>
-  <si>
-    <t>09.07.202624</t>
-  </si>
-  <si>
-    <t>09.07.202625</t>
-  </si>
-  <si>
-    <t>09.07.202626</t>
-  </si>
-  <si>
-    <t>09.07.202627</t>
-  </si>
-  <si>
-    <t>09.07.202628</t>
-  </si>
-  <si>
-    <t>09.07.202629</t>
-  </si>
-  <si>
-    <t>09.07.202630</t>
-  </si>
-  <si>
-    <t>09.07.202631</t>
-  </si>
-  <si>
-    <t>09.07.202632</t>
-  </si>
-  <si>
-    <t>09.07.202633</t>
-  </si>
-  <si>
-    <t>09.07.202634</t>
-  </si>
-  <si>
-    <t>09.07.202635</t>
-  </si>
-  <si>
-    <t>09.07.202636</t>
-  </si>
-  <si>
-    <t>09.07.202637</t>
-  </si>
-  <si>
-    <t>09.07.202638</t>
-  </si>
-  <si>
-    <t>09.07.202639</t>
-  </si>
-  <si>
-    <t>09.07.202640</t>
-  </si>
-  <si>
-    <t>09.07.202641</t>
-  </si>
-  <si>
-    <t>09.07.202642</t>
-  </si>
-  <si>
-    <t>09.07.202643</t>
-  </si>
-  <si>
-    <t>09.07.202644</t>
-  </si>
-  <si>
-    <t>09.07.202645</t>
-  </si>
-  <si>
-    <t>09.07.202646</t>
-  </si>
-  <si>
-    <t>09.07.202647</t>
-  </si>
-  <si>
-    <t>09.07.202648</t>
-  </si>
-  <si>
-    <t>09.07.202649</t>
-  </si>
-  <si>
-    <t>09.07.202650</t>
-  </si>
-  <si>
-    <t>09.07.202651</t>
-  </si>
-  <si>
-    <t>09.07.202652</t>
-  </si>
-  <si>
-    <t>09.07.202653</t>
-  </si>
-  <si>
-    <t>09.07.202654</t>
-  </si>
-  <si>
-    <t>09.07.202655</t>
-  </si>
-  <si>
-    <t>09.07.202656</t>
-  </si>
-  <si>
-    <t>09.07.202657</t>
-  </si>
-  <si>
-    <t>09.07.202658</t>
-  </si>
-  <si>
-    <t>09.07.202659</t>
-  </si>
-  <si>
-    <t>09.07.202660</t>
-  </si>
-  <si>
-    <t>09.07.202661</t>
-  </si>
-  <si>
-    <t>09.07.202662</t>
-  </si>
-  <si>
-    <t>09.07.202663</t>
-  </si>
-  <si>
-    <t>09.07.202664</t>
-  </si>
-  <si>
-    <t>09.07.202665</t>
-  </si>
-  <si>
-    <t>09.07.202666</t>
-  </si>
-  <si>
-    <t>09.07.202667</t>
-  </si>
-  <si>
-    <t>09.07.202668</t>
-  </si>
-  <si>
-    <t>09.07.202669</t>
-  </si>
-  <si>
-    <t>09.07.202670</t>
-  </si>
-  <si>
-    <t>09.07.202671</t>
-  </si>
-  <si>
-    <t>09.07.202672</t>
-  </si>
-  <si>
-    <t>09.07.202673</t>
-  </si>
-  <si>
-    <t>09.07.202674</t>
-  </si>
-  <si>
-    <t>09.07.202675</t>
-  </si>
-  <si>
-    <t>09.07.202676</t>
-  </si>
-  <si>
-    <t>09.07.202677</t>
-  </si>
-  <si>
-    <t>09.07.202678</t>
-  </si>
-  <si>
-    <t>09.07.202679</t>
-  </si>
-  <si>
-    <t>09.07.202680</t>
-  </si>
-  <si>
-    <t>09.07.202681</t>
-  </si>
-  <si>
-    <t>09.07.202682</t>
-  </si>
-  <si>
-    <t>09.07.202683</t>
-  </si>
-  <si>
-    <t>09.07.202684</t>
-  </si>
-  <si>
-    <t>09.07.202685</t>
-  </si>
-  <si>
-    <t>09.07.202686</t>
-  </si>
-  <si>
-    <t>09.07.202687</t>
-  </si>
-  <si>
-    <t>09.07.202688</t>
-  </si>
-  <si>
-    <t>09.07.202689</t>
-  </si>
-  <si>
-    <t>09.07.202690</t>
-  </si>
-  <si>
-    <t>09.07.202691</t>
-  </si>
-  <si>
-    <t>09.07.202692</t>
-  </si>
-  <si>
-    <t>09.07.202693</t>
-  </si>
-  <si>
-    <t>09.07.202694</t>
-  </si>
-  <si>
-    <t>09.07.202695</t>
-  </si>
-  <si>
-    <t>09.07.202696</t>
-  </si>
-  <si>
     <t>10.07.20261</t>
   </si>
   <si>
@@ -452,6 +164,891 @@
   </si>
   <si>
     <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
+  </si>
+  <si>
+    <t>10.07.202693</t>
+  </si>
+  <si>
+    <t>10.07.202694</t>
+  </si>
+  <si>
+    <t>10.07.202695</t>
+  </si>
+  <si>
+    <t>10.07.202696</t>
+  </si>
+  <si>
+    <t>11.07.20261</t>
+  </si>
+  <si>
+    <t>11.07.20262</t>
+  </si>
+  <si>
+    <t>11.07.20263</t>
+  </si>
+  <si>
+    <t>11.07.20264</t>
+  </si>
+  <si>
+    <t>11.07.20265</t>
+  </si>
+  <si>
+    <t>11.07.20266</t>
+  </si>
+  <si>
+    <t>11.07.20267</t>
+  </si>
+  <si>
+    <t>11.07.20268</t>
+  </si>
+  <si>
+    <t>11.07.20269</t>
+  </si>
+  <si>
+    <t>11.07.202610</t>
+  </si>
+  <si>
+    <t>11.07.202611</t>
+  </si>
+  <si>
+    <t>11.07.202612</t>
+  </si>
+  <si>
+    <t>11.07.202613</t>
+  </si>
+  <si>
+    <t>11.07.202614</t>
+  </si>
+  <si>
+    <t>11.07.202615</t>
+  </si>
+  <si>
+    <t>11.07.202616</t>
+  </si>
+  <si>
+    <t>11.07.202617</t>
+  </si>
+  <si>
+    <t>11.07.202618</t>
+  </si>
+  <si>
+    <t>11.07.202619</t>
+  </si>
+  <si>
+    <t>11.07.202620</t>
+  </si>
+  <si>
+    <t>11.07.202621</t>
+  </si>
+  <si>
+    <t>11.07.202622</t>
+  </si>
+  <si>
+    <t>11.07.202623</t>
+  </si>
+  <si>
+    <t>11.07.202624</t>
+  </si>
+  <si>
+    <t>11.07.202625</t>
+  </si>
+  <si>
+    <t>11.07.202626</t>
+  </si>
+  <si>
+    <t>11.07.202627</t>
+  </si>
+  <si>
+    <t>11.07.202628</t>
+  </si>
+  <si>
+    <t>11.07.202629</t>
+  </si>
+  <si>
+    <t>11.07.202630</t>
+  </si>
+  <si>
+    <t>11.07.202631</t>
+  </si>
+  <si>
+    <t>11.07.202632</t>
+  </si>
+  <si>
+    <t>11.07.202633</t>
+  </si>
+  <si>
+    <t>11.07.202634</t>
+  </si>
+  <si>
+    <t>11.07.202635</t>
+  </si>
+  <si>
+    <t>11.07.202636</t>
+  </si>
+  <si>
+    <t>11.07.202637</t>
+  </si>
+  <si>
+    <t>11.07.202638</t>
+  </si>
+  <si>
+    <t>11.07.202639</t>
+  </si>
+  <si>
+    <t>11.07.202640</t>
+  </si>
+  <si>
+    <t>11.07.202641</t>
+  </si>
+  <si>
+    <t>11.07.202642</t>
+  </si>
+  <si>
+    <t>11.07.202643</t>
+  </si>
+  <si>
+    <t>11.07.202644</t>
+  </si>
+  <si>
+    <t>11.07.202645</t>
+  </si>
+  <si>
+    <t>11.07.202646</t>
+  </si>
+  <si>
+    <t>11.07.202647</t>
+  </si>
+  <si>
+    <t>11.07.202648</t>
+  </si>
+  <si>
+    <t>11.07.202649</t>
+  </si>
+  <si>
+    <t>11.07.202650</t>
+  </si>
+  <si>
+    <t>11.07.202651</t>
+  </si>
+  <si>
+    <t>11.07.202652</t>
+  </si>
+  <si>
+    <t>11.07.202653</t>
+  </si>
+  <si>
+    <t>11.07.202654</t>
+  </si>
+  <si>
+    <t>11.07.202655</t>
+  </si>
+  <si>
+    <t>11.07.202656</t>
+  </si>
+  <si>
+    <t>11.07.202657</t>
+  </si>
+  <si>
+    <t>11.07.202658</t>
+  </si>
+  <si>
+    <t>11.07.202659</t>
+  </si>
+  <si>
+    <t>11.07.202660</t>
+  </si>
+  <si>
+    <t>11.07.202661</t>
+  </si>
+  <si>
+    <t>11.07.202662</t>
+  </si>
+  <si>
+    <t>11.07.202663</t>
+  </si>
+  <si>
+    <t>11.07.202664</t>
+  </si>
+  <si>
+    <t>11.07.202665</t>
+  </si>
+  <si>
+    <t>11.07.202666</t>
+  </si>
+  <si>
+    <t>11.07.202667</t>
+  </si>
+  <si>
+    <t>11.07.202668</t>
+  </si>
+  <si>
+    <t>11.07.202669</t>
+  </si>
+  <si>
+    <t>11.07.202670</t>
+  </si>
+  <si>
+    <t>11.07.202671</t>
+  </si>
+  <si>
+    <t>11.07.202672</t>
+  </si>
+  <si>
+    <t>11.07.202673</t>
+  </si>
+  <si>
+    <t>11.07.202674</t>
+  </si>
+  <si>
+    <t>11.07.202675</t>
+  </si>
+  <si>
+    <t>11.07.202676</t>
+  </si>
+  <si>
+    <t>11.07.202677</t>
+  </si>
+  <si>
+    <t>11.07.202678</t>
+  </si>
+  <si>
+    <t>11.07.202679</t>
+  </si>
+  <si>
+    <t>11.07.202680</t>
+  </si>
+  <si>
+    <t>11.07.202681</t>
+  </si>
+  <si>
+    <t>11.07.202682</t>
+  </si>
+  <si>
+    <t>11.07.202683</t>
+  </si>
+  <si>
+    <t>11.07.202684</t>
+  </si>
+  <si>
+    <t>11.07.202685</t>
+  </si>
+  <si>
+    <t>11.07.202686</t>
+  </si>
+  <si>
+    <t>11.07.202687</t>
+  </si>
+  <si>
+    <t>11.07.202688</t>
+  </si>
+  <si>
+    <t>11.07.202689</t>
+  </si>
+  <si>
+    <t>11.07.202690</t>
+  </si>
+  <si>
+    <t>11.07.202691</t>
+  </si>
+  <si>
+    <t>11.07.202692</t>
+  </si>
+  <si>
+    <t>11.07.202693</t>
+  </si>
+  <si>
+    <t>11.07.202694</t>
+  </si>
+  <si>
+    <t>11.07.202695</t>
+  </si>
+  <si>
+    <t>11.07.202696</t>
+  </si>
+  <si>
+    <t>12.07.20261</t>
+  </si>
+  <si>
+    <t>12.07.20262</t>
+  </si>
+  <si>
+    <t>12.07.20263</t>
+  </si>
+  <si>
+    <t>12.07.20264</t>
+  </si>
+  <si>
+    <t>12.07.20265</t>
+  </si>
+  <si>
+    <t>12.07.20266</t>
+  </si>
+  <si>
+    <t>12.07.20267</t>
+  </si>
+  <si>
+    <t>12.07.20268</t>
+  </si>
+  <si>
+    <t>12.07.20269</t>
+  </si>
+  <si>
+    <t>12.07.202610</t>
+  </si>
+  <si>
+    <t>12.07.202611</t>
+  </si>
+  <si>
+    <t>12.07.202612</t>
+  </si>
+  <si>
+    <t>12.07.202613</t>
+  </si>
+  <si>
+    <t>12.07.202614</t>
+  </si>
+  <si>
+    <t>12.07.202615</t>
+  </si>
+  <si>
+    <t>12.07.202616</t>
+  </si>
+  <si>
+    <t>12.07.202617</t>
+  </si>
+  <si>
+    <t>12.07.202618</t>
+  </si>
+  <si>
+    <t>12.07.202619</t>
+  </si>
+  <si>
+    <t>12.07.202620</t>
+  </si>
+  <si>
+    <t>12.07.202621</t>
+  </si>
+  <si>
+    <t>12.07.202622</t>
+  </si>
+  <si>
+    <t>12.07.202623</t>
+  </si>
+  <si>
+    <t>12.07.202624</t>
+  </si>
+  <si>
+    <t>12.07.202625</t>
+  </si>
+  <si>
+    <t>12.07.202626</t>
+  </si>
+  <si>
+    <t>12.07.202627</t>
+  </si>
+  <si>
+    <t>12.07.202628</t>
+  </si>
+  <si>
+    <t>12.07.202629</t>
+  </si>
+  <si>
+    <t>12.07.202630</t>
+  </si>
+  <si>
+    <t>12.07.202631</t>
+  </si>
+  <si>
+    <t>12.07.202632</t>
+  </si>
+  <si>
+    <t>12.07.202633</t>
+  </si>
+  <si>
+    <t>12.07.202634</t>
+  </si>
+  <si>
+    <t>12.07.202635</t>
+  </si>
+  <si>
+    <t>12.07.202636</t>
+  </si>
+  <si>
+    <t>12.07.202637</t>
+  </si>
+  <si>
+    <t>12.07.202638</t>
+  </si>
+  <si>
+    <t>12.07.202639</t>
+  </si>
+  <si>
+    <t>12.07.202640</t>
+  </si>
+  <si>
+    <t>12.07.202641</t>
+  </si>
+  <si>
+    <t>12.07.202642</t>
+  </si>
+  <si>
+    <t>12.07.202643</t>
+  </si>
+  <si>
+    <t>12.07.202644</t>
+  </si>
+  <si>
+    <t>12.07.202645</t>
+  </si>
+  <si>
+    <t>12.07.202646</t>
+  </si>
+  <si>
+    <t>12.07.202647</t>
+  </si>
+  <si>
+    <t>12.07.202648</t>
+  </si>
+  <si>
+    <t>12.07.202649</t>
+  </si>
+  <si>
+    <t>12.07.202650</t>
+  </si>
+  <si>
+    <t>12.07.202651</t>
+  </si>
+  <si>
+    <t>12.07.202652</t>
+  </si>
+  <si>
+    <t>12.07.202653</t>
+  </si>
+  <si>
+    <t>12.07.202654</t>
+  </si>
+  <si>
+    <t>12.07.202655</t>
+  </si>
+  <si>
+    <t>12.07.202656</t>
+  </si>
+  <si>
+    <t>12.07.202657</t>
+  </si>
+  <si>
+    <t>12.07.202658</t>
+  </si>
+  <si>
+    <t>12.07.202659</t>
+  </si>
+  <si>
+    <t>12.07.202660</t>
+  </si>
+  <si>
+    <t>12.07.202661</t>
+  </si>
+  <si>
+    <t>12.07.202662</t>
+  </si>
+  <si>
+    <t>12.07